--- a/rapid7_cves.xlsx
+++ b/rapid7_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1523,6 +1523,1086 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>CVE-2026-43077</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>CVE-2026-8094</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>CVE-2026-8093</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>CVE-2026-8092</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>CVE-2026-8091</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>CVE-2026-8090</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>CVE-2026-8022</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>CVE-2026-8021</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>CVE-2026-8020</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>CVE-2026-8019</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>CVE-2026-8018</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>CVE-2026-8017</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>CVE-2026-8016</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>CVE-2026-8015</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>CVE-2026-8014</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>CVE-2026-8013</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>CVE-2026-8012</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>CVE-2026-8011</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>CVE-2026-8010</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>CVE-2026-8009</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>CVE-2026-43077</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>vulnerability Red Hat: CVE-2026-43077: kernel: crypto: algif_aead - Fix minimum RX size check for decryption (Multiple Advisories) Published: 2026-05-</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/redhat_linux-cve-2026-43077/</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>CVE-2026-8094</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>vulnerability FreeBSD: VID-818efa2a-4aae-11f1-88d3-b42e991fc52e (CVE-2026-8094): firefox ESR -- Other issue in the WebRTC component Published: 2026-05</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/freebsd-cve-2026-8094/</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>CVE-2026-8093</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>vulnerability FreeBSD: VID-7eae7f45-4aae-11f1-88d3-b42e991fc52e (CVE-2026-8093): firefox -- Memory safety bugs present in Firefox 150 Published: 2026-</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/freebsd-cve-2026-8093/</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>CVE-2026-8092</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>vulnerability FreeBSD: VID-7a9f1c15-4aae-11f1-88d3-b42e991fc52e (CVE-2026-8092): firefox -- Memory safety bugs present in Firefox ESR 115 Published: 2</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/freebsd-cve-2026-8092/</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>CVE-2026-8091</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>vulnerability FreeBSD: VID-76763f24-4aae-11f1-88d3-b42e991fc52e (CVE-2026-8091): Mozilla -- Incorrect boundary conditions Published: 2026-05-08 | Seve</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/freebsd-cve-2026-8091/</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>CVE-2026-8090</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>vulnerability FreeBSD: VID-7360cdae-4aae-11f1-88d3-b42e991fc52e (CVE-2026-8090): firefox -- Use-after-free Published: 2026-05-08 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/freebsd-cve-2026-8090/</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>CVE-2026-8022</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>vulnerability FreeBSD: VID-da4d7162-4aa3-11f1-b189-a8a1599412c6 (CVE-2026-8022): chromium -- security fixes Published: 2026-05-08 | Severity: 3 EXPLOR</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/freebsd-cve-2026-8022/</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>CVE-2026-8021</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>vulnerability FreeBSD: VID-da4d7162-4aa3-11f1-b189-a8a1599412c6 (CVE-2026-8021): chromium -- security fixes Published: 2026-05-08 | Severity: 4 EXPLOR</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/freebsd-cve-2026-8021/</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>CVE-2026-8020</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>vulnerability FreeBSD: VID-da4d7162-4aa3-11f1-b189-a8a1599412c6 (CVE-2026-8020): chromium -- security fixes Published: 2026-05-08 | Severity: 5 EXPLOR</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/freebsd-cve-2026-8020/</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>CVE-2026-8019</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>vulnerability FreeBSD: VID-da4d7162-4aa3-11f1-b189-a8a1599412c6 (CVE-2026-8019): chromium -- security fixes Published: 2026-05-08 | Severity: 6 EXPLOR</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/freebsd-cve-2026-8019/</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>CVE-2026-8018</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>vulnerability FreeBSD: VID-da4d7162-4aa3-11f1-b189-a8a1599412c6 (CVE-2026-8018): chromium -- security fixes Published: 2026-05-08 | Severity: 9 EXPLOR</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/freebsd-cve-2026-8018/</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>CVE-2026-8017</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>vulnerability FreeBSD: VID-da4d7162-4aa3-11f1-b189-a8a1599412c6 (CVE-2026-8017): chromium -- security fixes Published: 2026-05-08 | Severity: 3 EXPLOR</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/freebsd-cve-2026-8017/</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>CVE-2026-8016</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>vulnerability FreeBSD: VID-da4d7162-4aa3-11f1-b189-a8a1599412c6 (CVE-2026-8016): chromium -- security fixes Published: 2026-05-08 | Severity: 9 EXPLOR</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/freebsd-cve-2026-8016/</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>CVE-2026-8015</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>vulnerability FreeBSD: VID-da4d7162-4aa3-11f1-b189-a8a1599412c6 (CVE-2026-8015): chromium -- security fixes Published: 2026-05-08 | Severity: 6 EXPLOR</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/freebsd-cve-2026-8015/</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>CVE-2026-8014</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>vulnerability FreeBSD: VID-da4d7162-4aa3-11f1-b189-a8a1599412c6 (CVE-2026-8014): chromium -- security fixes Published: 2026-05-08 | Severity: 4 EXPLOR</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/freebsd-cve-2026-8014/</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>CVE-2026-8013</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>vulnerability FreeBSD: VID-da4d7162-4aa3-11f1-b189-a8a1599412c6 (CVE-2026-8013): chromium -- security fixes Published: 2026-05-08 | Severity: 4 EXPLOR</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/freebsd-cve-2026-8013/</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>CVE-2026-8012</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>vulnerability FreeBSD: VID-da4d7162-4aa3-11f1-b189-a8a1599412c6 (CVE-2026-8012): chromium -- security fixes Published: 2026-05-08 | Severity: 6 EXPLOR</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/freebsd-cve-2026-8012/</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>CVE-2026-8011</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>vulnerability FreeBSD: VID-da4d7162-4aa3-11f1-b189-a8a1599412c6 (CVE-2026-8011): chromium -- security fixes Published: 2026-05-08 | Severity: 4 EXPLOR</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/freebsd-cve-2026-8011/</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>CVE-2026-8010</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>vulnerability FreeBSD: VID-da4d7162-4aa3-11f1-b189-a8a1599412c6 (CVE-2026-8010): chromium -- security fixes Published: 2026-05-08 | Severity: 7 EXPLOR</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/freebsd-cve-2026-8010/</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>CVE-2026-8009</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>vulnerability FreeBSD: VID-da4d7162-4aa3-11f1-b189-a8a1599412c6 (CVE-2026-8009): chromium -- security fixes Published: 2026-05-08 | Severity: 5 EXPLOR</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/freebsd-cve-2026-8009/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rapid7_cves.xlsx
+++ b/rapid7_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E81"/>
+  <dimension ref="A1:E121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2603,6 +2603,1086 @@
         </is>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>CVE-2026-28920</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A curated repository of over 180,000 exploitable vulnerabil</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>CVE-2026-28994</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A curated repository of over 180,000 exploitable vulnerabil</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>CVE-2026-28819</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A curated repository of over 180,000 exploitable vulnerabil</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>CVE-2026-39871</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A curated repository of over 180,000 exploitable vulnerabil</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>CVE-2026-28924</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A curated repository of over 180,000 exploitable vulnerabil</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>CVE-2026-28919</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A curated repository of over 180,000 exploitable vulnerabil</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>CVE-2026-28996</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A curated repository of over 180,000 exploitable vulnerabil</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>CVE-2026-28974</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A curated repository of over 180,000 exploitable vulnerabil</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>CVE-2026-28848</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A curated repository of over 180,000 exploitable vulnerabil</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>CVE-2026-28993</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A curated repository of over 180,000 exploitable vulnerabil</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>CVE-2026-28860</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A curated repository of over 180,000 exploitable vulnerabil</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>CVE-2026-28830</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A curated repository of over 180,000 exploitable vulnerabil</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>CVE-2026-39870</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A curated repository of over 180,000 exploitable vulnerabil</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>CVE-2026-28846</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A curated repository of over 180,000 exploitable vulnerabil</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>CVE-2026-43656</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A curated repository of over 180,000 exploitable vulnerabil</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>CVE-2026-28840</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A curated repository of over 180,000 exploitable vulnerabil</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>CVE-2026-28906</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A curated repository of over 180,000 exploitable vulnerabil</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>CVE-2026-28941</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A curated repository of over 180,000 exploitable vulnerabil</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>CVE-2026-28940</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A curated repository of over 180,000 exploitable vulnerabil</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>CVE-2026-43668</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A curated repository of over 180,000 exploitable vulnerabil</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>CVE-2026-28920</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>vulnerability OS X update for zlib (CVE-2026-28920) Published: 2026-05-12 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/apple-osx-zlib-cve-2026-28920/</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>CVE-2026-28994</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>vulnerability OS X update for Wi-Fi (CVE-2026-28994) Published: 2026-05-12 | Severity: 10 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/apple-osx-wifi-cve-2026-28994/</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>CVE-2026-28819</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>vulnerability OS X update for Wi-Fi (CVE-2026-28819) Published: 2026-05-12 | Severity: 10 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/apple-osx-wifi-cve-2026-28819/</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>CVE-2026-39871</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>vulnerability OS X update for TV App (CVE-2026-39871) Published: 2026-05-12 | Severity: 10 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/apple-osx-tvapp-cve-2026-39871/</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>CVE-2026-28924</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>vulnerability OS X update for Sync Services (CVE-2026-28924) Published: 2026-05-12 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/apple-osx-syncservices-cve-2026-28924/</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>CVE-2026-28919</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>vulnerability OS X update for StorageKit (CVE-2026-28919) Published: 2026-05-12 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/apple-osx-storagekit-cve-2026-28919/</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>CVE-2026-28996</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>vulnerability OS X update for Storage (CVE-2026-28996) Published: 2026-05-12 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/apple-osx-storage-cve-2026-28996/</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>CVE-2026-28974</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>vulnerability OS X update for Spotlight (CVE-2026-28974) Published: 2026-05-12 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/apple-osx-spotlight-cve-2026-28974/</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>CVE-2026-28848</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>vulnerability OS X update for SMB (CVE-2026-28848) Published: 2026-05-12 | Severity: 10 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/apple-osx-smb-cve-2026-28848/</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>CVE-2026-28993</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>vulnerability OS X update for Shortcuts (CVE-2026-28993) Published: 2026-05-12 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/apple-osx-shortcuts-cve-2026-28993/</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>CVE-2026-28860</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>vulnerability OS X update for Security (CVE-2026-28860) Published: 2026-05-12 | Severity: 10 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/apple-osx-security-cve-2026-28860/</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>CVE-2026-28830</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>vulnerability OS X update for Security (CVE-2026-28830) Published: 2026-05-12 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/apple-osx-security-cve-2026-28830/</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>CVE-2026-39870</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>vulnerability OS X update for SceneKit (CVE-2026-39870) Published: 2026-05-12 | Severity: 10 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/apple-osx-scenekit-cve-2026-39870/</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>CVE-2026-28846</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>vulnerability OS X update for SceneKit (CVE-2026-28846) Published: 2026-05-12 | Severity: 10 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/apple-osx-scenekit-cve-2026-28846/</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>CVE-2026-43656</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>vulnerability OS X update for Quick Look (CVE-2026-43656) Published: 2026-05-12 | Severity: 10 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/apple-osx-quicklook-cve-2026-43656/</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>CVE-2026-28840</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>vulnerability OS X update for PackageKit (CVE-2026-28840) Published: 2026-05-12 | Severity: 10 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/apple-osx-packagekit-cve-2026-28840/</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>CVE-2026-28906</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>vulnerability OS X update for Networking (CVE-2026-28906) Published: 2026-05-12 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/apple-osx-networking-cve-2026-28906/</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>CVE-2026-28941</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>vulnerability OS X update for Model I/O (CVE-2026-28941) Published: 2026-05-12 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/apple-osx-modelio-cve-2026-28941/</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>CVE-2026-28940</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>vulnerability OS X update for Model I/O (CVE-2026-28940) Published: 2026-05-12 | Severity: 10 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/apple-osx-modelio-cve-2026-28940/</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>CVE-2026-43668</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>vulnerability OS X update for mDNSResponder (CVE-2026-43668) Published: 2026-05-12 | Severity: 10 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/apple-osx-mdnsresponder-cve-2026-43668/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rapid7_cves.xlsx
+++ b/rapid7_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E121"/>
+  <dimension ref="A1:E161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3683,6 +3683,1086 @@
         </is>
       </c>
     </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>CVE-2026-2291</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>CVE-2026-44873</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>CVE-2026-44872</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>CVE-2026-44870</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>CVE-2026-44869</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>CVE-2026-44868</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>CVE-2026-44867</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>CVE-2026-44866</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>CVE-2026-44865</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>CVE-2026-44864</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>CVE-2026-44863</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>CVE-2026-44862</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>CVE-2026-44861</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>CVE-2026-44860</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>CVE-2026-44859</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>CVE-2026-44858</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>CVE-2026-44857</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>CVE-2026-44856</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>CVE-2026-44855</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>CVE-2026-44854</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>CVE-2026-2291</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>vulnerability SUSE: CVE-2026-2291: SUSE Linux Security Advisory Published: 2026-05-13 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/suse-cve-2026-2291/</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>CVE-2026-44873</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>vulnerability Aruba AOS-8: CVE-2026-44873: Insufficient Session Invalidation on User Account Deactivation in AOS-8 Operating System Published: 2026-05</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/aruba-aos-8-cve-2026-44873/</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>CVE-2026-44872</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>vulnerability Aruba AOS-8: CVE-2026-44872: Authenticated Arbitrary File Upload via Command Injection in AOS-8 AND AOS-10 Web-Based Management Interfac</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/aruba-aos-8-cve-2026-44872/</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>CVE-2026-44870</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>vulnerability Aruba AOS-8: CVE-2026-44870: Authenticated Command Injection Vulnerabilities in Command Line Interface (CLI) Service Accessed by PAPI Pr</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/aruba-aos-8-cve-2026-44870/</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>CVE-2026-44869</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>vulnerability Aruba AOS-8: CVE-2026-44869: Authenticated Command Injection Vulnerabilities in the Web-Based Management Interface of AOS-8 and AOS-10 P</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/aruba-aos-8-cve-2026-44869/</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>CVE-2026-44868</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>vulnerability Aruba AOS-8: CVE-2026-44868: Authenticated Command Injection Vulnerabilities in the Web-Based Management Interface of AOS-8 and AOS-10 P</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/aruba-aos-8-cve-2026-44868/</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>CVE-2026-44867</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>vulnerability Aruba AOS-8: CVE-2026-44867: Authenticated Command Injection Vulnerabilities in the Web-Based Management Interface of AOS-8 and AOS-10 P</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/aruba-aos-8-cve-2026-44867/</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>CVE-2026-44866</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>vulnerability Aruba AOS-8: CVE-2026-44866: Authenticated Command Injection Vulnerabilities in the Web-Based Management Interface of AOS-8 and AOS-10 P</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/aruba-aos-8-cve-2026-44866/</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>CVE-2026-44865</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>vulnerability Aruba AOS-8: CVE-2026-44865: Authenticated Command Injection Vulnerabilities in the Web-Based Management Interface of AOS-8 and AOS-10 P</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/aruba-aos-8-cve-2026-44865/</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>CVE-2026-44864</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>vulnerability Aruba AOS-8: CVE-2026-44864: Authenticated Remote Code Execution via SQL Injection in AOS-8 and AOS-10 Operating Systems Published: 2026</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/aruba-aos-8-cve-2026-44864/</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>CVE-2026-44863</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>vulnerability Aruba AOS-8: CVE-2026-44863: Authenticated Remote Code Execution via SQL Injection in AOS-8 and AOS-10 Operating Systems Published: 2026</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/aruba-aos-8-cve-2026-44863/</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>CVE-2026-44862</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>vulnerability Aruba AOS-8: CVE-2026-44862: Authenticated Remote Code Execution via SQL Injection in AOS-8 and AOS-10 Operating Systems Published: 2026</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/aruba-aos-8-cve-2026-44862/</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>CVE-2026-44861</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>vulnerability Aruba AOS-8: CVE-2026-44861: Authenticated Remote Code Execution via SQL Injection in AOS-8 and AOS-10 Operating Systems Published: 2026</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/aruba-aos-8-cve-2026-44861/</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>CVE-2026-44860</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>vulnerability Aruba AOS-8: CVE-2026-44860: Authenticated Remote Code Execution via SQL Injection in AOS-8 and AOS-10 Operating Systems Published: 2026</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/aruba-aos-8-cve-2026-44860/</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>CVE-2026-44859</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>vulnerability Aruba AOS-8: CVE-2026-44859: Authenticated Stack-Based Buffer Overflow in PAPI Services Published: 2026-05-12 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/aruba-aos-8-cve-2026-44859/</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>CVE-2026-44858</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>vulnerability Aruba AOS-8: CVE-2026-44858: Authenticated Stack-Based Buffer Overflow in PAPI Services Published: 2026-05-12 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/aruba-aos-8-cve-2026-44858/</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>CVE-2026-44857</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>vulnerability Aruba AOS-8: CVE-2026-44857: Authenticated Stack-Based Buffer Overflow in PAPI Services Published: 2026-05-12 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/aruba-aos-8-cve-2026-44857/</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>CVE-2026-44856</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>vulnerability Aruba AOS-8: CVE-2026-44856: Authenticated Stack-Based Buffer Overflow in PAPI Services Published: 2026-05-12 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/aruba-aos-8-cve-2026-44856/</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>CVE-2026-44855</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>vulnerability Aruba AOS-8: CVE-2026-44855: Authenticated Stack-Based Buffer Overflow in PAPI Services Published: 2026-05-12 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/aruba-aos-8-cve-2026-44855/</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>CVE-2026-44854</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>vulnerability Aruba AOS-8: CVE-2026-44854: Authenticated Remote Code Execution via Arbitrary File Write in AOS-8 and AOS-10 Web-Based Management Inter</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/aruba-aos-8-cve-2026-44854/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rapid7_cves.xlsx
+++ b/rapid7_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E161"/>
+  <dimension ref="A1:E179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4763,6 +4763,492 @@
         </is>
       </c>
     </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>CVE-2026-2291</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>2023-05-29</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>CVE-2026-44873</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>2023-05-29</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>CVE-2026-44872</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>2023-05-29</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>CVE-2026-44870</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>2023-05-29</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>CVE-2026-44869</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>2023-05-29</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>CVE-2026-44868</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>2023-05-29</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>CVE-2026-44867</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>2023-05-29</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>CVE-2026-44866</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>2023-05-29</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>CVE-2026-44865</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>2023-05-29</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>CVE-2026-44864</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>2023-05-29</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>CVE-2026-44863</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>2023-05-29</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>CVE-2026-44862</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>2023-05-29</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>CVE-2026-44861</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>2023-05-29</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>CVE-2026-44860</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>2023-05-29</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>CVE-2026-44859</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>2023-05-29</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>CVE-2026-44858</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>2023-05-29</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>CVE-2026-44857</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>2023-05-29</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>CVE-2026-44856</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>2023-05-29</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rapid7_cves.xlsx
+++ b/rapid7_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E179"/>
+  <dimension ref="A1:E219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5249,6 +5249,1086 @@
         </is>
       </c>
     </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>CVE-2026-7360</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>CVE-2026-7359</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>CVE-2026-7357</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>CVE-2026-7356</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>CVE-2026-7354</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>CVE-2026-7353</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>CVE-2026-7351</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>CVE-2026-7350</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>CVE-2026-7349</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>CVE-2026-7345</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>CVE-2026-7341</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>CVE-2026-7340</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>CVE-2026-7339</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>CVE-2026-7333</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>CVE-2026-6638</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>CVE-2026-6637</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>CVE-2026-6575</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>CVE-2026-6479</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>CVE-2026-6478</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>CVE-2026-6477</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>CVE-2026-7360</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>vulnerability Alpine Linux: CVE-2026-7360: Improper Input Validation Published: 2026-04-28 | Severity: 3 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alpine-linux-cve-2026-7360/</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>CVE-2026-7359</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>vulnerability Alpine Linux: CVE-2026-7359: Use After Free Published: 2026-04-28 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alpine-linux-cve-2026-7359/</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>CVE-2026-7357</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>vulnerability Alpine Linux: CVE-2026-7357: Use After Free Published: 2026-04-28 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alpine-linux-cve-2026-7357/</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>CVE-2026-7356</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>vulnerability Alpine Linux: CVE-2026-7356: Use After Free Published: 2026-04-28 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alpine-linux-cve-2026-7356/</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>CVE-2026-7354</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>vulnerability Alpine Linux: CVE-2026-7354: Out-of-bounds Read Published: 2026-04-28 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alpine-linux-cve-2026-7354/</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>CVE-2026-7353</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>vulnerability Alpine Linux: CVE-2026-7353: Heap-based Buffer Overflow Published: 2026-04-28 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alpine-linux-cve-2026-7353/</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>CVE-2026-7351</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>vulnerability Alpine Linux: CVE-2026-7351: Race Condition Published: 2026-04-28 | Severity: 3 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alpine-linux-cve-2026-7351/</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>CVE-2026-7350</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>vulnerability Alpine Linux: CVE-2026-7350: Use After Free Published: 2026-04-28 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alpine-linux-cve-2026-7350/</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>CVE-2026-7349</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>vulnerability Alpine Linux: CVE-2026-7349: Use After Free Published: 2026-04-28 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alpine-linux-cve-2026-7349/</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>CVE-2026-7345</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>vulnerability Alpine Linux: CVE-2026-7345: Improper Input Validation Published: 2026-04-28 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alpine-linux-cve-2026-7345/</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>CVE-2026-7341</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>vulnerability Alpine Linux: CVE-2026-7341: Use After Free Published: 2026-04-28 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alpine-linux-cve-2026-7341/</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>CVE-2026-7340</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>vulnerability Alpine Linux: CVE-2026-7340: External Control of Assumed-Immutable Web Parameter Published: 2026-04-28 | Severity: 4 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alpine-linux-cve-2026-7340/</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>CVE-2026-7339</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>vulnerability Alpine Linux: CVE-2026-7339: Heap-based Buffer Overflow Published: 2026-04-28 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alpine-linux-cve-2026-7339/</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>CVE-2026-7333</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>vulnerability Alpine Linux: CVE-2026-7333: Use After Free Published: 2026-04-28 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alpine-linux-cve-2026-7333/</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>CVE-2026-6638</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>vulnerability Alpine Linux: CVE-2026-6638: SQL Injection Published: 2026-05-14 | Severity: 4 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alpine-linux-cve-2026-6638/</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>CVE-2026-6637</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>vulnerability Alpine Linux: CVE-2026-6637: Stack-based Buffer Overflow Published: 2026-05-14 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alpine-linux-cve-2026-6637/</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>CVE-2026-6575</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>vulnerability Alpine Linux: CVE-2026-6575: Buffer Over-read Published: 2026-05-14 | Severity: 4 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alpine-linux-cve-2026-6575/</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>CVE-2026-6479</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>vulnerability Alpine Linux: CVE-2026-6479: Uncontrolled Recursion Published: 2026-05-14 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alpine-linux-cve-2026-6479/</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>CVE-2026-6478</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>vulnerability Alpine Linux: CVE-2026-6478: Covert Timing Channel Published: 2026-05-14 | Severity: 6 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alpine-linux-cve-2026-6478/</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>CVE-2026-6477</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>vulnerability Alpine Linux: CVE-2026-6477: Use of Inherently Dangerous Function Published: 2026-05-14 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alpine-linux-cve-2026-6477/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rapid7_cves.xlsx
+++ b/rapid7_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E219"/>
+  <dimension ref="A1:E259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6329,6 +6329,1086 @@
         </is>
       </c>
     </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>CVE-2026-41882</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>CVE-2026-8587</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>CVE-2026-8586</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>CVE-2026-8585</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>CVE-2026-8584</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>CVE-2026-8583</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>CVE-2026-8582</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>CVE-2026-8581</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>CVE-2026-8580</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>CVE-2026-8579</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>CVE-2026-8578</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>CVE-2026-8577</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>CVE-2026-8576</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>CVE-2026-8575</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>CVE-2026-8574</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>CVE-2026-8573</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>CVE-2026-8572</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>CVE-2026-8571</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>CVE-2026-8570</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>CVE-2026-8569</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>CVE-2026-41882</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>vulnerability JetBrains IntelliJ IDEA: CVE-2026-41882: Reading arbitrary local files was possible via built-in web server. Reported by Antoni Tremblay</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/jetbrains-intellij-idea-cve-2026-41882/</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>CVE-2026-8587</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-8587: chromium -- security update Published: 2026-05-17 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-8587/</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>CVE-2026-8586</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-8586: chromium -- security update Published: 2026-05-17 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-8586/</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>CVE-2026-8585</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-8585: chromium -- security update Published: 2026-05-17 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-8585/</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>CVE-2026-8584</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-8584: chromium -- security update Published: 2026-05-17 | Severity: 4 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-8584/</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>CVE-2026-8583</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-8583: chromium -- security update Published: 2026-05-17 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-8583/</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>CVE-2026-8582</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-8582: chromium -- security update Published: 2026-05-17 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-8582/</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>CVE-2026-8581</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-8581: chromium -- security update Published: 2026-05-17 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-8581/</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>CVE-2026-8580</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-8580: chromium -- security update Published: 2026-05-17 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-8580/</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>CVE-2026-8579</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-8579: chromium -- security update Published: 2026-05-17 | Severity: 3 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-8579/</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>CVE-2026-8578</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-8578: chromium -- security update Published: 2026-05-17 | Severity: 3 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-8578/</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>CVE-2026-8577</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-8577: chromium -- security update Published: 2026-05-17 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-8577/</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>CVE-2026-8576</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-8576: chromium -- security update Published: 2026-05-17 | Severity: 4 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-8576/</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>CVE-2026-8575</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-8575: chromium -- security update Published: 2026-05-17 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-8575/</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>CVE-2026-8574</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-8574: chromium -- security update Published: 2026-05-17 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-8574/</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>CVE-2026-8573</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-8573: chromium -- security update Published: 2026-05-17 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-8573/</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>CVE-2026-8572</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-8572: chromium -- security update Published: 2026-05-17 | Severity: 3 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-8572/</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>CVE-2026-8571</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-8571: chromium -- security update Published: 2026-05-17 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-8571/</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>CVE-2026-8570</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-8570: chromium -- security update Published: 2026-05-17 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-8570/</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>CVE-2026-8569</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-8569: chromium -- security update Published: 2026-05-17 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-8569/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rapid7_cves.xlsx
+++ b/rapid7_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E259"/>
+  <dimension ref="A1:E299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7409,6 +7409,1086 @@
         </is>
       </c>
     </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>CVE-2017-17151</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>2017-12-06</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>CVE-2026-21863</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>2017-12-06</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>CVE-2025-67733</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>2017-12-06</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>CVE-2026-3718</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>2017-12-06</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>CVE-2025-11800</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>2017-12-06</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>CVE-2026-3004</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>2017-12-06</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>CVE-2026-6504</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>2017-12-06</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>CVE-2026-5694</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>2017-12-06</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>CVE-2026-1985</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>2017-12-06</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>CVE-2026-40742</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>2017-12-06</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>CVE-2026-6670</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>2017-12-06</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>CVE-2026-6512</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>2017-12-06</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>CVE-2026-6252</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>2017-12-06</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>CVE-2026-6177</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>2017-12-06</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>CVE-2025-14755</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>2017-12-06</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>CVE-2025-9989</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>2017-12-06</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>CVE-2026-7051</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>2017-12-06</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>CVE-2025-15463</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>2017-12-06</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>CVE-2026-42945</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>2017-12-06</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>CVE-2026-41035</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>2017-12-06</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>CVE-2017-17151</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>2017-12-06</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>vulnerability Huawei VRP: CVE-2017-17151: Input Validation Vulnerability in H323 Protocol of Huawei products Published: 2017-12-06 | Severity: 4 EXPLO</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/huawei-vrp-cve-2017-17151/</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>CVE-2026-21863</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-21863: redis -- security update Published: 2026-05-18 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-21863/</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>CVE-2025-67733</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2025-67733: redis -- security update Published: 2026-05-18 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2025-67733/</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>CVE-2026-3718</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: worker: CVE-2026-3718: Improper Neutralization of Input During Web Page Generation ('Cross-site Scripting') Published:</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/worker-plugin-cve-2026-3718/</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>CVE-2025-11800</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: surbma-minicrm-shortcode: CVE-2025-11800: Improper Neutralization of Input During Web Page Generation ('Cross-site Scr</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/surbma-minicrm-shortcode-plugin-cve-2025-11800/</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>CVE-2026-3004</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: snow-monkey-blocks: CVE-2026-3004: Improper Neutralization of Input During Web Page Generation ('Cross-site Scripting'</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/snow-monkey-blocks-plugin-cve-2026-3004/</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>CVE-2026-6504</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: royal-elementor-addons: CVE-2026-6504: Improper Neutralization of Input During Web Page Generation ('Cross-site Script</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/royal-elementor-addons-plugin-cve-2026-6504/</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>CVE-2026-5694</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: quick-interest-slider: CVE-2026-5694: Improper Neutralization of Input During Web Page Generation ('Cross-site Scripti</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/quick-interest-slider-plugin-cve-2026-5694/</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>CVE-2026-1985</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: press3d: CVE-2026-1985: Improper Neutralization of Input During Web Page Generation ('Cross-site Scripting') Published</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/press3d-plugin-cve-2026-1985/</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>CVE-2026-40742</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: nelio-ab-testing: CVE-2026-40742: Exposure of Sensitive Information to an Unauthorized Actor Published: 2026-03-17 | S</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/nelio-ab-testing-plugin-cve-2026-40742/</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>CVE-2026-6670</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: media-sync: CVE-2026-6670: Improper Limitation of a Pathname to a Restricted Directory ('Path Traversal') Published: 2</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/media-sync-plugin-cve-2026-6670/</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>CVE-2026-6512</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: infusedwooPRO: CVE-2026-6512: Missing Authorization Published: 2026-05-13 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/infusedwoopro-plugin-cve-2026-6512/</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>CVE-2026-6252</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: display-a-meta-field-as-block: CVE-2026-6252: Improper Neutralization of Input During Web Page Generation ('Cross-site</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/display-a-meta-field-as-block-plugin-cve-2026-6252/</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>CVE-2026-6177</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: custom-twitter-feeds: CVE-2026-6177: Improper Neutralization of Input During Web Page Generation ('Cross-site Scriptin</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/custom-twitter-feeds-plugin-cve-2026-6177/</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>CVE-2025-14755</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: cost-calculator-builder: CVE-2025-14755: Missing Authorization Published: 2026-05-12 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/cost-calculator-builder-plugin-cve-2025-14755/</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>CVE-2025-9989</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: broadstreet: CVE-2025-9989: Improper Neutralization of Input During Web Page Generation ('Cross-site Scripting') Publi</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/broadstreet-plugin-cve-2025-9989/</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>CVE-2026-7051</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: blog2social: CVE-2026-7051: Missing Authorization Published: 2026-05-12 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/blog2social-plugin-cve-2026-7051/</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>CVE-2025-15463</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: acf-extended: CVE-2025-15463: Improper Control of Generation of Code ('Code Injection') Published: 2026-05-12 | Severi</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/acf-extended-plugin-cve-2025-15463/</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>CVE-2026-42945</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vulnerability Red Hat: CVE-2026-42945: nginx: NGINX: Arbitrary Code Execution Vulnerability (Multiple Advisories) Published: 2026-05-13 | Severity: 9 </t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/redhat_linux-cve-2026-42945/</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>CVE-2026-41035</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>vulnerability Red Hat: CVE-2026-41035: rsync: Rsync: Use-after-free vulnerability in extended attribute handling (Multiple Advisories) Published: 2026</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/redhat_linux-cve-2026-41035/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rapid7_cves.xlsx
+++ b/rapid7_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E299"/>
+  <dimension ref="A1:E339"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8489,6 +8489,1086 @@
         </is>
       </c>
     </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>CVE-2026-23943</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>CVE-2026-23942</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>CVE-2026-23941</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>CVE-2026-21620</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>CVE-2026-46483</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>CVE-2026-43206</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>CVE-2026-42501</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>CVE-2026-42499</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>CVE-2026-42009</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>CVE-2026-39836</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>CVE-2026-39826</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>CVE-2026-39825</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>CVE-2026-39823</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>CVE-2026-39820</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>CVE-2026-39819</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>CVE-2026-39817</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>CVE-2026-3805</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>CVE-2026-3784</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>CVE-2026-3783</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>CVE-2026-34282</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>CVE-2026-23943</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-23943: erlang -- security update Published: 2026-05-19 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-23943/</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>CVE-2026-23942</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-23942: erlang -- security update Published: 2026-05-19 | Severity: 6 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-23942/</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>CVE-2026-23941</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-23941: erlang -- security update Published: 2026-05-19 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-23941/</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>CVE-2026-21620</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-21620: erlang -- security update Published: 2026-05-19 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-21620/</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>CVE-2026-46483</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>vulnerability Alpine Linux: CVE-2026-46483: OS Command Injection Published: 2026-05-15 | Severity: 3 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alpine-linux-cve-2026-46483/</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>CVE-2026-43206</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>vulnerability Alpine Linux: CVE-2026-43206: Out-of-bounds Write Published: 2026-05-06 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alpine-linux-cve-2026-43206/</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>CVE-2026-42501</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>vulnerability Alpine Linux: CVE-2026-42501: Improper Verification of Cryptographic Signature Published: 2026-05-07 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alpine-linux-cve-2026-42501/</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>CVE-2026-42499</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>vulnerability Alpine Linux: CVE-2026-42499: Vulnerability in Multiple Components Published: 2026-05-07 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alpine-linux-cve-2026-42499/</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>CVE-2026-42009</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>vulnerability Alpine Linux: CVE-2026-42009: Undefined Behavior for Input to API Published: 2026-05-18 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alpine-linux-cve-2026-42009/</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>CVE-2026-39836</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>vulnerability Alpine Linux: CVE-2026-39836: NULL Pointer Dereference Published: 2026-05-07 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alpine-linux-cve-2026-39836/</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>CVE-2026-39826</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>vulnerability Alpine Linux: CVE-2026-39826: Improper Encoding or Escaping of Output Published: 2026-05-07 | Severity: 6 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alpine-linux-cve-2026-39826/</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>CVE-2026-39825</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>vulnerability Alpine Linux: CVE-2026-39825: Vulnerability in Multiple Components Published: 2026-05-07 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alpine-linux-cve-2026-39825/</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>CVE-2026-39823</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>vulnerability Alpine Linux: CVE-2026-39823: Cross-site Scripting Published: 2026-05-07 | Severity: 6 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alpine-linux-cve-2026-39823/</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>CVE-2026-39820</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>vulnerability Alpine Linux: CVE-2026-39820: Allocation of Resources Without Limits or Throttling Published: 2026-05-07 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alpine-linux-cve-2026-39820/</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>CVE-2026-39819</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>vulnerability Alpine Linux: CVE-2026-39819: Link Following Published: 2026-05-07 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alpine-linux-cve-2026-39819/</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>CVE-2026-39817</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>vulnerability Alpine Linux: CVE-2026-39817: Out-of-bounds Write Published: 2026-05-07 | Severity: 4 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alpine-linux-cve-2026-39817/</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>CVE-2026-3805</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>vulnerability Alpine Linux: CVE-2026-3805: Use After Free Published: 2026-03-11 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alpine-linux-cve-2026-3805/</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>CVE-2026-3784</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>vulnerability Alpine Linux: CVE-2026-3784: Authentication Bypass by Primary Weakness Published: 2026-03-11 | Severity: 6 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alpine-linux-cve-2026-3784/</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>CVE-2026-3783</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>vulnerability Alpine Linux: CVE-2026-3783: Insufficiently Protected Credentials Published: 2026-03-11 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alpine-linux-cve-2026-3783/</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>CVE-2026-34282</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>vulnerability Alpine Linux: CVE-2026-34282: Uncontrolled Resource Consumption Published: 2026-04-21 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alpine-linux-cve-2026-34282/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rapid7_cves.xlsx
+++ b/rapid7_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E339"/>
+  <dimension ref="A1:E379"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9569,6 +9569,1086 @@
         </is>
       </c>
     </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>CVE-2020-1875</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>2020-02-19</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>CVE-2026-4887</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>2020-02-19</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>CVE-2026-42945</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>2020-02-19</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>CVE-2026-4154</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>2020-02-19</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>CVE-2026-4153</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>2020-02-19</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>CVE-2026-4152</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>2020-02-19</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>CVE-2026-4151</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>2020-02-19</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>CVE-2026-4150</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>2020-02-19</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>CVE-2026-41316</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>2020-02-19</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>CVE-2026-41035</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>2020-02-19</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>CVE-2026-40356</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>2020-02-19</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>CVE-2026-40355</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>2020-02-19</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>CVE-2026-40164</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>2020-02-19</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>CVE-2026-39979</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>2020-02-19</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>CVE-2026-23278</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>2020-02-19</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>CVE-2025-15369</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>2020-02-19</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>CVE-2026-45438</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>2020-02-19</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>CVE-2026-42672</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>2020-02-19</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>CVE-2026-23970</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>2020-02-19</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>CVE-2025-14767</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>2020-02-19</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>The Rapid7 2026 Global Threat Landscape Report is out now. Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Explo</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>CVE-2020-1875</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>2020-02-19</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>vulnerability Huawei VRP: CVE-2020-1875: Invalid Pointer Access Vulnerability in Some Huawei Products Published: 2020-02-19 | Severity: 2 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/huawei-vrp-cve-2020-1875/</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>CVE-2026-4887</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vulnerability Oracle Linux: CVE-2026-4887: ELSA-2026-16484:  gimp security update (IMPORTANT) (Multiple Advisories) Published: 2026-03-26 | Severity: </t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/oracle_linux-cve-2026-4887/</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>CVE-2026-42945</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>vulnerability Oracle Linux: CVE-2026-42945: ELSA-2026-18029:  nginx security update (CRITICAL) (Multiple Advisories) Published: 2026-05-13 | Severity:</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/oracle_linux-cve-2026-42945/</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>CVE-2026-4154</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vulnerability Oracle Linux: CVE-2026-4154: ELSA-2026-16484:  gimp security update (IMPORTANT) (Multiple Advisories) Published: 2026-04-11 | Severity: </t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/oracle_linux-cve-2026-4154/</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>CVE-2026-4153</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vulnerability Oracle Linux: CVE-2026-4153: ELSA-2026-16484:  gimp security update (IMPORTANT) (Multiple Advisories) Published: 2026-04-11 | Severity: </t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/oracle_linux-cve-2026-4153/</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>CVE-2026-4152</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>vulnerability Oracle Linux: CVE-2026-4152: ELSA-2026-16484:  gimp security update (IMPORTANT) Published: 2026-04-11 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/oracle_linux-cve-2026-4152/</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>CVE-2026-4151</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>vulnerability Oracle Linux: CVE-2026-4151: ELSA-2026-16484:  gimp security update (IMPORTANT) Published: 2026-04-11 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/oracle_linux-cve-2026-4151/</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>CVE-2026-4150</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vulnerability Oracle Linux: CVE-2026-4150: ELSA-2026-16484:  gimp security update (IMPORTANT) (Multiple Advisories) Published: 2026-04-11 | Severity: </t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/oracle_linux-cve-2026-4150/</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>CVE-2026-41316</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>vulnerability Oracle Linux: CVE-2026-41316: ELSA-2026-18030:  ruby:3.3 security update (IMPORTANT) (Multiple Advisories) Published: 2026-04-24 | Sever</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/oracle_linux-cve-2026-41316/</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>CVE-2026-41035</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>vulnerability Oracle Linux: CVE-2026-41035: ELSA-2026-17481:  rsync security update (IMPORTANT) Published: 2026-04-16 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/oracle_linux-cve-2026-41035/</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>CVE-2026-40356</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>vulnerability Oracle Linux: CVE-2026-40356: ELSA-2026-16799:  krb5 security update (IMPORTANT) Published: 2026-04-28 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/oracle_linux-cve-2026-40356/</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>CVE-2026-40355</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>vulnerability Oracle Linux: CVE-2026-40355: ELSA-2026-16799:  krb5 security update (IMPORTANT) Published: 2026-04-28 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/oracle_linux-cve-2026-40355/</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>CVE-2026-40164</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>vulnerability Oracle Linux: CVE-2026-40164: ELSA-2026-16252:  jq security update (IMPORTANT) (Multiple Advisories) Published: 2026-04-13 | Severity: 8</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/oracle_linux-cve-2026-40164/</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>CVE-2026-39979</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>vulnerability Oracle Linux: CVE-2026-39979: ELSA-2026-16252:  jq security update (IMPORTANT) (Multiple Advisories) Published: 2026-04-13 | Severity: 8</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/oracle_linux-cve-2026-39979/</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>CVE-2026-23278</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>vulnerability Oracle Linux: CVE-2026-23278: ELSA-2026-50270: Unbreakable Enterprise kernel security update (IMPORTANT) Published: 2026-03-20 | Severit</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/oracle_linux-cve-2026-23278/</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>CVE-2025-15369</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: xpro-elementor-addons: CVE-2025-15369: Missing Authorization Published: 2026-05-19 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/xpro-elementor-addons-plugin-cve-2025-15369/</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>CVE-2026-45438</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: wt-smart-coupons-for-woocommerce: CVE-2026-45438: Missing Authorization Published: 2026-05-15 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/wt-smart-coupons-for-woocommerce-plugin-cve-2026-45438/</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>CVE-2026-42672</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: wpdirectorykit: CVE-2026-42672: Improper Neutralization of Special Elements used in an SQL Command ('SQL Injection') P</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/wpdirectorykit-plugin-cve-2026-42672/</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>CVE-2026-23970</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: wpcf7-redirect: CVE-2026-23970: Improper Neutralization of Input During Web Page Generation ('Cross-site Scripting') P</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/wpcf7-redirect-plugin-cve-2026-23970/</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>CVE-2025-14767</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: wpc-badge-management: CVE-2025-14767: Improper Neutralization of Input During Web Page Generation ('Cross-site Scripti</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/wpc-badge-management-plugin-cve-2025-14767/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rapid7_cves.xlsx
+++ b/rapid7_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E379"/>
+  <dimension ref="A1:E419"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10649,6 +10649,1086 @@
         </is>
       </c>
     </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>CVE-2026-2740</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Read the Q1 2026 Threat Landscape Report now Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A </t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>CVE-2026-4177</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Read the Q1 2026 Threat Landscape Report now Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A </t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>CVE-2026-5843</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Read the Q1 2026 Threat Landscape Report now Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A </t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>CVE-2026-5817</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Read the Q1 2026 Threat Landscape Report now Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A </t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>CVE-2026-20171</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Read the Q1 2026 Threat Landscape Report now Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A </t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>CVE-2026-9126</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Read the Q1 2026 Threat Landscape Report now Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A </t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>CVE-2026-9124</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Read the Q1 2026 Threat Landscape Report now Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A </t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>CVE-2026-9123</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Read the Q1 2026 Threat Landscape Report now Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A </t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>CVE-2026-9122</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Read the Q1 2026 Threat Landscape Report now Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A </t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>CVE-2026-9121</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Read the Q1 2026 Threat Landscape Report now Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A </t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>CVE-2026-9120</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Read the Q1 2026 Threat Landscape Report now Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A </t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>CVE-2026-9119</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Read the Q1 2026 Threat Landscape Report now Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A </t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>CVE-2026-9118</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Read the Q1 2026 Threat Landscape Report now Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A </t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>CVE-2026-9117</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Read the Q1 2026 Threat Landscape Report now Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A </t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>CVE-2026-9116</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Read the Q1 2026 Threat Landscape Report now Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A </t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>CVE-2026-9115</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Read the Q1 2026 Threat Landscape Report now Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A </t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>CVE-2026-9114</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Read the Q1 2026 Threat Landscape Report now Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A </t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>CVE-2026-9113</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Read the Q1 2026 Threat Landscape Report now Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A </t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>CVE-2026-9112</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Read the Q1 2026 Threat Landscape Report now Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A </t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>CVE-2026-9111</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Read the Q1 2026 Threat Landscape Report now Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A </t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>CVE-2026-2740</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>vulnerability Zoho ManageEngine ADSelfService Plus: CVE-2026-2740: Authenticate Remote Code Execution Published: 2026-02-05 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/zoho-manageengine-adselfservice-plus-cve-2026-2740/</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>CVE-2026-4177</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>vulnerability SUSE: CVE-2026-4177: SUSE Linux Security Advisory Published: 2026-04-03 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/suse-cve-2026-4177/</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>CVE-2026-5843</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>vulnerability Docker Desktop: CVE-2026-5843: Inclusion of Functionality from Untrusted Control Sphere Published: 2026-05-22 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/docker-desktop-cve-2026-5843/</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>CVE-2026-5817</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>vulnerability Docker Desktop: CVE-2026-5817: Inclusion of Functionality from Untrusted Control Sphere Published: 2026-05-22 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/docker-desktop-cve-2026-5817/</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>CVE-2026-20171</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>vulnerability Cisco NX-OS: CVE-2026-20171: Cisco Nexus 3000 and 9000 Series Switches Border Gateway Protocol Denial of Service Vulnerability Published</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/cisco-nx-os-cve-2026-20171/</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>CVE-2026-9126</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>vulnerability Google Chrome Vulnerability: CVE-2026-9126 Use after free in DOM Published: 2026-05-24 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/google-chrome-cve-2026-9126/</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>CVE-2026-9124</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>vulnerability Google Chrome Vulnerability: CVE-2026-9124 Insufficient validation of untrusted input in Input Published: 2026-05-24 | Severity: 5 EXPLO</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/google-chrome-cve-2026-9124/</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>CVE-2026-9123</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>vulnerability Google Chrome Vulnerability: CVE-2026-9123 Heap buffer overflow in Chromecast Published: 2026-05-24 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/google-chrome-cve-2026-9123/</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>CVE-2026-9122</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>vulnerability Google Chrome Vulnerability: CVE-2026-9122 Out of bounds read in GPU Published: 2026-05-24 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/google-chrome-cve-2026-9122/</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>CVE-2026-9121</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>vulnerability Google Chrome Vulnerability: CVE-2026-9121 Out of bounds read in GPU Published: 2026-05-24 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/google-chrome-cve-2026-9121/</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>CVE-2026-9120</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>vulnerability Google Chrome Vulnerability: CVE-2026-9120 Use after free in WebRTC Published: 2026-05-24 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/google-chrome-cve-2026-9120/</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>CVE-2026-9119</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>vulnerability Google Chrome Vulnerability: CVE-2026-9119 Heap buffer overflow in WebRTC Published: 2026-05-24 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/google-chrome-cve-2026-9119/</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>CVE-2026-9118</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>vulnerability Google Chrome Vulnerability: CVE-2026-9118 Use after free in XR Published: 2026-05-24 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/google-chrome-cve-2026-9118/</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>CVE-2026-9117</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>vulnerability Google Chrome Vulnerability: CVE-2026-9117 Type Confusion in GFX Published: 2026-05-24 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/google-chrome-cve-2026-9117/</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>CVE-2026-9116</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>vulnerability Google Chrome Vulnerability: CVE-2026-9116 Insufficient policy enforcement in ServiceWorker Published: 2026-05-24 | Severity: 4 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/google-chrome-cve-2026-9116/</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>CVE-2026-9115</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>vulnerability Google Chrome Vulnerability: CVE-2026-9115 Insufficient policy enforcement in Service Worker Published: 2026-05-24 | Severity: 4 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/google-chrome-cve-2026-9115/</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>CVE-2026-9114</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>vulnerability Google Chrome Vulnerability: CVE-2026-9114 Use after free in QUIC Published: 2026-05-24 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/google-chrome-cve-2026-9114/</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>CVE-2026-9113</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>vulnerability Google Chrome Vulnerability: CVE-2026-9113 Out of bounds read in GPU Published: 2026-05-24 | Severity: 4 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/google-chrome-cve-2026-9113/</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>CVE-2026-9112</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>vulnerability Google Chrome Vulnerability: CVE-2026-9112 Use after free in GPU Published: 2026-05-24 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/google-chrome-cve-2026-9112/</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>CVE-2026-9111</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>vulnerability Google Chrome Vulnerability: CVE-2026-9111 Use after free in WebRTC Published: 2026-05-24 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/google-chrome-cve-2026-9111/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rapid7_cves.xlsx
+++ b/rapid7_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E419"/>
+  <dimension ref="A1:E459"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11729,6 +11729,1086 @@
         </is>
       </c>
     </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>CVE-2026-21709</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Read the Q1 2026 Threat Landscape Report now Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A </t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>CVE-2025-6965</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Read the Q1 2026 Threat Landscape Report now Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A </t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>CVE-2026-5172</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Read the Q1 2026 Threat Landscape Report now Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A </t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>CVE-2026-5107</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Read the Q1 2026 Threat Landscape Report now Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A </t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>CVE-2026-4948</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Read the Q1 2026 Threat Landscape Report now Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A </t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>CVE-2026-4893</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Read the Q1 2026 Threat Landscape Report now Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A </t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>CVE-2026-4892</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Read the Q1 2026 Threat Landscape Report now Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A </t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>CVE-2026-4891</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Read the Q1 2026 Threat Landscape Report now Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A </t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>CVE-2026-4890</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Read the Q1 2026 Threat Landscape Report now Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A </t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>CVE-2026-4873</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Read the Q1 2026 Threat Landscape Report now Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A </t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>CVE-2026-4786</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Read the Q1 2026 Threat Landscape Report now Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A </t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>CVE-2026-4775</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Read the Q1 2026 Threat Landscape Report now Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A </t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>CVE-2026-48829</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Read the Q1 2026 Threat Landscape Report now Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A </t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>CVE-2026-21637</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Read the Q1 2026 Threat Landscape Report now Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A </t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>CVE-2026-0206</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Read the Q1 2026 Threat Landscape Report now Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A </t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>CVE-2026-0205</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Read the Q1 2026 Threat Landscape Report now Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A </t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>CVE-2026-0204</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Read the Q1 2026 Threat Landscape Report now Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A </t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>CVE-2025-32818</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Read the Q1 2026 Threat Landscape Report now Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A </t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>CVE-2024-40765</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Read the Q1 2026 Threat Landscape Report now Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A </t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>CVE-2024-22396</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Read the Q1 2026 Threat Landscape Report now Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A </t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>CVE-2026-21709</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>vulnerability Veeam Backup and Replication: CVE-2026-21709: Command Injection Published: 2026-03-12 | Severity: 6 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/veeam-backup-and-replication-cve-2026-21709/</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>CVE-2025-6965</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>vulnerability Microsoft Visual Studio: CVE-2025-6965: Integer Truncation on SQLite Published: 2025-08-14 | Severity: 10 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/microsoft-visual_studio-cve-2025-6965/</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>CVE-2026-5172</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>vulnerability SUSE: CVE-2026-5172: SUSE Linux Security Advisory Published: 2026-05-18 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/suse-cve-2026-5172/</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>CVE-2026-5107</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>vulnerability SUSE: CVE-2026-5107: SUSE Linux Security Advisory Published: 2026-05-05 | Severity: 4 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/suse-cve-2026-5107/</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>CVE-2026-4948</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>vulnerability SUSE: CVE-2026-4948: SUSE Linux Security Advisory Published: 2026-05-15 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/suse-cve-2026-4948/</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>CVE-2026-4893</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>vulnerability SUSE: CVE-2026-4893: SUSE Linux Security Advisory Published: 2026-05-18 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/suse-cve-2026-4893/</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>CVE-2026-4892</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>vulnerability SUSE: CVE-2026-4892: SUSE Linux Security Advisory Published: 2026-05-18 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/suse-cve-2026-4892/</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>CVE-2026-4891</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>vulnerability SUSE: CVE-2026-4891: SUSE Linux Security Advisory Published: 2026-05-18 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/suse-cve-2026-4891/</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>CVE-2026-4890</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>vulnerability SUSE: CVE-2026-4890: SUSE Linux Security Advisory Published: 2026-05-18 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/suse-cve-2026-4890/</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>CVE-2026-4873</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>vulnerability SUSE: CVE-2026-4873: SUSE Linux Security Advisory Published: 2026-05-06 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/suse-cve-2026-4873/</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>CVE-2026-4786</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>vulnerability SUSE: CVE-2026-4786: SUSE Linux Security Advisory Published: 2026-04-28 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/suse-cve-2026-4786/</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>CVE-2026-4775</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>vulnerability SUSE: CVE-2026-4775: SUSE Linux Security Advisory Published: 2026-05-04 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/suse-cve-2026-4775/</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>CVE-2026-48829</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-48829: gsasl -- security update Published: 2026-05-25 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-48829/</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>CVE-2026-21637</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-21637: nodejs -- security update Published: 2026-05-25 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-21637/</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>CVE-2026-0206</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>vulnerability SonicWall SonicOS: CVE-2026-0206: SonicOS post-authentication Stack-based Buffer Overflow vulnerability Published: 2026-04-29 | Severity</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/sonicwall-sonicos-cve-2026-0206/</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>CVE-2026-0205</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>vulnerability SonicWall SonicOS: CVE-2026-0205: SonicOS post-authentication Path Traversal vulnerability Published: 2026-04-29 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/sonicwall-sonicos-cve-2026-0205/</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>CVE-2026-0204</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>vulnerability SonicWall SonicOS: CVE-2026-0204: SonicOS Improper Access Control Vulnerability Published: 2026-04-29 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/sonicwall-sonicos-cve-2026-0204/</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>CVE-2025-32818</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>vulnerability SonicWall SonicOS: CVE-2025-32818: SonicOS SSLVPN NULL Pointer Dereference Denial-of-Service (DoS) Vulnerability Published: 2025-04-24 |</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/sonicwall-sonicos-cve-2025-32818/</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>CVE-2024-40765</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>2025-01-07</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vulnerability SonicWall SonicOS: CVE-2024-40765: Integer-Based Buffer Overflow Vulnerability In SonicOS via IPSec Published: 2025-01-07 | Severity: 6 </t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/sonicwall-sonicos-cve-2024-40765/</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>CVE-2024-22396</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>2024-03-13</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vulnerability SonicWall SonicOS: CVE-2024-22396: Integer-Based Buffer Overflow Vulnerability In SonicOS via IPSec Published: 2024-03-13 | Severity: 6 </t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/sonicwall-sonicos-cve-2024-22396/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rapid7_cves.xlsx
+++ b/rapid7_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E459"/>
+  <dimension ref="A1:E499"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12809,6 +12809,1086 @@
         </is>
       </c>
     </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>CVE-2026-45130</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Read the Q1 2026 Threat Landscape Report now Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A </t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>CVE-2026-44656</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Read the Q1 2026 Threat Landscape Report now Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A </t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>CVE-2026-42899</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Read the Q1 2026 Threat Landscape Report now Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A </t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>CVE-2026-42307</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Read the Q1 2026 Threat Landscape Report now Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A </t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>CVE-2026-33236</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Read the Q1 2026 Threat Landscape Report now Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A </t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>CVE-2026-33231</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Read the Q1 2026 Threat Landscape Report now Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A </t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>CVE-2026-33230</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Read the Q1 2026 Threat Landscape Report now Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A </t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>CVE-2026-32640</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Read the Q1 2026 Threat Landscape Report now Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A </t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>CVE-2026-0848</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Read the Q1 2026 Threat Landscape Report now Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A </t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>CVE-2026-0847</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Read the Q1 2026 Threat Landscape Report now Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A </t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>CVE-2026-0846</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Read the Q1 2026 Threat Landscape Report now Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A </t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>CVE-2026-4408</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Read the Q1 2026 Threat Landscape Report now Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A </t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>CVE-2026-3833</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Read the Q1 2026 Threat Landscape Report now Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A </t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>CVE-2026-3238</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Read the Q1 2026 Threat Landscape Report now Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A </t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>CVE-2026-3012</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Read the Q1 2026 Threat Landscape Report now Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A </t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>CVE-2026-2340</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Read the Q1 2026 Threat Landscape Report now Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A </t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>CVE-2026-1933</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Read the Q1 2026 Threat Landscape Report now Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A </t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>CVE-2026-8992</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Read the Q1 2026 Threat Landscape Report now Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A </t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>CVE-2026-5656</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Read the Q1 2026 Threat Landscape Report now Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A </t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>CVE-2026-5405</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Read the Q1 2026 Threat Landscape Report now Read report Platform Services Resources Partners Company Request Demo Vulnerability &amp; Exploit Database A </t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>CVE-2026-45130</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>vulnerability Ubuntu: USN-8304-1 (CVE-2026-45130): Vim vulnerabilities Published: 2026-05-25 | Severity: 6 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ubuntu-cve-2026-45130/</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>CVE-2026-44656</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>vulnerability Ubuntu: USN-8304-1 (CVE-2026-44656): Vim vulnerabilities Published: 2026-05-25 | Severity: 4 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ubuntu-cve-2026-44656/</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>CVE-2026-42899</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>vulnerability Ubuntu: USN-8298-1 (CVE-2026-42899): .NET vulnerability Published: 2026-05-25 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ubuntu-cve-2026-42899/</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>CVE-2026-42307</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>vulnerability Ubuntu: USN-8304-1 (CVE-2026-42307): Vim vulnerabilities Published: 2026-05-25 | Severity: 3 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ubuntu-cve-2026-42307/</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>CVE-2026-33236</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>vulnerability Ubuntu: USN-8302-1 (CVE-2026-33236): NLTK vulnerabilities Published: 2026-05-25 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ubuntu-cve-2026-33236/</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>CVE-2026-33231</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>vulnerability Ubuntu: USN-8302-1 (CVE-2026-33231): NLTK vulnerabilities Published: 2026-05-25 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ubuntu-cve-2026-33231/</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>CVE-2026-33230</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>vulnerability Ubuntu: USN-8302-1 (CVE-2026-33230): NLTK vulnerabilities Published: 2026-05-25 | Severity: 6 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ubuntu-cve-2026-33230/</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>CVE-2026-32640</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>vulnerability Ubuntu: USN-8301-1 (CVE-2026-32640): SimpleEval vulnerability Published: 2026-05-25 | Severity: 10 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ubuntu-cve-2026-32640/</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>CVE-2026-0848</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>vulnerability Ubuntu: USN-8302-1 (CVE-2026-0848): NLTK vulnerabilities Published: 2026-05-25 | Severity: 10 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ubuntu-cve-2026-0848/</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>CVE-2026-0847</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>vulnerability Ubuntu: USN-8302-1 (CVE-2026-0847): NLTK vulnerabilities Published: 2026-05-25 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ubuntu-cve-2026-0847/</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>CVE-2026-0846</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>vulnerability Ubuntu: USN-8302-1 (CVE-2026-0846): NLTK vulnerabilities Published: 2026-05-25 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ubuntu-cve-2026-0846/</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>CVE-2026-4408</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>vulnerability SUSE: CVE-2026-4408: SUSE Linux Security Advisory Published: 2026-05-27 | Severity: 10 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/suse-cve-2026-4408/</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>CVE-2026-3833</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>vulnerability SUSE: CVE-2026-3833: SUSE Linux Security Advisory Published: 2026-05-27 | Severity: 6 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/suse-cve-2026-3833/</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>CVE-2026-3238</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>vulnerability SUSE: CVE-2026-3238: SUSE Linux Security Advisory Published: 2026-05-27 | Severity: 10 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/suse-cve-2026-3238/</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>CVE-2026-3012</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>vulnerability SUSE: CVE-2026-3012: SUSE Linux Security Advisory Published: 2026-05-27 | Severity: 10 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/suse-cve-2026-3012/</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>CVE-2026-2340</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>vulnerability SUSE: CVE-2026-2340: SUSE Linux Security Advisory Published: 2026-05-27 | Severity: 10 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/suse-cve-2026-2340/</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>CVE-2026-1933</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>vulnerability SUSE: CVE-2026-1933: SUSE Linux Security Advisory Published: 2026-05-27 | Severity: 10 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/suse-cve-2026-1933/</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>CVE-2026-8992</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>vulnerability Ivanti Secure Access Client: CVE-2026-8992: Improper Certificate Validation Published: 2026-05-12 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ivanti-secure-access-client-cve-2026-8992/</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>CVE-2026-5656</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>vulnerability Red Hat: CVE-2026-5656: wireshark: Improper Limitation of a Pathname to a Restricted Directory ('Path Traversal') in Wireshark (Multiple</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/redhat_linux-cve-2026-5656/</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>CVE-2026-5405</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>vulnerability Red Hat: CVE-2026-5405: wireshark: Heap-based Buffer Overflow in Wireshark (Multiple Advisories) Published: 2026-04-30 | Severity: 7 EXP</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/redhat_linux-cve-2026-5405/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rapid7_cves.xlsx
+++ b/rapid7_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E499"/>
+  <dimension ref="A1:E539"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13889,6 +13889,1086 @@
         </is>
       </c>
     </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>CVE-2026-7634</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>CVE-2025-14467</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>CVE-2026-6455</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>CVE-2026-9241</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>CVE-2026-8689</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>CVE-2026-7651</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>CVE-2026-7660</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>CVE-2026-7621</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>CVE-2026-7797</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>CVE-2026-6937</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>CVE-2026-4334</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>CVE-2026-7048</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>CVE-2026-9618</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>CVE-2026-7526</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>CVE-2026-9644</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>CVE-2026-9228</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>CVE-2026-2374</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>CVE-2026-5737</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>CVE-2026-7052</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>CVE-2026-9227</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>CVE-2026-7634</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: wp-slimstat: CVE-2026-7634: Improper Neutralization of Input During Web Page Generation ('Cross-site Scripting') Publi</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/wp-slimstat-plugin-cve-2026-7634/</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>CVE-2025-14467</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: wp-job-portal: CVE-2025-14467: Improper Neutralization of Input During Web Page Generation ('Cross-site Scripting') Pu</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/wp-job-portal-plugin-cve-2025-14467/</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>CVE-2026-6455</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: wp-contact-form-7-db-handler: CVE-2026-6455: Cross-Site Request Forgery (CSRF) Published: 2026-05-27 | Severity: 9 EXP</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/wp-contact-form-7-db-handler-plugin-cve-2026-6455/</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>CVE-2026-9241</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: woocommerce-currency-switcher: CVE-2026-9241: Authorization Bypass Through User-Controlled Key Published: 2026-05-27 |</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/woocommerce-currency-switcher-plugin-cve-2026-9241/</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>CVE-2026-8689</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: visualizer: CVE-2026-8689: Missing Authorization Published: 2026-05-27 | Severity: 4 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/visualizer-plugin-cve-2026-8689/</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>CVE-2026-7651</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: user-registration: CVE-2026-7651: Authorization Bypass Through User-Controlled Key Published: 2026-05-27 | Severity: 5</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/user-registration-plugin-cve-2026-7651/</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>CVE-2026-7660</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: stops-core-theme-and-plugin-updates: CVE-2026-7660: Improper Neutralization of Input During Web Page Generation ('Cros</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/stops-core-theme-and-plugin-updates-plugin-cve-2026-7660/</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>CVE-2026-7621</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: smtp2go: CVE-2026-7621: Missing Authorization Published: 2026-05-27 | Severity: 4 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/smtp2go-plugin-cve-2026-7621/</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>CVE-2026-7797</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vulnerability WordPress Plugin: simply-schedule-appointments: CVE-2026-7797: Improper Neutralization of Special Elements used in an SQL Command ('SQL </t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/simply-schedule-appointments-plugin-cve-2026-7797/</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>CVE-2026-6937</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: simply-schedule-appointments: CVE-2026-6937: Missing Authorization Published: 2026-05-27 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/simply-schedule-appointments-plugin-cve-2026-6937/</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>CVE-2026-4334</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: shariff: CVE-2026-4334: Improper Neutralization of Input During Web Page Generation ('Cross-site Scripting') Published</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/shariff-plugin-cve-2026-4334/</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>CVE-2026-7048</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: photo-gallery: CVE-2026-7048: Improper Neutralization of Special Elements used in an SQL Command ('SQL Injection') Pub</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/photo-gallery-plugin-cve-2026-7048/</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>CVE-2026-9618</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: peachpay-for-woocommerce: CVE-2026-9618: Cross-Site Request Forgery (CSRF) Published: 2026-05-27 | Severity: 4 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/peachpay-for-woocommerce-plugin-cve-2026-9618/</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>CVE-2026-7526</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: pdf-embedder: CVE-2026-7526: Exposure of Sensitive Information to an Unauthorized Actor Published: 2026-05-27 | Severi</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/pdf-embedder-plugin-cve-2026-7526/</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>CVE-2026-9644</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vulnerability WordPress Plugin: new-dev-livesmart-video-chat: CVE-2026-9644: Improper Neutralization of Input During Web Page Generation ('Cross-site </t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/new-dev-livesmart-video-chat-plugin-cve-2026-9644/</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>CVE-2026-9228</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: mp-timetable: CVE-2026-9228: Authorization Bypass Through User-Controlled Key Published: 2026-05-27 | Severity: 4 EXPL</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/mp-timetable-plugin-cve-2026-9228/</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>CVE-2026-2374</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: login-recaptcha: CVE-2026-2374: Improper Neutralization of Input During Web Page Generation ('Cross-site Scripting') P</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/login-recaptcha-plugin-cve-2026-2374/</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>CVE-2026-5737</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: independent-analytics: CVE-2026-5737: Server-Side Request Forgery (SSRF) Published: 2026-05-27 | Severity: 6 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/independent-analytics-plugin-cve-2026-5737/</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>CVE-2026-7052</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: ht-contactform: CVE-2026-7052: Improper Neutralization of Input During Web Page Generation ('Cross-site Scripting') Pu</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ht-contactform-plugin-cve-2026-7052/</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>CVE-2026-9227</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: gutenbee: CVE-2026-9227: Unrestricted Upload of File with Dangerous Type Published: 2026-05-27 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/gutenbee-plugin-cve-2026-9227/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rapid7_cves.xlsx
+++ b/rapid7_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E539"/>
+  <dimension ref="A1:E579"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14969,6 +14969,1086 @@
         </is>
       </c>
     </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>CVE-2020-27871</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>2021-02-10</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>CVE-2020-27870</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>2021-02-10</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>CVE-2020-13169</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>2021-02-10</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>CVE-2020-10148</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>2021-02-10</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>CVE-2019-9546</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>2021-02-10</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>CVE-2019-17127</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>2021-02-10</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>CVE-2019-17125</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>2021-02-10</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>CVE-2019-12864</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>2021-02-10</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>CVE-2019-12863</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>2021-02-10</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>CVE-2026-0875</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>2021-02-10</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>CVE-2026-0874</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>2021-02-10</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>CVE-2025-9460</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>2021-02-10</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>CVE-2025-9459</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>2021-02-10</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>CVE-2025-9458</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>2021-02-10</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>CVE-2025-9457</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>2021-02-10</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>CVE-2025-9456</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>2021-02-10</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>CVE-2025-9455</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>2021-02-10</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>CVE-2025-9454</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>2021-02-10</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>CVE-2025-9453</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>2021-02-10</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>CVE-2025-9452</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>2021-02-10</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>CVE-2020-27871</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>2021-02-10</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>vulnerability SolarWinds Orion Platform: Improper Limitation of a Pathname to a Restricted Directory (CVE-2020-27871) Published: 2021-02-10 | Severity</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/solarwinds-orion_platform-cve-2020-27871/</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>CVE-2020-27870</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>2021-02-10</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>vulnerability SolarWinds Orion Platform: Improper Limitation of a Pathname to a Restricted Directory (CVE-2020-27870) Published: 2021-02-10 | Severity</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/solarwinds-orion_platform-cve-2020-27870/</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>CVE-2020-13169</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>2020-09-17</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>vulnerability SolarWinds Orion Platform: Improper Neutralization of Input During Web Page Generation (CVE-2020-13169) Published: 2020-09-17 | Severity</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/solarwinds-orion_platform-cve-2020-13169/</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>CVE-2020-10148</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>2020-12-29</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>vulnerability SolarWinds Orion Platform: Authentication Bypass Using an Alternate Path or Channel (CVE-2020-10148) Published: 2020-12-29 | Severity: 7</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/solarwinds-orion_platform-cve-2020-10148/</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>CVE-2019-9546</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>2019-03-01</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>vulnerability SolarWinds Orion Platform: Uncontrolled Search Path Element (CVE-2019-9546) Published: 2019-03-01 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/solarwinds-orion_platform-cve-2019-9546/</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>CVE-2019-17127</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>2020-01-17</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>vulnerability SolarWinds Orion Platform: Improper Neutralization of Input During Web Page Generation (CVE-2019-17127) Published: 2020-01-17 | Severity</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/solarwinds-orion_platform-cve-2019-17127/</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>CVE-2019-17125</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>2020-01-17</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>vulnerability SolarWinds Orion Platform: Improper Neutralization of Input During Web Page Generation (CVE-2019-17125) Published: 2020-01-17 | Severity</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/solarwinds-orion_platform-cve-2019-17125/</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>CVE-2019-12864</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>2020-05-04</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>vulnerability SolarWinds Orion Platform: Generation of Error Message Containing Sensitive Information (CVE-2019-12864) Published: 2020-05-04 | Severit</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/solarwinds-orion_platform-cve-2019-12864/</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>CVE-2019-12863</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>2020-02-25</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>vulnerability SolarWinds Orion Platform: Improper Neutralization of Input During Web Page Generation (CVE-2019-12863) Published: 2020-02-25 | Severity</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/solarwinds-orion_platform-cve-2019-12863/</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>CVE-2026-0875</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>vulnerability AutoDesk AutoCAD: CVE-2026-0875: Autodesk Security Advisory ADSK-SA-2026-0004 Published: 2026-02-18 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/autodesk-autocad-cve-2026-0875/</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>CVE-2026-0874</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>vulnerability AutoDesk AutoCAD: CVE-2026-0874: Autodesk Security Advisory ADSK-SA-2026-0004 Published: 2026-02-18 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/autodesk-autocad-cve-2026-0874/</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>CVE-2025-9460</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>vulnerability AutoDesk AutoCAD: CVE-2025-9460: Security Advisory for Autodesk AutoCAD and Certain Specialized Toolsets, Autodesk Advance Steel, Autode</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/autodesk-autocad-cve-2025-9460/</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>CVE-2025-9459</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>vulnerability AutoDesk AutoCAD: CVE-2025-9459: Security Advisory for Autodesk AutoCAD and Certain Specialized Toolsets, Autodesk Advance Steel, Autode</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/autodesk-autocad-cve-2025-9459/</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>CVE-2025-9458</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>vulnerability AutoDesk AutoCAD: CVE-2025-9458: Autodesk Security Advisory ADSK-SA-2025-0019 - Memory Corruption Vulnerabilities in Autodesk Products P</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/autodesk-autocad-cve-2025-9458/</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>CVE-2025-9457</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>vulnerability AutoDesk AutoCAD: CVE-2025-9457: Security Advisory for Autodesk AutoCAD and Certain Specialized Toolsets, Autodesk Advance Steel, Autode</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/autodesk-autocad-cve-2025-9457/</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>CVE-2025-9456</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>vulnerability AutoDesk AutoCAD: CVE-2025-9456: Security Advisory for Autodesk AutoCAD and Certain Specialized Toolsets, Autodesk Advance Steel, Autode</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/autodesk-autocad-cve-2025-9456/</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>CVE-2025-9455</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>vulnerability AutoDesk AutoCAD: CVE-2025-9455: Security Advisory for Autodesk AutoCAD and Certain Specialized Toolsets, Autodesk Advance Steel, Autode</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/autodesk-autocad-cve-2025-9455/</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>CVE-2025-9454</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>vulnerability AutoDesk AutoCAD: CVE-2025-9454: Security Advisory for Autodesk AutoCAD and Certain Specialized Toolsets, Autodesk Advance Steel, Autode</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/autodesk-autocad-cve-2025-9454/</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>CVE-2025-9453</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>vulnerability AutoDesk AutoCAD: CVE-2025-9453: Security Advisory for Autodesk AutoCAD and Certain Specialized Toolsets, Autodesk Advance Steel, Autode</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/autodesk-autocad-cve-2025-9453/</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>CVE-2025-9452</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>vulnerability AutoDesk AutoCAD: CVE-2025-9452: Security Advisory for Autodesk AutoCAD and Certain Specialized Toolsets, Autodesk Advance Steel, Autode</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/autodesk-autocad-cve-2025-9452/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rapid7_cves.xlsx
+++ b/rapid7_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E579"/>
+  <dimension ref="A1:E619"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16049,6 +16049,1086 @@
         </is>
       </c>
     </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>CVE-2026-6732</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>CVE-2026-35414</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>CVE-2026-35388</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>CVE-2026-35387</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>CVE-2026-35386</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>CVE-2026-35385</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>CVE-2026-0992</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>CVE-2026-0990</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>CVE-2026-0989</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>CVE-2026-7465</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>CVE-2026-7459</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>CVE-2026-9757</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>CVE-2026-8382</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>CVE-2026-48840</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>CVE-2026-47166</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>CVE-2026-47165</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>CVE-2026-46693</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>CVE-2026-46692</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>CVE-2026-46559</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>CVE-2026-46523</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>CVE-2026-6732</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>vulnerability IBM AIX: libxml2_advisory11 (CVE-2026-6732): Vulnerability in libxml2 affects AIX Published: 2026-05-28 | Severity: 6 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ibm-aix-cve-2026-6732/</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>CVE-2026-35414</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>vulnerability IBM AIX: openssh_advisory21 (CVE-2026-35414): Vulnerability in openssh affects AIX Published: 2026-05-28 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ibm-aix-cve-2026-35414/</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>CVE-2026-35388</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>vulnerability IBM AIX: openssh_advisory21 (CVE-2026-35388): Vulnerability in openssh affects AIX Published: 2026-05-28 | Severity: 1 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ibm-aix-cve-2026-35388/</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>CVE-2026-35387</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>vulnerability IBM AIX: openssh_advisory21 (CVE-2026-35387): Vulnerability in openssh affects AIX Published: 2026-05-28 | Severity: 4 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ibm-aix-cve-2026-35387/</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>CVE-2026-35386</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>vulnerability IBM AIX: openssh_advisory21 (CVE-2026-35386): Vulnerability in openssh affects AIX Published: 2026-05-28 | Severity: 3 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ibm-aix-cve-2026-35386/</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>CVE-2026-35385</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>vulnerability IBM AIX: openssh_advisory21 (CVE-2026-35385): Vulnerability in openssh affects AIX Published: 2026-05-28 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ibm-aix-cve-2026-35385/</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>CVE-2026-0992</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>vulnerability IBM AIX: libxml2_advisory11 (CVE-2026-0992): Vulnerability in libxml2 affects AIX Published: 2026-05-28 | Severity: 2 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ibm-aix-cve-2026-0992/</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>CVE-2026-0990</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>vulnerability IBM AIX: libxml2_advisory11 (CVE-2026-0990): Vulnerability in libxml2 affects AIX Published: 2026-05-28 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ibm-aix-cve-2026-0990/</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>CVE-2026-0989</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>vulnerability IBM AIX: libxml2_advisory11 (CVE-2026-0989): Vulnerability in libxml2 affects AIX Published: 2026-05-28 | Severity: 4 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ibm-aix-cve-2026-0989/</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>CVE-2026-7465</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: ultimate-addons-for-gutenberg: CVE-2026-7465: Improper Privilege Management Published: 2026-05-29 | Severity: 9 EXPLOR</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ultimate-addons-for-gutenberg-plugin-cve-2026-7465/</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>CVE-2026-7459</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: simple-history: CVE-2026-7459: Weak Password Recovery Mechanism for Forgotten Password Published: 2026-05-29 | Severit</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/simple-history-plugin-cve-2026-7459/</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>CVE-2026-9757</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: geo-my-wp: CVE-2026-9757: Improper Neutralization of Special Elements used in an SQL Command ('SQL Injection') Publish</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/geo-my-wp-plugin-cve-2026-9757/</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>CVE-2026-8382</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: advanced-custom-fields: CVE-2026-8382: Missing Authorization Published: 2026-05-30 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/advanced-custom-fields-plugin-cve-2026-8382/</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>CVE-2026-48840</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-48840: exim4 -- security update Published: 2026-05-31 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-48840/</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>CVE-2026-47166</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-47166: imagemagick -- security update Published: 2026-05-31 | Severity: 10 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-47166/</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>CVE-2026-47165</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-47165: imagemagick -- security update Published: 2026-05-31 | Severity: 10 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-47165/</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>CVE-2026-46693</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-46693: imagemagick -- security update Published: 2026-05-31 | Severity: 10 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-46693/</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>CVE-2026-46692</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-46692: imagemagick -- security update Published: 2026-05-31 | Severity: 10 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-46692/</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>CVE-2026-46559</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-46559: imagemagick -- security update Published: 2026-05-31 | Severity: 10 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-46559/</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>CVE-2026-46523</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-46523: imagemagick -- security update Published: 2026-05-31 | Severity: 10 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-46523/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rapid7_cves.xlsx
+++ b/rapid7_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E619"/>
+  <dimension ref="A1:E659"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17129,6 +17129,1086 @@
         </is>
       </c>
     </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>CVE-2026-47294</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>CVE-2026-48835</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>CVE-2026-42750</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>CVE-2026-48839</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>CVE-2026-49051</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>CVE-2025-31871</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>CVE-2026-24592</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>CVE-2026-42753</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>CVE-2026-42742</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>CVE-2026-42741</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>CVE-2026-27053</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>CVE-2026-25425</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>CVE-2026-27331</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>CVE-2025-68841</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>CVE-2026-42740</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>CVE-2026-48973</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>CVE-2026-39447</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>CVE-2026-10100</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>CVE-2026-25444</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>CVE-2026-48972</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>CVE-2026-47294</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vulnerability Microsoft SharePoint: CVE-2026-47294: Microsoft SharePoint Server Remote Code Execution Vulnerability Published: 2026-05-29 | Severity: </t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/microsoft-sharepoint-cve-2026-47294/</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>CVE-2026-48835</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: wpforms-lite: CVE-2026-48835: Missing Authorization Published: 2026-05-28 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/wpforms-lite-plugin-cve-2026-48835/</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>CVE-2026-42750</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: wpcomplete: CVE-2026-42750: Improper Neutralization of Input During Web Page Generation ('Cross-site Scripting') Publi</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/wpcomplete-plugin-cve-2026-42750/</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>CVE-2026-48839</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: wp-statistics: CVE-2026-48839: Improper Neutralization of Input During Web Page Generation ('Cross-site Scripting') Pu</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/wp-statistics-plugin-cve-2026-48839/</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>CVE-2026-49051</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: wp-meta-and-date-remover: CVE-2026-49051: Missing Authorization Published: 2026-05-27 | Severity: 4 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/wp-meta-and-date-remover-plugin-cve-2026-49051/</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>CVE-2025-31871</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: wp-clone-any-post-type: CVE-2025-31871: URL Redirection to Untrusted Site ('Open Redirect') Published: 2025-04-01 | Se</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/wp-clone-any-post-type-plugin-cve-2025-31871/</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>CVE-2026-24592</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: wp-auto-affiliate-links: CVE-2026-24592: Missing Authorization Published: 2026-05-25 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/wp-auto-affiliate-links-plugin-cve-2026-24592/</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>CVE-2026-42753</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: wc-multivendor-membership: CVE-2026-42753: Missing Authorization Published: 2026-05-29 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/wc-multivendor-membership-plugin-cve-2026-42753/</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>CVE-2026-42742</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: views-for-wpforms-lite: CVE-2026-42742: Improper Neutralization of Special Elements used in an SQL Command ('SQL Injec</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/views-for-wpforms-lite-plugin-cve-2026-42742/</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>CVE-2026-42741</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: views-for-ninja-forms: CVE-2026-42741: Improper Neutralization of Special Elements used in an SQL Command ('SQL Inject</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/views-for-ninja-forms-plugin-cve-2026-42741/</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>CVE-2026-27053</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: videowhisper-live-streaming-integration: CVE-2026-27053: Deserialization of Untrusted Data Published: 2026-05-28 | Sev</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/videowhisper-live-streaming-integration-plugin-cve-2026-27053/</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>CVE-2026-25425</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: user-registration: CVE-2026-25425: Missing Authorization Published: 2026-05-28 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/user-registration-plugin-cve-2026-25425/</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>CVE-2026-27331</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: tour-booking-manager: CVE-2026-27331: Missing Authorization Published: 2026-05-26 | Severity: 4 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/tour-booking-manager-plugin-cve-2026-27331/</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>CVE-2025-68841</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: topper-pack: CVE-2025-68841: Improper Control of Filename for Include/Require Statement in PHP Program ('PHP Remote Fi</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/topper-pack-plugin-cve-2025-68841/</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>CVE-2026-42740</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: tainacan: CVE-2026-42740: Improper Neutralization of Special Elements used in an SQL Command ('SQL Injection') Publish</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/tainacan-plugin-cve-2026-42740/</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>CVE-2026-48973</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: svg-support: CVE-2026-48973: Missing Authorization Published: 2026-05-27 | Severity: 4 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/svg-support-plugin-cve-2026-48973/</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>CVE-2026-39447</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: simply-schedule-appointments: CVE-2026-39447: Improper Neutralization of Input During Web Page Generation ('Cross-site</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/simply-schedule-appointments-plugin-cve-2026-39447/</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>CVE-2026-10100</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: simple-custom-login-page: CVE-2026-10100: Improper Neutralization of Input During Web Page Generation ('Cross-site Scr</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/simple-custom-login-page-plugin-cve-2026-10100/</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>CVE-2026-25444</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: service-booking-manager: CVE-2026-25444: Missing Authorization Published: 2026-05-26 | Severity: 4 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/service-booking-manager-plugin-cve-2026-25444/</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>CVE-2026-48972</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vulnerability WordPress Plugin: seedprod-coming-soon-pro-5: CVE-2026-48972: Improper Control of Filename for Include/Require Statement in PHP Program </t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/seedprod-coming-soon-pro-5-plugin-cve-2026-48972/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rapid7_cves.xlsx
+++ b/rapid7_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E659"/>
+  <dimension ref="A1:E699"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18209,6 +18209,1086 @@
         </is>
       </c>
     </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>CVE-2026-4410</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>CVE-2026-48784</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>CVE-2026-48736</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>CVE-2026-48489</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>CVE-2026-46626</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>CVE-2026-46243</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>CVE-2026-45305</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>CVE-2026-45304</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>CVE-2026-45133</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>CVE-2026-45077</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>CVE-2026-45073</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>CVE-2026-45071</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>CVE-2026-45068</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>CVE-2026-45067</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>CVE-2026-45065</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>CVE-2026-45063</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>CVE-2026-34525</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>CVE-2026-34520</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E677" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>CVE-2026-34519</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E678" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>CVE-2026-34518</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E679" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>CVE-2026-4410</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vulnerability IBM WebSphere Application Server: CVE-2026-4410: IBM WebSphere Application Server and WebSphere Application Server Liberty are affected </t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ibm-was-cve-2026-4410/</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>CVE-2026-48784</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-48784: symfony -- security update Published: 2026-06-02 | Severity: 10 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-48784/</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>CVE-2026-48736</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-48736: symfony -- security update Published: 2026-06-02 | Severity: 10 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E682" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-48736/</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>CVE-2026-48489</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-48489: symfony -- security update Published: 2026-06-02 | Severity: 10 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-48489/</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>CVE-2026-46626</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-46626: symfony -- security update Published: 2026-06-02 | Severity: 10 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-46626/</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>CVE-2026-46243</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-46243: linux -- security update Published: 2026-06-02 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-46243/</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>CVE-2026-45305</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-45305: symfony -- security update Published: 2026-06-02 | Severity: 10 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-45305/</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>CVE-2026-45304</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-45304: symfony -- security update Published: 2026-06-02 | Severity: 10 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-45304/</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>CVE-2026-45133</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-45133: symfony -- security update Published: 2026-06-02 | Severity: 10 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-45133/</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>CVE-2026-45077</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-45077: symfony -- security update Published: 2026-06-02 | Severity: 10 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-45077/</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>CVE-2026-45073</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-45073: symfony -- security update Published: 2026-06-02 | Severity: 10 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-45073/</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>CVE-2026-45071</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-45071: symfony -- security update Published: 2026-06-02 | Severity: 10 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-45071/</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>CVE-2026-45068</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-45068: symfony -- security update Published: 2026-06-02 | Severity: 10 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-45068/</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>CVE-2026-45067</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-45067: symfony -- security update Published: 2026-06-02 | Severity: 10 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E693" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-45067/</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>CVE-2026-45065</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-45065: symfony -- security update Published: 2026-06-02 | Severity: 10 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E694" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-45065/</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>CVE-2026-45063</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-45063: symfony -- security update Published: 2026-06-02 | Severity: 10 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E695" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-45063/</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>CVE-2026-34525</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-34525: python-aiohttp -- security update Published: 2026-06-02 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E696" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-34525/</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>CVE-2026-34520</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-34520: python-aiohttp -- security update Published: 2026-06-02 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-34520/</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>CVE-2026-34519</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-34519: python-aiohttp -- security update Published: 2026-06-02 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E698" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-34519/</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>CVE-2026-34518</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-34518: python-aiohttp -- security update Published: 2026-06-02 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E699" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-34518/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rapid7_cves.xlsx
+++ b/rapid7_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E699"/>
+  <dimension ref="A1:E738"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19289,6 +19289,1059 @@
         </is>
       </c>
     </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>CVE-2026-45186</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E700" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>CVE-2026-4480</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E701" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>CVE-2026-4408</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E702" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>CVE-2026-3012</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E703" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>CVE-2026-28390</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E704" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>CVE-2025-53020</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E705" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>CVE-2026-7568</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E706" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>CVE-2026-7262</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E707" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>CVE-2026-7258</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E708" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>CVE-2026-6735</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E709" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>CVE-2026-5260</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E710" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>CVE-2026-42015</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E711" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>CVE-2026-42013</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E712" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>CVE-2026-42012</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E713" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>CVE-2026-42011</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E714" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>CVE-2026-42010</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E715" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>CVE-2026-42009</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E716" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>CVE-2026-3833</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E717" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>CVE-2026-33846</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E718" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>CVE-2026-45186</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-45186: Important: expat security update (ALSA-2026-22721) Published: 2026-06-03 | Severity: 2 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E719" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-45186/</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>CVE-2026-4480</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-4480: Important: samba security update (ALSA-2026-22644) Published: 2026-06-02 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E720" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-4480/</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>CVE-2026-4408</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-4408: Important: samba security update (ALSA-2026-22644) Published: 2026-06-02 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E721" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-4408/</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>CVE-2026-3012</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-3012: Important: samba security update (ALSA-2026-22644) Published: 2026-06-02 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E722" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-3012/</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>CVE-2026-28390</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-28390: Moderate: openssl security update (Multiple Advisories) Published: 2026-06-01 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E723" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-28390/</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>CVE-2025-53020</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2025-53020: Important: httpd:2.4 security update (ALSA-2026-22140) Published: 2026-06-01 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E724" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2025-53020/</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>CVE-2026-7568</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>vulnerability Oracle Linux: CVE-2026-7568: ELSA-2026-22305:  php:8.2 security update (IMPORTANT) Published: 2026-05-10 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E725" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/oracle_linux-cve-2026-7568/</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>CVE-2026-7262</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>vulnerability Oracle Linux: CVE-2026-7262: ELSA-2026-22305:  php:8.2 security update (IMPORTANT) Published: 2026-05-10 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E726" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/oracle_linux-cve-2026-7262/</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>CVE-2026-7258</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>vulnerability Oracle Linux: CVE-2026-7258: ELSA-2026-22305:  php:8.2 security update (IMPORTANT) Published: 2026-05-10 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E727" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/oracle_linux-cve-2026-7258/</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>CVE-2026-6735</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>vulnerability Oracle Linux: CVE-2026-6735: ELSA-2026-22305:  php:8.2 security update (IMPORTANT) Published: 2026-05-10 | Severity: 6 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E728" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/oracle_linux-cve-2026-6735/</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>CVE-2026-5260</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>vulnerability Oracle Linux: CVE-2026-5260: ELSA-2026-20611:  gnutls security update (IMPORTANT) Published: 2026-05-26 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E729" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/oracle_linux-cve-2026-5260/</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>CVE-2026-45186</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>vulnerability Oracle Linux: CVE-2026-45186: ELSA-2026-22721:  expat security update (IMPORTANT) Published: 2026-05-10 | Severity: 2 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E730" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/oracle_linux-cve-2026-45186/</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>CVE-2026-42015</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>vulnerability Oracle Linux: CVE-2026-42015: ELSA-2026-20611:  gnutls security update (IMPORTANT) Published: 2026-05-26 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E731" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/oracle_linux-cve-2026-42015/</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>CVE-2026-42013</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>vulnerability Oracle Linux: CVE-2026-42013: ELSA-2026-20611:  gnutls security update (IMPORTANT) Published: 2026-05-26 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E732" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/oracle_linux-cve-2026-42013/</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>CVE-2026-42012</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>vulnerability Oracle Linux: CVE-2026-42012: ELSA-2026-20611:  gnutls security update (IMPORTANT) Published: 2026-05-26 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E733" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/oracle_linux-cve-2026-42012/</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>CVE-2026-42011</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>vulnerability Oracle Linux: CVE-2026-42011: ELSA-2026-20611:  gnutls security update (IMPORTANT) Published: 2026-05-07 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E734" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/oracle_linux-cve-2026-42011/</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>CVE-2026-42010</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>vulnerability Oracle Linux: CVE-2026-42010: ELSA-2026-20611:  gnutls security update (IMPORTANT) Published: 2026-05-07 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E735" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/oracle_linux-cve-2026-42010/</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>CVE-2026-42009</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>vulnerability Oracle Linux: CVE-2026-42009: ELSA-2026-20611:  gnutls security update (IMPORTANT) Published: 2026-05-18 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E736" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/oracle_linux-cve-2026-42009/</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>CVE-2026-3833</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>vulnerability Oracle Linux: CVE-2026-3833: ELSA-2026-20611:  gnutls security update (IMPORTANT) Published: 2026-04-30 | Severity: 6 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E737" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/oracle_linux-cve-2026-3833/</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>CVE-2026-33846</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>vulnerability Oracle Linux: CVE-2026-33846: ELSA-2026-20611:  gnutls security update (IMPORTANT) Published: 2026-05-04 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E738" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/oracle_linux-cve-2026-33846/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rapid7_cves.xlsx
+++ b/rapid7_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E738"/>
+  <dimension ref="A1:E761"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20342,6 +20342,627 @@
         </is>
       </c>
     </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>CVE-2026-42930</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E739" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>CVE-2026-42924</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E740" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>CVE-2026-42781</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E741" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>CVE-2026-42408</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E742" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>CVE-2026-28758</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E743" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>CVE-2026-45186</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E744" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>CVE-2026-4480</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E745" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>CVE-2026-4408</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E746" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>CVE-2026-3012</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E747" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>CVE-2026-28390</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E748" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>CVE-2025-53020</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E749" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>CVE-2026-7568</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E750" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>CVE-2026-7262</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E751" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>CVE-2026-7258</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E752" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>CVE-2026-6735</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E753" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>CVE-2026-5260</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E754" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>CVE-2026-42015</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E755" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>CVE-2026-42013</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E756" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>CVE-2026-42930</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>vulnerability F5: CVE-2026-42930: K000160876: Appliance mode iControl REST vulnerability CVE-2026-42930 Published: 2026-05-13 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E757" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/f5-big-ip-cve-2026-42930/</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>CVE-2026-42924</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>vulnerability F5: CVE-2026-42924: K000160926: BIG-IP iControl SOAP vulnerability CVE-2026-42924 Published: 2026-05-13 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E758" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/f5-big-ip-cve-2026-42924/</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>CVE-2026-42781</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>vulnerability F5: CVE-2026-42781: K000160862: BIG-IP FastL4 virtual server vulnerability CVE-2026-42781 Published: 2026-05-13 | Severity: 6 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E759" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/f5-big-ip-cve-2026-42781/</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>CVE-2026-42408</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>vulnerability F5: CVE-2026-42408: K000157981: BIG-IP DNS tmsh vulnerability CVE-2026-42408 Published: 2026-05-13 | Severity: 4 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E760" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/f5-big-ip-cve-2026-42408/</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>CVE-2026-28758</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>vulnerability F5: CVE-2026-28758: K000158070: iControl REST vulnerability CVE-2026-28758 Published: 2026-05-13 | Severity: 4 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E761" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/f5-big-ip-cve-2026-28758/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rapid7_cves.xlsx
+++ b/rapid7_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E761"/>
+  <dimension ref="A1:E791"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20963,6 +20963,816 @@
         </is>
       </c>
     </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>CVE-2026-8959</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E762" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>CVE-2026-4480</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E763" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>CVE-2026-4408</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E764" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>CVE-2026-35177</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E765" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>CVE-2026-33814</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E766" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>CVE-2026-33811</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E767" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>CVE-2026-3012</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E768" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>CVE-2026-45186</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E769" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>CVE-2026-40170</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E770" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>CVE-2026-2340</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E771" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>CVE-2026-8959</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>vulnerability Oracle Linux: CVE-2026-8959: ELSA-2026-22643:  thunderbird security update (IMPORTANT) Published: 2026-05-19 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D772" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E772" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/oracle_linux-cve-2026-8959/</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>CVE-2026-4480</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>vulnerability Oracle Linux: CVE-2026-4480: ELSA-2026-22644:  samba security update (IMPORTANT) Published: 2026-05-26 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D773" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E773" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/oracle_linux-cve-2026-4480/</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>CVE-2026-4408</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>vulnerability Oracle Linux: CVE-2026-4408: ELSA-2026-22644:  samba security update (IMPORTANT) Published: 2026-05-28 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D774" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E774" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/oracle_linux-cve-2026-4408/</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>CVE-2026-42501</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>vulnerability Oracle Linux: CVE-2026-42501: ELSA-2026-22112:  go-toolset:ol8 security update (IMPORTANT) Published: 2026-05-07 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D775" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E775" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/oracle_linux-cve-2026-42501/</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>CVE-2026-42499</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>vulnerability Oracle Linux: CVE-2026-42499: ELSA-2026-22112:  go-toolset:ol8 security update (IMPORTANT) Published: 2026-05-07 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E776" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/oracle_linux-cve-2026-42499/</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>CVE-2026-39836</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>vulnerability Oracle Linux: CVE-2026-39836: ELSA-2026-22112:  go-toolset:ol8 security update (IMPORTANT) Published: 2026-05-07 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D777" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E777" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/oracle_linux-cve-2026-39836/</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>CVE-2026-39826</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>vulnerability Oracle Linux: CVE-2026-39826: ELSA-2026-22112:  go-toolset:ol8 security update (IMPORTANT) Published: 2026-05-07 | Severity: 6 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D778" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E778" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/oracle_linux-cve-2026-39826/</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>CVE-2026-39825</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>vulnerability Oracle Linux: CVE-2026-39825: ELSA-2026-22112:  go-toolset:ol8 security update (IMPORTANT) Published: 2026-05-07 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D779" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E779" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/oracle_linux-cve-2026-39825/</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>CVE-2026-39823</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>vulnerability Oracle Linux: CVE-2026-39823: ELSA-2026-22112:  go-toolset:ol8 security update (IMPORTANT) Published: 2026-05-07 | Severity: 6 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D780" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E780" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/oracle_linux-cve-2026-39823/</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>CVE-2026-39820</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>vulnerability Oracle Linux: CVE-2026-39820: ELSA-2026-22112:  go-toolset:ol8 security update (IMPORTANT) Published: 2026-05-07 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D781" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E781" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/oracle_linux-cve-2026-39820/</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>CVE-2026-39819</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C782" t="inlineStr">
+        <is>
+          <t>vulnerability Oracle Linux: CVE-2026-39819: ELSA-2026-22112:  go-toolset:ol8 security update (IMPORTANT) Published: 2026-05-07 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D782" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E782" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/oracle_linux-cve-2026-39819/</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>CVE-2026-39817</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C783" t="inlineStr">
+        <is>
+          <t>vulnerability Oracle Linux: CVE-2026-39817: ELSA-2026-22112:  go-toolset:ol8 security update (IMPORTANT) Published: 2026-05-07 | Severity: 4 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D783" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E783" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/oracle_linux-cve-2026-39817/</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>CVE-2026-35177</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>vulnerability Oracle Linux: CVE-2026-35177: ELSA-2026-22730:  vim security update (MODERATE) Published: 2026-04-06 | Severity: 3 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D784" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E784" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/oracle_linux-cve-2026-35177/</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>CVE-2026-33814</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>vulnerability Oracle Linux: CVE-2026-33814: ELSA-2026-22112:  go-toolset:ol8 security update (IMPORTANT) Published: 2026-05-07 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D785" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E785" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/oracle_linux-cve-2026-33814/</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>CVE-2026-33811</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C786" t="inlineStr">
+        <is>
+          <t>vulnerability Oracle Linux: CVE-2026-33811: ELSA-2026-22112:  go-toolset:ol8 security update (IMPORTANT) Published: 2026-05-07 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D786" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E786" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/oracle_linux-cve-2026-33811/</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>CVE-2026-3012</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>vulnerability Oracle Linux: CVE-2026-3012: ELSA-2026-22644:  samba security update (IMPORTANT) Published: 2026-05-27 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D787" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E787" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/oracle_linux-cve-2026-3012/</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>CVE-2026-45186</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="C788" t="inlineStr">
+        <is>
+          <t>vulnerability Red Hat: CVE-2026-45186: libexpat: denial of service via crafted XML input (Multiple Advisories) Published: 2026-05-10 | Severity: 8 EXP</t>
+        </is>
+      </c>
+      <c r="D788" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E788" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/redhat_linux-cve-2026-45186/</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>CVE-2026-40170</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="C789" t="inlineStr">
+        <is>
+          <t>vulnerability Red Hat: CVE-2026-40170: ngtcp2: ngtcp2: Denial of service via stack buffer overflow during QUIC handshake (Multiple Advisories) Publish</t>
+        </is>
+      </c>
+      <c r="D789" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E789" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/redhat_linux-cve-2026-40170/</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>CVE-2026-35177</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="C790" t="inlineStr">
+        <is>
+          <t>vulnerability Red Hat: CVE-2026-35177: vim: zip.vim: Vim zip.vim plugin: Arbitrary file overwrite via path traversal bypass (Multiple Advisories) Publ</t>
+        </is>
+      </c>
+      <c r="D790" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E790" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/redhat_linux-cve-2026-35177/</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>CVE-2026-2340</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C791" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vulnerability Red Hat: CVE-2026-2340: samba: vfs_worm does not block directory modification (Multiple Advisories) Published: 2026-05-27 | Severity: 7 </t>
+        </is>
+      </c>
+      <c r="D791" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E791" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/redhat_linux-cve-2026-2340/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rapid7_cves.xlsx
+++ b/rapid7_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E791"/>
+  <dimension ref="A1:E831"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21773,6 +21773,1086 @@
         </is>
       </c>
     </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>CVE-2026-5946</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C792" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D792" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E792" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>CVE-2026-46243</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C793" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D793" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E793" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>CVE-2026-35240</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C794" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D794" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E794" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>CVE-2026-35239</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C795" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D795" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E795" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>CVE-2026-35238</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C796" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D796" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E796" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>CVE-2026-35237</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C797" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D797" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E797" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>CVE-2026-35236</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D798" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E798" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>CVE-2026-34308</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D799" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E799" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>CVE-2026-34304</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E800" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>CVE-2026-34303</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D801" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E801" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>CVE-2026-34293</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D802" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E802" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>CVE-2026-34278</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C803" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D803" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E803" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>CVE-2026-34276</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C804" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D804" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E804" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>CVE-2026-34271</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C805" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D805" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E805" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>CVE-2026-34270</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C806" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D806" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E806" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>CVE-2026-34267</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C807" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D807" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E807" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>CVE-2026-3039</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D808" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E808" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>CVE-2026-22017</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D809" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E809" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>CVE-2026-22015</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D810" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E810" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>CVE-2026-22009</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D811" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E811" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>CVE-2026-5946</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-5946: Important: bind9.16 security update (ALSA-2026-23360) Published: 2026-06-04 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D812" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E812" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-5946/</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>CVE-2026-46243</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-46243: Important: kernel security update (Multiple Advisories) Published: 2026-06-04 | Severity: 6 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D813" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E813" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-46243/</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>CVE-2026-35240</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-35240: Moderate: mysql security update (ALSA-2026-23332) Published: 2026-06-04 | Severity: 6 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D814" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E814" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-35240/</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>CVE-2026-35239</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-35239: Moderate: mysql security update (ALSA-2026-23332) Published: 2026-06-04 | Severity: 6 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D815" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E815" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-35239/</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>CVE-2026-35238</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-35238: Moderate: mysql security update (ALSA-2026-23332) Published: 2026-06-04 | Severity: 6 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D816" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E816" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-35238/</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>CVE-2026-35237</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-35237: Moderate: mysql security update (ALSA-2026-23332) Published: 2026-06-04 | Severity: 6 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D817" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E817" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-35237/</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>CVE-2026-35236</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-35236: Moderate: mysql security update (ALSA-2026-23332) Published: 2026-06-04 | Severity: 6 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D818" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E818" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-35236/</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>CVE-2026-34308</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C819" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-34308: Moderate: mysql security update (ALSA-2026-23332) Published: 2026-06-04 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D819" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E819" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-34308/</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>CVE-2026-34304</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-34304: Moderate: mysql security update (ALSA-2026-23332) Published: 2026-06-04 | Severity: 6 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D820" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E820" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-34304/</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>CVE-2026-34303</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C821" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-34303: Moderate: mysql security update (ALSA-2026-23332) Published: 2026-06-04 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D821" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E821" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-34303/</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>CVE-2026-34293</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-34293: Moderate: mysql security update (ALSA-2026-23332) Published: 2026-06-04 | Severity: 6 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D822" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E822" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-34293/</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>CVE-2026-34278</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-34278: Moderate: mysql security update (ALSA-2026-23332) Published: 2026-06-04 | Severity: 6 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E823" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-34278/</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>CVE-2026-34276</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-34276: Moderate: mysql security update (ALSA-2026-23332) Published: 2026-06-04 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D824" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E824" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-34276/</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>CVE-2026-34271</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C825" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-34271: Moderate: mysql security update (ALSA-2026-23332) Published: 2026-06-04 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D825" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E825" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-34271/</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>CVE-2026-34270</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-34270: Moderate: mysql security update (ALSA-2026-23332) Published: 2026-06-04 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D826" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E826" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-34270/</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>CVE-2026-34267</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-34267: Moderate: mysql security update (ALSA-2026-23332) Published: 2026-06-04 | Severity: 6 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D827" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E827" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-34267/</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>CVE-2026-3039</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-3039: Important: bind9.16 security update (ALSA-2026-23360) Published: 2026-06-04 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D828" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E828" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-3039/</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>CVE-2026-22017</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-22017: Moderate: mysql security update (ALSA-2026-23332) Published: 2026-06-04 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D829" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E829" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-22017/</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>CVE-2026-22015</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-22015: Moderate: mysql security update (ALSA-2026-23332) Published: 2026-06-04 | Severity: 4 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D830" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E830" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-22015/</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>CVE-2026-22009</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-22009: Moderate: mysql security update (ALSA-2026-23332) Published: 2026-06-04 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D831" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E831" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-22009/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rapid7_cves.xlsx
+++ b/rapid7_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E831"/>
+  <dimension ref="A1:E871"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22853,6 +22853,1086 @@
         </is>
       </c>
     </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>CVE-2026-9256</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D832" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E832" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>CVE-2026-9150</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D833" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E833" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>CVE-2026-9149</t>
+        </is>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C834" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D834" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E834" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>CVE-2026-8975</t>
+        </is>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D835" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E835" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>CVE-2026-8974</t>
+        </is>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D836" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E836" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>CVE-2026-8970</t>
+        </is>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C837" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D837" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E837" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>CVE-2026-8968</t>
+        </is>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C838" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D838" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E838" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>CVE-2026-8962</t>
+        </is>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C839" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D839" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E839" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>CVE-2026-8961</t>
+        </is>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C840" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D840" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E840" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>CVE-2026-8958</t>
+        </is>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C841" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D841" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E841" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>CVE-2026-8957</t>
+        </is>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C842" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D842" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E842" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>CVE-2026-8956</t>
+        </is>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C843" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D843" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E843" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>CVE-2026-8955</t>
+        </is>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C844" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D844" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E844" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>CVE-2026-8954</t>
+        </is>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C845" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D845" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E845" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>CVE-2026-8953</t>
+        </is>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C846" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D846" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E846" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>CVE-2026-8950</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C847" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D847" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E847" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>CVE-2026-8947</t>
+        </is>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C848" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D848" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E848" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>CVE-2026-8946</t>
+        </is>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C849" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D849" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E849" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>CVE-2026-8376</t>
+        </is>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C850" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D850" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E850" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>CVE-2026-8177</t>
+        </is>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C851" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D851" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E851" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>CVE-2026-9256</t>
+        </is>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C852" t="inlineStr">
+        <is>
+          <t>vulnerability Amazon Linux 2023: CVE-2026-9256: Important priority package update for nginx Published: 2026-05-22 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D852" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E852" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/amazon_linux_2023-cve-2026-9256/</t>
+        </is>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>CVE-2026-9150</t>
+        </is>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C853" t="inlineStr">
+        <is>
+          <t>vulnerability Amazon Linux 2023: CVE-2026-9150: Important priority package update for libsolv Published: 2026-05-20 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D853" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E853" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/amazon_linux_2023-cve-2026-9150/</t>
+        </is>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>CVE-2026-9149</t>
+        </is>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C854" t="inlineStr">
+        <is>
+          <t>vulnerability Amazon Linux 2023: CVE-2026-9149: Important priority package update for libsolv Published: 2026-05-20 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D854" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E854" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/amazon_linux_2023-cve-2026-9149/</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>CVE-2026-8975</t>
+        </is>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C855" t="inlineStr">
+        <is>
+          <t>vulnerability Amazon Linux 2023: CVE-2026-8975: Important priority package update for firefox Published: 2026-05-19 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D855" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E855" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/amazon_linux_2023-cve-2026-8975/</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="inlineStr">
+        <is>
+          <t>CVE-2026-8974</t>
+        </is>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C856" t="inlineStr">
+        <is>
+          <t>vulnerability Amazon Linux 2023: CVE-2026-8974: Important priority package update for firefox Published: 2026-05-19 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D856" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E856" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/amazon_linux_2023-cve-2026-8974/</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>CVE-2026-8970</t>
+        </is>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C857" t="inlineStr">
+        <is>
+          <t>vulnerability Amazon Linux 2023: CVE-2026-8970: Important priority package update for firefox Published: 2026-05-19 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D857" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E857" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/amazon_linux_2023-cve-2026-8970/</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="inlineStr">
+        <is>
+          <t>CVE-2026-8968</t>
+        </is>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C858" t="inlineStr">
+        <is>
+          <t>vulnerability Amazon Linux 2023: CVE-2026-8968: Important priority package update for firefox Published: 2026-05-19 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D858" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E858" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/amazon_linux_2023-cve-2026-8968/</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="inlineStr">
+        <is>
+          <t>CVE-2026-8962</t>
+        </is>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C859" t="inlineStr">
+        <is>
+          <t>vulnerability Amazon Linux 2023: CVE-2026-8962: Important priority package update for firefox Published: 2026-05-19 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D859" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E859" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/amazon_linux_2023-cve-2026-8962/</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
+          <t>CVE-2026-8961</t>
+        </is>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C860" t="inlineStr">
+        <is>
+          <t>vulnerability Amazon Linux 2023: CVE-2026-8961: Important priority package update for firefox Published: 2026-05-19 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D860" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E860" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/amazon_linux_2023-cve-2026-8961/</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>CVE-2026-8958</t>
+        </is>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C861" t="inlineStr">
+        <is>
+          <t>vulnerability Amazon Linux 2023: CVE-2026-8958: Important priority package update for firefox Published: 2026-05-19 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D861" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E861" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/amazon_linux_2023-cve-2026-8958/</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>CVE-2026-8957</t>
+        </is>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C862" t="inlineStr">
+        <is>
+          <t>vulnerability Amazon Linux 2023: CVE-2026-8957: Important priority package update for firefox Published: 2026-05-19 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D862" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E862" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/amazon_linux_2023-cve-2026-8957/</t>
+        </is>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="inlineStr">
+        <is>
+          <t>CVE-2026-8956</t>
+        </is>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C863" t="inlineStr">
+        <is>
+          <t>vulnerability Amazon Linux 2023: CVE-2026-8956: Important priority package update for firefox Published: 2026-05-19 | Severity: 10 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D863" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E863" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/amazon_linux_2023-cve-2026-8956/</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="inlineStr">
+        <is>
+          <t>CVE-2026-8955</t>
+        </is>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C864" t="inlineStr">
+        <is>
+          <t>vulnerability Amazon Linux 2023: CVE-2026-8955: Important priority package update for firefox Published: 2026-05-19 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D864" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E864" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/amazon_linux_2023-cve-2026-8955/</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>CVE-2026-8954</t>
+        </is>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C865" t="inlineStr">
+        <is>
+          <t>vulnerability Amazon Linux 2023: CVE-2026-8954: Important priority package update for firefox Published: 2026-05-19 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D865" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E865" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/amazon_linux_2023-cve-2026-8954/</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>CVE-2026-8953</t>
+        </is>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C866" t="inlineStr">
+        <is>
+          <t>vulnerability Amazon Linux 2023: CVE-2026-8953: Important priority package update for firefox Published: 2026-05-19 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D866" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E866" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/amazon_linux_2023-cve-2026-8953/</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>CVE-2026-8950</t>
+        </is>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C867" t="inlineStr">
+        <is>
+          <t>vulnerability Amazon Linux 2023: CVE-2026-8950: Important priority package update for firefox Published: 2026-05-19 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D867" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E867" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/amazon_linux_2023-cve-2026-8950/</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>CVE-2026-8947</t>
+        </is>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C868" t="inlineStr">
+        <is>
+          <t>vulnerability Amazon Linux 2023: CVE-2026-8947: Important priority package update for firefox Published: 2026-05-19 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D868" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E868" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/amazon_linux_2023-cve-2026-8947/</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>CVE-2026-8946</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C869" t="inlineStr">
+        <is>
+          <t>vulnerability Amazon Linux 2023: CVE-2026-8946: Important priority package update for firefox Published: 2026-05-19 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D869" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E869" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/amazon_linux_2023-cve-2026-8946/</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>CVE-2026-8376</t>
+        </is>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C870" t="inlineStr">
+        <is>
+          <t>vulnerability Amazon Linux 2023: CVE-2026-8376: Medium priority package update for perl Published: 2026-05-25 | Severity: 10 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D870" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E870" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/amazon_linux_2023-cve-2026-8376/</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>CVE-2026-8177</t>
+        </is>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="C871" t="inlineStr">
+        <is>
+          <t>vulnerability Amazon Linux 2023: CVE-2026-8177: Medium priority package update for perl-XML-LibXML Published: 2026-05-10 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D871" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E871" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/amazon_linux_2023-cve-2026-8177/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rapid7_cves.xlsx
+++ b/rapid7_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E871"/>
+  <dimension ref="A1:E910"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23933,6 +23933,1059 @@
         </is>
       </c>
     </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>CVE-2026-45591</t>
+        </is>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C872" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D872" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E872" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>CVE-2026-48112</t>
+        </is>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C873" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D873" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E873" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>CVE-2026-48111</t>
+        </is>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C874" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D874" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E874" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>CVE-2026-48104</t>
+        </is>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C875" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D875" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E875" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>CVE-2026-48103</t>
+        </is>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C876" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D876" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E876" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>CVE-2026-48102</t>
+        </is>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C877" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D877" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E877" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>CVE-2026-48101</t>
+        </is>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C878" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D878" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E878" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>CVE-2026-48095</t>
+        </is>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C879" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D879" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E879" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>CVE-2026-48092</t>
+        </is>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C880" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D880" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E880" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>CVE-2026-48569</t>
+        </is>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C881" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D881" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E881" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>CVE-2026-47287</t>
+        </is>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C882" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D882" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E882" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>CVE-2026-47284</t>
+        </is>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C883" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D883" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E883" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>CVE-2026-47281</t>
+        </is>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C884" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D884" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E884" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>CVE-2026-40376</t>
+        </is>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C885" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D885" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E885" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>CVE-2026-49975</t>
+        </is>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C886" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D886" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E886" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>CVE-2026-40215</t>
+        </is>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C887" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D887" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E887" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>CVE-2026-35058</t>
+        </is>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C888" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D888" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E888" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>CVE-2026-3238</t>
+        </is>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C889" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D889" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E889" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>CVE-2026-47631</t>
+        </is>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C890" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D890" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E890" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>CVE-2026-45591</t>
+        </is>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C891" t="inlineStr">
+        <is>
+          <t>vulnerability Microsoft ASP.NET: CVE-2026-45591: ASP.NET Core Denial of Service Vulnerability Published: 2026-06-09 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D891" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E891" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/microsoft-asp_net_core-cve-2026-45591/</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>CVE-2026-48112</t>
+        </is>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C892" t="inlineStr">
+        <is>
+          <t>vulnerability 7-Zip: CVE-2026-48112: Out-of-bounds Read Published: 2026-06-05 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D892" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E892" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/7-zip-7-zip-cve-2026-48112/</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>CVE-2026-48111</t>
+        </is>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C893" t="inlineStr">
+        <is>
+          <t>vulnerability 7-Zip: CVE-2026-48111: Out-of-bounds Read Published: 2026-06-05 | Severity: 4 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D893" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E893" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/7-zip-7-zip-cve-2026-48111/</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>CVE-2026-48104</t>
+        </is>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C894" t="inlineStr">
+        <is>
+          <t>vulnerability 7-Zip: CVE-2026-48104: Out-of-bounds Read Published: 2026-06-05 | Severity: 4 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D894" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E894" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/7-zip-7-zip-cve-2026-48104/</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>CVE-2026-48103</t>
+        </is>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C895" t="inlineStr">
+        <is>
+          <t>vulnerability 7-Zip: CVE-2026-48103: Out-of-bounds Read Published: 2026-06-05 | Severity: 4 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D895" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E895" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/7-zip-7-zip-cve-2026-48103/</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>CVE-2026-48102</t>
+        </is>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C896" t="inlineStr">
+        <is>
+          <t>vulnerability 7-Zip: CVE-2026-48102: Out-of-bounds Read Published: 2026-06-05 | Severity: 3 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D896" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E896" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/7-zip-7-zip-cve-2026-48102/</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>CVE-2026-48101</t>
+        </is>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C897" t="inlineStr">
+        <is>
+          <t>vulnerability 7-Zip: CVE-2026-48101: Use of Uninitialized Resource Published: 2026-06-05 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D897" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E897" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/7-zip-7-zip-cve-2026-48101/</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>CVE-2026-48095</t>
+        </is>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C898" t="inlineStr">
+        <is>
+          <t>vulnerability 7-Zip: CVE-2026-48095: Integer Overflow or Wraparound Published: 2026-06-05 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D898" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E898" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/7-zip-7-zip-cve-2026-48095/</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>CVE-2026-48092</t>
+        </is>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C899" t="inlineStr">
+        <is>
+          <t>vulnerability 7-Zip: CVE-2026-48092: Out-of-bounds Read Published: 2026-06-05 | Severity: 4 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D899" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E899" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/7-zip-7-zip-cve-2026-48092/</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>CVE-2026-45591</t>
+        </is>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C900" t="inlineStr">
+        <is>
+          <t>vulnerability Microsoft Visual Studio: CVE-2026-45591: ASP.NET Core Denial of Service Vulnerability Published: 2026-06-09 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D900" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E900" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/microsoft-visual_studio-cve-2026-45591/</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>CVE-2026-48569</t>
+        </is>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C901" t="inlineStr">
+        <is>
+          <t>vulnerability Microsoft VS Code: CVE-2026-48569: Visual Studio Code Security Feature Bypass Vulnerability Published: 2026-06-09 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D901" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E901" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/microsoft-vs_code-cve-2026-48569/</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>CVE-2026-47287</t>
+        </is>
+      </c>
+      <c r="B902" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C902" t="inlineStr">
+        <is>
+          <t>vulnerability Microsoft VS Code: CVE-2026-47287: Visual Studio Code Tampering Vulnerability Published: 2026-06-09 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D902" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E902" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/microsoft-vs_code-cve-2026-47287/</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>CVE-2026-47284</t>
+        </is>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C903" t="inlineStr">
+        <is>
+          <t>vulnerability Microsoft VS Code: CVE-2026-47284: Visual Studio Code Information Disclosure Vulnerability Published: 2026-06-09 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D903" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E903" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/microsoft-vs_code-cve-2026-47284/</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>CVE-2026-47281</t>
+        </is>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C904" t="inlineStr">
+        <is>
+          <t>vulnerability Microsoft VS Code: CVE-2026-47281: Visual Studio Code Elevation of Privilege Vulnerability Published: 2026-06-09 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D904" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E904" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/microsoft-vs_code-cve-2026-47281/</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>CVE-2026-40376</t>
+        </is>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C905" t="inlineStr">
+        <is>
+          <t>vulnerability Microsoft VS Code: CVE-2026-40376: Visual Studio Code Elevation of Privilege Vulnerability Published: 2026-06-09 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D905" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E905" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/microsoft-vs_code-cve-2026-40376/</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>CVE-2026-49975</t>
+        </is>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C906" t="inlineStr">
+        <is>
+          <t>vulnerability Alpine Linux: CVE-2026-49975: Memory Allocation with Excessive Size Value Published: 2026-06-08 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D906" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E906" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alpine-linux-cve-2026-49975/</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>CVE-2026-40215</t>
+        </is>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C907" t="inlineStr">
+        <is>
+          <t>vulnerability Alpine Linux: CVE-2026-40215: Out-of-bounds Read Published: 2026-06-08 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D907" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E907" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alpine-linux-cve-2026-40215/</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>CVE-2026-35058</t>
+        </is>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C908" t="inlineStr">
+        <is>
+          <t>vulnerability Alpine Linux: CVE-2026-35058: Reachable Assertion Published: 2026-06-08 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D908" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E908" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alpine-linux-cve-2026-35058/</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>CVE-2026-3238</t>
+        </is>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C909" t="inlineStr">
+        <is>
+          <t>vulnerability Alpine Linux: CVE-2026-3238: NULL Pointer Dereference Published: 2026-06-08 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D909" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E909" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alpine-linux-cve-2026-3238/</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>CVE-2026-47631</t>
+        </is>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C910" t="inlineStr">
+        <is>
+          <t>vulnerability Microsoft Exchange: CVE-2026-47631: Microsoft Exchange Server Spoofing Vulnerability Published: 2026-06-09 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D910" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E910" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/microsoft-exchange-cve-2026-47631/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rapid7_cves.xlsx
+++ b/rapid7_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E910"/>
+  <dimension ref="A1:E928"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24986,6 +24986,492 @@
         </is>
       </c>
     </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>CVE-2026-45591</t>
+        </is>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>2015-04-29</t>
+        </is>
+      </c>
+      <c r="C911" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D911" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E911" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>CVE-2026-48112</t>
+        </is>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>2015-04-29</t>
+        </is>
+      </c>
+      <c r="C912" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D912" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E912" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>CVE-2026-48111</t>
+        </is>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>2015-04-29</t>
+        </is>
+      </c>
+      <c r="C913" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D913" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E913" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>CVE-2026-48104</t>
+        </is>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>2015-04-29</t>
+        </is>
+      </c>
+      <c r="C914" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D914" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E914" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>CVE-2026-48103</t>
+        </is>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>2015-04-29</t>
+        </is>
+      </c>
+      <c r="C915" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D915" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E915" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>CVE-2026-48102</t>
+        </is>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>2015-04-29</t>
+        </is>
+      </c>
+      <c r="C916" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D916" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E916" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>CVE-2026-48101</t>
+        </is>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>2015-04-29</t>
+        </is>
+      </c>
+      <c r="C917" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D917" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E917" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>CVE-2026-48095</t>
+        </is>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>2015-04-29</t>
+        </is>
+      </c>
+      <c r="C918" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D918" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E918" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>CVE-2026-48092</t>
+        </is>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>2015-04-29</t>
+        </is>
+      </c>
+      <c r="C919" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D919" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E919" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>CVE-2026-48569</t>
+        </is>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>2015-04-29</t>
+        </is>
+      </c>
+      <c r="C920" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D920" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E920" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>CVE-2026-47287</t>
+        </is>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>2015-04-29</t>
+        </is>
+      </c>
+      <c r="C921" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D921" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E921" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>CVE-2026-47284</t>
+        </is>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>2015-04-29</t>
+        </is>
+      </c>
+      <c r="C922" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D922" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E922" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>CVE-2026-47281</t>
+        </is>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>2015-04-29</t>
+        </is>
+      </c>
+      <c r="C923" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D923" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E923" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>CVE-2026-40376</t>
+        </is>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>2015-04-29</t>
+        </is>
+      </c>
+      <c r="C924" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D924" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E924" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>CVE-2026-49975</t>
+        </is>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>2015-04-29</t>
+        </is>
+      </c>
+      <c r="C925" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D925" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E925" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>CVE-2026-40215</t>
+        </is>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>2015-04-29</t>
+        </is>
+      </c>
+      <c r="C926" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D926" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E926" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>CVE-2026-35058</t>
+        </is>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>2015-04-29</t>
+        </is>
+      </c>
+      <c r="C927" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D927" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E927" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>CVE-2026-3238</t>
+        </is>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>2015-04-29</t>
+        </is>
+      </c>
+      <c r="C928" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D928" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E928" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rapid7_cves.xlsx
+++ b/rapid7_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E928"/>
+  <dimension ref="A1:E968"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25472,6 +25472,1086 @@
         </is>
       </c>
     </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>CVE-2026-44673</t>
+        </is>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C929" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D929" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E929" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>CVE-2026-31786</t>
+        </is>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C930" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D930" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E930" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>CVE-2026-9538</t>
+        </is>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C931" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D931" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E931" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>CVE-2026-9256</t>
+        </is>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C932" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D932" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E932" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>CVE-2026-9150</t>
+        </is>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C933" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D933" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E933" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>CVE-2026-9149</t>
+        </is>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C934" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D934" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E934" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>CVE-2026-9064</t>
+        </is>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C935" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D935" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E935" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>CVE-2026-8975</t>
+        </is>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C936" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D936" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E936" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>CVE-2026-8974</t>
+        </is>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C937" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D937" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E937" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="inlineStr">
+        <is>
+          <t>CVE-2026-8970</t>
+        </is>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C938" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D938" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E938" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>CVE-2026-8968</t>
+        </is>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C939" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D939" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E939" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="inlineStr">
+        <is>
+          <t>CVE-2026-8962</t>
+        </is>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C940" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D940" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E940" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>CVE-2026-8961</t>
+        </is>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C941" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D941" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E941" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>CVE-2026-8958</t>
+        </is>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C942" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D942" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E942" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>CVE-2026-8957</t>
+        </is>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C943" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D943" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E943" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>CVE-2026-8956</t>
+        </is>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C944" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D944" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E944" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>CVE-2026-8955</t>
+        </is>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C945" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D945" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E945" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>CVE-2026-8954</t>
+        </is>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C946" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D946" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E946" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>CVE-2026-8953</t>
+        </is>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C947" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D947" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E947" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>CVE-2026-8950</t>
+        </is>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D948" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E948" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>CVE-2026-44673</t>
+        </is>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>vulnerability Red Hat: CVE-2026-44673: libyang: libyang: Denial of Service or arbitrary code execution via maliciously crafted LYB binary blob (Multip</t>
+        </is>
+      </c>
+      <c r="D949" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E949" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/redhat_linux-cve-2026-44673/</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>CVE-2026-31786</t>
+        </is>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C950" t="inlineStr">
+        <is>
+          <t>vulnerability Red Hat: CVE-2026-31786: kernel: Buffer overflow in drivers/xen/sys-hypervisor.c (Multiple Advisories) Published: 2026-04-30 | Severity:</t>
+        </is>
+      </c>
+      <c r="D950" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E950" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/redhat_linux-cve-2026-31786/</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>CVE-2026-9538</t>
+        </is>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C951" t="inlineStr">
+        <is>
+          <t>vulnerability Amazon Linux AMI 2: CVE-2026-9538: Security patch for perl-Archive-Tar (ALAS-2026-3347) Published: 2026-06-09 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D951" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E951" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/amazon-linux-ami-2-cve-2026-9538/</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>CVE-2026-9256</t>
+        </is>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C952" t="inlineStr">
+        <is>
+          <t>vulnerability Amazon Linux AMI 2: CVE-2026-9256: Security patch for nginx (ALAS2NGINX1-2026-013) Published: 2026-06-09 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D952" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E952" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/amazon-linux-ami-2-cve-2026-9256/</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>CVE-2026-9150</t>
+        </is>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C953" t="inlineStr">
+        <is>
+          <t>vulnerability Amazon Linux AMI 2: CVE-2026-9150: Security patch for libsolv (ALAS-2026-3338) Published: 2026-06-09 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D953" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E953" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/amazon-linux-ami-2-cve-2026-9150/</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>CVE-2026-9149</t>
+        </is>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C954" t="inlineStr">
+        <is>
+          <t>vulnerability Amazon Linux AMI 2: CVE-2026-9149: Security patch for libsolv (ALAS-2026-3338) Published: 2026-06-09 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D954" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E954" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/amazon-linux-ami-2-cve-2026-9149/</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>CVE-2026-9064</t>
+        </is>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C955" t="inlineStr">
+        <is>
+          <t>vulnerability Amazon Linux AMI 2: CVE-2026-9064: Security patch for 389-ds-base (ALAS-2026-3339) Published: 2026-06-09 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D955" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E955" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/amazon-linux-ami-2-cve-2026-9064/</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>CVE-2026-8975</t>
+        </is>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C956" t="inlineStr">
+        <is>
+          <t>vulnerability Amazon Linux AMI 2: CVE-2026-8975: Security patch for firefox, thunderbird (Multiple Advisories) Published: 2026-06-09 | Severity: 9 EXP</t>
+        </is>
+      </c>
+      <c r="D956" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E956" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/amazon-linux-ami-2-cve-2026-8975/</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>CVE-2026-8974</t>
+        </is>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C957" t="inlineStr">
+        <is>
+          <t>vulnerability Amazon Linux AMI 2: CVE-2026-8974: Security patch for firefox, thunderbird (Multiple Advisories) Published: 2026-06-09 | Severity: 9 EXP</t>
+        </is>
+      </c>
+      <c r="D957" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E957" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/amazon-linux-ami-2-cve-2026-8974/</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>CVE-2026-8970</t>
+        </is>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C958" t="inlineStr">
+        <is>
+          <t>vulnerability Amazon Linux AMI 2: CVE-2026-8970: Security patch for firefox, thunderbird (Multiple Advisories) Published: 2026-06-09 | Severity: 9 EXP</t>
+        </is>
+      </c>
+      <c r="D958" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E958" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/amazon-linux-ami-2-cve-2026-8970/</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>CVE-2026-8968</t>
+        </is>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C959" t="inlineStr">
+        <is>
+          <t>vulnerability Amazon Linux AMI 2: CVE-2026-8968: Security patch for firefox, thunderbird (Multiple Advisories) Published: 2026-06-09 | Severity: 8 EXP</t>
+        </is>
+      </c>
+      <c r="D959" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E959" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/amazon-linux-ami-2-cve-2026-8968/</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>CVE-2026-8962</t>
+        </is>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C960" t="inlineStr">
+        <is>
+          <t>vulnerability Amazon Linux AMI 2: CVE-2026-8962: Security patch for firefox, thunderbird (Multiple Advisories) Published: 2026-06-09 | Severity: 9 EXP</t>
+        </is>
+      </c>
+      <c r="D960" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E960" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/amazon-linux-ami-2-cve-2026-8962/</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>CVE-2026-8961</t>
+        </is>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C961" t="inlineStr">
+        <is>
+          <t>vulnerability Amazon Linux AMI 2: CVE-2026-8961: Security patch for firefox, thunderbird (Multiple Advisories) Published: 2026-06-09 | Severity: 7 EXP</t>
+        </is>
+      </c>
+      <c r="D961" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E961" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/amazon-linux-ami-2-cve-2026-8961/</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>CVE-2026-8958</t>
+        </is>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C962" t="inlineStr">
+        <is>
+          <t>vulnerability Amazon Linux AMI 2: CVE-2026-8958: Security patch for firefox, thunderbird (Multiple Advisories) Published: 2026-06-09 | Severity: 8 EXP</t>
+        </is>
+      </c>
+      <c r="D962" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E962" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/amazon-linux-ami-2-cve-2026-8958/</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>CVE-2026-8957</t>
+        </is>
+      </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C963" t="inlineStr">
+        <is>
+          <t>vulnerability Amazon Linux AMI 2: CVE-2026-8957: Security patch for firefox, thunderbird (Multiple Advisories) Published: 2026-06-09 | Severity: 9 EXP</t>
+        </is>
+      </c>
+      <c r="D963" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E963" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/amazon-linux-ami-2-cve-2026-8957/</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>CVE-2026-8956</t>
+        </is>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C964" t="inlineStr">
+        <is>
+          <t>vulnerability Amazon Linux AMI 2: CVE-2026-8956: Security patch for firefox, thunderbird (Multiple Advisories) Published: 2026-06-09 | Severity: 10 EX</t>
+        </is>
+      </c>
+      <c r="D964" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E964" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/amazon-linux-ami-2-cve-2026-8956/</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>CVE-2026-8955</t>
+        </is>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C965" t="inlineStr">
+        <is>
+          <t>vulnerability Amazon Linux AMI 2: CVE-2026-8955: Security patch for firefox, thunderbird (Multiple Advisories) Published: 2026-06-09 | Severity: 9 EXP</t>
+        </is>
+      </c>
+      <c r="D965" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E965" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/amazon-linux-ami-2-cve-2026-8955/</t>
+        </is>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>CVE-2026-8954</t>
+        </is>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C966" t="inlineStr">
+        <is>
+          <t>vulnerability Amazon Linux AMI 2: CVE-2026-8954: Security patch for firefox, thunderbird (Multiple Advisories) Published: 2026-06-09 | Severity: 8 EXP</t>
+        </is>
+      </c>
+      <c r="D966" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E966" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/amazon-linux-ami-2-cve-2026-8954/</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>CVE-2026-8953</t>
+        </is>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C967" t="inlineStr">
+        <is>
+          <t>vulnerability Amazon Linux AMI 2: CVE-2026-8953: Security patch for firefox, thunderbird (Multiple Advisories) Published: 2026-06-09 | Severity: 9 EXP</t>
+        </is>
+      </c>
+      <c r="D967" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E967" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/amazon-linux-ami-2-cve-2026-8953/</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>CVE-2026-8950</t>
+        </is>
+      </c>
+      <c r="B968" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C968" t="inlineStr">
+        <is>
+          <t>vulnerability Amazon Linux AMI 2: CVE-2026-8950: Security patch for firefox, thunderbird (Multiple Advisories) Published: 2026-06-09 | Severity: 9 EXP</t>
+        </is>
+      </c>
+      <c r="D968" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E968" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/amazon-linux-ami-2-cve-2026-8950/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rapid7_cves.xlsx
+++ b/rapid7_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E968"/>
+  <dimension ref="A1:E989"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26552,6 +26552,573 @@
         </is>
       </c>
     </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>CVE-2026-41679</t>
+        </is>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C969" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D969" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E969" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>CVE-2026-44673</t>
+        </is>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C970" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D970" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E970" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>CVE-2026-31786</t>
+        </is>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C971" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D971" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E971" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>CVE-2026-9538</t>
+        </is>
+      </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C972" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D972" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E972" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>CVE-2026-9256</t>
+        </is>
+      </c>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C973" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D973" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E973" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>CVE-2026-9150</t>
+        </is>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C974" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D974" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E974" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>CVE-2026-9149</t>
+        </is>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C975" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D975" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E975" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="inlineStr">
+        <is>
+          <t>CVE-2026-9064</t>
+        </is>
+      </c>
+      <c r="B976" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C976" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D976" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E976" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="inlineStr">
+        <is>
+          <t>CVE-2026-8975</t>
+        </is>
+      </c>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C977" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D977" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E977" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="inlineStr">
+        <is>
+          <t>CVE-2026-8974</t>
+        </is>
+      </c>
+      <c r="B978" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C978" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D978" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E978" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="inlineStr">
+        <is>
+          <t>CVE-2026-8970</t>
+        </is>
+      </c>
+      <c r="B979" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C979" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D979" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E979" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="inlineStr">
+        <is>
+          <t>CVE-2026-8968</t>
+        </is>
+      </c>
+      <c r="B980" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C980" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D980" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E980" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="inlineStr">
+        <is>
+          <t>CVE-2026-8962</t>
+        </is>
+      </c>
+      <c r="B981" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C981" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D981" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E981" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="inlineStr">
+        <is>
+          <t>CVE-2026-8961</t>
+        </is>
+      </c>
+      <c r="B982" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C982" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D982" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E982" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="inlineStr">
+        <is>
+          <t>CVE-2026-8958</t>
+        </is>
+      </c>
+      <c r="B983" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C983" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D983" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E983" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="inlineStr">
+        <is>
+          <t>CVE-2026-8957</t>
+        </is>
+      </c>
+      <c r="B984" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C984" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D984" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E984" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="inlineStr">
+        <is>
+          <t>CVE-2026-8956</t>
+        </is>
+      </c>
+      <c r="B985" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C985" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D985" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E985" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="inlineStr">
+        <is>
+          <t>CVE-2026-8955</t>
+        </is>
+      </c>
+      <c r="B986" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C986" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D986" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E986" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="inlineStr">
+        <is>
+          <t>CVE-2026-8954</t>
+        </is>
+      </c>
+      <c r="B987" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C987" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D987" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E987" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="inlineStr">
+        <is>
+          <t>CVE-2026-8953</t>
+        </is>
+      </c>
+      <c r="B988" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C988" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D988" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E988" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="inlineStr">
+        <is>
+          <t>CVE-2026-41679</t>
+        </is>
+      </c>
+      <c r="B989" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C989" t="inlineStr">
+        <is>
+          <t>module Paperclip AI RCE using a chain of six API calls (CVE-2026-41679). Published: 2026-04-10 | Severity: Unknown EXPLORE</t>
+        </is>
+      </c>
+      <c r="D989" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E989" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/modules/exploit/linux/http/paperclipai_unauth_rce_cve_2026_41679/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rapid7_cves.xlsx
+++ b/rapid7_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E989"/>
+  <dimension ref="A1:E1029"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27119,6 +27119,1086 @@
         </is>
       </c>
     </row>
+    <row r="990">
+      <c r="A990" t="inlineStr">
+        <is>
+          <t>CVE-2026-24051</t>
+        </is>
+      </c>
+      <c r="B990" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="C990" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D990" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E990" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>CVE-2026-20259</t>
+        </is>
+      </c>
+      <c r="B991" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="C991" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D991" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E991" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="inlineStr">
+        <is>
+          <t>CVE-2026-20258</t>
+        </is>
+      </c>
+      <c r="B992" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="C992" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D992" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E992" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="inlineStr">
+        <is>
+          <t>CVE-2026-20257</t>
+        </is>
+      </c>
+      <c r="B993" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="C993" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D993" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E993" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="inlineStr">
+        <is>
+          <t>CVE-2026-20256</t>
+        </is>
+      </c>
+      <c r="B994" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="C994" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D994" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E994" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="inlineStr">
+        <is>
+          <t>CVE-2026-20255</t>
+        </is>
+      </c>
+      <c r="B995" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="C995" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D995" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E995" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="inlineStr">
+        <is>
+          <t>CVE-2026-20254</t>
+        </is>
+      </c>
+      <c r="B996" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="C996" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D996" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E996" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="inlineStr">
+        <is>
+          <t>CVE-2026-20253</t>
+        </is>
+      </c>
+      <c r="B997" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="C997" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D997" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E997" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="inlineStr">
+        <is>
+          <t>CVE-2026-20252</t>
+        </is>
+      </c>
+      <c r="B998" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="C998" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D998" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E998" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="inlineStr">
+        <is>
+          <t>CVE-2026-20251</t>
+        </is>
+      </c>
+      <c r="B999" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="C999" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D999" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E999" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="inlineStr">
+        <is>
+          <t>CVE-2026-1229</t>
+        </is>
+      </c>
+      <c r="B1000" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="C1000" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D1000" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1000" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="inlineStr">
+        <is>
+          <t>CVE-2026-46273</t>
+        </is>
+      </c>
+      <c r="B1001" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="C1001" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D1001" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1001" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="inlineStr">
+        <is>
+          <t>CVE-2026-46243</t>
+        </is>
+      </c>
+      <c r="B1002" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="C1002" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D1002" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1002" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" t="inlineStr">
+        <is>
+          <t>CVE-2026-46051</t>
+        </is>
+      </c>
+      <c r="B1003" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="C1003" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D1003" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1003" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="inlineStr">
+        <is>
+          <t>CVE-2026-46049</t>
+        </is>
+      </c>
+      <c r="B1004" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="C1004" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D1004" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1004" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="inlineStr">
+        <is>
+          <t>CVE-2026-46047</t>
+        </is>
+      </c>
+      <c r="B1005" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="C1005" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D1005" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1005" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="inlineStr">
+        <is>
+          <t>CVE-2026-46046</t>
+        </is>
+      </c>
+      <c r="B1006" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="C1006" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D1006" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1006" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="inlineStr">
+        <is>
+          <t>CVE-2026-46044</t>
+        </is>
+      </c>
+      <c r="B1007" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="C1007" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D1007" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1007" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="inlineStr">
+        <is>
+          <t>CVE-2026-46040</t>
+        </is>
+      </c>
+      <c r="B1008" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="C1008" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D1008" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1008" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="inlineStr">
+        <is>
+          <t>CVE-2026-46033</t>
+        </is>
+      </c>
+      <c r="B1009" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="C1009" t="inlineStr">
+        <is>
+          <t>The Q1 2026 Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request Dem</t>
+        </is>
+      </c>
+      <c r="D1009" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1009" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="inlineStr">
+        <is>
+          <t>CVE-2026-24051</t>
+        </is>
+      </c>
+      <c r="B1010" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="C1010" t="inlineStr">
+        <is>
+          <t>vulnerability Splunk: CVE-2026-24051: Untrusted Search Path Published: 2026-02-02 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1010" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1010" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/splunk-cve-2026-24051/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="inlineStr">
+        <is>
+          <t>CVE-2026-20259</t>
+        </is>
+      </c>
+      <c r="B1011" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C1011" t="inlineStr">
+        <is>
+          <t>vulnerability Splunk: CVE-2026-20259: Improper Access Control in Splunk Enterprise Published: 2026-06-10 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1011" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1011" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/splunk-cve-2026-20259/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="inlineStr">
+        <is>
+          <t>CVE-2026-20258</t>
+        </is>
+      </c>
+      <c r="B1012" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C1012" t="inlineStr">
+        <is>
+          <t>vulnerability Splunk: CVE-2026-20258: Stored Cross-Site Scripting (XSS) through Classic Dashboard in Splunk Enterprise Published: 2026-06-10 | Severit</t>
+        </is>
+      </c>
+      <c r="D1012" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1012" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/splunk-cve-2026-20258/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="inlineStr">
+        <is>
+          <t>CVE-2026-20257</t>
+        </is>
+      </c>
+      <c r="B1013" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C1013" t="inlineStr">
+        <is>
+          <t>vulnerability Splunk: CVE-2026-20257: Improper Input Validation through Classic Dashboard CSS in Splunk Enterprise Published: 2026-06-10 | Severity: 6</t>
+        </is>
+      </c>
+      <c r="D1013" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1013" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/splunk-cve-2026-20257/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="inlineStr">
+        <is>
+          <t>CVE-2026-20256</t>
+        </is>
+      </c>
+      <c r="B1014" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C1014" t="inlineStr">
+        <is>
+          <t>vulnerability Splunk: CVE-2026-20256: Improper Input Validation through Protocol-Relative URL in Classic Dashboards in Splunk Enterprise Published: 20</t>
+        </is>
+      </c>
+      <c r="D1014" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1014" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/splunk-cve-2026-20256/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="inlineStr">
+        <is>
+          <t>CVE-2026-20255</t>
+        </is>
+      </c>
+      <c r="B1015" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C1015" t="inlineStr">
+        <is>
+          <t>vulnerability Splunk: CVE-2026-20255: Improper Input Validation through Classic Dashboards in Splunk Enterprise Published: 2026-06-10 | Severity: 6 EX</t>
+        </is>
+      </c>
+      <c r="D1015" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1015" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/splunk-cve-2026-20255/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="inlineStr">
+        <is>
+          <t>CVE-2026-20254</t>
+        </is>
+      </c>
+      <c r="B1016" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C1016" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vulnerability Splunk: CVE-2026-20254: Information Disclosure through External Content Restriction Bypass in Splunk Enterprise Published: 2026-06-10 | </t>
+        </is>
+      </c>
+      <c r="D1016" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1016" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/splunk-cve-2026-20254/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="inlineStr">
+        <is>
+          <t>CVE-2026-20253</t>
+        </is>
+      </c>
+      <c r="B1017" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C1017" t="inlineStr">
+        <is>
+          <t>vulnerability Splunk: CVE-2026-20253: Unauthenticated Arbitrary File Creation and Truncation in a PostgreSQL Sidecar Service Endpoint in Splunk Enterp</t>
+        </is>
+      </c>
+      <c r="D1017" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1017" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/splunk-cve-2026-20253/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="inlineStr">
+        <is>
+          <t>CVE-2026-20252</t>
+        </is>
+      </c>
+      <c r="B1018" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C1018" t="inlineStr">
+        <is>
+          <t>vulnerability Splunk: CVE-2026-20252: Server-Side Request Forgery (SSRF) through Dashboard Studio PDF Export in Splunk Enterprise Published: 2026-06-1</t>
+        </is>
+      </c>
+      <c r="D1018" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1018" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/splunk-cve-2026-20252/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="inlineStr">
+        <is>
+          <t>CVE-2026-20251</t>
+        </is>
+      </c>
+      <c r="B1019" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C1019" t="inlineStr">
+        <is>
+          <t>vulnerability Splunk: CVE-2026-20251: Remote Code Execution through Deserialization of Untrusted Data in Splunk Secure Gateway Published: 2026-06-10 |</t>
+        </is>
+      </c>
+      <c r="D1019" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1019" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/splunk-cve-2026-20251/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="inlineStr">
+        <is>
+          <t>CVE-2026-1229</t>
+        </is>
+      </c>
+      <c r="B1020" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="C1020" t="inlineStr">
+        <is>
+          <t>vulnerability Splunk: CVE-2026-1229: Incorrect Calculation Published: 2026-02-24 | Severity: 10 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1020" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1020" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/splunk-cve-2026-1229/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="inlineStr">
+        <is>
+          <t>CVE-2026-46273</t>
+        </is>
+      </c>
+      <c r="B1021" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C1021" t="inlineStr">
+        <is>
+          <t>vulnerability VMware Photon OS: CVE-2026-46273 Published: 2026-06-03 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1021" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1021" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/vmware-photon_os-cve-2026-46273/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="inlineStr">
+        <is>
+          <t>CVE-2026-46243</t>
+        </is>
+      </c>
+      <c r="B1022" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C1022" t="inlineStr">
+        <is>
+          <t>vulnerability VMware Photon OS: CVE-2026-46243 Published: 2026-06-01 | Severity: 6 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1022" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1022" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/vmware-photon_os-cve-2026-46243/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="inlineStr">
+        <is>
+          <t>CVE-2026-46051</t>
+        </is>
+      </c>
+      <c r="B1023" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C1023" t="inlineStr">
+        <is>
+          <t>vulnerability VMware Photon OS: CVE-2026-46051 Published: 2026-05-27 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1023" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1023" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/vmware-photon_os-cve-2026-46051/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="inlineStr">
+        <is>
+          <t>CVE-2026-46049</t>
+        </is>
+      </c>
+      <c r="B1024" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C1024" t="inlineStr">
+        <is>
+          <t>vulnerability VMware Photon OS: CVE-2026-46049 Published: 2026-05-27 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1024" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1024" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/vmware-photon_os-cve-2026-46049/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="inlineStr">
+        <is>
+          <t>CVE-2026-46047</t>
+        </is>
+      </c>
+      <c r="B1025" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C1025" t="inlineStr">
+        <is>
+          <t>vulnerability VMware Photon OS: CVE-2026-46047 Published: 2026-05-27 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1025" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1025" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/vmware-photon_os-cve-2026-46047/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="inlineStr">
+        <is>
+          <t>CVE-2026-46046</t>
+        </is>
+      </c>
+      <c r="B1026" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C1026" t="inlineStr">
+        <is>
+          <t>vulnerability VMware Photon OS: CVE-2026-46046 Published: 2026-05-27 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1026" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1026" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/vmware-photon_os-cve-2026-46046/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="inlineStr">
+        <is>
+          <t>CVE-2026-46044</t>
+        </is>
+      </c>
+      <c r="B1027" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C1027" t="inlineStr">
+        <is>
+          <t>vulnerability VMware Photon OS: CVE-2026-46044 Published: 2026-05-27 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1027" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1027" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/vmware-photon_os-cve-2026-46044/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="inlineStr">
+        <is>
+          <t>CVE-2026-46040</t>
+        </is>
+      </c>
+      <c r="B1028" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C1028" t="inlineStr">
+        <is>
+          <t>vulnerability VMware Photon OS: CVE-2026-46040 Published: 2026-05-27 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1028" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1028" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/vmware-photon_os-cve-2026-46040/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="inlineStr">
+        <is>
+          <t>CVE-2026-46033</t>
+        </is>
+      </c>
+      <c r="B1029" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C1029" t="inlineStr">
+        <is>
+          <t>vulnerability VMware Photon OS: CVE-2026-46033 Published: 2026-05-27 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1029" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1029" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/vmware-photon_os-cve-2026-46033/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rapid7_cves.xlsx
+++ b/rapid7_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1029"/>
+  <dimension ref="A1:E1069"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28199,6 +28199,1086 @@
         </is>
       </c>
     </row>
+    <row r="1030">
+      <c r="A1030" t="inlineStr">
+        <is>
+          <t>CVE-2026-46333</t>
+        </is>
+      </c>
+      <c r="B1030" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="C1030" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1030" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1030" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="inlineStr">
+        <is>
+          <t>CVE-2026-46300</t>
+        </is>
+      </c>
+      <c r="B1031" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="C1031" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1031" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1031" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="inlineStr">
+        <is>
+          <t>CVE-2026-46123</t>
+        </is>
+      </c>
+      <c r="B1032" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="C1032" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1032" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1032" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="inlineStr">
+        <is>
+          <t>CVE-2026-46024</t>
+        </is>
+      </c>
+      <c r="B1033" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="C1033" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1033" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1033" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="inlineStr">
+        <is>
+          <t>CVE-2026-43503</t>
+        </is>
+      </c>
+      <c r="B1034" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="C1034" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1034" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1034" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="inlineStr">
+        <is>
+          <t>CVE-2026-43067</t>
+        </is>
+      </c>
+      <c r="B1035" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="C1035" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1035" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1035" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="inlineStr">
+        <is>
+          <t>CVE-2026-42501</t>
+        </is>
+      </c>
+      <c r="B1036" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="C1036" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1036" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1036" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="inlineStr">
+        <is>
+          <t>CVE-2026-42499</t>
+        </is>
+      </c>
+      <c r="B1037" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="C1037" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1037" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1037" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="inlineStr">
+        <is>
+          <t>CVE-2026-39836</t>
+        </is>
+      </c>
+      <c r="B1038" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="C1038" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1038" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1038" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="inlineStr">
+        <is>
+          <t>CVE-2026-39826</t>
+        </is>
+      </c>
+      <c r="B1039" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="C1039" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1039" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1039" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="inlineStr">
+        <is>
+          <t>CVE-2026-39825</t>
+        </is>
+      </c>
+      <c r="B1040" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="C1040" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1040" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1040" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="inlineStr">
+        <is>
+          <t>CVE-2026-39823</t>
+        </is>
+      </c>
+      <c r="B1041" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="C1041" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1041" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1041" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" t="inlineStr">
+        <is>
+          <t>CVE-2026-39820</t>
+        </is>
+      </c>
+      <c r="B1042" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="C1042" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1042" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1042" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" t="inlineStr">
+        <is>
+          <t>CVE-2026-39819</t>
+        </is>
+      </c>
+      <c r="B1043" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="C1043" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1043" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1043" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" t="inlineStr">
+        <is>
+          <t>CVE-2026-39817</t>
+        </is>
+      </c>
+      <c r="B1044" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="C1044" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1044" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1044" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" t="inlineStr">
+        <is>
+          <t>CVE-2026-33814</t>
+        </is>
+      </c>
+      <c r="B1045" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="C1045" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1045" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1045" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="inlineStr">
+        <is>
+          <t>CVE-2026-33811</t>
+        </is>
+      </c>
+      <c r="B1046" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="C1046" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1046" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1046" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" t="inlineStr">
+        <is>
+          <t>CVE-2026-33810</t>
+        </is>
+      </c>
+      <c r="B1047" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="C1047" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1047" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1047" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" t="inlineStr">
+        <is>
+          <t>CVE-2026-32283</t>
+        </is>
+      </c>
+      <c r="B1048" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="C1048" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1048" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1048" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" t="inlineStr">
+        <is>
+          <t>CVE-2026-32282</t>
+        </is>
+      </c>
+      <c r="B1049" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="C1049" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1049" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1049" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="inlineStr">
+        <is>
+          <t>CVE-2026-46333</t>
+        </is>
+      </c>
+      <c r="B1050" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="C1050" t="inlineStr">
+        <is>
+          <t>vulnerability VMware Photon OS: CVE-2026-46333 Published: 2026-05-15 | Severity: 6 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1050" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1050" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/vmware-photon_os-cve-2026-46333/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" t="inlineStr">
+        <is>
+          <t>CVE-2026-46300</t>
+        </is>
+      </c>
+      <c r="B1051" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="C1051" t="inlineStr">
+        <is>
+          <t>vulnerability VMware Photon OS: CVE-2026-46300 Published: 2026-05-23 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1051" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1051" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/vmware-photon_os-cve-2026-46300/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" t="inlineStr">
+        <is>
+          <t>CVE-2026-46123</t>
+        </is>
+      </c>
+      <c r="B1052" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C1052" t="inlineStr">
+        <is>
+          <t>vulnerability VMware Photon OS: CVE-2026-46123 Published: 2026-05-28 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1052" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1052" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/vmware-photon_os-cve-2026-46123/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" t="inlineStr">
+        <is>
+          <t>CVE-2026-46024</t>
+        </is>
+      </c>
+      <c r="B1053" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C1053" t="inlineStr">
+        <is>
+          <t>vulnerability VMware Photon OS: CVE-2026-46024 Published: 2026-05-27 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1053" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1053" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/vmware-photon_os-cve-2026-46024/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" t="inlineStr">
+        <is>
+          <t>CVE-2026-43503</t>
+        </is>
+      </c>
+      <c r="B1054" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="C1054" t="inlineStr">
+        <is>
+          <t>vulnerability VMware Photon OS: CVE-2026-43503 Published: 2026-05-23 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1054" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1054" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/vmware-photon_os-cve-2026-43503/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" t="inlineStr">
+        <is>
+          <t>CVE-2026-43067</t>
+        </is>
+      </c>
+      <c r="B1055" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="C1055" t="inlineStr">
+        <is>
+          <t>vulnerability VMware Photon OS: CVE-2026-43067 Published: 2026-05-05 | Severity: 10 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1055" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1055" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/vmware-photon_os-cve-2026-43067/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" t="inlineStr">
+        <is>
+          <t>CVE-2026-42501</t>
+        </is>
+      </c>
+      <c r="B1056" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C1056" t="inlineStr">
+        <is>
+          <t>vulnerability VMware Photon OS: CVE-2026-42501 Published: 2026-05-07 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1056" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1056" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/vmware-photon_os-cve-2026-42501/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="inlineStr">
+        <is>
+          <t>CVE-2026-42499</t>
+        </is>
+      </c>
+      <c r="B1057" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C1057" t="inlineStr">
+        <is>
+          <t>vulnerability VMware Photon OS: CVE-2026-42499 Published: 2026-05-07 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1057" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1057" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/vmware-photon_os-cve-2026-42499/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" t="inlineStr">
+        <is>
+          <t>CVE-2026-39836</t>
+        </is>
+      </c>
+      <c r="B1058" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C1058" t="inlineStr">
+        <is>
+          <t>vulnerability VMware Photon OS: CVE-2026-39836 Published: 2026-05-07 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1058" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1058" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/vmware-photon_os-cve-2026-39836/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" t="inlineStr">
+        <is>
+          <t>CVE-2026-39826</t>
+        </is>
+      </c>
+      <c r="B1059" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C1059" t="inlineStr">
+        <is>
+          <t>vulnerability VMware Photon OS: CVE-2026-39826 Published: 2026-05-07 | Severity: 6 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1059" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1059" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/vmware-photon_os-cve-2026-39826/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" t="inlineStr">
+        <is>
+          <t>CVE-2026-39825</t>
+        </is>
+      </c>
+      <c r="B1060" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C1060" t="inlineStr">
+        <is>
+          <t>vulnerability VMware Photon OS: CVE-2026-39825 Published: 2026-05-07 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1060" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1060" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/vmware-photon_os-cve-2026-39825/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" t="inlineStr">
+        <is>
+          <t>CVE-2026-39823</t>
+        </is>
+      </c>
+      <c r="B1061" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C1061" t="inlineStr">
+        <is>
+          <t>vulnerability VMware Photon OS: CVE-2026-39823 Published: 2026-05-07 | Severity: 6 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1061" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1061" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/vmware-photon_os-cve-2026-39823/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" t="inlineStr">
+        <is>
+          <t>CVE-2026-39820</t>
+        </is>
+      </c>
+      <c r="B1062" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C1062" t="inlineStr">
+        <is>
+          <t>vulnerability VMware Photon OS: CVE-2026-39820 Published: 2026-05-07 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1062" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1062" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/vmware-photon_os-cve-2026-39820/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="inlineStr">
+        <is>
+          <t>CVE-2026-39819</t>
+        </is>
+      </c>
+      <c r="B1063" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C1063" t="inlineStr">
+        <is>
+          <t>vulnerability VMware Photon OS: CVE-2026-39819 Published: 2026-05-07 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1063" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1063" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/vmware-photon_os-cve-2026-39819/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="inlineStr">
+        <is>
+          <t>CVE-2026-39817</t>
+        </is>
+      </c>
+      <c r="B1064" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C1064" t="inlineStr">
+        <is>
+          <t>vulnerability VMware Photon OS: CVE-2026-39817 Published: 2026-05-07 | Severity: 4 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1064" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1064" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/vmware-photon_os-cve-2026-39817/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="inlineStr">
+        <is>
+          <t>CVE-2026-33814</t>
+        </is>
+      </c>
+      <c r="B1065" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C1065" t="inlineStr">
+        <is>
+          <t>vulnerability VMware Photon OS: CVE-2026-33814 Published: 2026-05-07 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1065" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1065" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/vmware-photon_os-cve-2026-33814/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" t="inlineStr">
+        <is>
+          <t>CVE-2026-33811</t>
+        </is>
+      </c>
+      <c r="B1066" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C1066" t="inlineStr">
+        <is>
+          <t>vulnerability VMware Photon OS: CVE-2026-33811 Published: 2026-05-07 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1066" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1066" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/vmware-photon_os-cve-2026-33811/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="inlineStr">
+        <is>
+          <t>CVE-2026-33810</t>
+        </is>
+      </c>
+      <c r="B1067" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="C1067" t="inlineStr">
+        <is>
+          <t>vulnerability VMware Photon OS: CVE-2026-33810 Published: 2026-04-08 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1067" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1067" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/vmware-photon_os-cve-2026-33810/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" t="inlineStr">
+        <is>
+          <t>CVE-2026-32283</t>
+        </is>
+      </c>
+      <c r="B1068" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="C1068" t="inlineStr">
+        <is>
+          <t>vulnerability VMware Photon OS: CVE-2026-32283 Published: 2026-04-08 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1068" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1068" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/vmware-photon_os-cve-2026-32283/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="inlineStr">
+        <is>
+          <t>CVE-2026-32282</t>
+        </is>
+      </c>
+      <c r="B1069" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="C1069" t="inlineStr">
+        <is>
+          <t>vulnerability VMware Photon OS: CVE-2026-32282 Published: 2026-04-08 | Severity: 6 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1069" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1069" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/vmware-photon_os-cve-2026-32282/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rapid7_cves.xlsx
+++ b/rapid7_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1069"/>
+  <dimension ref="A1:E1109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29279,6 +29279,1086 @@
         </is>
       </c>
     </row>
+    <row r="1070">
+      <c r="A1070" t="inlineStr">
+        <is>
+          <t>CVE-2025-61985</t>
+        </is>
+      </c>
+      <c r="B1070" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="C1070" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1070" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E1070" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="inlineStr">
+        <is>
+          <t>CVE-2025-61984</t>
+        </is>
+      </c>
+      <c r="B1071" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="C1071" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1071" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E1071" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="inlineStr">
+        <is>
+          <t>CVE-2025-6018</t>
+        </is>
+      </c>
+      <c r="B1072" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="C1072" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1072" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E1072" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="inlineStr">
+        <is>
+          <t>CVE-2025-54509</t>
+        </is>
+      </c>
+      <c r="B1073" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="C1073" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1073" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E1073" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="inlineStr">
+        <is>
+          <t>CVE-2026-42937</t>
+        </is>
+      </c>
+      <c r="B1074" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="C1074" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1074" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E1074" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="inlineStr">
+        <is>
+          <t>CVE-2026-42920</t>
+        </is>
+      </c>
+      <c r="B1075" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="C1075" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1075" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E1075" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="inlineStr">
+        <is>
+          <t>CVE-2026-42919</t>
+        </is>
+      </c>
+      <c r="B1076" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="C1076" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1076" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E1076" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="inlineStr">
+        <is>
+          <t>CVE-2026-42409</t>
+        </is>
+      </c>
+      <c r="B1077" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="C1077" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1077" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E1077" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="inlineStr">
+        <is>
+          <t>CVE-2026-42406</t>
+        </is>
+      </c>
+      <c r="B1078" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="C1078" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1078" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E1078" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="inlineStr">
+        <is>
+          <t>CVE-2026-42063</t>
+        </is>
+      </c>
+      <c r="B1079" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="C1079" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1079" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E1079" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="inlineStr">
+        <is>
+          <t>CVE-2026-42058</t>
+        </is>
+      </c>
+      <c r="B1080" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="C1080" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1080" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E1080" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t>CVE-2026-41959</t>
+        </is>
+      </c>
+      <c r="B1081" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="C1081" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1081" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E1081" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="inlineStr">
+        <is>
+          <t>CVE-2026-41957</t>
+        </is>
+      </c>
+      <c r="B1082" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="C1082" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1082" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E1082" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="inlineStr">
+        <is>
+          <t>CVE-2026-41956</t>
+        </is>
+      </c>
+      <c r="B1083" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="C1083" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1083" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E1083" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="inlineStr">
+        <is>
+          <t>CVE-2026-41953</t>
+        </is>
+      </c>
+      <c r="B1084" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="C1084" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1084" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E1084" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t>CVE-2026-41227</t>
+        </is>
+      </c>
+      <c r="B1085" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="C1085" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1085" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E1085" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="inlineStr">
+        <is>
+          <t>CVE-2026-41225</t>
+        </is>
+      </c>
+      <c r="B1086" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="C1086" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1086" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E1086" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>CVE-2026-41219</t>
+        </is>
+      </c>
+      <c r="B1087" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="C1087" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1087" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E1087" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t>CVE-2026-41218</t>
+        </is>
+      </c>
+      <c r="B1088" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="C1088" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1088" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E1088" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>CVE-2026-41217</t>
+        </is>
+      </c>
+      <c r="B1089" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="C1089" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1089" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E1089" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>CVE-2025-61985</t>
+        </is>
+      </c>
+      <c r="B1090" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="C1090" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vulnerability Dell PowerStoreOS: CVE-2025-61985: DSA-2026-115: Dell PowerStore T Security Update for Multiple Vulnerabilities Published: 2026-02-24 | </t>
+        </is>
+      </c>
+      <c r="D1090" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E1090" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/dell-powerstore-dsa2026115-cve-2025-61985/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>CVE-2025-61984</t>
+        </is>
+      </c>
+      <c r="B1091" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="C1091" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vulnerability Dell PowerStoreOS: CVE-2025-61984: DSA-2026-115: Dell PowerStore T Security Update for Multiple Vulnerabilities Published: 2026-02-24 | </t>
+        </is>
+      </c>
+      <c r="D1091" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E1091" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/dell-powerstore-dsa2026115-cve-2025-61984/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>CVE-2025-6018</t>
+        </is>
+      </c>
+      <c r="B1092" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="C1092" t="inlineStr">
+        <is>
+          <t>vulnerability Dell PowerStoreOS: CVE-2025-6018: DSA-2026-115: Dell PowerStore T Security Update for Multiple Vulnerabilities Published: 2026-02-24 | S</t>
+        </is>
+      </c>
+      <c r="D1092" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1092" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/dell-powerstore-dsa2026115-cve-2025-6018/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr">
+        <is>
+          <t>CVE-2025-54509</t>
+        </is>
+      </c>
+      <c r="B1093" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C1093" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vulnerability Dell PowerEdge: CVE-2025-54509: DSA-2026-042: Security Update for Dell AMD-based PowerEdge Server Vulnerability Published: 2026-06-10 | </t>
+        </is>
+      </c>
+      <c r="D1093" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1093" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/dell-poweredge-dsa2026042-cve-2025-54509/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="inlineStr">
+        <is>
+          <t>CVE-2026-42937</t>
+        </is>
+      </c>
+      <c r="B1094" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C1094" t="inlineStr">
+        <is>
+          <t>vulnerability F5: CVE-2026-42937: K000161018: iControl REST and tmsh vulnerability CVE-2026-42937 Published: 2026-05-13 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1094" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1094" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/f5-big-ip-cve-2026-42937/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="inlineStr">
+        <is>
+          <t>CVE-2026-42920</t>
+        </is>
+      </c>
+      <c r="B1095" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C1095" t="inlineStr">
+        <is>
+          <t>vulnerability F5: CVE-2026-42920: K000160901: BIG-IP DTLS vulnerability CVE-2026-42920 Published: 2026-05-13 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1095" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1095" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/f5-big-ip-cve-2026-42920/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="inlineStr">
+        <is>
+          <t>CVE-2026-42919</t>
+        </is>
+      </c>
+      <c r="B1096" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C1096" t="inlineStr">
+        <is>
+          <t>vulnerability F5: CVE-2026-42919: K000158971: BIG-IP Appliance mode vulnerability CVE-2026-42919 Published: 2026-05-13 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1096" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1096" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/f5-big-ip-cve-2026-42919/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="inlineStr">
+        <is>
+          <t>CVE-2026-42409</t>
+        </is>
+      </c>
+      <c r="B1097" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C1097" t="inlineStr">
+        <is>
+          <t>vulnerability F5: CVE-2026-42409: K000159034: BIG-IP HTTP/2 vulnerability CVE-2026-42409 Published: 2026-05-13 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1097" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1097" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/f5-big-ip-cve-2026-42409/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="inlineStr">
+        <is>
+          <t>CVE-2026-42406</t>
+        </is>
+      </c>
+      <c r="B1098" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C1098" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vulnerability F5: CVE-2026-42406: K000160971: BIG-IP and BIG-IQ privilege escalation vulnerability CVE-2026-42406 Published: 2026-05-13 | Severity: 8 </t>
+        </is>
+      </c>
+      <c r="D1098" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1098" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/f5-big-ip-cve-2026-42406/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="inlineStr">
+        <is>
+          <t>CVE-2026-42063</t>
+        </is>
+      </c>
+      <c r="B1099" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C1099" t="inlineStr">
+        <is>
+          <t>vulnerability F5: CVE-2026-42063: K000160973: iControl SOAP vulnerability CVE-2026-42063 Published: 2026-05-13 | Severity: 6 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1099" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1099" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/f5-big-ip-cve-2026-42063/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="inlineStr">
+        <is>
+          <t>CVE-2026-42058</t>
+        </is>
+      </c>
+      <c r="B1100" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C1100" t="inlineStr">
+        <is>
+          <t>vulnerability F5: CVE-2026-42058: K000160903: iControl REST vulnerability CVE-2026-42058 Published: 2026-05-13 | Severity: 4 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1100" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1100" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/f5-big-ip-cve-2026-42058/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="inlineStr">
+        <is>
+          <t>CVE-2026-41959</t>
+        </is>
+      </c>
+      <c r="B1101" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C1101" t="inlineStr">
+        <is>
+          <t>vulnerability F5: CVE-2026-41959: K000161022: iControl REST and tmsh vulnerability CVE-2026-41959 Published: 2026-05-13 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1101" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1101" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/f5-big-ip-cve-2026-41959/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="inlineStr">
+        <is>
+          <t>CVE-2026-41957</t>
+        </is>
+      </c>
+      <c r="B1102" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C1102" t="inlineStr">
+        <is>
+          <t>vulnerability F5: CVE-2026-41957: K000156761: BIG-IP and BIG-IQ Configuration utility vulnerability CVE-2026-41957 Published: 2026-05-13 | Severity: 9</t>
+        </is>
+      </c>
+      <c r="D1102" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1102" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/f5-big-ip-cve-2026-41957/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="inlineStr">
+        <is>
+          <t>CVE-2026-41956</t>
+        </is>
+      </c>
+      <c r="B1103" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C1103" t="inlineStr">
+        <is>
+          <t>vulnerability F5: CVE-2026-41956: K000158038: BIG-IP TMM vulnerability CVE-2026-41956 Published: 2026-05-13 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1103" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1103" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/f5-big-ip-cve-2026-41956/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="inlineStr">
+        <is>
+          <t>CVE-2026-41953</t>
+        </is>
+      </c>
+      <c r="B1104" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C1104" t="inlineStr">
+        <is>
+          <t>vulnerability F5: CVE-2026-41953: K000160975: BIG-IP privilege escalation vulnerability CVE-2026-41953 Published: 2026-05-13 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1104" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1104" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/f5-big-ip-cve-2026-41953/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="inlineStr">
+        <is>
+          <t>CVE-2026-41227</t>
+        </is>
+      </c>
+      <c r="B1105" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C1105" t="inlineStr">
+        <is>
+          <t>vulnerability F5: CVE-2026-41227: K000158979: BIG-IP HTTP/2 Layer 7 DoS Protection vulnerability CVE-2026-41227 Published: 2026-05-13 | Severity: 8 EX</t>
+        </is>
+      </c>
+      <c r="D1105" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1105" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/f5-big-ip-cve-2026-41227/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="inlineStr">
+        <is>
+          <t>CVE-2026-41225</t>
+        </is>
+      </c>
+      <c r="B1106" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C1106" t="inlineStr">
+        <is>
+          <t>vulnerability F5: CVE-2026-41225: K000160916: iControl REST vulnerability CVE-2026-41225 Published: 2026-05-13 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1106" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1106" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/f5-big-ip-cve-2026-41225/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="inlineStr">
+        <is>
+          <t>CVE-2026-41219</t>
+        </is>
+      </c>
+      <c r="B1107" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C1107" t="inlineStr">
+        <is>
+          <t>vulnerability F5: CVE-2026-41219: K000157895: BIG-IP qkview vulnerability CVE-2026-41219 Published: 2026-05-13 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1107" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1107" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/f5-big-ip-cve-2026-41219/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="inlineStr">
+        <is>
+          <t>CVE-2026-41218</t>
+        </is>
+      </c>
+      <c r="B1108" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C1108" t="inlineStr">
+        <is>
+          <t>vulnerability F5: CVE-2026-41218: K000160875: BIG-IP PEM iRules vulnerability CVE-2026-41218 Published: 2026-05-13 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1108" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1108" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/f5-big-ip-cve-2026-41218/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" t="inlineStr">
+        <is>
+          <t>CVE-2026-41217</t>
+        </is>
+      </c>
+      <c r="B1109" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C1109" t="inlineStr">
+        <is>
+          <t>vulnerability F5: CVE-2026-41217: K000161107: BIG-IP tmsh vulnerability CVE-2026-41217 Published: 2026-05-13 | Severity: 6 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1109" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1109" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/f5-big-ip-cve-2026-41217/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rapid7_cves.xlsx
+++ b/rapid7_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1109"/>
+  <dimension ref="A1:E1148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30359,6 +30359,1059 @@
         </is>
       </c>
     </row>
+    <row r="1110">
+      <c r="A1110" t="inlineStr">
+        <is>
+          <t>CVE-2026-10735</t>
+        </is>
+      </c>
+      <c r="B1110" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1110" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1110" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1110" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" t="inlineStr">
+        <is>
+          <t>CVE-2026-8494</t>
+        </is>
+      </c>
+      <c r="B1111" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1111" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1111" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1111" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" t="inlineStr">
+        <is>
+          <t>CVE-2026-8607</t>
+        </is>
+      </c>
+      <c r="B1112" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1112" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1112" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1112" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" t="inlineStr">
+        <is>
+          <t>CVE-2026-12360</t>
+        </is>
+      </c>
+      <c r="B1113" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1113" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1113" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1113" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="inlineStr">
+        <is>
+          <t>CVE-2026-12115</t>
+        </is>
+      </c>
+      <c r="B1114" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1114" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1114" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1114" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="inlineStr">
+        <is>
+          <t>CVE-2026-12165</t>
+        </is>
+      </c>
+      <c r="B1115" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1115" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1115" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1115" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="inlineStr">
+        <is>
+          <t>CVE-2026-11701</t>
+        </is>
+      </c>
+      <c r="B1116" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1116" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1116" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1116" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="inlineStr">
+        <is>
+          <t>CVE-2026-11700</t>
+        </is>
+      </c>
+      <c r="B1117" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1117" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1117" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1117" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="inlineStr">
+        <is>
+          <t>CVE-2026-11699</t>
+        </is>
+      </c>
+      <c r="B1118" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1118" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1118" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1118" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="inlineStr">
+        <is>
+          <t>CVE-2026-11698</t>
+        </is>
+      </c>
+      <c r="B1119" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1119" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1119" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1119" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" t="inlineStr">
+        <is>
+          <t>CVE-2026-11697</t>
+        </is>
+      </c>
+      <c r="B1120" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1120" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1120" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1120" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="inlineStr">
+        <is>
+          <t>CVE-2026-11696</t>
+        </is>
+      </c>
+      <c r="B1121" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1121" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1121" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1121" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="inlineStr">
+        <is>
+          <t>CVE-2026-11695</t>
+        </is>
+      </c>
+      <c r="B1122" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1122" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1122" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1122" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="inlineStr">
+        <is>
+          <t>CVE-2026-11694</t>
+        </is>
+      </c>
+      <c r="B1123" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1123" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1123" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1123" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="inlineStr">
+        <is>
+          <t>CVE-2026-11693</t>
+        </is>
+      </c>
+      <c r="B1124" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1124" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1124" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1124" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="inlineStr">
+        <is>
+          <t>CVE-2026-11692</t>
+        </is>
+      </c>
+      <c r="B1125" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1125" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1125" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1125" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="inlineStr">
+        <is>
+          <t>CVE-2026-11691</t>
+        </is>
+      </c>
+      <c r="B1126" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1126" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1126" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1126" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="inlineStr">
+        <is>
+          <t>CVE-2026-11690</t>
+        </is>
+      </c>
+      <c r="B1127" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1127" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1127" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1127" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="inlineStr">
+        <is>
+          <t>CVE-2026-11689</t>
+        </is>
+      </c>
+      <c r="B1128" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1128" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1128" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1128" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" t="inlineStr">
+        <is>
+          <t>CVE-2026-10735</t>
+        </is>
+      </c>
+      <c r="B1129" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1129" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: woo-product-slider-pro: CVE-2026-10735: Embedded Malicious Code Published: 2026-06-04 | Severity: 10 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1129" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1129" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/woo-product-slider-pro-plugin-cve-2026-10735/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" t="inlineStr">
+        <is>
+          <t>CVE-2026-10735</t>
+        </is>
+      </c>
+      <c r="B1130" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1130" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: smart-show-post-pro: CVE-2026-10735: Embedded Malicious Code Published: 2026-06-04 | Severity: 10 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1130" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1130" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/smart-show-post-pro-plugin-cve-2026-10735/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="inlineStr">
+        <is>
+          <t>CVE-2026-8494</t>
+        </is>
+      </c>
+      <c r="B1131" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C1131" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: permalink-manager: CVE-2026-8494: Improper Neutralization of Input During Web Page Generation ('Cross-site Scripting')</t>
+        </is>
+      </c>
+      <c r="D1131" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1131" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/permalink-manager-plugin-cve-2026-8494/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="inlineStr">
+        <is>
+          <t>CVE-2026-8607</t>
+        </is>
+      </c>
+      <c r="B1132" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C1132" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: mycred: CVE-2026-8607: Improper Neutralization of Input During Web Page Generation ('Cross-site Scripting') Published:</t>
+        </is>
+      </c>
+      <c r="D1132" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1132" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/mycred-plugin-cve-2026-8607/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="inlineStr">
+        <is>
+          <t>CVE-2026-12360</t>
+        </is>
+      </c>
+      <c r="B1133" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C1133" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: jet-engine: CVE-2026-12360: Improper Neutralization of Special Elements used in an SQL Command ('SQL Injection') Publi</t>
+        </is>
+      </c>
+      <c r="D1133" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1133" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/jet-engine-plugin-cve-2026-12360/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" t="inlineStr">
+        <is>
+          <t>CVE-2026-12115</t>
+        </is>
+      </c>
+      <c r="B1134" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C1134" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: counter-box: CVE-2026-12115: Deserialization of Untrusted Data Published: 2026-06-16 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1134" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1134" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/counter-box-plugin-cve-2026-12115/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" t="inlineStr">
+        <is>
+          <t>CVE-2026-12165</t>
+        </is>
+      </c>
+      <c r="B1135" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C1135" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: contest-gallery: CVE-2026-12165: Improper Privilege Management Published: 2026-06-16 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1135" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1135" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/contest-gallery-plugin-cve-2026-12165/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="inlineStr">
+        <is>
+          <t>CVE-2026-11701</t>
+        </is>
+      </c>
+      <c r="B1136" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="C1136" t="inlineStr">
+        <is>
+          <t>vulnerability Microsoft Edge (Chromium-based): CVE-2026-11701: Use after free in Tracing Published: 2026-06-15 | Severity: 6 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1136" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1136" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/microsoft-edge-cve-2026-11701/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" t="inlineStr">
+        <is>
+          <t>CVE-2026-11700</t>
+        </is>
+      </c>
+      <c r="B1137" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="C1137" t="inlineStr">
+        <is>
+          <t>vulnerability Microsoft Edge (Chromium-based): CVE-2026-11700: Use after free in Bluetooth Published: 2026-06-15 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1137" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1137" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/microsoft-edge-cve-2026-11700/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" t="inlineStr">
+        <is>
+          <t>CVE-2026-11699</t>
+        </is>
+      </c>
+      <c r="B1138" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="C1138" t="inlineStr">
+        <is>
+          <t>vulnerability Microsoft Edge (Chromium-based): CVE-2026-11699: Use after free in Bluetooth Published: 2026-06-15 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1138" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1138" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/microsoft-edge-cve-2026-11699/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" t="inlineStr">
+        <is>
+          <t>CVE-2026-11698</t>
+        </is>
+      </c>
+      <c r="B1139" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="C1139" t="inlineStr">
+        <is>
+          <t>vulnerability Microsoft Edge (Chromium-based): CVE-2026-11698: Insufficient validation of untrusted input in UI Published: 2026-06-15 | Severity: 9 EX</t>
+        </is>
+      </c>
+      <c r="D1139" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1139" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/microsoft-edge-cve-2026-11698/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" t="inlineStr">
+        <is>
+          <t>CVE-2026-11697</t>
+        </is>
+      </c>
+      <c r="B1140" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="C1140" t="inlineStr">
+        <is>
+          <t>vulnerability Microsoft Edge (Chromium-based): CVE-2026-11697: Uninitialized Use in Video Published: 2026-06-15 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1140" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1140" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/microsoft-edge-cve-2026-11697/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" t="inlineStr">
+        <is>
+          <t>CVE-2026-11696</t>
+        </is>
+      </c>
+      <c r="B1141" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="C1141" t="inlineStr">
+        <is>
+          <t>vulnerability Microsoft Edge (Chromium-based): CVE-2026-11696: Inappropriate implementation in Passwords Published: 2026-06-15 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1141" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1141" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/microsoft-edge-cve-2026-11696/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="inlineStr">
+        <is>
+          <t>CVE-2026-11695</t>
+        </is>
+      </c>
+      <c r="B1142" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="C1142" t="inlineStr">
+        <is>
+          <t>vulnerability Microsoft Edge (Chromium-based): CVE-2026-11695: Use after free in ServiceWorker Published: 2026-06-15 | Severity: 4 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1142" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1142" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/microsoft-edge-cve-2026-11695/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" t="inlineStr">
+        <is>
+          <t>CVE-2026-11694</t>
+        </is>
+      </c>
+      <c r="B1143" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="C1143" t="inlineStr">
+        <is>
+          <t>vulnerability Microsoft Edge (Chromium-based): CVE-2026-11694: Inappropriate implementation in Plugins Published: 2026-06-15 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1143" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1143" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/microsoft-edge-cve-2026-11694/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" t="inlineStr">
+        <is>
+          <t>CVE-2026-11693</t>
+        </is>
+      </c>
+      <c r="B1144" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="C1144" t="inlineStr">
+        <is>
+          <t>vulnerability Microsoft Edge (Chromium-based): CVE-2026-11693: Use after free in Read Anything Published: 2026-06-15 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1144" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1144" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/microsoft-edge-cve-2026-11693/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" t="inlineStr">
+        <is>
+          <t>CVE-2026-11692</t>
+        </is>
+      </c>
+      <c r="B1145" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="C1145" t="inlineStr">
+        <is>
+          <t>vulnerability Microsoft Edge (Chromium-based): CVE-2026-11692: Insufficient validation of untrusted input in New Tab Page Published: 2026-06-15 | Seve</t>
+        </is>
+      </c>
+      <c r="D1145" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1145" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/microsoft-edge-cve-2026-11692/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" t="inlineStr">
+        <is>
+          <t>CVE-2026-11691</t>
+        </is>
+      </c>
+      <c r="B1146" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="C1146" t="inlineStr">
+        <is>
+          <t>vulnerability Microsoft Edge (Chromium-based): CVE-2026-11691: Out of bounds read and write in Media Published: 2026-06-15 | Severity: 3 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1146" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E1146" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/microsoft-edge-cve-2026-11691/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" t="inlineStr">
+        <is>
+          <t>CVE-2026-11690</t>
+        </is>
+      </c>
+      <c r="B1147" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="C1147" t="inlineStr">
+        <is>
+          <t>vulnerability Microsoft Edge (Chromium-based): CVE-2026-11690: Insufficient validation of untrusted input in Passwords Published: 2026-06-15 | Severit</t>
+        </is>
+      </c>
+      <c r="D1147" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1147" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/microsoft-edge-cve-2026-11690/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="inlineStr">
+        <is>
+          <t>CVE-2026-11689</t>
+        </is>
+      </c>
+      <c r="B1148" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="C1148" t="inlineStr">
+        <is>
+          <t>vulnerability Microsoft Edge (Chromium-based): CVE-2026-11689: Object lifecycle issue in SVG Published: 2026-06-15 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1148" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1148" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/microsoft-edge-cve-2026-11689/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rapid7_cves.xlsx
+++ b/rapid7_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1148"/>
+  <dimension ref="A1:E1188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31412,6 +31412,1086 @@
         </is>
       </c>
     </row>
+    <row r="1149">
+      <c r="A1149" t="inlineStr">
+        <is>
+          <t>CVE-2026-46328</t>
+        </is>
+      </c>
+      <c r="B1149" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C1149" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1149" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1149" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="inlineStr">
+        <is>
+          <t>CVE-2026-46259</t>
+        </is>
+      </c>
+      <c r="B1150" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C1150" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1150" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1150" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="inlineStr">
+        <is>
+          <t>CVE-2026-46253</t>
+        </is>
+      </c>
+      <c r="B1151" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C1151" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1151" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1151" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="inlineStr">
+        <is>
+          <t>CVE-2026-46174</t>
+        </is>
+      </c>
+      <c r="B1152" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C1152" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1152" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1152" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" t="inlineStr">
+        <is>
+          <t>CVE-2026-46028</t>
+        </is>
+      </c>
+      <c r="B1153" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C1153" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1153" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1153" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="inlineStr">
+        <is>
+          <t>CVE-2026-45985</t>
+        </is>
+      </c>
+      <c r="B1154" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C1154" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1154" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1154" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" t="inlineStr">
+        <is>
+          <t>CVE-2026-45984</t>
+        </is>
+      </c>
+      <c r="B1155" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C1155" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1155" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1155" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" t="inlineStr">
+        <is>
+          <t>CVE-2026-45983</t>
+        </is>
+      </c>
+      <c r="B1156" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C1156" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1156" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1156" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" t="inlineStr">
+        <is>
+          <t>CVE-2026-45974</t>
+        </is>
+      </c>
+      <c r="B1157" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C1157" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1157" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1157" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="inlineStr">
+        <is>
+          <t>CVE-2026-45970</t>
+        </is>
+      </c>
+      <c r="B1158" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C1158" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1158" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1158" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" t="inlineStr">
+        <is>
+          <t>CVE-2026-45968</t>
+        </is>
+      </c>
+      <c r="B1159" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C1159" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1159" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1159" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" t="inlineStr">
+        <is>
+          <t>CVE-2026-45964</t>
+        </is>
+      </c>
+      <c r="B1160" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C1160" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1160" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1160" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" t="inlineStr">
+        <is>
+          <t>CVE-2026-45960</t>
+        </is>
+      </c>
+      <c r="B1161" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C1161" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1161" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1161" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" t="inlineStr">
+        <is>
+          <t>CVE-2026-45948</t>
+        </is>
+      </c>
+      <c r="B1162" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C1162" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1162" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1162" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" t="inlineStr">
+        <is>
+          <t>CVE-2026-45935</t>
+        </is>
+      </c>
+      <c r="B1163" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C1163" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1163" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1163" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" t="inlineStr">
+        <is>
+          <t>CVE-2026-45923</t>
+        </is>
+      </c>
+      <c r="B1164" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C1164" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1164" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1164" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" t="inlineStr">
+        <is>
+          <t>CVE-2026-45920</t>
+        </is>
+      </c>
+      <c r="B1165" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C1165" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1165" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1165" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" t="inlineStr">
+        <is>
+          <t>CVE-2026-45919</t>
+        </is>
+      </c>
+      <c r="B1166" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C1166" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1166" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1166" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" t="inlineStr">
+        <is>
+          <t>CVE-2026-45915</t>
+        </is>
+      </c>
+      <c r="B1167" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C1167" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1167" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1167" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" t="inlineStr">
+        <is>
+          <t>CVE-2026-45912</t>
+        </is>
+      </c>
+      <c r="B1168" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C1168" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1168" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1168" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" t="inlineStr">
+        <is>
+          <t>CVE-2026-46328</t>
+        </is>
+      </c>
+      <c r="B1169" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C1169" t="inlineStr">
+        <is>
+          <t>vulnerability Amazon Linux AMI 2: CVE-2026-46328: Security patch for kernel (Multiple Advisories) Published: 2026-06-17 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1169" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1169" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/amazon-linux-ami-2-cve-2026-46328/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" t="inlineStr">
+        <is>
+          <t>CVE-2026-46259</t>
+        </is>
+      </c>
+      <c r="B1170" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C1170" t="inlineStr">
+        <is>
+          <t>vulnerability Amazon Linux AMI 2: CVE-2026-46259: Security patch for kernel (Multiple Advisories) Published: 2026-06-17 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1170" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1170" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/amazon-linux-ami-2-cve-2026-46259/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" t="inlineStr">
+        <is>
+          <t>CVE-2026-46253</t>
+        </is>
+      </c>
+      <c r="B1171" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C1171" t="inlineStr">
+        <is>
+          <t>vulnerability Amazon Linux AMI 2: CVE-2026-46253: Security patch for kernel (Multiple Advisories) Published: 2026-06-17 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1171" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1171" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/amazon-linux-ami-2-cve-2026-46253/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" t="inlineStr">
+        <is>
+          <t>CVE-2026-46174</t>
+        </is>
+      </c>
+      <c r="B1172" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C1172" t="inlineStr">
+        <is>
+          <t>vulnerability Amazon Linux AMI 2: CVE-2026-46174: Security patch for kernel (ALAS2KERNEL-5.10-2026-121) Published: 2026-06-17 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1172" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1172" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/amazon-linux-ami-2-cve-2026-46174/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" t="inlineStr">
+        <is>
+          <t>CVE-2026-46028</t>
+        </is>
+      </c>
+      <c r="B1173" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C1173" t="inlineStr">
+        <is>
+          <t>vulnerability Amazon Linux AMI 2: CVE-2026-46028: Security patch for kernel (Multiple Advisories) Published: 2026-06-17 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1173" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1173" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/amazon-linux-ami-2-cve-2026-46028/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" t="inlineStr">
+        <is>
+          <t>CVE-2026-45985</t>
+        </is>
+      </c>
+      <c r="B1174" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C1174" t="inlineStr">
+        <is>
+          <t>vulnerability Amazon Linux AMI 2: CVE-2026-45985: Security patch for kernel (ALAS2KERNEL-5.10-2026-117) Published: 2026-06-17 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1174" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1174" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/amazon-linux-ami-2-cve-2026-45985/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" t="inlineStr">
+        <is>
+          <t>CVE-2026-45984</t>
+        </is>
+      </c>
+      <c r="B1175" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C1175" t="inlineStr">
+        <is>
+          <t>vulnerability Amazon Linux AMI 2: CVE-2026-45984: Security patch for kernel (ALAS2KERNEL-5.10-2026-115) Published: 2026-06-17 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1175" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1175" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/amazon-linux-ami-2-cve-2026-45984/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" t="inlineStr">
+        <is>
+          <t>CVE-2026-45983</t>
+        </is>
+      </c>
+      <c r="B1176" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C1176" t="inlineStr">
+        <is>
+          <t>vulnerability Amazon Linux AMI 2: CVE-2026-45983: Security patch for kernel (Multiple Advisories) Published: 2026-06-17 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1176" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1176" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/amazon-linux-ami-2-cve-2026-45983/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" t="inlineStr">
+        <is>
+          <t>CVE-2026-45974</t>
+        </is>
+      </c>
+      <c r="B1177" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C1177" t="inlineStr">
+        <is>
+          <t>vulnerability Amazon Linux AMI 2: CVE-2026-45974: Security patch for kernel (Multiple Advisories) Published: 2026-06-17 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1177" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1177" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/amazon-linux-ami-2-cve-2026-45974/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" t="inlineStr">
+        <is>
+          <t>CVE-2026-45970</t>
+        </is>
+      </c>
+      <c r="B1178" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C1178" t="inlineStr">
+        <is>
+          <t>vulnerability Amazon Linux AMI 2: CVE-2026-45970: Security patch for kernel (Multiple Advisories) Published: 2026-06-17 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1178" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1178" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/amazon-linux-ami-2-cve-2026-45970/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" t="inlineStr">
+        <is>
+          <t>CVE-2026-45968</t>
+        </is>
+      </c>
+      <c r="B1179" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C1179" t="inlineStr">
+        <is>
+          <t>vulnerability Amazon Linux AMI 2: CVE-2026-45968: Security patch for kernel (Multiple Advisories) Published: 2026-06-17 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1179" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1179" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/amazon-linux-ami-2-cve-2026-45968/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" t="inlineStr">
+        <is>
+          <t>CVE-2026-45964</t>
+        </is>
+      </c>
+      <c r="B1180" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C1180" t="inlineStr">
+        <is>
+          <t>vulnerability Amazon Linux AMI 2: CVE-2026-45964: Security patch for kernel (Multiple Advisories) Published: 2026-06-17 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1180" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1180" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/amazon-linux-ami-2-cve-2026-45964/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" t="inlineStr">
+        <is>
+          <t>CVE-2026-45960</t>
+        </is>
+      </c>
+      <c r="B1181" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C1181" t="inlineStr">
+        <is>
+          <t>vulnerability Amazon Linux AMI 2: CVE-2026-45960: Security patch for kernel (ALAS2KERNEL-5.10-2026-115) Published: 2026-06-17 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1181" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1181" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/amazon-linux-ami-2-cve-2026-45960/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" t="inlineStr">
+        <is>
+          <t>CVE-2026-45948</t>
+        </is>
+      </c>
+      <c r="B1182" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C1182" t="inlineStr">
+        <is>
+          <t>vulnerability Amazon Linux AMI 2: CVE-2026-45948: Security patch for kernel (Multiple Advisories) Published: 2026-06-17 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1182" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1182" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/amazon-linux-ami-2-cve-2026-45948/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" t="inlineStr">
+        <is>
+          <t>CVE-2026-45935</t>
+        </is>
+      </c>
+      <c r="B1183" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C1183" t="inlineStr">
+        <is>
+          <t>vulnerability Amazon Linux AMI 2: CVE-2026-45935: Security patch for kernel (ALAS2KERNEL-5.15-2026-100) Published: 2026-06-17 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1183" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1183" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/amazon-linux-ami-2-cve-2026-45935/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" t="inlineStr">
+        <is>
+          <t>CVE-2026-45923</t>
+        </is>
+      </c>
+      <c r="B1184" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C1184" t="inlineStr">
+        <is>
+          <t>vulnerability Amazon Linux AMI 2: CVE-2026-45923: Security patch for kernel (ALAS2KERNEL-5.10-2026-115) Published: 2026-06-17 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1184" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1184" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/amazon-linux-ami-2-cve-2026-45923/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" t="inlineStr">
+        <is>
+          <t>CVE-2026-45920</t>
+        </is>
+      </c>
+      <c r="B1185" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C1185" t="inlineStr">
+        <is>
+          <t>vulnerability Amazon Linux AMI 2: CVE-2026-45920: Security patch for kernel (ALAS2KERNEL-5.10-2026-117) Published: 2026-06-17 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1185" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1185" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/amazon-linux-ami-2-cve-2026-45920/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" t="inlineStr">
+        <is>
+          <t>CVE-2026-45919</t>
+        </is>
+      </c>
+      <c r="B1186" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C1186" t="inlineStr">
+        <is>
+          <t>vulnerability Amazon Linux AMI 2: CVE-2026-45919: Security patch for kernel (Multiple Advisories) Published: 2026-06-17 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1186" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1186" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/amazon-linux-ami-2-cve-2026-45919/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" t="inlineStr">
+        <is>
+          <t>CVE-2026-45915</t>
+        </is>
+      </c>
+      <c r="B1187" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C1187" t="inlineStr">
+        <is>
+          <t>vulnerability Amazon Linux AMI 2: CVE-2026-45915: Security patch for kernel (Multiple Advisories) Published: 2026-06-17 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1187" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1187" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/amazon-linux-ami-2-cve-2026-45915/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" t="inlineStr">
+        <is>
+          <t>CVE-2026-45912</t>
+        </is>
+      </c>
+      <c r="B1188" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C1188" t="inlineStr">
+        <is>
+          <t>vulnerability Amazon Linux AMI 2: CVE-2026-45912: Security patch for kernel (Multiple Advisories) Published: 2026-06-17 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1188" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1188" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/amazon-linux-ami-2-cve-2026-45912/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rapid7_cves.xlsx
+++ b/rapid7_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1188"/>
+  <dimension ref="A1:E1228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32492,6 +32492,1086 @@
         </is>
       </c>
     </row>
+    <row r="1189">
+      <c r="A1189" t="inlineStr">
+        <is>
+          <t>CVE-2026-8358</t>
+        </is>
+      </c>
+      <c r="B1189" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="C1189" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1189" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1189" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" t="inlineStr">
+        <is>
+          <t>CVE-2026-8357</t>
+        </is>
+      </c>
+      <c r="B1190" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="C1190" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1190" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1190" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" t="inlineStr">
+        <is>
+          <t>CVE-2026-8356</t>
+        </is>
+      </c>
+      <c r="B1191" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="C1191" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1191" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1191" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" t="inlineStr">
+        <is>
+          <t>CVE-2026-6045</t>
+        </is>
+      </c>
+      <c r="B1192" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="C1192" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1192" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1192" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" t="inlineStr">
+        <is>
+          <t>CVE-2026-6039</t>
+        </is>
+      </c>
+      <c r="B1193" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="C1193" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1193" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1193" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" t="inlineStr">
+        <is>
+          <t>CVE-2026-42271</t>
+        </is>
+      </c>
+      <c r="B1194" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="C1194" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1194" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1194" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" t="inlineStr">
+        <is>
+          <t>CVE-2026-20262</t>
+        </is>
+      </c>
+      <c r="B1195" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="C1195" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1195" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1195" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" t="inlineStr">
+        <is>
+          <t>CVE-2025-22782</t>
+        </is>
+      </c>
+      <c r="B1196" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="C1196" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1196" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1196" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" t="inlineStr">
+        <is>
+          <t>CVE-2026-39610</t>
+        </is>
+      </c>
+      <c r="B1197" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="C1197" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1197" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1197" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" t="inlineStr">
+        <is>
+          <t>CVE-2026-49061</t>
+        </is>
+      </c>
+      <c r="B1198" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="C1198" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1198" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1198" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" t="inlineStr">
+        <is>
+          <t>CVE-2026-39451</t>
+        </is>
+      </c>
+      <c r="B1199" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="C1199" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1199" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1199" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" t="inlineStr">
+        <is>
+          <t>CVE-2026-49071</t>
+        </is>
+      </c>
+      <c r="B1200" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="C1200" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1200" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1200" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" t="inlineStr">
+        <is>
+          <t>CVE-2026-52694</t>
+        </is>
+      </c>
+      <c r="B1201" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="C1201" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1201" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1201" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" t="inlineStr">
+        <is>
+          <t>CVE-2026-49072</t>
+        </is>
+      </c>
+      <c r="B1202" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="C1202" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1202" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1202" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" t="inlineStr">
+        <is>
+          <t>CVE-2026-49068</t>
+        </is>
+      </c>
+      <c r="B1203" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="C1203" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1203" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1203" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" t="inlineStr">
+        <is>
+          <t>CVE-2025-49352</t>
+        </is>
+      </c>
+      <c r="B1204" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="C1204" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1204" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1204" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" t="inlineStr">
+        <is>
+          <t>CVE-2026-52699</t>
+        </is>
+      </c>
+      <c r="B1205" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="C1205" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1205" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1205" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" t="inlineStr">
+        <is>
+          <t>CVE-2026-11775</t>
+        </is>
+      </c>
+      <c r="B1206" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="C1206" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1206" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1206" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" t="inlineStr">
+        <is>
+          <t>CVE-2026-39708</t>
+        </is>
+      </c>
+      <c r="B1207" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="C1207" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1207" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1207" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" t="inlineStr">
+        <is>
+          <t>CVE-2025-23973</t>
+        </is>
+      </c>
+      <c r="B1208" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="C1208" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1208" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1208" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" t="inlineStr">
+        <is>
+          <t>CVE-2026-8358</t>
+        </is>
+      </c>
+      <c r="B1209" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="C1209" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-8358: libreoffice -- security update Published: 2026-06-18 | Severity: 6 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1209" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1209" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-8358/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" t="inlineStr">
+        <is>
+          <t>CVE-2026-8357</t>
+        </is>
+      </c>
+      <c r="B1210" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="C1210" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-8357: libreoffice -- security update Published: 2026-06-18 | Severity: 6 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1210" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1210" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-8357/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" t="inlineStr">
+        <is>
+          <t>CVE-2026-8356</t>
+        </is>
+      </c>
+      <c r="B1211" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="C1211" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-8356: libreoffice -- security update Published: 2026-06-18 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1211" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1211" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-8356/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" t="inlineStr">
+        <is>
+          <t>CVE-2026-6045</t>
+        </is>
+      </c>
+      <c r="B1212" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="C1212" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-6045: libreoffice -- security update Published: 2026-06-18 | Severity: 6 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1212" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1212" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-6045/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" t="inlineStr">
+        <is>
+          <t>CVE-2026-6039</t>
+        </is>
+      </c>
+      <c r="B1213" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="C1213" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-6039: libreoffice -- security update Published: 2026-06-18 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1213" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1213" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-6039/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="inlineStr">
+        <is>
+          <t>CVE-2026-42271</t>
+        </is>
+      </c>
+      <c r="B1214" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="C1214" t="inlineStr">
+        <is>
+          <t>vulnerability LiteLLM: CVE-2026-42271: Command Injection via MCP stdio test endpoints Published: 2026-05-08 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1214" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1214" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/litellm-cve-2026-42271/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" t="inlineStr">
+        <is>
+          <t>CVE-2026-20262</t>
+        </is>
+      </c>
+      <c r="B1215" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="C1215" t="inlineStr">
+        <is>
+          <t>vulnerability Cisco Catalyst SD-WAN: CVE-2026-20262: Cisco Catalyst SD-WAN Manager Arbitrary File Write Vulnerability Published: 2026-06-15 | Severity</t>
+        </is>
+      </c>
+      <c r="D1215" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1215" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/cisco-catalyst-sdwan-cve-2026-20262/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" t="inlineStr">
+        <is>
+          <t>CVE-2025-22782</t>
+        </is>
+      </c>
+      <c r="B1216" t="inlineStr">
+        <is>
+          <t>2025-01-13</t>
+        </is>
+      </c>
+      <c r="C1216" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: wr-price-list-for-woocommerce: CVE-2025-22782: Unrestricted Upload of File with Dangerous Type Published: 2025-01-13 |</t>
+        </is>
+      </c>
+      <c r="D1216" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1216" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/wr-price-list-for-woocommerce-plugin-cve-2025-22782/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" t="inlineStr">
+        <is>
+          <t>CVE-2026-39610</t>
+        </is>
+      </c>
+      <c r="B1217" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="C1217" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: wpxmas-snow: CVE-2026-39610: Missing Authorization Published: 2026-02-07 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1217" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1217" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/wpxmas-snow-plugin-cve-2026-39610/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" t="inlineStr">
+        <is>
+          <t>CVE-2026-49061</t>
+        </is>
+      </c>
+      <c r="B1218" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1218" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: wpc-product-options: CVE-2026-49061: Improper Limitation of a Pathname to a Restricted Directory ('Path Traversal') Pu</t>
+        </is>
+      </c>
+      <c r="D1218" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1218" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/wpc-product-options-plugin-cve-2026-49061/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" t="inlineStr">
+        <is>
+          <t>CVE-2026-39451</t>
+        </is>
+      </c>
+      <c r="B1219" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C1219" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: wp-google-places-review-slider: CVE-2026-39451: Improper Neutralization of Input During Web Page Generation ('Cross-si</t>
+        </is>
+      </c>
+      <c r="D1219" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1219" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/wp-google-places-review-slider-plugin-cve-2026-39451/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" t="inlineStr">
+        <is>
+          <t>CVE-2026-49071</t>
+        </is>
+      </c>
+      <c r="B1220" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1220" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: woocommerce-dropshipping: CVE-2026-49071: Missing Authorization Published: 2026-06-08 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1220" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1220" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/woocommerce-dropshipping-plugin-cve-2026-49071/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" t="inlineStr">
+        <is>
+          <t>CVE-2026-52694</t>
+        </is>
+      </c>
+      <c r="B1221" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C1221" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: woocommerce-digital-signature: CVE-2026-52694: Exposure of Sensitive Information to an Unauthorized Actor Published: 2</t>
+        </is>
+      </c>
+      <c r="D1221" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1221" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/woocommerce-digital-signature-plugin-cve-2026-52694/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" t="inlineStr">
+        <is>
+          <t>CVE-2026-49072</t>
+        </is>
+      </c>
+      <c r="B1222" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1222" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: woocommerce-anti-fraud: CVE-2026-49072: Missing Authorization Published: 2026-06-08 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1222" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1222" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/woocommerce-anti-fraud-plugin-cve-2026-49072/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="inlineStr">
+        <is>
+          <t>CVE-2026-49068</t>
+        </is>
+      </c>
+      <c r="B1223" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C1223" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: woo-coupon-usage: CVE-2026-49068: Exposure of Sensitive Information to an Unauthorized Actor Published: 2026-06-09 | S</t>
+        </is>
+      </c>
+      <c r="D1223" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1223" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/woo-coupon-usage-plugin-cve-2026-49068/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" t="inlineStr">
+        <is>
+          <t>CVE-2025-49352</t>
+        </is>
+      </c>
+      <c r="B1224" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="C1224" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: wc-order-cancellation-return: CVE-2025-49352: Authorization Bypass Through User-Controlled Key Published: 2025-12-31 |</t>
+        </is>
+      </c>
+      <c r="D1224" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1224" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/wc-order-cancellation-return-plugin-cve-2025-49352/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" t="inlineStr">
+        <is>
+          <t>CVE-2026-52699</t>
+        </is>
+      </c>
+      <c r="B1225" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C1225" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: vikrentcar: CVE-2026-52699: Authorization Bypass Through User-Controlled Key Published: 2026-06-10 | Severity: 5 EXPLO</t>
+        </is>
+      </c>
+      <c r="D1225" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1225" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/vikrentcar-plugin-cve-2026-52699/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" t="inlineStr">
+        <is>
+          <t>CVE-2026-11775</t>
+        </is>
+      </c>
+      <c r="B1226" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="C1226" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: user-admin-simplifier: CVE-2026-11775: Cross-Site Request Forgery (CSRF) Published: 2026-06-18 | Severity: 4 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1226" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1226" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/user-admin-simplifier-plugin-cve-2026-11775/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" t="inlineStr">
+        <is>
+          <t>CVE-2026-39708</t>
+        </is>
+      </c>
+      <c r="B1227" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="C1227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vulnerability WordPress Plugin: uicore-elements: CVE-2026-39708: Improper Neutralization of Input During Web Page Generation ('Cross-site Scripting') </t>
+        </is>
+      </c>
+      <c r="D1227" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1227" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/uicore-elements-plugin-cve-2026-39708/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" t="inlineStr">
+        <is>
+          <t>CVE-2025-23973</t>
+        </is>
+      </c>
+      <c r="B1228" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="C1228" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: try-on-for-woocommerce: CVE-2025-23973: Improper Neutralization of Input During Web Page Generation ('Cross-site Scrip</t>
+        </is>
+      </c>
+      <c r="D1228" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1228" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/try-on-for-woocommerce-plugin-cve-2025-23973/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rapid7_cves.xlsx
+++ b/rapid7_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1228"/>
+  <dimension ref="A1:E1268"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33572,6 +33572,1086 @@
         </is>
       </c>
     </row>
+    <row r="1229">
+      <c r="A1229" t="inlineStr">
+        <is>
+          <t>CVE-2026-12330</t>
+        </is>
+      </c>
+      <c r="B1229" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C1229" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1229" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1229" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" t="inlineStr">
+        <is>
+          <t>CVE-2026-12329</t>
+        </is>
+      </c>
+      <c r="B1230" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C1230" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1230" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1230" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" t="inlineStr">
+        <is>
+          <t>CVE-2026-12328</t>
+        </is>
+      </c>
+      <c r="B1231" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C1231" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1231" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1231" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" t="inlineStr">
+        <is>
+          <t>CVE-2026-12327</t>
+        </is>
+      </c>
+      <c r="B1232" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C1232" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1232" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1232" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" t="inlineStr">
+        <is>
+          <t>CVE-2026-12326</t>
+        </is>
+      </c>
+      <c r="B1233" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C1233" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1233" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1233" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" t="inlineStr">
+        <is>
+          <t>CVE-2026-12325</t>
+        </is>
+      </c>
+      <c r="B1234" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C1234" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1234" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1234" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" t="inlineStr">
+        <is>
+          <t>CVE-2026-12324</t>
+        </is>
+      </c>
+      <c r="B1235" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C1235" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1235" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1235" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" t="inlineStr">
+        <is>
+          <t>CVE-2026-12323</t>
+        </is>
+      </c>
+      <c r="B1236" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C1236" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1236" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1236" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" t="inlineStr">
+        <is>
+          <t>CVE-2026-12322</t>
+        </is>
+      </c>
+      <c r="B1237" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C1237" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1237" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1237" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" t="inlineStr">
+        <is>
+          <t>CVE-2026-12321</t>
+        </is>
+      </c>
+      <c r="B1238" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C1238" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1238" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1238" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" t="inlineStr">
+        <is>
+          <t>CVE-2026-12320</t>
+        </is>
+      </c>
+      <c r="B1239" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C1239" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1239" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1239" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" t="inlineStr">
+        <is>
+          <t>CVE-2026-12319</t>
+        </is>
+      </c>
+      <c r="B1240" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C1240" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1240" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1240" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" t="inlineStr">
+        <is>
+          <t>CVE-2026-12318</t>
+        </is>
+      </c>
+      <c r="B1241" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C1241" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1241" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1241" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" t="inlineStr">
+        <is>
+          <t>CVE-2026-12317</t>
+        </is>
+      </c>
+      <c r="B1242" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C1242" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1242" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1242" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" t="inlineStr">
+        <is>
+          <t>CVE-2026-12316</t>
+        </is>
+      </c>
+      <c r="B1243" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C1243" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1243" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1243" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" t="inlineStr">
+        <is>
+          <t>CVE-2026-12315</t>
+        </is>
+      </c>
+      <c r="B1244" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C1244" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1244" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1244" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" t="inlineStr">
+        <is>
+          <t>CVE-2026-12314</t>
+        </is>
+      </c>
+      <c r="B1245" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C1245" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1245" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1245" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" t="inlineStr">
+        <is>
+          <t>CVE-2026-12313</t>
+        </is>
+      </c>
+      <c r="B1246" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C1246" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1246" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1246" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" t="inlineStr">
+        <is>
+          <t>CVE-2026-12312</t>
+        </is>
+      </c>
+      <c r="B1247" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C1247" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1247" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1247" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" t="inlineStr">
+        <is>
+          <t>CVE-2026-12311</t>
+        </is>
+      </c>
+      <c r="B1248" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C1248" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1248" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1248" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" t="inlineStr">
+        <is>
+          <t>CVE-2026-12330</t>
+        </is>
+      </c>
+      <c r="B1249" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C1249" t="inlineStr">
+        <is>
+          <t>vulnerability MFSA2026-61 Thunderbird: Security Vulnerabilities fixed in Thunderbird 140.12 (CVE-2026-12330) Published: 2026-06-16 | Severity: 6 EXPLO</t>
+        </is>
+      </c>
+      <c r="D1249" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1249" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/mozilla-thunderbird-cve-2026-12330/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" t="inlineStr">
+        <is>
+          <t>CVE-2026-12329</t>
+        </is>
+      </c>
+      <c r="B1250" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C1250" t="inlineStr">
+        <is>
+          <t>vulnerability MFSA2026-61 Thunderbird: Security Vulnerabilities fixed in Thunderbird 140.12 (CVE-2026-12329) Published: 2026-06-16 | Severity: 5 EXPLO</t>
+        </is>
+      </c>
+      <c r="D1250" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1250" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/mozilla-thunderbird-cve-2026-12329/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" t="inlineStr">
+        <is>
+          <t>CVE-2026-12328</t>
+        </is>
+      </c>
+      <c r="B1251" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C1251" t="inlineStr">
+        <is>
+          <t>vulnerability MFSA2026-61 Thunderbird: Security Vulnerabilities fixed in Thunderbird 140.12 (CVE-2026-12328) Published: 2026-06-16 | Severity: 9 EXPLO</t>
+        </is>
+      </c>
+      <c r="D1251" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1251" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/mozilla-thunderbird-cve-2026-12328/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" t="inlineStr">
+        <is>
+          <t>CVE-2026-12327</t>
+        </is>
+      </c>
+      <c r="B1252" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C1252" t="inlineStr">
+        <is>
+          <t>vulnerability MFSA2026-61 Thunderbird: Security Vulnerabilities fixed in Thunderbird 140.12 (CVE-2026-12327) Published: 2026-06-16 | Severity: 8 EXPLO</t>
+        </is>
+      </c>
+      <c r="D1252" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1252" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/mozilla-thunderbird-cve-2026-12327/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" t="inlineStr">
+        <is>
+          <t>CVE-2026-12326</t>
+        </is>
+      </c>
+      <c r="B1253" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C1253" t="inlineStr">
+        <is>
+          <t>vulnerability MFSA2026-60 Thunderbird: Security Vulnerabilities fixed in Thunderbird 152 (CVE-2026-12326) Published: 2026-06-16 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1253" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1253" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/mozilla-thunderbird-cve-2026-12326/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" t="inlineStr">
+        <is>
+          <t>CVE-2026-12325</t>
+        </is>
+      </c>
+      <c r="B1254" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C1254" t="inlineStr">
+        <is>
+          <t>vulnerability MFSA2026-61 Thunderbird: Security Vulnerabilities fixed in Thunderbird 140.12 (CVE-2026-12325) Published: 2026-06-16 | Severity: 7 EXPLO</t>
+        </is>
+      </c>
+      <c r="D1254" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1254" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/mozilla-thunderbird-cve-2026-12325/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" t="inlineStr">
+        <is>
+          <t>CVE-2026-12324</t>
+        </is>
+      </c>
+      <c r="B1255" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C1255" t="inlineStr">
+        <is>
+          <t>vulnerability MFSA2026-61 Thunderbird: Security Vulnerabilities fixed in Thunderbird 140.12 (CVE-2026-12324) Published: 2026-06-16 | Severity: 8 EXPLO</t>
+        </is>
+      </c>
+      <c r="D1255" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1255" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/mozilla-thunderbird-cve-2026-12324/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" t="inlineStr">
+        <is>
+          <t>CVE-2026-12323</t>
+        </is>
+      </c>
+      <c r="B1256" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C1256" t="inlineStr">
+        <is>
+          <t>vulnerability MFSA2026-60 Thunderbird: Security Vulnerabilities fixed in Thunderbird 152 (CVE-2026-12323) Published: 2026-06-16 | Severity: 6 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1256" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1256" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/mozilla-thunderbird-cve-2026-12323/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" t="inlineStr">
+        <is>
+          <t>CVE-2026-12322</t>
+        </is>
+      </c>
+      <c r="B1257" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C1257" t="inlineStr">
+        <is>
+          <t>vulnerability MFSA2026-60 Thunderbird: Security Vulnerabilities fixed in Thunderbird 152 (CVE-2026-12322) Published: 2026-06-16 | Severity: 6 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1257" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1257" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/mozilla-thunderbird-cve-2026-12322/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" t="inlineStr">
+        <is>
+          <t>CVE-2026-12321</t>
+        </is>
+      </c>
+      <c r="B1258" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C1258" t="inlineStr">
+        <is>
+          <t>vulnerability MFSA2026-60 Thunderbird: Security Vulnerabilities fixed in Thunderbird 152 (CVE-2026-12321) Published: 2026-06-16 | Severity: 6 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1258" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1258" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/mozilla-thunderbird-cve-2026-12321/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" t="inlineStr">
+        <is>
+          <t>CVE-2026-12320</t>
+        </is>
+      </c>
+      <c r="B1259" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C1259" t="inlineStr">
+        <is>
+          <t>vulnerability MFSA2026-60 Thunderbird: Security Vulnerabilities fixed in Thunderbird 152 (CVE-2026-12320) Published: 2026-06-16 | Severity: 4 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1259" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1259" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/mozilla-thunderbird-cve-2026-12320/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" t="inlineStr">
+        <is>
+          <t>CVE-2026-12319</t>
+        </is>
+      </c>
+      <c r="B1260" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C1260" t="inlineStr">
+        <is>
+          <t>vulnerability MFSA2026-60 Thunderbird: Security Vulnerabilities fixed in Thunderbird 152 (CVE-2026-12319) Published: 2026-06-16 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1260" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1260" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/mozilla-thunderbird-cve-2026-12319/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" t="inlineStr">
+        <is>
+          <t>CVE-2026-12318</t>
+        </is>
+      </c>
+      <c r="B1261" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C1261" t="inlineStr">
+        <is>
+          <t>vulnerability MFSA2026-60 Thunderbird: Security Vulnerabilities fixed in Thunderbird 152 (CVE-2026-12318) Published: 2026-06-16 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1261" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1261" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/mozilla-thunderbird-cve-2026-12318/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" t="inlineStr">
+        <is>
+          <t>CVE-2026-12317</t>
+        </is>
+      </c>
+      <c r="B1262" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C1262" t="inlineStr">
+        <is>
+          <t>vulnerability MFSA2026-60 Thunderbird: Security Vulnerabilities fixed in Thunderbird 152 (CVE-2026-12317) Published: 2026-06-16 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1262" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1262" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/mozilla-thunderbird-cve-2026-12317/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" t="inlineStr">
+        <is>
+          <t>CVE-2026-12316</t>
+        </is>
+      </c>
+      <c r="B1263" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C1263" t="inlineStr">
+        <is>
+          <t>vulnerability MFSA2026-60 Thunderbird: Security Vulnerabilities fixed in Thunderbird 152 (CVE-2026-12316) Published: 2026-06-16 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1263" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1263" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/mozilla-thunderbird-cve-2026-12316/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" t="inlineStr">
+        <is>
+          <t>CVE-2026-12315</t>
+        </is>
+      </c>
+      <c r="B1264" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C1264" t="inlineStr">
+        <is>
+          <t>vulnerability MFSA2026-61 Thunderbird: Security Vulnerabilities fixed in Thunderbird 140.12 (CVE-2026-12315) Published: 2026-06-16 | Severity: 9 EXPLO</t>
+        </is>
+      </c>
+      <c r="D1264" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1264" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/mozilla-thunderbird-cve-2026-12315/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="A1265" t="inlineStr">
+        <is>
+          <t>CVE-2026-12314</t>
+        </is>
+      </c>
+      <c r="B1265" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C1265" t="inlineStr">
+        <is>
+          <t>vulnerability MFSA2026-61 Thunderbird: Security Vulnerabilities fixed in Thunderbird 140.12 (CVE-2026-12314) Published: 2026-06-16 | Severity: 8 EXPLO</t>
+        </is>
+      </c>
+      <c r="D1265" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1265" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/mozilla-thunderbird-cve-2026-12314/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="A1266" t="inlineStr">
+        <is>
+          <t>CVE-2026-12313</t>
+        </is>
+      </c>
+      <c r="B1266" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C1266" t="inlineStr">
+        <is>
+          <t>vulnerability MFSA2026-61 Thunderbird: Security Vulnerabilities fixed in Thunderbird 140.12 (CVE-2026-12313) Published: 2026-06-16 | Severity: 4 EXPLO</t>
+        </is>
+      </c>
+      <c r="D1266" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1266" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/mozilla-thunderbird-cve-2026-12313/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" t="inlineStr">
+        <is>
+          <t>CVE-2026-12312</t>
+        </is>
+      </c>
+      <c r="B1267" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C1267" t="inlineStr">
+        <is>
+          <t>vulnerability MFSA2026-61 Thunderbird: Security Vulnerabilities fixed in Thunderbird 140.12 (CVE-2026-12312) Published: 2026-06-16 | Severity: 8 EXPLO</t>
+        </is>
+      </c>
+      <c r="D1267" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1267" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/mozilla-thunderbird-cve-2026-12312/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" t="inlineStr">
+        <is>
+          <t>CVE-2026-12311</t>
+        </is>
+      </c>
+      <c r="B1268" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C1268" t="inlineStr">
+        <is>
+          <t>vulnerability MFSA2026-61 Thunderbird: Security Vulnerabilities fixed in Thunderbird 140.12 (CVE-2026-12311) Published: 2026-06-16 | Severity: 4 EXPLO</t>
+        </is>
+      </c>
+      <c r="D1268" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1268" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/mozilla-thunderbird-cve-2026-12311/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rapid7_cves.xlsx
+++ b/rapid7_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1268"/>
+  <dimension ref="A1:E1308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34652,6 +34652,1086 @@
         </is>
       </c>
     </row>
+    <row r="1269">
+      <c r="A1269" t="inlineStr">
+        <is>
+          <t>CVE-2025-68900</t>
+        </is>
+      </c>
+      <c r="B1269" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="C1269" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1269" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1269" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="A1270" t="inlineStr">
+        <is>
+          <t>CVE-2026-9029</t>
+        </is>
+      </c>
+      <c r="B1270" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="C1270" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1270" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1270" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="A1271" t="inlineStr">
+        <is>
+          <t>CVE-2026-48931</t>
+        </is>
+      </c>
+      <c r="B1271" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="C1271" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1271" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1271" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" t="inlineStr">
+        <is>
+          <t>CVE-2026-48142</t>
+        </is>
+      </c>
+      <c r="B1272" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="C1272" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1272" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1272" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="A1273" t="inlineStr">
+        <is>
+          <t>CVE-2026-42129</t>
+        </is>
+      </c>
+      <c r="B1273" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="C1273" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1273" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1273" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="A1274" t="inlineStr">
+        <is>
+          <t>CVE-2026-42127</t>
+        </is>
+      </c>
+      <c r="B1274" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="C1274" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1274" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1274" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" t="inlineStr">
+        <is>
+          <t>CVE-2026-42055</t>
+        </is>
+      </c>
+      <c r="B1275" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="C1275" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1275" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1275" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" t="inlineStr">
+        <is>
+          <t>CVE-2026-10601</t>
+        </is>
+      </c>
+      <c r="B1276" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="C1276" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1276" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1276" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" t="inlineStr">
+        <is>
+          <t>CVE-2026-8450</t>
+        </is>
+      </c>
+      <c r="B1277" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="C1277" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1277" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1277" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" t="inlineStr">
+        <is>
+          <t>CVE-2026-41035</t>
+        </is>
+      </c>
+      <c r="B1278" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="C1278" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1278" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1278" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" t="inlineStr">
+        <is>
+          <t>CVE-2026-11526</t>
+        </is>
+      </c>
+      <c r="B1279" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="C1279" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1279" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1279" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" t="inlineStr">
+        <is>
+          <t>CVE-2026-8461</t>
+        </is>
+      </c>
+      <c r="B1280" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="C1280" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1280" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1280" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" t="inlineStr">
+        <is>
+          <t>CVE-2025-67306</t>
+        </is>
+      </c>
+      <c r="B1281" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="C1281" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1281" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1281" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" t="inlineStr">
+        <is>
+          <t>CVE-2026-12469</t>
+        </is>
+      </c>
+      <c r="B1282" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="C1282" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1282" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1282" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" t="inlineStr">
+        <is>
+          <t>CVE-2026-12468</t>
+        </is>
+      </c>
+      <c r="B1283" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="C1283" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1283" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1283" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" t="inlineStr">
+        <is>
+          <t>CVE-2026-12467</t>
+        </is>
+      </c>
+      <c r="B1284" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="C1284" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1284" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1284" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" t="inlineStr">
+        <is>
+          <t>CVE-2026-12466</t>
+        </is>
+      </c>
+      <c r="B1285" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="C1285" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1285" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1285" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" t="inlineStr">
+        <is>
+          <t>CVE-2026-12465</t>
+        </is>
+      </c>
+      <c r="B1286" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="C1286" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1286" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1286" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="A1287" t="inlineStr">
+        <is>
+          <t>CVE-2026-12464</t>
+        </is>
+      </c>
+      <c r="B1287" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="C1287" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1287" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1287" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" t="inlineStr">
+        <is>
+          <t>CVE-2026-12463</t>
+        </is>
+      </c>
+      <c r="B1288" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="C1288" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1288" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1288" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="A1289" t="inlineStr">
+        <is>
+          <t>CVE-2025-68900</t>
+        </is>
+      </c>
+      <c r="B1289" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="C1289" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Theme: enfold: CVE-2025-68900: Improper Neutralization of Input During Web Page Generation ('Cross-site Scripting') Published:</t>
+        </is>
+      </c>
+      <c r="D1289" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1289" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/enfold-theme-cve-2025-68900/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" t="inlineStr">
+        <is>
+          <t>CVE-2026-9029</t>
+        </is>
+      </c>
+      <c r="B1290" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C1290" t="inlineStr">
+        <is>
+          <t>vulnerability Alpine Linux: CVE-2026-9029: Vulnerability in Multiple Components Published: 2026-06-22 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1290" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1290" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alpine-linux-cve-2026-9029/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="A1291" t="inlineStr">
+        <is>
+          <t>CVE-2026-48931</t>
+        </is>
+      </c>
+      <c r="B1291" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C1291" t="inlineStr">
+        <is>
+          <t>vulnerability Alpine Linux: CVE-2026-48931: Time-of-check Time-of-use (TOCTOU) Race Condition Published: 2026-06-22 | Severity: 4 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1291" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1291" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alpine-linux-cve-2026-48931/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="A1292" t="inlineStr">
+        <is>
+          <t>CVE-2026-48142</t>
+        </is>
+      </c>
+      <c r="B1292" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C1292" t="inlineStr">
+        <is>
+          <t>vulnerability Alpine Linux: CVE-2026-48142: Out-of-bounds Read Published: 2026-06-17 | Severity: 6 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1292" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1292" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alpine-linux-cve-2026-48142/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="A1293" t="inlineStr">
+        <is>
+          <t>CVE-2026-42129</t>
+        </is>
+      </c>
+      <c r="B1293" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C1293" t="inlineStr">
+        <is>
+          <t>vulnerability Alpine Linux: CVE-2026-42129: Vulnerability in Multiple Components Published: 2026-06-22 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1293" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1293" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alpine-linux-cve-2026-42129/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="A1294" t="inlineStr">
+        <is>
+          <t>CVE-2026-42127</t>
+        </is>
+      </c>
+      <c r="B1294" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C1294" t="inlineStr">
+        <is>
+          <t>vulnerability Alpine Linux: CVE-2026-42127: Vulnerability in Multiple Components Published: 2026-06-22 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1294" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1294" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alpine-linux-cve-2026-42127/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="A1295" t="inlineStr">
+        <is>
+          <t>CVE-2026-42055</t>
+        </is>
+      </c>
+      <c r="B1295" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C1295" t="inlineStr">
+        <is>
+          <t>vulnerability Alpine Linux: CVE-2026-42055: Heap-based Buffer Overflow Published: 2026-06-17 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1295" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1295" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alpine-linux-cve-2026-42055/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="A1296" t="inlineStr">
+        <is>
+          <t>CVE-2026-10601</t>
+        </is>
+      </c>
+      <c r="B1296" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C1296" t="inlineStr">
+        <is>
+          <t>vulnerability Alpine Linux: CVE-2026-10601: Vulnerability in Multiple Components Published: 2026-06-22 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1296" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1296" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alpine-linux-cve-2026-10601/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="A1297" t="inlineStr">
+        <is>
+          <t>CVE-2026-8450</t>
+        </is>
+      </c>
+      <c r="B1297" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C1297" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-8450: libhttp-daemon-perl -- security update Published: 2026-06-22 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1297" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1297" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-8450/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="A1298" t="inlineStr">
+        <is>
+          <t>CVE-2026-41035</t>
+        </is>
+      </c>
+      <c r="B1298" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C1298" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-41035: rsync -- security update Published: 2026-06-22 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1298" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1298" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-41035/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="A1299" t="inlineStr">
+        <is>
+          <t>CVE-2026-11526</t>
+        </is>
+      </c>
+      <c r="B1299" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C1299" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-11526: libgd-perl -- security update Published: 2026-06-22 | Severity: 10 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1299" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1299" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-11526/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="A1300" t="inlineStr">
+        <is>
+          <t>CVE-2026-8461</t>
+        </is>
+      </c>
+      <c r="B1300" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C1300" t="inlineStr">
+        <is>
+          <t>vulnerability FFmpeg: CVE-2026-8461: Unspecified Security Vulnerability Published: 2026-06-22 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1300" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1300" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ffmpeg-cve-2026-8461/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="A1301" t="inlineStr">
+        <is>
+          <t>CVE-2025-67306</t>
+        </is>
+      </c>
+      <c r="B1301" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C1301" t="inlineStr">
+        <is>
+          <t>vulnerability FFmpeg: CVE-2025-67306: Unspecified Security Vulnerability Published: 2026-06-22 | Severity: 10 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1301" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1301" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ffmpeg-cve-2025-67306/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" t="inlineStr">
+        <is>
+          <t>CVE-2026-12469</t>
+        </is>
+      </c>
+      <c r="B1302" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C1302" t="inlineStr">
+        <is>
+          <t>vulnerability Google Chrome Vulnerability: CVE-2026-12469 Uninitialized Use in GPU Published: 2026-06-22 | Severity: 4 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1302" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1302" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/google-chrome-cve-2026-12469/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" t="inlineStr">
+        <is>
+          <t>CVE-2026-12468</t>
+        </is>
+      </c>
+      <c r="B1303" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C1303" t="inlineStr">
+        <is>
+          <t>vulnerability Google Chrome Vulnerability: CVE-2026-12468 Inappropriate implementation in Updater Published: 2026-06-22 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1303" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1303" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/google-chrome-cve-2026-12468/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" t="inlineStr">
+        <is>
+          <t>CVE-2026-12467</t>
+        </is>
+      </c>
+      <c r="B1304" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C1304" t="inlineStr">
+        <is>
+          <t>vulnerability Google Chrome Vulnerability: CVE-2026-12467 Use after free in Extensions Published: 2026-06-22 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1304" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1304" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/google-chrome-cve-2026-12467/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="A1305" t="inlineStr">
+        <is>
+          <t>CVE-2026-12466</t>
+        </is>
+      </c>
+      <c r="B1305" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C1305" t="inlineStr">
+        <is>
+          <t>vulnerability Google Chrome Vulnerability: CVE-2026-12466 Heap buffer overflow in WebRTC Published: 2026-06-22 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1305" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1305" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/google-chrome-cve-2026-12466/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="A1306" t="inlineStr">
+        <is>
+          <t>CVE-2026-12465</t>
+        </is>
+      </c>
+      <c r="B1306" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C1306" t="inlineStr">
+        <is>
+          <t>vulnerability Google Chrome Vulnerability: CVE-2026-12465 Insufficient validation of untrusted input in Metrics Published: 2026-06-22 | Severity: 8 EX</t>
+        </is>
+      </c>
+      <c r="D1306" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1306" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/google-chrome-cve-2026-12465/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" t="inlineStr">
+        <is>
+          <t>CVE-2026-12464</t>
+        </is>
+      </c>
+      <c r="B1307" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C1307" t="inlineStr">
+        <is>
+          <t>vulnerability Google Chrome Vulnerability: CVE-2026-12464 Use after free in Browser Published: 2026-06-22 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1307" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1307" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/google-chrome-cve-2026-12464/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" t="inlineStr">
+        <is>
+          <t>CVE-2026-12463</t>
+        </is>
+      </c>
+      <c r="B1308" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C1308" t="inlineStr">
+        <is>
+          <t>vulnerability Google Chrome Vulnerability: CVE-2026-12463 Inappropriate implementation in Views Published: 2026-06-22 | Severity: 4 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1308" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1308" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/google-chrome-cve-2026-12463/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rapid7_cves.xlsx
+++ b/rapid7_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1308"/>
+  <dimension ref="A1:E1348"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35732,6 +35732,1086 @@
         </is>
       </c>
     </row>
+    <row r="1309">
+      <c r="A1309" t="inlineStr">
+        <is>
+          <t>CVE-2026-3950</t>
+        </is>
+      </c>
+      <c r="B1309" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C1309" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1309" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E1309" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" t="inlineStr">
+        <is>
+          <t>CVE-2026-3593</t>
+        </is>
+      </c>
+      <c r="B1310" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C1310" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1310" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E1310" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" t="inlineStr">
+        <is>
+          <t>CVE-2026-48027</t>
+        </is>
+      </c>
+      <c r="B1311" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C1311" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1311" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E1311" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" t="inlineStr">
+        <is>
+          <t>CVE-2026-44517</t>
+        </is>
+      </c>
+      <c r="B1312" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C1312" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1312" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E1312" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" t="inlineStr">
+        <is>
+          <t>CVE-2026-46054</t>
+        </is>
+      </c>
+      <c r="B1313" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C1313" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1313" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E1313" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="A1314" t="inlineStr">
+        <is>
+          <t>CVE-2026-12330</t>
+        </is>
+      </c>
+      <c r="B1314" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C1314" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1314" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E1314" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="A1315" t="inlineStr">
+        <is>
+          <t>CVE-2026-12329</t>
+        </is>
+      </c>
+      <c r="B1315" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C1315" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1315" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E1315" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="A1316" t="inlineStr">
+        <is>
+          <t>CVE-2026-12328</t>
+        </is>
+      </c>
+      <c r="B1316" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C1316" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1316" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E1316" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="A1317" t="inlineStr">
+        <is>
+          <t>CVE-2026-12327</t>
+        </is>
+      </c>
+      <c r="B1317" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C1317" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1317" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E1317" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" t="inlineStr">
+        <is>
+          <t>CVE-2026-12325</t>
+        </is>
+      </c>
+      <c r="B1318" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C1318" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1318" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E1318" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="A1319" t="inlineStr">
+        <is>
+          <t>CVE-2026-12324</t>
+        </is>
+      </c>
+      <c r="B1319" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C1319" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1319" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E1319" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="A1320" t="inlineStr">
+        <is>
+          <t>CVE-2026-12315</t>
+        </is>
+      </c>
+      <c r="B1320" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C1320" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1320" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E1320" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="A1321" t="inlineStr">
+        <is>
+          <t>CVE-2026-12314</t>
+        </is>
+      </c>
+      <c r="B1321" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C1321" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1321" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E1321" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="A1322" t="inlineStr">
+        <is>
+          <t>CVE-2026-12313</t>
+        </is>
+      </c>
+      <c r="B1322" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C1322" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1322" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E1322" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="A1323" t="inlineStr">
+        <is>
+          <t>CVE-2026-12312</t>
+        </is>
+      </c>
+      <c r="B1323" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C1323" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1323" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E1323" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" t="inlineStr">
+        <is>
+          <t>CVE-2026-12311</t>
+        </is>
+      </c>
+      <c r="B1324" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C1324" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1324" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E1324" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" t="inlineStr">
+        <is>
+          <t>CVE-2026-12310</t>
+        </is>
+      </c>
+      <c r="B1325" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C1325" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1325" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E1325" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" t="inlineStr">
+        <is>
+          <t>CVE-2026-12309</t>
+        </is>
+      </c>
+      <c r="B1326" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C1326" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1326" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E1326" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" t="inlineStr">
+        <is>
+          <t>CVE-2026-12308</t>
+        </is>
+      </c>
+      <c r="B1327" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C1327" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1327" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E1327" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" t="inlineStr">
+        <is>
+          <t>CVE-2026-12307</t>
+        </is>
+      </c>
+      <c r="B1328" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C1328" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1328" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E1328" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" t="inlineStr">
+        <is>
+          <t>CVE-2026-3950</t>
+        </is>
+      </c>
+      <c r="B1329" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C1329" t="inlineStr">
+        <is>
+          <t>vulnerability SUSE: CVE-2026-3950: SUSE Linux Security Advisory Published: 2026-06-24 | Severity: 2 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1329" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E1329" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/suse-cve-2026-3950/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" t="inlineStr">
+        <is>
+          <t>CVE-2026-3593</t>
+        </is>
+      </c>
+      <c r="B1330" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C1330" t="inlineStr">
+        <is>
+          <t>vulnerability SUSE: CVE-2026-3593: SUSE Linux Security Advisory Published: 2026-06-24 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1330" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1330" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/suse-cve-2026-3593/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331" t="inlineStr">
+        <is>
+          <t>CVE-2026-48027</t>
+        </is>
+      </c>
+      <c r="B1331" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C1331" t="inlineStr">
+        <is>
+          <t>vulnerability Nx Console: CVE-2026-48027: Embedded Malicious Code via Supply Chain Compromise Published: 2026-05-27 | Severity: 10 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1331" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1331" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/nx-console-cve-2026-48027/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" t="inlineStr">
+        <is>
+          <t>CVE-2026-44517</t>
+        </is>
+      </c>
+      <c r="B1332" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C1332" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vulnerability FreeBSD: VID-fe2e8bdc-ff48-4166-b285-59822c7cf473 (CVE-2026-44517): podman -- files outside build context may be included via malicious </t>
+        </is>
+      </c>
+      <c r="D1332" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1332" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/freebsd-cve-2026-44517/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="A1333" t="inlineStr">
+        <is>
+          <t>CVE-2026-46054</t>
+        </is>
+      </c>
+      <c r="B1333" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C1333" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-46054: Important: kernel security update (Multiple Advisories) Published: 2026-06-22 | Severity: 6 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1333" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1333" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-46054/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="A1334" t="inlineStr">
+        <is>
+          <t>CVE-2026-12330</t>
+        </is>
+      </c>
+      <c r="B1334" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C1334" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-12330: Important: firefox security update (ALSA-2026-27717) Published: 2026-06-22 | Severity: 6 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1334" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1334" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-12330/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="A1335" t="inlineStr">
+        <is>
+          <t>CVE-2026-12329</t>
+        </is>
+      </c>
+      <c r="B1335" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C1335" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-12329: Important: firefox security update (ALSA-2026-27717) Published: 2026-06-22 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1335" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1335" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-12329/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336" t="inlineStr">
+        <is>
+          <t>CVE-2026-12328</t>
+        </is>
+      </c>
+      <c r="B1336" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C1336" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-12328: Important: firefox security update (ALSA-2026-27717) Published: 2026-06-22 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1336" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1336" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-12328/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="A1337" t="inlineStr">
+        <is>
+          <t>CVE-2026-12327</t>
+        </is>
+      </c>
+      <c r="B1337" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C1337" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-12327: Important: firefox security update (ALSA-2026-27717) Published: 2026-06-22 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1337" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1337" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-12327/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="A1338" t="inlineStr">
+        <is>
+          <t>CVE-2026-12325</t>
+        </is>
+      </c>
+      <c r="B1338" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C1338" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-12325: Important: firefox security update (ALSA-2026-27717) Published: 2026-06-22 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1338" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1338" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-12325/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1339">
+      <c r="A1339" t="inlineStr">
+        <is>
+          <t>CVE-2026-12324</t>
+        </is>
+      </c>
+      <c r="B1339" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C1339" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-12324: Important: firefox security update (ALSA-2026-27717) Published: 2026-06-22 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1339" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1339" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-12324/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1340">
+      <c r="A1340" t="inlineStr">
+        <is>
+          <t>CVE-2026-12315</t>
+        </is>
+      </c>
+      <c r="B1340" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C1340" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-12315: Important: firefox security update (ALSA-2026-27717) Published: 2026-06-22 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1340" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1340" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-12315/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="A1341" t="inlineStr">
+        <is>
+          <t>CVE-2026-12314</t>
+        </is>
+      </c>
+      <c r="B1341" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C1341" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-12314: Important: firefox security update (ALSA-2026-27717) Published: 2026-06-22 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1341" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1341" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-12314/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1342">
+      <c r="A1342" t="inlineStr">
+        <is>
+          <t>CVE-2026-12313</t>
+        </is>
+      </c>
+      <c r="B1342" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C1342" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-12313: Important: firefox security update (ALSA-2026-27717) Published: 2026-06-22 | Severity: 4 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1342" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1342" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-12313/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1343">
+      <c r="A1343" t="inlineStr">
+        <is>
+          <t>CVE-2026-12312</t>
+        </is>
+      </c>
+      <c r="B1343" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C1343" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-12312: Important: firefox security update (ALSA-2026-27717) Published: 2026-06-22 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1343" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1343" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-12312/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1344">
+      <c r="A1344" t="inlineStr">
+        <is>
+          <t>CVE-2026-12311</t>
+        </is>
+      </c>
+      <c r="B1344" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C1344" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-12311: Important: firefox security update (ALSA-2026-27717) Published: 2026-06-22 | Severity: 4 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1344" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1344" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-12311/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1345">
+      <c r="A1345" t="inlineStr">
+        <is>
+          <t>CVE-2026-12310</t>
+        </is>
+      </c>
+      <c r="B1345" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C1345" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-12310: Important: firefox security update (ALSA-2026-27717) Published: 2026-06-22 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1345" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1345" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-12310/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1346">
+      <c r="A1346" t="inlineStr">
+        <is>
+          <t>CVE-2026-12309</t>
+        </is>
+      </c>
+      <c r="B1346" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C1346" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-12309: Important: firefox security update (ALSA-2026-27717) Published: 2026-06-22 | Severity: 6 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1346" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1346" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-12309/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1347">
+      <c r="A1347" t="inlineStr">
+        <is>
+          <t>CVE-2026-12308</t>
+        </is>
+      </c>
+      <c r="B1347" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C1347" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-12308: Important: firefox security update (ALSA-2026-27717) Published: 2026-06-22 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1347" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1347" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-12308/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1348">
+      <c r="A1348" t="inlineStr">
+        <is>
+          <t>CVE-2026-12307</t>
+        </is>
+      </c>
+      <c r="B1348" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C1348" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-12307: Important: firefox security update (ALSA-2026-27717) Published: 2026-06-22 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1348" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1348" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-12307/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rapid7_cves.xlsx
+++ b/rapid7_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1348"/>
+  <dimension ref="A1:E1387"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36812,6 +36812,1059 @@
         </is>
       </c>
     </row>
+    <row r="1349">
+      <c r="A1349" t="inlineStr">
+        <is>
+          <t>CVE-2026-54827</t>
+        </is>
+      </c>
+      <c r="B1349" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C1349" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1349" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1349" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1350">
+      <c r="A1350" t="inlineStr">
+        <is>
+          <t>CVE-2026-39620</t>
+        </is>
+      </c>
+      <c r="B1350" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C1350" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1350" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1350" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1351">
+      <c r="A1351" t="inlineStr">
+        <is>
+          <t>CVE-2026-9256</t>
+        </is>
+      </c>
+      <c r="B1351" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C1351" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1351" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1351" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1352">
+      <c r="A1352" t="inlineStr">
+        <is>
+          <t>CVE-2026-9150</t>
+        </is>
+      </c>
+      <c r="B1352" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C1352" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1352" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1352" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1353">
+      <c r="A1353" t="inlineStr">
+        <is>
+          <t>CVE-2026-9149</t>
+        </is>
+      </c>
+      <c r="B1353" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C1353" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1353" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1353" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1354">
+      <c r="A1354" t="inlineStr">
+        <is>
+          <t>CVE-2026-6420</t>
+        </is>
+      </c>
+      <c r="B1354" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C1354" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1354" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1354" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1355">
+      <c r="A1355" t="inlineStr">
+        <is>
+          <t>CVE-2026-6019</t>
+        </is>
+      </c>
+      <c r="B1355" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C1355" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1355" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1355" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1356">
+      <c r="A1356" t="inlineStr">
+        <is>
+          <t>CVE-2026-48864</t>
+        </is>
+      </c>
+      <c r="B1356" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C1356" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1356" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1356" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1357">
+      <c r="A1357" t="inlineStr">
+        <is>
+          <t>CVE-2025-13151</t>
+        </is>
+      </c>
+      <c r="B1357" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C1357" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1357" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1357" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1358">
+      <c r="A1358" t="inlineStr">
+        <is>
+          <t>CVE-2026-47783</t>
+        </is>
+      </c>
+      <c r="B1358" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C1358" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1358" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1358" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1359">
+      <c r="A1359" t="inlineStr">
+        <is>
+          <t>CVE-2026-46173</t>
+        </is>
+      </c>
+      <c r="B1359" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C1359" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1359" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1359" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1360">
+      <c r="A1360" t="inlineStr">
+        <is>
+          <t>CVE-2026-46166</t>
+        </is>
+      </c>
+      <c r="B1360" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C1360" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1360" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1360" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1361">
+      <c r="A1361" t="inlineStr">
+        <is>
+          <t>CVE-2026-46117</t>
+        </is>
+      </c>
+      <c r="B1361" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C1361" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1361" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1361" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1362">
+      <c r="A1362" t="inlineStr">
+        <is>
+          <t>CVE-2026-43414</t>
+        </is>
+      </c>
+      <c r="B1362" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C1362" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1362" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1362" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1363">
+      <c r="A1363" t="inlineStr">
+        <is>
+          <t>CVE-2026-43260</t>
+        </is>
+      </c>
+      <c r="B1363" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C1363" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1363" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1363" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1364">
+      <c r="A1364" t="inlineStr">
+        <is>
+          <t>CVE-2026-41411</t>
+        </is>
+      </c>
+      <c r="B1364" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C1364" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1364" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1364" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1365">
+      <c r="A1365" t="inlineStr">
+        <is>
+          <t>CVE-2026-34000</t>
+        </is>
+      </c>
+      <c r="B1365" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C1365" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1365" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1365" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1366">
+      <c r="A1366" t="inlineStr">
+        <is>
+          <t>CVE-2026-31772</t>
+        </is>
+      </c>
+      <c r="B1366" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C1366" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1366" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1366" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1367">
+      <c r="A1367" t="inlineStr">
+        <is>
+          <t>CVE-2026-31474</t>
+        </is>
+      </c>
+      <c r="B1367" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C1367" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1367" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1367" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1368">
+      <c r="A1368" t="inlineStr">
+        <is>
+          <t>CVE-2026-54827</t>
+        </is>
+      </c>
+      <c r="B1368" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C1368" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Theme: realestate-7: CVE-2026-54827: Improper Neutralization of Special Elements used in an SQL Command ('SQL Injection') Publ</t>
+        </is>
+      </c>
+      <c r="D1368" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1368" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/realestate-7-theme-cve-2026-54827/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1369">
+      <c r="A1369" t="inlineStr">
+        <is>
+          <t>CVE-2026-39620</t>
+        </is>
+      </c>
+      <c r="B1369" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="C1369" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Theme: appointment: CVE-2026-39620: Cross-Site Request Forgery (CSRF) Published: 2026-02-11 | Severity: 4 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1369" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1369" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/appointment-theme-cve-2026-39620/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1370">
+      <c r="A1370" t="inlineStr">
+        <is>
+          <t>CVE-2026-9256</t>
+        </is>
+      </c>
+      <c r="B1370" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C1370" t="inlineStr">
+        <is>
+          <t>vulnerability Red Hat: CVE-2026-9256: nginx: ngx_http_rewrite_module: code execution and denial of service (Multiple Advisories) Published: 2026-05-22</t>
+        </is>
+      </c>
+      <c r="D1370" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1370" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/redhat_linux-cve-2026-9256/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1371">
+      <c r="A1371" t="inlineStr">
+        <is>
+          <t>CVE-2026-9150</t>
+        </is>
+      </c>
+      <c r="B1371" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C1371" t="inlineStr">
+        <is>
+          <t>vulnerability Red Hat: CVE-2026-9150: libsolv: Stack-based buffer overflow in libsolv's Debian metadata parser when handling SHA384/SHA512 checksums (</t>
+        </is>
+      </c>
+      <c r="D1371" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1371" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/redhat_linux-cve-2026-9150/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1372">
+      <c r="A1372" t="inlineStr">
+        <is>
+          <t>CVE-2026-9149</t>
+        </is>
+      </c>
+      <c r="B1372" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C1372" t="inlineStr">
+        <is>
+          <t>vulnerability Red Hat: CVE-2026-9149: libsolv: Heap buffer overflow in libsolv repo_add_solv via negative maxsize from crafted .solv file (Multiple Ad</t>
+        </is>
+      </c>
+      <c r="D1372" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1372" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/redhat_linux-cve-2026-9149/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1373">
+      <c r="A1373" t="inlineStr">
+        <is>
+          <t>CVE-2026-6420</t>
+        </is>
+      </c>
+      <c r="B1373" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C1373" t="inlineStr">
+        <is>
+          <t>vulnerability Red Hat: CVE-2026-6420: keylime: Keylime: Security bypass due to hardcoded TPM quote nonce (Multiple Advisories) Published: 2026-05-06 |</t>
+        </is>
+      </c>
+      <c r="D1373" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1373" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/redhat_linux-cve-2026-6420/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1374">
+      <c r="A1374" t="inlineStr">
+        <is>
+          <t>CVE-2026-6019</t>
+        </is>
+      </c>
+      <c r="B1374" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="C1374" t="inlineStr">
+        <is>
+          <t>vulnerability Red Hat: CVE-2026-6019: python: Python: Cross-Site Scripting (XSS) vulnerability in http.cookies module (Multiple Advisories) Published:</t>
+        </is>
+      </c>
+      <c r="D1374" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1374" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/redhat_linux-cve-2026-6019/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1375">
+      <c r="A1375" t="inlineStr">
+        <is>
+          <t>CVE-2026-48864</t>
+        </is>
+      </c>
+      <c r="B1375" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C1375" t="inlineStr">
+        <is>
+          <t>vulnerability Red Hat: CVE-2026-48864: libsolv: Heap buffer overflow in libsolv repopagestore via unchecked decompression of malicious .solv page data</t>
+        </is>
+      </c>
+      <c r="D1375" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1375" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/redhat_linux-cve-2026-48864/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1376">
+      <c r="A1376" t="inlineStr">
+        <is>
+          <t>CVE-2025-13151</t>
+        </is>
+      </c>
+      <c r="B1376" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="C1376" t="inlineStr">
+        <is>
+          <t>vulnerability Red Hat: CVE-2025-13151: libtasn1: libtasn1: Denial of Service via stack-based buffer overflow in asn1_expend_octet_string (Multiple Adv</t>
+        </is>
+      </c>
+      <c r="D1376" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1376" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/redhat_linux-cve-2025-13151/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1377">
+      <c r="A1377" t="inlineStr">
+        <is>
+          <t>CVE-2026-47783</t>
+        </is>
+      </c>
+      <c r="B1377" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C1377" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-47783: Important: memcached security update (ALSA-2026-27862) Published: 2026-06-22 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1377" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1377" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-47783/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1378">
+      <c r="A1378" t="inlineStr">
+        <is>
+          <t>CVE-2026-46173</t>
+        </is>
+      </c>
+      <c r="B1378" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C1378" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-46173: Important: kernel security, bug fix, and enhancement update (ALSA-2026-27789) Published: 2026-06-22 | Severi</t>
+        </is>
+      </c>
+      <c r="D1378" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1378" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-46173/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1379">
+      <c r="A1379" t="inlineStr">
+        <is>
+          <t>CVE-2026-46166</t>
+        </is>
+      </c>
+      <c r="B1379" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C1379" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-46166: Important: kernel security, bug fix, and enhancement update (ALSA-2026-27789) Published: 2026-06-22 | Severi</t>
+        </is>
+      </c>
+      <c r="D1379" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1379" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-46166/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1380">
+      <c r="A1380" t="inlineStr">
+        <is>
+          <t>CVE-2026-46117</t>
+        </is>
+      </c>
+      <c r="B1380" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C1380" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-46117: Important: kernel security, bug fix, and enhancement update (ALSA-2026-27789) Published: 2026-06-22 | Severi</t>
+        </is>
+      </c>
+      <c r="D1380" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1380" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-46117/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1381">
+      <c r="A1381" t="inlineStr">
+        <is>
+          <t>CVE-2026-45984</t>
+        </is>
+      </c>
+      <c r="B1381" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C1381" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-45984: Important: kernel security, bug fix, and enhancement update (ALSA-2026-27789) Published: 2026-06-22 | Severi</t>
+        </is>
+      </c>
+      <c r="D1381" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1381" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-45984/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1382">
+      <c r="A1382" t="inlineStr">
+        <is>
+          <t>CVE-2026-43414</t>
+        </is>
+      </c>
+      <c r="B1382" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C1382" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-43414: Important: kernel security, bug fix, and enhancement update (ALSA-2026-27789) Published: 2026-06-22 | Severi</t>
+        </is>
+      </c>
+      <c r="D1382" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1382" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-43414/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1383">
+      <c r="A1383" t="inlineStr">
+        <is>
+          <t>CVE-2026-43260</t>
+        </is>
+      </c>
+      <c r="B1383" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C1383" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-43260: Important: kernel security, bug fix, and enhancement update (ALSA-2026-27789) Published: 2026-06-22 | Severi</t>
+        </is>
+      </c>
+      <c r="D1383" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1383" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-43260/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1384">
+      <c r="A1384" t="inlineStr">
+        <is>
+          <t>CVE-2026-41411</t>
+        </is>
+      </c>
+      <c r="B1384" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C1384" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-41411: Moderate: vim security update (ALSA-2026-28553) Published: 2026-06-23 | Severity: 6 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1384" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1384" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-41411/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1385">
+      <c r="A1385" t="inlineStr">
+        <is>
+          <t>CVE-2026-34000</t>
+        </is>
+      </c>
+      <c r="B1385" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C1385" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-34000: Important: tigervnc security update (ALSA-2026-19342) Published: 2026-05-19 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1385" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1385" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-34000/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1386">
+      <c r="A1386" t="inlineStr">
+        <is>
+          <t>CVE-2026-31772</t>
+        </is>
+      </c>
+      <c r="B1386" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C1386" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-31772: Important: kernel security, bug fix, and enhancement update (ALSA-2026-27789) Published: 2026-06-22 | Severi</t>
+        </is>
+      </c>
+      <c r="D1386" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1386" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-31772/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1387">
+      <c r="A1387" t="inlineStr">
+        <is>
+          <t>CVE-2026-31474</t>
+        </is>
+      </c>
+      <c r="B1387" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C1387" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-31474: Important: kernel security, bug fix, and enhancement update (ALSA-2026-27789) Published: 2026-06-22 | Severi</t>
+        </is>
+      </c>
+      <c r="D1387" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1387" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-31474/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rapid7_cves.xlsx
+++ b/rapid7_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1387"/>
+  <dimension ref="A1:E1427"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37865,6 +37865,1086 @@
         </is>
       </c>
     </row>
+    <row r="1388">
+      <c r="A1388" t="inlineStr">
+        <is>
+          <t>CVE-2026-40372</t>
+        </is>
+      </c>
+      <c r="B1388" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C1388" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1388" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1388" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1389">
+      <c r="A1389" t="inlineStr">
+        <is>
+          <t>CVE-2026-49839</t>
+        </is>
+      </c>
+      <c r="B1389" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C1389" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1389" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1389" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1390">
+      <c r="A1390" t="inlineStr">
+        <is>
+          <t>CVE-2026-7473</t>
+        </is>
+      </c>
+      <c r="B1390" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C1390" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1390" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1390" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1391">
+      <c r="A1391" t="inlineStr">
+        <is>
+          <t>CVE-2026-23303</t>
+        </is>
+      </c>
+      <c r="B1391" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C1391" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1391" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1391" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1392">
+      <c r="A1392" t="inlineStr">
+        <is>
+          <t>CVE-2026-2581</t>
+        </is>
+      </c>
+      <c r="B1392" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C1392" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1392" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1392" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1393">
+      <c r="A1393" t="inlineStr">
+        <is>
+          <t>CVE-2025-61730</t>
+        </is>
+      </c>
+      <c r="B1393" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C1393" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1393" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1393" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1394">
+      <c r="A1394" t="inlineStr">
+        <is>
+          <t>CVE-2025-61729</t>
+        </is>
+      </c>
+      <c r="B1394" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C1394" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1394" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1394" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1395">
+      <c r="A1395" t="inlineStr">
+        <is>
+          <t>CVE-2025-61727</t>
+        </is>
+      </c>
+      <c r="B1395" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C1395" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1395" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1395" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1396">
+      <c r="A1396" t="inlineStr">
+        <is>
+          <t>CVE-2025-61726</t>
+        </is>
+      </c>
+      <c r="B1396" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C1396" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1396" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1396" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1397">
+      <c r="A1397" t="inlineStr">
+        <is>
+          <t>CVE-2025-61725</t>
+        </is>
+      </c>
+      <c r="B1397" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C1397" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1397" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1397" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1398">
+      <c r="A1398" t="inlineStr">
+        <is>
+          <t>CVE-2025-61723</t>
+        </is>
+      </c>
+      <c r="B1398" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C1398" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1398" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1398" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1399">
+      <c r="A1399" t="inlineStr">
+        <is>
+          <t>CVE-2025-58189</t>
+        </is>
+      </c>
+      <c r="B1399" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C1399" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1399" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1399" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1400">
+      <c r="A1400" t="inlineStr">
+        <is>
+          <t>CVE-2025-58188</t>
+        </is>
+      </c>
+      <c r="B1400" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C1400" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1400" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1400" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1401">
+      <c r="A1401" t="inlineStr">
+        <is>
+          <t>CVE-2025-58187</t>
+        </is>
+      </c>
+      <c r="B1401" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C1401" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1401" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1401" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1402">
+      <c r="A1402" t="inlineStr">
+        <is>
+          <t>CVE-2025-58185</t>
+        </is>
+      </c>
+      <c r="B1402" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C1402" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1402" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1402" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1403">
+      <c r="A1403" t="inlineStr">
+        <is>
+          <t>CVE-2025-47912</t>
+        </is>
+      </c>
+      <c r="B1403" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C1403" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1403" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1403" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1404">
+      <c r="A1404" t="inlineStr">
+        <is>
+          <t>CVE-2025-47907</t>
+        </is>
+      </c>
+      <c r="B1404" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C1404" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1404" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1404" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1405">
+      <c r="A1405" t="inlineStr">
+        <is>
+          <t>CVE-2023-45288</t>
+        </is>
+      </c>
+      <c r="B1405" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C1405" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1405" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1405" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1406">
+      <c r="A1406" t="inlineStr">
+        <is>
+          <t>CVE-2026-34282</t>
+        </is>
+      </c>
+      <c r="B1406" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C1406" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1406" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1406" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1407">
+      <c r="A1407" t="inlineStr">
+        <is>
+          <t>CVE-2026-34268</t>
+        </is>
+      </c>
+      <c r="B1407" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C1407" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1407" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1407" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1408">
+      <c r="A1408" t="inlineStr">
+        <is>
+          <t>CVE-2026-40372</t>
+        </is>
+      </c>
+      <c r="B1408" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C1408" t="inlineStr">
+        <is>
+          <t>vulnerability Microsoft ASP.NET: CVE-2026-40372: ASP.NET Core Elevation of Privilege Vulnerability Published: 2026-04-21 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1408" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1408" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/microsoft-asp_net_core-cve-2026-40372/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1409">
+      <c r="A1409" t="inlineStr">
+        <is>
+          <t>CVE-2026-49839</t>
+        </is>
+      </c>
+      <c r="B1409" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C1409" t="inlineStr">
+        <is>
+          <t>vulnerability Amazon Linux 2023: CVE-2026-49839: Important priority package update for jq Published: 2026-06-25 | Severity: 6 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1409" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1409" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/amazon_linux_2023-cve-2026-49839/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1410">
+      <c r="A1410" t="inlineStr">
+        <is>
+          <t>CVE-2026-7473</t>
+        </is>
+      </c>
+      <c r="B1410" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="C1410" t="inlineStr">
+        <is>
+          <t>vulnerability Arista: EOS: CVE-2026-7473: security-advisory-0137 Published: 2026-05-05 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1410" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1410" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/arista-eos-cve-2026-7473/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1411">
+      <c r="A1411" t="inlineStr">
+        <is>
+          <t>CVE-2026-23303</t>
+        </is>
+      </c>
+      <c r="B1411" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C1411" t="inlineStr">
+        <is>
+          <t>vulnerability F5: CVE-2026-23303: K000161897: Linux kernel vulnerability CVE-2026-23303 Published: 2026-06-25 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1411" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1411" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/f5-big-ip-cve-2026-23303/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1412">
+      <c r="A1412" t="inlineStr">
+        <is>
+          <t>CVE-2026-2581</t>
+        </is>
+      </c>
+      <c r="B1412" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="C1412" t="inlineStr">
+        <is>
+          <t>vulnerability SUSE: CVE-2026-2581: SUSE Linux Security Advisory Published: 2026-04-11 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1412" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1412" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/suse-cve-2026-2581/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1413">
+      <c r="A1413" t="inlineStr">
+        <is>
+          <t>CVE-2025-61730</t>
+        </is>
+      </c>
+      <c r="B1413" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C1413" t="inlineStr">
+        <is>
+          <t>vulnerability Dell iDRAC: CVE-2025-61730: DSA-2026-270: Security Update for Dell iDRAC10 Vulnerabilities Published: 2026-06-25 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1413" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1413" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/dell-idrac-cve-2025-61730/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1414">
+      <c r="A1414" t="inlineStr">
+        <is>
+          <t>CVE-2025-61729</t>
+        </is>
+      </c>
+      <c r="B1414" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C1414" t="inlineStr">
+        <is>
+          <t>vulnerability Dell iDRAC: CVE-2025-61729: DSA-2026-270: Security Update for Dell iDRAC10 Vulnerabilities Published: 2026-06-25 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1414" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1414" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/dell-idrac-cve-2025-61729/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1415">
+      <c r="A1415" t="inlineStr">
+        <is>
+          <t>CVE-2025-61727</t>
+        </is>
+      </c>
+      <c r="B1415" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C1415" t="inlineStr">
+        <is>
+          <t>vulnerability Dell iDRAC: CVE-2025-61727: DSA-2026-270: Security Update for Dell iDRAC10 Vulnerabilities Published: 2026-06-25 | Severity: 6 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1415" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1415" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/dell-idrac-cve-2025-61727/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1416">
+      <c r="A1416" t="inlineStr">
+        <is>
+          <t>CVE-2025-61726</t>
+        </is>
+      </c>
+      <c r="B1416" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C1416" t="inlineStr">
+        <is>
+          <t>vulnerability Dell iDRAC: CVE-2025-61726: DSA-2026-270: Security Update for Dell iDRAC10 Vulnerabilities Published: 2026-06-25 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1416" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1416" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/dell-idrac-cve-2025-61726/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1417">
+      <c r="A1417" t="inlineStr">
+        <is>
+          <t>CVE-2025-61725</t>
+        </is>
+      </c>
+      <c r="B1417" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C1417" t="inlineStr">
+        <is>
+          <t>vulnerability Dell iDRAC: CVE-2025-61725: DSA-2026-270: Security Update for Dell iDRAC10 Vulnerabilities Published: 2026-06-25 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1417" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1417" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/dell-idrac-cve-2025-61725/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1418">
+      <c r="A1418" t="inlineStr">
+        <is>
+          <t>CVE-2025-61723</t>
+        </is>
+      </c>
+      <c r="B1418" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C1418" t="inlineStr">
+        <is>
+          <t>vulnerability Dell iDRAC: CVE-2025-61723: DSA-2026-270: Security Update for Dell iDRAC10 Vulnerabilities Published: 2026-06-25 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1418" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1418" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/dell-idrac-cve-2025-61723/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1419">
+      <c r="A1419" t="inlineStr">
+        <is>
+          <t>CVE-2025-58189</t>
+        </is>
+      </c>
+      <c r="B1419" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C1419" t="inlineStr">
+        <is>
+          <t>vulnerability Dell iDRAC: CVE-2025-58189: DSA-2026-270: Security Update for Dell iDRAC10 Vulnerabilities Published: 2026-06-25 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1419" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1419" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/dell-idrac-cve-2025-58189/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1420">
+      <c r="A1420" t="inlineStr">
+        <is>
+          <t>CVE-2025-58188</t>
+        </is>
+      </c>
+      <c r="B1420" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C1420" t="inlineStr">
+        <is>
+          <t>vulnerability Dell iDRAC: CVE-2025-58188: DSA-2026-270: Security Update for Dell iDRAC10 Vulnerabilities Published: 2026-06-25 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1420" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1420" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/dell-idrac-cve-2025-58188/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1421">
+      <c r="A1421" t="inlineStr">
+        <is>
+          <t>CVE-2025-58187</t>
+        </is>
+      </c>
+      <c r="B1421" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C1421" t="inlineStr">
+        <is>
+          <t>vulnerability Dell iDRAC: CVE-2025-58187: DSA-2026-270: Security Update for Dell iDRAC10 Vulnerabilities Published: 2026-06-25 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1421" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1421" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/dell-idrac-cve-2025-58187/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1422">
+      <c r="A1422" t="inlineStr">
+        <is>
+          <t>CVE-2025-58185</t>
+        </is>
+      </c>
+      <c r="B1422" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C1422" t="inlineStr">
+        <is>
+          <t>vulnerability Dell iDRAC: CVE-2025-58185: DSA-2026-270: Security Update for Dell iDRAC10 Vulnerabilities Published: 2026-06-25 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1422" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1422" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/dell-idrac-cve-2025-58185/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1423">
+      <c r="A1423" t="inlineStr">
+        <is>
+          <t>CVE-2025-47912</t>
+        </is>
+      </c>
+      <c r="B1423" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C1423" t="inlineStr">
+        <is>
+          <t>vulnerability Dell iDRAC: CVE-2025-47912: DSA-2026-270: Security Update for Dell iDRAC10 Vulnerabilities Published: 2026-06-25 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1423" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1423" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/dell-idrac-cve-2025-47912/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1424">
+      <c r="A1424" t="inlineStr">
+        <is>
+          <t>CVE-2025-47907</t>
+        </is>
+      </c>
+      <c r="B1424" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C1424" t="inlineStr">
+        <is>
+          <t>vulnerability Dell iDRAC: CVE-2025-47907: DSA-2026-270: Security Update for Dell iDRAC10 Vulnerabilities Published: 2026-06-25 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1424" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1424" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/dell-idrac-cve-2025-47907/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1425">
+      <c r="A1425" t="inlineStr">
+        <is>
+          <t>CVE-2023-45288</t>
+        </is>
+      </c>
+      <c r="B1425" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C1425" t="inlineStr">
+        <is>
+          <t>vulnerability Dell iDRAC: CVE-2023-45288: DSA-2026-270: Security Update for Dell iDRAC10 Vulnerabilities Published: 2026-06-25 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1425" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1425" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/dell-idrac-cve-2023-45288/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1426">
+      <c r="A1426" t="inlineStr">
+        <is>
+          <t>CVE-2026-34282</t>
+        </is>
+      </c>
+      <c r="B1426" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C1426" t="inlineStr">
+        <is>
+          <t>vulnerability Eclipse Adoptium: CVE-2026-34282: Vulnerability with Networking component Published: 2026-04-21 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1426" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1426" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/eclipseadoptium-cve-2026-34282/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1427">
+      <c r="A1427" t="inlineStr">
+        <is>
+          <t>CVE-2026-34268</t>
+        </is>
+      </c>
+      <c r="B1427" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C1427" t="inlineStr">
+        <is>
+          <t>vulnerability Eclipse Adoptium: CVE-2026-34268: Vulnerability with Security component Published: 2026-04-21 | Severity: 2 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1427" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E1427" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/eclipseadoptium-cve-2026-34268/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rapid7_cves.xlsx
+++ b/rapid7_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1427"/>
+  <dimension ref="A1:E1467"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38945,6 +38945,1086 @@
         </is>
       </c>
     </row>
+    <row r="1428">
+      <c r="A1428" t="inlineStr">
+        <is>
+          <t>CVE-2026-13283</t>
+        </is>
+      </c>
+      <c r="B1428" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C1428" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1428" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1428" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1429">
+      <c r="A1429" t="inlineStr">
+        <is>
+          <t>CVE-2026-13282</t>
+        </is>
+      </c>
+      <c r="B1429" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C1429" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1429" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1429" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1430">
+      <c r="A1430" t="inlineStr">
+        <is>
+          <t>CVE-2026-13281</t>
+        </is>
+      </c>
+      <c r="B1430" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C1430" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1430" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1430" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1431">
+      <c r="A1431" t="inlineStr">
+        <is>
+          <t>CVE-2026-13038</t>
+        </is>
+      </c>
+      <c r="B1431" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C1431" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1431" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1431" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1432">
+      <c r="A1432" t="inlineStr">
+        <is>
+          <t>CVE-2026-13037</t>
+        </is>
+      </c>
+      <c r="B1432" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C1432" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1432" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1432" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1433">
+      <c r="A1433" t="inlineStr">
+        <is>
+          <t>CVE-2026-13036</t>
+        </is>
+      </c>
+      <c r="B1433" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C1433" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1433" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1433" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1434">
+      <c r="A1434" t="inlineStr">
+        <is>
+          <t>CVE-2026-13035</t>
+        </is>
+      </c>
+      <c r="B1434" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C1434" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1434" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1434" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1435">
+      <c r="A1435" t="inlineStr">
+        <is>
+          <t>CVE-2026-13034</t>
+        </is>
+      </c>
+      <c r="B1435" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C1435" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1435" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1435" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1436">
+      <c r="A1436" t="inlineStr">
+        <is>
+          <t>CVE-2026-13033</t>
+        </is>
+      </c>
+      <c r="B1436" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C1436" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1436" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1436" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1437">
+      <c r="A1437" t="inlineStr">
+        <is>
+          <t>CVE-2026-13032</t>
+        </is>
+      </c>
+      <c r="B1437" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C1437" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1437" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1437" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1438">
+      <c r="A1438" t="inlineStr">
+        <is>
+          <t>CVE-2026-13031</t>
+        </is>
+      </c>
+      <c r="B1438" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C1438" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1438" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1438" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1439">
+      <c r="A1439" t="inlineStr">
+        <is>
+          <t>CVE-2026-13030</t>
+        </is>
+      </c>
+      <c r="B1439" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C1439" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1439" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1439" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1440">
+      <c r="A1440" t="inlineStr">
+        <is>
+          <t>CVE-2026-13029</t>
+        </is>
+      </c>
+      <c r="B1440" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C1440" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1440" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1440" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1441">
+      <c r="A1441" t="inlineStr">
+        <is>
+          <t>CVE-2026-13028</t>
+        </is>
+      </c>
+      <c r="B1441" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C1441" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1441" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1441" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1442">
+      <c r="A1442" t="inlineStr">
+        <is>
+          <t>CVE-2026-13027</t>
+        </is>
+      </c>
+      <c r="B1442" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C1442" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1442" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1442" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1443">
+      <c r="A1443" t="inlineStr">
+        <is>
+          <t>CVE-2026-13026</t>
+        </is>
+      </c>
+      <c r="B1443" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C1443" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1443" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1443" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1444">
+      <c r="A1444" t="inlineStr">
+        <is>
+          <t>CVE-2026-13025</t>
+        </is>
+      </c>
+      <c r="B1444" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C1444" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1444" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1444" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1445">
+      <c r="A1445" t="inlineStr">
+        <is>
+          <t>CVE-2026-13024</t>
+        </is>
+      </c>
+      <c r="B1445" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C1445" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1445" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1445" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1446">
+      <c r="A1446" t="inlineStr">
+        <is>
+          <t>CVE-2026-13023</t>
+        </is>
+      </c>
+      <c r="B1446" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C1446" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1446" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1446" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1447">
+      <c r="A1447" t="inlineStr">
+        <is>
+          <t>CVE-2026-13022</t>
+        </is>
+      </c>
+      <c r="B1447" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C1447" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1447" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1447" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1448">
+      <c r="A1448" t="inlineStr">
+        <is>
+          <t>CVE-2026-13283</t>
+        </is>
+      </c>
+      <c r="B1448" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C1448" t="inlineStr">
+        <is>
+          <t>vulnerability Google Chrome Vulnerability: CVE-2026-13283 Use after free in AdFilter Published: 2026-06-28 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1448" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1448" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/google-chrome-cve-2026-13283/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1449">
+      <c r="A1449" t="inlineStr">
+        <is>
+          <t>CVE-2026-13282</t>
+        </is>
+      </c>
+      <c r="B1449" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C1449" t="inlineStr">
+        <is>
+          <t>vulnerability Google Chrome Vulnerability: CVE-2026-13282 Use after free in Payments Published: 2026-06-28 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1449" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1449" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/google-chrome-cve-2026-13282/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1450">
+      <c r="A1450" t="inlineStr">
+        <is>
+          <t>CVE-2026-13281</t>
+        </is>
+      </c>
+      <c r="B1450" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C1450" t="inlineStr">
+        <is>
+          <t>vulnerability Google Chrome Vulnerability: CVE-2026-13281 Integer overflow in Mojo Published: 2026-06-28 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1450" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1450" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/google-chrome-cve-2026-13281/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1451">
+      <c r="A1451" t="inlineStr">
+        <is>
+          <t>CVE-2026-13038</t>
+        </is>
+      </c>
+      <c r="B1451" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C1451" t="inlineStr">
+        <is>
+          <t>vulnerability Google Chrome Vulnerability: CVE-2026-13038 Use after free in Autofill Published: 2026-06-28 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1451" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1451" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/google-chrome-cve-2026-13038/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1452">
+      <c r="A1452" t="inlineStr">
+        <is>
+          <t>CVE-2026-13037</t>
+        </is>
+      </c>
+      <c r="B1452" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C1452" t="inlineStr">
+        <is>
+          <t>vulnerability Google Chrome Vulnerability: CVE-2026-13037 Use after free in WebView Published: 2026-06-28 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1452" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1452" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/google-chrome-cve-2026-13037/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1453">
+      <c r="A1453" t="inlineStr">
+        <is>
+          <t>CVE-2026-13036</t>
+        </is>
+      </c>
+      <c r="B1453" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C1453" t="inlineStr">
+        <is>
+          <t>vulnerability Google Chrome Vulnerability: CVE-2026-13036 Use after free in Blink Published: 2026-06-28 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1453" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1453" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/google-chrome-cve-2026-13036/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1454">
+      <c r="A1454" t="inlineStr">
+        <is>
+          <t>CVE-2026-13035</t>
+        </is>
+      </c>
+      <c r="B1454" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C1454" t="inlineStr">
+        <is>
+          <t>vulnerability Google Chrome Vulnerability: CVE-2026-13035 Use after free in Bluetooth Published: 2026-06-28 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1454" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1454" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/google-chrome-cve-2026-13035/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1455">
+      <c r="A1455" t="inlineStr">
+        <is>
+          <t>CVE-2026-13034</t>
+        </is>
+      </c>
+      <c r="B1455" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C1455" t="inlineStr">
+        <is>
+          <t>vulnerability Google Chrome Vulnerability: CVE-2026-13034 Inappropriate implementation in Passwords Published: 2026-06-28 | Severity: 4 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1455" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1455" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/google-chrome-cve-2026-13034/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1456">
+      <c r="A1456" t="inlineStr">
+        <is>
+          <t>CVE-2026-13033</t>
+        </is>
+      </c>
+      <c r="B1456" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C1456" t="inlineStr">
+        <is>
+          <t>vulnerability Google Chrome Vulnerability: CVE-2026-13033 Out of bounds read in Blink&gt;InterestGroups Published: 2026-06-28 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1456" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1456" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/google-chrome-cve-2026-13033/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1457">
+      <c r="A1457" t="inlineStr">
+        <is>
+          <t>CVE-2026-13032</t>
+        </is>
+      </c>
+      <c r="B1457" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C1457" t="inlineStr">
+        <is>
+          <t>vulnerability Google Chrome Vulnerability: CVE-2026-13032 Use after free in WebGL Published: 2026-06-28 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1457" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1457" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/google-chrome-cve-2026-13032/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1458">
+      <c r="A1458" t="inlineStr">
+        <is>
+          <t>CVE-2026-13031</t>
+        </is>
+      </c>
+      <c r="B1458" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C1458" t="inlineStr">
+        <is>
+          <t>vulnerability Google Chrome Vulnerability: CVE-2026-13031 Use after free in Blink Published: 2026-06-28 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1458" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1458" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/google-chrome-cve-2026-13031/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1459">
+      <c r="A1459" t="inlineStr">
+        <is>
+          <t>CVE-2026-13030</t>
+        </is>
+      </c>
+      <c r="B1459" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C1459" t="inlineStr">
+        <is>
+          <t>vulnerability Google Chrome Vulnerability: CVE-2026-13030 Uninitialized Use in GPU Published: 2026-06-28 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1459" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1459" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/google-chrome-cve-2026-13030/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1460">
+      <c r="A1460" t="inlineStr">
+        <is>
+          <t>CVE-2026-13029</t>
+        </is>
+      </c>
+      <c r="B1460" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C1460" t="inlineStr">
+        <is>
+          <t>vulnerability Google Chrome Vulnerability: CVE-2026-13029 Use after free in Web Authentication Published: 2026-06-28 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1460" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1460" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/google-chrome-cve-2026-13029/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1461">
+      <c r="A1461" t="inlineStr">
+        <is>
+          <t>CVE-2026-13028</t>
+        </is>
+      </c>
+      <c r="B1461" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C1461" t="inlineStr">
+        <is>
+          <t>vulnerability Google Chrome Vulnerability: CVE-2026-13028 Use after free in WebGL Published: 2026-06-28 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1461" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1461" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/google-chrome-cve-2026-13028/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1462">
+      <c r="A1462" t="inlineStr">
+        <is>
+          <t>CVE-2026-13027</t>
+        </is>
+      </c>
+      <c r="B1462" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C1462" t="inlineStr">
+        <is>
+          <t>vulnerability Google Chrome Vulnerability: CVE-2026-13027 Use after free in FileSystem Published: 2026-06-28 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1462" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1462" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/google-chrome-cve-2026-13027/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1463">
+      <c r="A1463" t="inlineStr">
+        <is>
+          <t>CVE-2026-13026</t>
+        </is>
+      </c>
+      <c r="B1463" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C1463" t="inlineStr">
+        <is>
+          <t>vulnerability Google Chrome Vulnerability: CVE-2026-13026 Use after free in Digital Credentials Published: 2026-06-28 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1463" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1463" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/google-chrome-cve-2026-13026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1464">
+      <c r="A1464" t="inlineStr">
+        <is>
+          <t>CVE-2026-13025</t>
+        </is>
+      </c>
+      <c r="B1464" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C1464" t="inlineStr">
+        <is>
+          <t>vulnerability Google Chrome Vulnerability: CVE-2026-13025 Insufficient validation of untrusted input in DevTools Published: 2026-06-28 | Severity: 8 E</t>
+        </is>
+      </c>
+      <c r="D1464" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1464" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/google-chrome-cve-2026-13025/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1465">
+      <c r="A1465" t="inlineStr">
+        <is>
+          <t>CVE-2026-13024</t>
+        </is>
+      </c>
+      <c r="B1465" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C1465" t="inlineStr">
+        <is>
+          <t>vulnerability Google Chrome Vulnerability: CVE-2026-13024 Insufficient validation of untrusted input in Navigation Published: 2026-06-28 | Severity: 4</t>
+        </is>
+      </c>
+      <c r="D1465" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1465" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/google-chrome-cve-2026-13024/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1466">
+      <c r="A1466" t="inlineStr">
+        <is>
+          <t>CVE-2026-13023</t>
+        </is>
+      </c>
+      <c r="B1466" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C1466" t="inlineStr">
+        <is>
+          <t>vulnerability Google Chrome Vulnerability: CVE-2026-13023 Uninitialized Use in GPU Published: 2026-06-28 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1466" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1466" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/google-chrome-cve-2026-13023/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1467">
+      <c r="A1467" t="inlineStr">
+        <is>
+          <t>CVE-2026-13022</t>
+        </is>
+      </c>
+      <c r="B1467" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C1467" t="inlineStr">
+        <is>
+          <t>vulnerability Google Chrome Vulnerability: CVE-2026-13022 Inappropriate implementation in Autofill Published: 2026-06-28 | Severity: 10 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1467" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1467" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/google-chrome-cve-2026-13022/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rapid7_cves.xlsx
+++ b/rapid7_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1467"/>
+  <dimension ref="A1:E1505"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40025,6 +40025,1032 @@
         </is>
       </c>
     </row>
+    <row r="1468">
+      <c r="A1468" t="inlineStr">
+        <is>
+          <t>CVE-2026-49980</t>
+        </is>
+      </c>
+      <c r="B1468" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C1468" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1468" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1468" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1469">
+      <c r="A1469" t="inlineStr">
+        <is>
+          <t>CVE-2023-53320</t>
+        </is>
+      </c>
+      <c r="B1469" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C1469" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1469" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1469" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1470">
+      <c r="A1470" t="inlineStr">
+        <is>
+          <t>CVE-2023-53037</t>
+        </is>
+      </c>
+      <c r="B1470" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C1470" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1470" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1470" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1471">
+      <c r="A1471" t="inlineStr">
+        <is>
+          <t>CVE-2026-5950</t>
+        </is>
+      </c>
+      <c r="B1471" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C1471" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1471" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1471" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1472">
+      <c r="A1472" t="inlineStr">
+        <is>
+          <t>CVE-2026-5946</t>
+        </is>
+      </c>
+      <c r="B1472" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C1472" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1472" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1472" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1473">
+      <c r="A1473" t="inlineStr">
+        <is>
+          <t>CVE-2026-3592</t>
+        </is>
+      </c>
+      <c r="B1473" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C1473" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1473" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1473" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1474">
+      <c r="A1474" t="inlineStr">
+        <is>
+          <t>CVE-2026-1519</t>
+        </is>
+      </c>
+      <c r="B1474" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C1474" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1474" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1474" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1475">
+      <c r="A1475" t="inlineStr">
+        <is>
+          <t>CVE-2025-13878</t>
+        </is>
+      </c>
+      <c r="B1475" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C1475" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1475" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1475" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1476">
+      <c r="A1476" t="inlineStr">
+        <is>
+          <t>CVE-2026-8461</t>
+        </is>
+      </c>
+      <c r="B1476" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C1476" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1476" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1476" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1477">
+      <c r="A1477" t="inlineStr">
+        <is>
+          <t>CVE-2026-8330</t>
+        </is>
+      </c>
+      <c r="B1477" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C1477" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1477" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1477" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1478">
+      <c r="A1478" t="inlineStr">
+        <is>
+          <t>CVE-2026-5952</t>
+        </is>
+      </c>
+      <c r="B1478" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C1478" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1478" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1478" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1479">
+      <c r="A1479" t="inlineStr">
+        <is>
+          <t>CVE-2026-5796</t>
+        </is>
+      </c>
+      <c r="B1479" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C1479" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1479" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1479" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1480">
+      <c r="A1480" t="inlineStr">
+        <is>
+          <t>CVE-2026-56412</t>
+        </is>
+      </c>
+      <c r="B1480" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C1480" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1480" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1480" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1481">
+      <c r="A1481" t="inlineStr">
+        <is>
+          <t>CVE-2026-56411</t>
+        </is>
+      </c>
+      <c r="B1481" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C1481" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1481" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1481" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1482">
+      <c r="A1482" t="inlineStr">
+        <is>
+          <t>CVE-2026-56410</t>
+        </is>
+      </c>
+      <c r="B1482" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C1482" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1482" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1482" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1483">
+      <c r="A1483" t="inlineStr">
+        <is>
+          <t>CVE-2026-56409</t>
+        </is>
+      </c>
+      <c r="B1483" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C1483" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1483" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1483" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1484">
+      <c r="A1484" t="inlineStr">
+        <is>
+          <t>CVE-2026-56408</t>
+        </is>
+      </c>
+      <c r="B1484" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C1484" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1484" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1484" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1485">
+      <c r="A1485" t="inlineStr">
+        <is>
+          <t>CVE-2026-56407</t>
+        </is>
+      </c>
+      <c r="B1485" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C1485" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1485" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1485" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1486">
+      <c r="A1486" t="inlineStr">
+        <is>
+          <t>CVE-2026-56406</t>
+        </is>
+      </c>
+      <c r="B1486" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C1486" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1486" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1486" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1487">
+      <c r="A1487" t="inlineStr">
+        <is>
+          <t>CVE-2026-49980</t>
+        </is>
+      </c>
+      <c r="B1487" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C1487" t="inlineStr">
+        <is>
+          <t>vulnerability Amazon Linux 2023: CVE-2026-49980: Critical priority package update for rclone Published: 2026-06-24 | Severity: 10 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1487" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1487" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/amazon_linux_2023-cve-2026-49980/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1488">
+      <c r="A1488" t="inlineStr">
+        <is>
+          <t>CVE-2023-53320</t>
+        </is>
+      </c>
+      <c r="B1488" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="C1488" t="inlineStr">
+        <is>
+          <t>vulnerability Amazon Linux 2023: CVE-2023-53320: Important priority package update for kernel Published: 2025-09-16 | Severity: 6 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1488" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1488" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/amazon_linux_2023-cve-2023-53320/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1489">
+      <c r="A1489" t="inlineStr">
+        <is>
+          <t>CVE-2023-53037</t>
+        </is>
+      </c>
+      <c r="B1489" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="C1489" t="inlineStr">
+        <is>
+          <t>vulnerability Amazon Linux 2023: CVE-2023-53037: Important priority package update for kernel Published: 2025-05-02 | Severity: 4 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1489" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1489" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/amazon_linux_2023-cve-2023-53037/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1490">
+      <c r="A1490" t="inlineStr">
+        <is>
+          <t>CVE-2026-5950</t>
+        </is>
+      </c>
+      <c r="B1490" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C1490" t="inlineStr">
+        <is>
+          <t>vulnerability IBM AIX: bind_advisory30 (CVE-2026-5950): Vulnerability in bind affects AIX Published: 2026-06-29 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1490" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1490" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ibm-aix-cve-2026-5950/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1491">
+      <c r="A1491" t="inlineStr">
+        <is>
+          <t>CVE-2026-5946</t>
+        </is>
+      </c>
+      <c r="B1491" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C1491" t="inlineStr">
+        <is>
+          <t>vulnerability IBM AIX: bind_advisory30 (CVE-2026-5946): Vulnerability in bind affects AIX Published: 2026-06-29 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1491" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1491" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ibm-aix-cve-2026-5946/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1492">
+      <c r="A1492" t="inlineStr">
+        <is>
+          <t>CVE-2026-3592</t>
+        </is>
+      </c>
+      <c r="B1492" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C1492" t="inlineStr">
+        <is>
+          <t>vulnerability IBM AIX: bind_advisory30 (CVE-2026-3592): Vulnerability in bind affects AIX Published: 2026-06-29 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1492" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1492" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ibm-aix-cve-2026-3592/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1493">
+      <c r="A1493" t="inlineStr">
+        <is>
+          <t>CVE-2026-1519</t>
+        </is>
+      </c>
+      <c r="B1493" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C1493" t="inlineStr">
+        <is>
+          <t>vulnerability IBM AIX: bind_advisory30 (CVE-2026-1519): Vulnerability in bind affects AIX Published: 2026-06-29 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1493" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1493" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ibm-aix-cve-2026-1519/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1494">
+      <c r="A1494" t="inlineStr">
+        <is>
+          <t>CVE-2025-13878</t>
+        </is>
+      </c>
+      <c r="B1494" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C1494" t="inlineStr">
+        <is>
+          <t>vulnerability IBM AIX: bind_advisory30 (CVE-2025-13878): Vulnerability in bind affects AIX Published: 2026-06-29 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1494" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1494" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ibm-aix-cve-2025-13878/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1495">
+      <c r="A1495" t="inlineStr">
+        <is>
+          <t>CVE-2026-8461</t>
+        </is>
+      </c>
+      <c r="B1495" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C1495" t="inlineStr">
+        <is>
+          <t>vulnerability FreeBSD: VID-ba8d239f-709f-11f1-a30e-28d2443e6cfa (CVE-2026-8461): ffmpeg -- Out-of-bounds write Published: 2026-06-25 | Severity: 9 EXP</t>
+        </is>
+      </c>
+      <c r="D1495" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1495" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/freebsd-cve-2026-8461/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1496">
+      <c r="A1496" t="inlineStr">
+        <is>
+          <t>CVE-2026-8330</t>
+        </is>
+      </c>
+      <c r="B1496" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C1496" t="inlineStr">
+        <is>
+          <t>vulnerability FreeBSD: VID-ee1e7aef-7117-11f1-873f-2cf05da270f3 (CVE-2026-8330): Gitlab -- Vulnerabilities Published: 2026-06-26 | Severity: 4 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1496" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1496" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/freebsd-cve-2026-8330/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1497">
+      <c r="A1497" t="inlineStr">
+        <is>
+          <t>CVE-2026-5952</t>
+        </is>
+      </c>
+      <c r="B1497" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C1497" t="inlineStr">
+        <is>
+          <t>vulnerability FreeBSD: VID-ee1e7aef-7117-11f1-873f-2cf05da270f3 (CVE-2026-5952): Gitlab -- Vulnerabilities Published: 2026-06-26 | Severity: 4 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1497" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1497" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/freebsd-cve-2026-5952/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1498">
+      <c r="A1498" t="inlineStr">
+        <is>
+          <t>CVE-2026-5796</t>
+        </is>
+      </c>
+      <c r="B1498" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C1498" t="inlineStr">
+        <is>
+          <t>vulnerability FreeBSD: VID-ee1e7aef-7117-11f1-873f-2cf05da270f3 (CVE-2026-5796): Gitlab -- Vulnerabilities Published: 2026-06-26 | Severity: 4 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1498" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1498" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/freebsd-cve-2026-5796/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1499">
+      <c r="A1499" t="inlineStr">
+        <is>
+          <t>CVE-2026-56412</t>
+        </is>
+      </c>
+      <c r="B1499" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C1499" t="inlineStr">
+        <is>
+          <t>vulnerability FreeBSD: VID-d06b1fa2-731f-11f1-a0d2-589cfc10a551 (CVE-2026-56412): Multiple vulnerability found in Expat Published: 2026-06-28 | Severi</t>
+        </is>
+      </c>
+      <c r="D1499" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1499" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/freebsd-cve-2026-56412/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1500">
+      <c r="A1500" t="inlineStr">
+        <is>
+          <t>CVE-2026-56411</t>
+        </is>
+      </c>
+      <c r="B1500" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C1500" t="inlineStr">
+        <is>
+          <t>vulnerability FreeBSD: VID-d06b1fa2-731f-11f1-a0d2-589cfc10a551 (CVE-2026-56411): Multiple vulnerability found in Expat Published: 2026-06-28 | Severi</t>
+        </is>
+      </c>
+      <c r="D1500" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1500" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/freebsd-cve-2026-56411/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1501">
+      <c r="A1501" t="inlineStr">
+        <is>
+          <t>CVE-2026-56410</t>
+        </is>
+      </c>
+      <c r="B1501" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C1501" t="inlineStr">
+        <is>
+          <t>vulnerability FreeBSD: VID-d06b1fa2-731f-11f1-a0d2-589cfc10a551 (CVE-2026-56410): Multiple vulnerability found in Expat Published: 2026-06-28 | Severi</t>
+        </is>
+      </c>
+      <c r="D1501" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1501" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/freebsd-cve-2026-56410/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1502">
+      <c r="A1502" t="inlineStr">
+        <is>
+          <t>CVE-2026-56409</t>
+        </is>
+      </c>
+      <c r="B1502" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C1502" t="inlineStr">
+        <is>
+          <t>vulnerability FreeBSD: VID-d06b1fa2-731f-11f1-a0d2-589cfc10a551 (CVE-2026-56409): Multiple vulnerability found in Expat Published: 2026-06-28 | Severi</t>
+        </is>
+      </c>
+      <c r="D1502" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1502" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/freebsd-cve-2026-56409/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1503">
+      <c r="A1503" t="inlineStr">
+        <is>
+          <t>CVE-2026-56408</t>
+        </is>
+      </c>
+      <c r="B1503" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C1503" t="inlineStr">
+        <is>
+          <t>vulnerability FreeBSD: VID-d06b1fa2-731f-11f1-a0d2-589cfc10a551 (CVE-2026-56408): Multiple vulnerability found in Expat Published: 2026-06-28 | Severi</t>
+        </is>
+      </c>
+      <c r="D1503" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1503" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/freebsd-cve-2026-56408/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1504">
+      <c r="A1504" t="inlineStr">
+        <is>
+          <t>CVE-2026-56407</t>
+        </is>
+      </c>
+      <c r="B1504" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C1504" t="inlineStr">
+        <is>
+          <t>vulnerability FreeBSD: VID-d06b1fa2-731f-11f1-a0d2-589cfc10a551 (CVE-2026-56407): Multiple vulnerability found in Expat Published: 2026-06-28 | Severi</t>
+        </is>
+      </c>
+      <c r="D1504" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1504" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/freebsd-cve-2026-56407/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1505">
+      <c r="A1505" t="inlineStr">
+        <is>
+          <t>CVE-2026-56406</t>
+        </is>
+      </c>
+      <c r="B1505" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C1505" t="inlineStr">
+        <is>
+          <t>vulnerability FreeBSD: VID-d06b1fa2-731f-11f1-a0d2-589cfc10a551 (CVE-2026-56406): Multiple vulnerability found in Expat Published: 2026-06-28 | Severi</t>
+        </is>
+      </c>
+      <c r="D1505" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1505" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/freebsd-cve-2026-56406/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rapid7_cves.xlsx
+++ b/rapid7_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1505"/>
+  <dimension ref="A1:E1523"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41051,6 +41051,492 @@
         </is>
       </c>
     </row>
+    <row r="1506">
+      <c r="A1506" t="inlineStr">
+        <is>
+          <t>CVE-2026-49980</t>
+        </is>
+      </c>
+      <c r="B1506" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="C1506" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1506" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E1506" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1507">
+      <c r="A1507" t="inlineStr">
+        <is>
+          <t>CVE-2023-53320</t>
+        </is>
+      </c>
+      <c r="B1507" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="C1507" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1507" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E1507" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1508">
+      <c r="A1508" t="inlineStr">
+        <is>
+          <t>CVE-2023-53037</t>
+        </is>
+      </c>
+      <c r="B1508" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="C1508" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1508" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E1508" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1509">
+      <c r="A1509" t="inlineStr">
+        <is>
+          <t>CVE-2026-5950</t>
+        </is>
+      </c>
+      <c r="B1509" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="C1509" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1509" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E1509" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1510">
+      <c r="A1510" t="inlineStr">
+        <is>
+          <t>CVE-2026-5946</t>
+        </is>
+      </c>
+      <c r="B1510" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="C1510" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1510" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E1510" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1511">
+      <c r="A1511" t="inlineStr">
+        <is>
+          <t>CVE-2026-3592</t>
+        </is>
+      </c>
+      <c r="B1511" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="C1511" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1511" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E1511" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1512">
+      <c r="A1512" t="inlineStr">
+        <is>
+          <t>CVE-2026-1519</t>
+        </is>
+      </c>
+      <c r="B1512" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="C1512" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1512" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E1512" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1513">
+      <c r="A1513" t="inlineStr">
+        <is>
+          <t>CVE-2025-13878</t>
+        </is>
+      </c>
+      <c r="B1513" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="C1513" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1513" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E1513" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1514">
+      <c r="A1514" t="inlineStr">
+        <is>
+          <t>CVE-2026-8461</t>
+        </is>
+      </c>
+      <c r="B1514" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="C1514" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1514" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E1514" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1515">
+      <c r="A1515" t="inlineStr">
+        <is>
+          <t>CVE-2026-8330</t>
+        </is>
+      </c>
+      <c r="B1515" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="C1515" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1515" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E1515" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1516">
+      <c r="A1516" t="inlineStr">
+        <is>
+          <t>CVE-2026-5952</t>
+        </is>
+      </c>
+      <c r="B1516" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="C1516" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1516" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E1516" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1517">
+      <c r="A1517" t="inlineStr">
+        <is>
+          <t>CVE-2026-5796</t>
+        </is>
+      </c>
+      <c r="B1517" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="C1517" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1517" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E1517" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1518">
+      <c r="A1518" t="inlineStr">
+        <is>
+          <t>CVE-2026-56412</t>
+        </is>
+      </c>
+      <c r="B1518" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="C1518" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1518" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E1518" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1519">
+      <c r="A1519" t="inlineStr">
+        <is>
+          <t>CVE-2026-56411</t>
+        </is>
+      </c>
+      <c r="B1519" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="C1519" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1519" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E1519" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1520">
+      <c r="A1520" t="inlineStr">
+        <is>
+          <t>CVE-2026-56410</t>
+        </is>
+      </c>
+      <c r="B1520" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="C1520" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1520" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E1520" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1521">
+      <c r="A1521" t="inlineStr">
+        <is>
+          <t>CVE-2026-56409</t>
+        </is>
+      </c>
+      <c r="B1521" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="C1521" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1521" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E1521" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1522">
+      <c r="A1522" t="inlineStr">
+        <is>
+          <t>CVE-2026-56408</t>
+        </is>
+      </c>
+      <c r="B1522" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="C1522" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1522" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E1522" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1523">
+      <c r="A1523" t="inlineStr">
+        <is>
+          <t>CVE-2026-56407</t>
+        </is>
+      </c>
+      <c r="B1523" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="C1523" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1523" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E1523" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rapid7_cves.xlsx
+++ b/rapid7_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1523"/>
+  <dimension ref="A1:E1567"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41537,6 +41537,1194 @@
         </is>
       </c>
     </row>
+    <row r="1524">
+      <c r="A1524" t="inlineStr">
+        <is>
+          <t>CVE-2026-57963</t>
+        </is>
+      </c>
+      <c r="B1524" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C1524" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1524" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1524" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1525">
+      <c r="A1525" t="inlineStr">
+        <is>
+          <t>CVE-2026-57962</t>
+        </is>
+      </c>
+      <c r="B1525" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C1525" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1525" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1525" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1526">
+      <c r="A1526" t="inlineStr">
+        <is>
+          <t>CVE-2025-59719</t>
+        </is>
+      </c>
+      <c r="B1526" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C1526" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1526" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1526" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1527">
+      <c r="A1527" t="inlineStr">
+        <is>
+          <t>CVE-2023-38546</t>
+        </is>
+      </c>
+      <c r="B1527" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C1527" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1527" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1527" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1528">
+      <c r="A1528" t="inlineStr">
+        <is>
+          <t>CVE-2023-38545</t>
+        </is>
+      </c>
+      <c r="B1528" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C1528" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1528" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1528" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1529">
+      <c r="A1529" t="inlineStr">
+        <is>
+          <t>CVE-2022-3786</t>
+        </is>
+      </c>
+      <c r="B1529" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C1529" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1529" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1529" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1530">
+      <c r="A1530" t="inlineStr">
+        <is>
+          <t>CVE-2022-3602</t>
+        </is>
+      </c>
+      <c r="B1530" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C1530" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1530" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1530" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1531">
+      <c r="A1531" t="inlineStr">
+        <is>
+          <t>CVE-2025-25254</t>
+        </is>
+      </c>
+      <c r="B1531" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C1531" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1531" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1531" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1532">
+      <c r="A1532" t="inlineStr">
+        <is>
+          <t>CVE-2024-55597</t>
+        </is>
+      </c>
+      <c r="B1532" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C1532" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1532" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1532" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1533">
+      <c r="A1533" t="inlineStr">
+        <is>
+          <t>CVE-2024-55594</t>
+        </is>
+      </c>
+      <c r="B1533" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C1533" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1533" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1533" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1534">
+      <c r="A1534" t="inlineStr">
+        <is>
+          <t>CVE-2024-55593</t>
+        </is>
+      </c>
+      <c r="B1534" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C1534" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1534" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1534" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1535">
+      <c r="A1535" t="inlineStr">
+        <is>
+          <t>CVE-2024-50569</t>
+        </is>
+      </c>
+      <c r="B1535" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C1535" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1535" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1535" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1536">
+      <c r="A1536" t="inlineStr">
+        <is>
+          <t>CVE-2024-50567</t>
+        </is>
+      </c>
+      <c r="B1536" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C1536" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1536" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1536" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1537">
+      <c r="A1537" t="inlineStr">
+        <is>
+          <t>CVE-2024-48885</t>
+        </is>
+      </c>
+      <c r="B1537" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C1537" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1537" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1537" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1538">
+      <c r="A1538" t="inlineStr">
+        <is>
+          <t>CVE-2024-48884</t>
+        </is>
+      </c>
+      <c r="B1538" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C1538" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1538" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1538" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1539">
+      <c r="A1539" t="inlineStr">
+        <is>
+          <t>CVE-2024-46671</t>
+        </is>
+      </c>
+      <c r="B1539" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C1539" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1539" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1539" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1540">
+      <c r="A1540" t="inlineStr">
+        <is>
+          <t>CVE-2024-36509</t>
+        </is>
+      </c>
+      <c r="B1540" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C1540" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1540" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1540" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1541">
+      <c r="A1541" t="inlineStr">
+        <is>
+          <t>CVE-2024-33509</t>
+        </is>
+      </c>
+      <c r="B1541" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C1541" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1541" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1541" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1542">
+      <c r="A1542" t="inlineStr">
+        <is>
+          <t>CVE-2024-23665</t>
+        </is>
+      </c>
+      <c r="B1542" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C1542" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1542" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1542" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1543">
+      <c r="A1543" t="inlineStr">
+        <is>
+          <t>CVE-2024-23107</t>
+        </is>
+      </c>
+      <c r="B1543" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C1543" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1543" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1543" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1544">
+      <c r="A1544" t="inlineStr">
+        <is>
+          <t>CVE-2024-21758</t>
+        </is>
+      </c>
+      <c r="B1544" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C1544" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1544" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1544" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1545">
+      <c r="A1545" t="inlineStr">
+        <is>
+          <t>CVE-2023-46713</t>
+        </is>
+      </c>
+      <c r="B1545" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C1545" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1545" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1545" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1546">
+      <c r="A1546" t="inlineStr">
+        <is>
+          <t>CVE-2026-57963</t>
+        </is>
+      </c>
+      <c r="B1546" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C1546" t="inlineStr">
+        <is>
+          <t>vulnerability MFSA2026-64 Thunderbird: Security Vulnerabilities fixed in Thunderbird 140.12.1 (CVE-2026-57963) Published: 2026-06-30 | Severity: 6 EXP</t>
+        </is>
+      </c>
+      <c r="D1546" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1546" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/mozilla-thunderbird-cve-2026-57963/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1547">
+      <c r="A1547" t="inlineStr">
+        <is>
+          <t>CVE-2026-57962</t>
+        </is>
+      </c>
+      <c r="B1547" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C1547" t="inlineStr">
+        <is>
+          <t>vulnerability MFSA2026-64 Thunderbird: Security Vulnerabilities fixed in Thunderbird 140.12.1 (CVE-2026-57962) Published: 2026-06-30 | Severity: 5 EXP</t>
+        </is>
+      </c>
+      <c r="D1547" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1547" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/mozilla-thunderbird-cve-2026-57962/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1548">
+      <c r="A1548" t="inlineStr">
+        <is>
+          <t>CVE-2025-59719</t>
+        </is>
+      </c>
+      <c r="B1548" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="C1548" t="inlineStr">
+        <is>
+          <t>vulnerability Fortinet FortiOS: CVE-2025-59719: Multiple Fortinet Products' FortiCloud SSO Login Authentication Bypass Published: 2025-12-09 | Severit</t>
+        </is>
+      </c>
+      <c r="D1548" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1548" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/fortios-cve-2025-59719/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1549">
+      <c r="A1549" t="inlineStr">
+        <is>
+          <t>CVE-2023-38546</t>
+        </is>
+      </c>
+      <c r="B1549" t="inlineStr">
+        <is>
+          <t>2023-11-14</t>
+        </is>
+      </c>
+      <c r="C1549" t="inlineStr">
+        <is>
+          <t>vulnerability Fortinet FortiOS: CVE-2023-38546: Curl and libcurl CVE-2023-38545 and CVE-2023-38546 vulnerabilities Published: 2023-11-14 | Severity: 6</t>
+        </is>
+      </c>
+      <c r="D1549" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1549" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/fortios-cve-2023-38546/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1550">
+      <c r="A1550" t="inlineStr">
+        <is>
+          <t>CVE-2023-38545</t>
+        </is>
+      </c>
+      <c r="B1550" t="inlineStr">
+        <is>
+          <t>2023-11-14</t>
+        </is>
+      </c>
+      <c r="C1550" t="inlineStr">
+        <is>
+          <t>vulnerability Fortinet FortiOS: CVE-2023-38546: Curl and libcurl CVE-2023-38545 and CVE-2023-38546 vulnerabilities Published: 2023-11-14 | Severity: 6</t>
+        </is>
+      </c>
+      <c r="D1550" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1550" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/fortios-cve-2023-38546/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1551">
+      <c r="A1551" t="inlineStr">
+        <is>
+          <t>CVE-2022-3786</t>
+        </is>
+      </c>
+      <c r="B1551" t="inlineStr">
+        <is>
+          <t>2022-10-28</t>
+        </is>
+      </c>
+      <c r="C1551" t="inlineStr">
+        <is>
+          <t>vulnerability Fortinet FortiOS: CVE-2022-3786: OpenSSL3 CVE-2022-3602 CVE-2022-3786 vulnerabilities Published: 2022-10-28 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1551" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1551" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/fortios-cve-2022-3786/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1552">
+      <c r="A1552" t="inlineStr">
+        <is>
+          <t>CVE-2022-3602</t>
+        </is>
+      </c>
+      <c r="B1552" t="inlineStr">
+        <is>
+          <t>2022-10-28</t>
+        </is>
+      </c>
+      <c r="C1552" t="inlineStr">
+        <is>
+          <t>vulnerability Fortinet FortiOS: CVE-2022-3786: OpenSSL3 CVE-2022-3602 CVE-2022-3786 vulnerabilities Published: 2022-10-28 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1552" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1552" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/fortios-cve-2022-3786/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1553">
+      <c r="A1553" t="inlineStr">
+        <is>
+          <t>CVE-2025-25254</t>
+        </is>
+      </c>
+      <c r="B1553" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="C1553" t="inlineStr">
+        <is>
+          <t>vulnerability Fortinet FortiWeb: CVE-2025-25254: Directory Traversal Published: 2025-04-08 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1553" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1553" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/fortinet-fortiweb-cve-2025-25254/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1554">
+      <c r="A1554" t="inlineStr">
+        <is>
+          <t>CVE-2024-55597</t>
+        </is>
+      </c>
+      <c r="B1554" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="C1554" t="inlineStr">
+        <is>
+          <t>vulnerability Fortinet FortiWeb: CVE-2024-55597: Directory Traversal Arbitrary File Write Vulnerability Published: 2025-03-11 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1554" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1554" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/fortinet-fortiweb-cve-2024-55597/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1555">
+      <c r="A1555" t="inlineStr">
+        <is>
+          <t>CVE-2024-55594</t>
+        </is>
+      </c>
+      <c r="B1555" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="C1555" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vulnerability Fortinet FortiWeb: CVE-2024-55594: Web application firewall rules bypass by using an empty filename Published: 2025-03-11 | Severity: 7 </t>
+        </is>
+      </c>
+      <c r="D1555" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1555" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/fortinet-fortiweb-cve-2024-55594/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1556">
+      <c r="A1556" t="inlineStr">
+        <is>
+          <t>CVE-2024-55593</t>
+        </is>
+      </c>
+      <c r="B1556" t="inlineStr">
+        <is>
+          <t>2025-01-14</t>
+        </is>
+      </c>
+      <c r="C1556" t="inlineStr">
+        <is>
+          <t>vulnerability Fortinet FortiWeb: CVE-2024-55593: SQL Injection in API EndPoints Published: 2025-01-14 | Severity: 3 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1556" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E1556" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/fortinet-fortiweb-cve-2024-55593/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1557">
+      <c r="A1557" t="inlineStr">
+        <is>
+          <t>CVE-2024-50569</t>
+        </is>
+      </c>
+      <c r="B1557" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="C1557" t="inlineStr">
+        <is>
+          <t>vulnerability Fortinet FortiWeb: CVE-2024-50569: OS Command Injections Published: 2025-02-11 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1557" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1557" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/fortinet-fortiweb-cve-2024-50569/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1558">
+      <c r="A1558" t="inlineStr">
+        <is>
+          <t>CVE-2024-50567</t>
+        </is>
+      </c>
+      <c r="B1558" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="C1558" t="inlineStr">
+        <is>
+          <t>vulnerability Fortinet FortiWeb: CVE-2024-50567: OS Command Injections Published: 2025-02-11 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1558" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1558" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/fortinet-fortiweb-cve-2024-50567/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1559">
+      <c r="A1559" t="inlineStr">
+        <is>
+          <t>CVE-2024-48885</t>
+        </is>
+      </c>
+      <c r="B1559" t="inlineStr">
+        <is>
+          <t>2025-01-14</t>
+        </is>
+      </c>
+      <c r="C1559" t="inlineStr">
+        <is>
+          <t>vulnerability Fortinet FortiWeb: CVE-2024-48885: Path traversal in csfd daemon Published: 2025-01-14 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1559" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1559" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/fortinet-fortiweb-cve-2024-48885/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1560">
+      <c r="A1560" t="inlineStr">
+        <is>
+          <t>CVE-2024-48884</t>
+        </is>
+      </c>
+      <c r="B1560" t="inlineStr">
+        <is>
+          <t>2025-01-14</t>
+        </is>
+      </c>
+      <c r="C1560" t="inlineStr">
+        <is>
+          <t>vulnerability Fortinet FortiWeb: CVE-2024-48884: Path traversal in csfd daemon Published: 2025-01-14 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1560" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1560" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/fortinet-fortiweb-cve-2024-48884/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1561">
+      <c r="A1561" t="inlineStr">
+        <is>
+          <t>CVE-2024-46671</t>
+        </is>
+      </c>
+      <c r="B1561" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="C1561" t="inlineStr">
+        <is>
+          <t>vulnerability Fortinet FortiWeb: CVE-2024-46671: Incorrect user management in widgets dashboard Published: 2025-04-08 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1561" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1561" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/fortinet-fortiweb-cve-2024-46671/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1562">
+      <c r="A1562" t="inlineStr">
+        <is>
+          <t>CVE-2024-36509</t>
+        </is>
+      </c>
+      <c r="B1562" t="inlineStr">
+        <is>
+          <t>2024-11-12</t>
+        </is>
+      </c>
+      <c r="C1562" t="inlineStr">
+        <is>
+          <t>vulnerability Fortinet FortiWeb: CVE-2024-36509: Exposure of password hashes to read-only admin Published: 2024-11-12 | Severity: 4 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1562" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1562" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/fortinet-fortiweb-cve-2024-36509/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1563">
+      <c r="A1563" t="inlineStr">
+        <is>
+          <t>CVE-2024-33509</t>
+        </is>
+      </c>
+      <c r="B1563" t="inlineStr">
+        <is>
+          <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="C1563" t="inlineStr">
+        <is>
+          <t>vulnerability Fortinet FortiWeb: CVE-2024-33509: [FortiWeb] Lack of client-side certificate validation when establishing secure connections Published:</t>
+        </is>
+      </c>
+      <c r="D1563" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1563" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/fortinet-fortiweb-cve-2024-33509/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1564">
+      <c r="A1564" t="inlineStr">
+        <is>
+          <t>CVE-2024-23665</t>
+        </is>
+      </c>
+      <c r="B1564" t="inlineStr">
+        <is>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="C1564" t="inlineStr">
+        <is>
+          <t>vulnerability Fortinet FortiWeb: CVE-2024-23665: Unauthorized ADOM operations Published: 2024-05-14 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1564" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1564" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/fortinet-fortiweb-cve-2024-23665/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1565">
+      <c r="A1565" t="inlineStr">
+        <is>
+          <t>CVE-2024-23107</t>
+        </is>
+      </c>
+      <c r="B1565" t="inlineStr">
+        <is>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="C1565" t="inlineStr">
+        <is>
+          <t>vulnerability Fortinet FortiWeb: CVE-2024-23107: Read only administrator can see passwords' hashes Published: 2024-05-14 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1565" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1565" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/fortinet-fortiweb-cve-2024-23107/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1566">
+      <c r="A1566" t="inlineStr">
+        <is>
+          <t>CVE-2024-21758</t>
+        </is>
+      </c>
+      <c r="B1566" t="inlineStr">
+        <is>
+          <t>2025-01-14</t>
+        </is>
+      </c>
+      <c r="C1566" t="inlineStr">
+        <is>
+          <t>vulnerability Fortinet FortiWeb: CVE-2024-21758: FortiWeb - Stack overflow in execute backup command Published: 2025-01-14 | Severity: 6 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1566" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1566" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/fortinet-fortiweb-cve-2024-21758/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1567">
+      <c r="A1567" t="inlineStr">
+        <is>
+          <t>CVE-2023-46713</t>
+        </is>
+      </c>
+      <c r="B1567" t="inlineStr">
+        <is>
+          <t>2023-12-12</t>
+        </is>
+      </c>
+      <c r="C1567" t="inlineStr">
+        <is>
+          <t>vulnerability Fortinet FortiWeb: CVE-2023-46713: Log injection Published: 2023-12-12 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1567" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1567" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/fortinet-fortiweb-cve-2023-46713/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rapid7_cves.xlsx
+++ b/rapid7_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1567"/>
+  <dimension ref="A1:E1607"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42725,6 +42725,1086 @@
         </is>
       </c>
     </row>
+    <row r="1568">
+      <c r="A1568" t="inlineStr">
+        <is>
+          <t>CVE-2026-7261</t>
+        </is>
+      </c>
+      <c r="B1568" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C1568" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1568" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1568" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1569">
+      <c r="A1569" t="inlineStr">
+        <is>
+          <t>CVE-2026-7259</t>
+        </is>
+      </c>
+      <c r="B1569" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C1569" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1569" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1569" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1570">
+      <c r="A1570" t="inlineStr">
+        <is>
+          <t>CVE-2026-6722</t>
+        </is>
+      </c>
+      <c r="B1570" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C1570" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1570" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1570" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1571">
+      <c r="A1571" t="inlineStr">
+        <is>
+          <t>CVE-2026-5419</t>
+        </is>
+      </c>
+      <c r="B1571" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C1571" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1571" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1571" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1572">
+      <c r="A1572" t="inlineStr">
+        <is>
+          <t>CVE-2026-48526</t>
+        </is>
+      </c>
+      <c r="B1572" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C1572" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1572" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1572" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1573">
+      <c r="A1573" t="inlineStr">
+        <is>
+          <t>CVE-2026-43198</t>
+        </is>
+      </c>
+      <c r="B1573" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C1573" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1573" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1573" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1574">
+      <c r="A1574" t="inlineStr">
+        <is>
+          <t>CVE-2026-42258</t>
+        </is>
+      </c>
+      <c r="B1574" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C1574" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1574" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1574" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1575">
+      <c r="A1575" t="inlineStr">
+        <is>
+          <t>CVE-2026-42246</t>
+        </is>
+      </c>
+      <c r="B1575" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C1575" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1575" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1575" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1576">
+      <c r="A1576" t="inlineStr">
+        <is>
+          <t>CVE-2026-42245</t>
+        </is>
+      </c>
+      <c r="B1576" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C1576" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1576" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1576" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1577">
+      <c r="A1577" t="inlineStr">
+        <is>
+          <t>CVE-2026-3832</t>
+        </is>
+      </c>
+      <c r="B1577" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C1577" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1577" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1577" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1578">
+      <c r="A1578" t="inlineStr">
+        <is>
+          <t>CVE-2026-37459</t>
+        </is>
+      </c>
+      <c r="B1578" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C1578" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1578" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1578" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1579">
+      <c r="A1579" t="inlineStr">
+        <is>
+          <t>CVE-2026-31411</t>
+        </is>
+      </c>
+      <c r="B1579" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C1579" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1579" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1579" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1580">
+      <c r="A1580" t="inlineStr">
+        <is>
+          <t>CVE-2026-2332</t>
+        </is>
+      </c>
+      <c r="B1580" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C1580" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1580" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1580" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1581">
+      <c r="A1581" t="inlineStr">
+        <is>
+          <t>CVE-2026-8655</t>
+        </is>
+      </c>
+      <c r="B1581" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C1581" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1581" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1581" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1582">
+      <c r="A1582" t="inlineStr">
+        <is>
+          <t>CVE-2026-8452</t>
+        </is>
+      </c>
+      <c r="B1582" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C1582" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1582" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1582" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1583">
+      <c r="A1583" t="inlineStr">
+        <is>
+          <t>CVE-2026-8451</t>
+        </is>
+      </c>
+      <c r="B1583" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C1583" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1583" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1583" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1584">
+      <c r="A1584" t="inlineStr">
+        <is>
+          <t>CVE-2026-13474</t>
+        </is>
+      </c>
+      <c r="B1584" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C1584" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1584" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1584" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1585">
+      <c r="A1585" t="inlineStr">
+        <is>
+          <t>CVE-2026-10817</t>
+        </is>
+      </c>
+      <c r="B1585" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C1585" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1585" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1585" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1586">
+      <c r="A1586" t="inlineStr">
+        <is>
+          <t>CVE-2026-10816</t>
+        </is>
+      </c>
+      <c r="B1586" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C1586" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1586" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1586" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1587">
+      <c r="A1587" t="inlineStr">
+        <is>
+          <t>CVE-2026-56149</t>
+        </is>
+      </c>
+      <c r="B1587" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C1587" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1587" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1587" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1588">
+      <c r="A1588" t="inlineStr">
+        <is>
+          <t>CVE-2026-7261</t>
+        </is>
+      </c>
+      <c r="B1588" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C1588" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-7261: Important: php security update (Multiple Advisories) Published: 2026-06-30 | Severity: 10 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1588" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1588" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-7261/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1589">
+      <c r="A1589" t="inlineStr">
+        <is>
+          <t>CVE-2026-7259</t>
+        </is>
+      </c>
+      <c r="B1589" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C1589" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-7259: Important: php security update (ALSA-2026-33449) Published: 2026-06-30 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1589" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1589" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-7259/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1590">
+      <c r="A1590" t="inlineStr">
+        <is>
+          <t>CVE-2026-6722</t>
+        </is>
+      </c>
+      <c r="B1590" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C1590" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-6722: Important: php security update (Multiple Advisories) Published: 2026-06-30 | Severity: 10 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1590" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1590" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-6722/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1591">
+      <c r="A1591" t="inlineStr">
+        <is>
+          <t>CVE-2026-5419</t>
+        </is>
+      </c>
+      <c r="B1591" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C1591" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-5419: Important: gnutls security update (ALSA-2026-20612) Published: 2026-05-26 | Severity: 4 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1591" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1591" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-5419/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1592">
+      <c r="A1592" t="inlineStr">
+        <is>
+          <t>CVE-2026-48526</t>
+        </is>
+      </c>
+      <c r="B1592" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C1592" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-48526: Important: fence-agents security update (ALSA-2026-26206) Published: 2026-06-16 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1592" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1592" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-48526/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1593">
+      <c r="A1593" t="inlineStr">
+        <is>
+          <t>CVE-2026-43198</t>
+        </is>
+      </c>
+      <c r="B1593" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C1593" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-43198: Important: kernel security, bug fix, and enhancement update (ALSA-2026-33285) Published: 2026-06-29 | Severi</t>
+        </is>
+      </c>
+      <c r="D1593" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1593" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-43198/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1594">
+      <c r="A1594" t="inlineStr">
+        <is>
+          <t>CVE-2026-42258</t>
+        </is>
+      </c>
+      <c r="B1594" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C1594" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-42258: Important: ruby security update (Multiple Advisories) Published: 2026-06-30 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1594" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1594" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-42258/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1595">
+      <c r="A1595" t="inlineStr">
+        <is>
+          <t>CVE-2026-42246</t>
+        </is>
+      </c>
+      <c r="B1595" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C1595" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-42246: Important: ruby security update (Multiple Advisories) Published: 2026-06-30 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1595" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1595" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-42246/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1596">
+      <c r="A1596" t="inlineStr">
+        <is>
+          <t>CVE-2026-42245</t>
+        </is>
+      </c>
+      <c r="B1596" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C1596" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-42245: Important: ruby:3.3 security update (Multiple Advisories) Published: 2026-06-30 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1596" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1596" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-42245/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1597">
+      <c r="A1597" t="inlineStr">
+        <is>
+          <t>CVE-2026-3832</t>
+        </is>
+      </c>
+      <c r="B1597" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C1597" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-3832: Important: gnutls security update (ALSA-2026-20612) Published: 2026-05-26 | Severity: 4 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1597" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1597" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-3832/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1598">
+      <c r="A1598" t="inlineStr">
+        <is>
+          <t>CVE-2026-37459</t>
+        </is>
+      </c>
+      <c r="B1598" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1598" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-37459: Important: frr10 security update (ALSA-2026-24370) Published: 2026-06-08 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1598" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1598" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-37459/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1599">
+      <c r="A1599" t="inlineStr">
+        <is>
+          <t>CVE-2026-31411</t>
+        </is>
+      </c>
+      <c r="B1599" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C1599" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-31411: Important: kernel security, bug fix, and enhancement update (ALSA-2026-33285) Published: 2026-06-29 | Severi</t>
+        </is>
+      </c>
+      <c r="D1599" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1599" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-31411/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1600">
+      <c r="A1600" t="inlineStr">
+        <is>
+          <t>CVE-2026-2332</t>
+        </is>
+      </c>
+      <c r="B1600" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C1600" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-2332: Important: jmc security update (ALSA-2026-20568) Published: 2026-05-26 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1600" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1600" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-2332/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1601">
+      <c r="A1601" t="inlineStr">
+        <is>
+          <t>CVE-2026-8655</t>
+        </is>
+      </c>
+      <c r="B1601" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C1601" t="inlineStr">
+        <is>
+          <t>vulnerability NetScaler ADC: CVE-2026-8655: NetScaler ADC Multiple Memory Overflow Vulnerabilities Leading to Denial of Service via Oracle LB, DNS Pro</t>
+        </is>
+      </c>
+      <c r="D1601" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1601" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/netscaler-adc-cve-2026-8655/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1602">
+      <c r="A1602" t="inlineStr">
+        <is>
+          <t>CVE-2026-8452</t>
+        </is>
+      </c>
+      <c r="B1602" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C1602" t="inlineStr">
+        <is>
+          <t>vulnerability NetScaler ADC: CVE-2026-8452: NetScaler ADC Memory Overflow Vulnerability Leading to Denial of Service via Gateway or AAA Virtual Server</t>
+        </is>
+      </c>
+      <c r="D1602" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1602" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/netscaler-adc-cve-2026-8452/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1603">
+      <c r="A1603" t="inlineStr">
+        <is>
+          <t>CVE-2026-8451</t>
+        </is>
+      </c>
+      <c r="B1603" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C1603" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vulnerability NetScaler ADC: CVE-2026-8451: NetScaler ADC Insufficient Input Validation Leading to Memory Overread via SAML IDP Published: 2026-06-30 </t>
+        </is>
+      </c>
+      <c r="D1603" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1603" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/netscaler-adc-cve-2026-8451/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1604">
+      <c r="A1604" t="inlineStr">
+        <is>
+          <t>CVE-2026-13474</t>
+        </is>
+      </c>
+      <c r="B1604" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C1604" t="inlineStr">
+        <is>
+          <t>vulnerability NetScaler ADC: CVE-2026-13474: NetScaler ADC Denial of Service via Malformed HTTP/2 Requests Published: 2026-06-30 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1604" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1604" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/netscaler-adc-cve-2026-13474/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1605">
+      <c r="A1605" t="inlineStr">
+        <is>
+          <t>CVE-2026-10817</t>
+        </is>
+      </c>
+      <c r="B1605" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C1605" t="inlineStr">
+        <is>
+          <t>vulnerability NetScaler ADC: CVE-2026-10817: NetScaler ADC Insufficient Input Validation Leading to Memory Overread via TCP Timestamp Published: 2026-</t>
+        </is>
+      </c>
+      <c r="D1605" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1605" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/netscaler-adc-cve-2026-10817/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1606">
+      <c r="A1606" t="inlineStr">
+        <is>
+          <t>CVE-2026-10816</t>
+        </is>
+      </c>
+      <c r="B1606" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C1606" t="inlineStr">
+        <is>
+          <t>vulnerability NetScaler ADC: CVE-2026-10816: NetScaler ADC Unauthenticated Arbitrary File Read via Management Interface Published: 2026-06-30 | Severi</t>
+        </is>
+      </c>
+      <c r="D1606" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1606" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/netscaler-adc-cve-2026-10816/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1607">
+      <c r="A1607" t="inlineStr">
+        <is>
+          <t>CVE-2026-56149</t>
+        </is>
+      </c>
+      <c r="B1607" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C1607" t="inlineStr">
+        <is>
+          <t>vulnerability Elastic Elasticsearch: CVE-2026-56149: Allocation of Resources Without Limits or Throttling Published: 2026-07-01 | Severity: 6 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1607" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1607" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/elastic-elasticsearch-cve-2026-56149/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rapid7_cves.xlsx
+++ b/rapid7_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1607"/>
+  <dimension ref="A1:E1647"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43805,6 +43805,1086 @@
         </is>
       </c>
     </row>
+    <row r="1608">
+      <c r="A1608" t="inlineStr">
+        <is>
+          <t>CVE-2026-57451</t>
+        </is>
+      </c>
+      <c r="B1608" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C1608" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1608" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1608" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1609">
+      <c r="A1609" t="inlineStr">
+        <is>
+          <t>CVE-2026-55895</t>
+        </is>
+      </c>
+      <c r="B1609" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C1609" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1609" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1609" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1610">
+      <c r="A1610" t="inlineStr">
+        <is>
+          <t>CVE-2026-55892</t>
+        </is>
+      </c>
+      <c r="B1610" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C1610" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1610" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1610" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1611">
+      <c r="A1611" t="inlineStr">
+        <is>
+          <t>CVE-2026-55693</t>
+        </is>
+      </c>
+      <c r="B1611" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C1611" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1611" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1611" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1612">
+      <c r="A1612" t="inlineStr">
+        <is>
+          <t>CVE-2026-55199</t>
+        </is>
+      </c>
+      <c r="B1612" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C1612" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1612" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1612" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1613">
+      <c r="A1613" t="inlineStr">
+        <is>
+          <t>CVE-2026-53702</t>
+        </is>
+      </c>
+      <c r="B1613" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C1613" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1613" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1613" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1614">
+      <c r="A1614" t="inlineStr">
+        <is>
+          <t>CVE-2026-53701</t>
+        </is>
+      </c>
+      <c r="B1614" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C1614" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1614" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1614" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1615">
+      <c r="A1615" t="inlineStr">
+        <is>
+          <t>CVE-2026-53266</t>
+        </is>
+      </c>
+      <c r="B1615" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C1615" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1615" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1615" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1616">
+      <c r="A1616" t="inlineStr">
+        <is>
+          <t>CVE-2026-53253</t>
+        </is>
+      </c>
+      <c r="B1616" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C1616" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1616" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1616" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1617">
+      <c r="A1617" t="inlineStr">
+        <is>
+          <t>CVE-2026-53245</t>
+        </is>
+      </c>
+      <c r="B1617" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C1617" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1617" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1617" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1618">
+      <c r="A1618" t="inlineStr">
+        <is>
+          <t>CVE-2026-53242</t>
+        </is>
+      </c>
+      <c r="B1618" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C1618" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1618" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1618" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1619">
+      <c r="A1619" t="inlineStr">
+        <is>
+          <t>CVE-2026-53239</t>
+        </is>
+      </c>
+      <c r="B1619" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C1619" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1619" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1619" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1620">
+      <c r="A1620" t="inlineStr">
+        <is>
+          <t>CVE-2026-53209</t>
+        </is>
+      </c>
+      <c r="B1620" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C1620" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1620" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1620" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1621">
+      <c r="A1621" t="inlineStr">
+        <is>
+          <t>CVE-2026-53208</t>
+        </is>
+      </c>
+      <c r="B1621" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C1621" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1621" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1621" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1622">
+      <c r="A1622" t="inlineStr">
+        <is>
+          <t>CVE-2026-53207</t>
+        </is>
+      </c>
+      <c r="B1622" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C1622" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1622" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1622" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1623">
+      <c r="A1623" t="inlineStr">
+        <is>
+          <t>CVE-2026-53199</t>
+        </is>
+      </c>
+      <c r="B1623" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C1623" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1623" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1623" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1624">
+      <c r="A1624" t="inlineStr">
+        <is>
+          <t>CVE-2026-53198</t>
+        </is>
+      </c>
+      <c r="B1624" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C1624" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1624" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1624" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1625">
+      <c r="A1625" t="inlineStr">
+        <is>
+          <t>CVE-2026-53196</t>
+        </is>
+      </c>
+      <c r="B1625" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C1625" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1625" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1625" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1626">
+      <c r="A1626" t="inlineStr">
+        <is>
+          <t>CVE-2026-53195</t>
+        </is>
+      </c>
+      <c r="B1626" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C1626" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1626" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1626" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1627">
+      <c r="A1627" t="inlineStr">
+        <is>
+          <t>CVE-2026-53194</t>
+        </is>
+      </c>
+      <c r="B1627" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C1627" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1627" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1627" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1628">
+      <c r="A1628" t="inlineStr">
+        <is>
+          <t>CVE-2026-57451</t>
+        </is>
+      </c>
+      <c r="B1628" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C1628" t="inlineStr">
+        <is>
+          <t>vulnerability VMware Photon OS: CVE-2026-57451 Published: 2026-06-25 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1628" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1628" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/vmware-photon_os-cve-2026-57451/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1629">
+      <c r="A1629" t="inlineStr">
+        <is>
+          <t>CVE-2026-55895</t>
+        </is>
+      </c>
+      <c r="B1629" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C1629" t="inlineStr">
+        <is>
+          <t>vulnerability VMware Photon OS: CVE-2026-55895 Published: 2026-06-25 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1629" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1629" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/vmware-photon_os-cve-2026-55895/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1630">
+      <c r="A1630" t="inlineStr">
+        <is>
+          <t>CVE-2026-55892</t>
+        </is>
+      </c>
+      <c r="B1630" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C1630" t="inlineStr">
+        <is>
+          <t>vulnerability VMware Photon OS: CVE-2026-55892 Published: 2026-06-25 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1630" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1630" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/vmware-photon_os-cve-2026-55892/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1631">
+      <c r="A1631" t="inlineStr">
+        <is>
+          <t>CVE-2026-55693</t>
+        </is>
+      </c>
+      <c r="B1631" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C1631" t="inlineStr">
+        <is>
+          <t>vulnerability VMware Photon OS: CVE-2026-55693 Published: 2026-06-25 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1631" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1631" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/vmware-photon_os-cve-2026-55693/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1632">
+      <c r="A1632" t="inlineStr">
+        <is>
+          <t>CVE-2026-55199</t>
+        </is>
+      </c>
+      <c r="B1632" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C1632" t="inlineStr">
+        <is>
+          <t>vulnerability VMware Photon OS: CVE-2026-55199 Published: 2026-06-17 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1632" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1632" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/vmware-photon_os-cve-2026-55199/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1633">
+      <c r="A1633" t="inlineStr">
+        <is>
+          <t>CVE-2026-53702</t>
+        </is>
+      </c>
+      <c r="B1633" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="C1633" t="inlineStr">
+        <is>
+          <t>vulnerability VMware Photon OS: CVE-2026-53702 Published: 2026-06-11 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1633" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1633" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/vmware-photon_os-cve-2026-53702/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1634">
+      <c r="A1634" t="inlineStr">
+        <is>
+          <t>CVE-2026-53701</t>
+        </is>
+      </c>
+      <c r="B1634" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="C1634" t="inlineStr">
+        <is>
+          <t>vulnerability VMware Photon OS: CVE-2026-53701 Published: 2026-06-11 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1634" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1634" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/vmware-photon_os-cve-2026-53701/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1635">
+      <c r="A1635" t="inlineStr">
+        <is>
+          <t>CVE-2026-53266</t>
+        </is>
+      </c>
+      <c r="B1635" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C1635" t="inlineStr">
+        <is>
+          <t>vulnerability VMware Photon OS: CVE-2026-53266 Published: 2026-06-25 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1635" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1635" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/vmware-photon_os-cve-2026-53266/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1636">
+      <c r="A1636" t="inlineStr">
+        <is>
+          <t>CVE-2026-53253</t>
+        </is>
+      </c>
+      <c r="B1636" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C1636" t="inlineStr">
+        <is>
+          <t>vulnerability VMware Photon OS: CVE-2026-53253 Published: 2026-06-25 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1636" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1636" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/vmware-photon_os-cve-2026-53253/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1637">
+      <c r="A1637" t="inlineStr">
+        <is>
+          <t>CVE-2026-53245</t>
+        </is>
+      </c>
+      <c r="B1637" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C1637" t="inlineStr">
+        <is>
+          <t>vulnerability VMware Photon OS: CVE-2026-53245 Published: 2026-06-25 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1637" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1637" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/vmware-photon_os-cve-2026-53245/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1638">
+      <c r="A1638" t="inlineStr">
+        <is>
+          <t>CVE-2026-53242</t>
+        </is>
+      </c>
+      <c r="B1638" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C1638" t="inlineStr">
+        <is>
+          <t>vulnerability VMware Photon OS: CVE-2026-53242 Published: 2026-06-25 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1638" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1638" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/vmware-photon_os-cve-2026-53242/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1639">
+      <c r="A1639" t="inlineStr">
+        <is>
+          <t>CVE-2026-53239</t>
+        </is>
+      </c>
+      <c r="B1639" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C1639" t="inlineStr">
+        <is>
+          <t>vulnerability VMware Photon OS: CVE-2026-53239 Published: 2026-06-25 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1639" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1639" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/vmware-photon_os-cve-2026-53239/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1640">
+      <c r="A1640" t="inlineStr">
+        <is>
+          <t>CVE-2026-53209</t>
+        </is>
+      </c>
+      <c r="B1640" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C1640" t="inlineStr">
+        <is>
+          <t>vulnerability VMware Photon OS: CVE-2026-53209 Published: 2026-06-25 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1640" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1640" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/vmware-photon_os-cve-2026-53209/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1641">
+      <c r="A1641" t="inlineStr">
+        <is>
+          <t>CVE-2026-53208</t>
+        </is>
+      </c>
+      <c r="B1641" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C1641" t="inlineStr">
+        <is>
+          <t>vulnerability VMware Photon OS: CVE-2026-53208 Published: 2026-06-25 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1641" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1641" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/vmware-photon_os-cve-2026-53208/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1642">
+      <c r="A1642" t="inlineStr">
+        <is>
+          <t>CVE-2026-53207</t>
+        </is>
+      </c>
+      <c r="B1642" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C1642" t="inlineStr">
+        <is>
+          <t>vulnerability VMware Photon OS: CVE-2026-53207 Published: 2026-06-25 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1642" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1642" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/vmware-photon_os-cve-2026-53207/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1643">
+      <c r="A1643" t="inlineStr">
+        <is>
+          <t>CVE-2026-53199</t>
+        </is>
+      </c>
+      <c r="B1643" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C1643" t="inlineStr">
+        <is>
+          <t>vulnerability VMware Photon OS: CVE-2026-53199 Published: 2026-06-25 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1643" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1643" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/vmware-photon_os-cve-2026-53199/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1644">
+      <c r="A1644" t="inlineStr">
+        <is>
+          <t>CVE-2026-53198</t>
+        </is>
+      </c>
+      <c r="B1644" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C1644" t="inlineStr">
+        <is>
+          <t>vulnerability VMware Photon OS: CVE-2026-53198 Published: 2026-06-25 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1644" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1644" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/vmware-photon_os-cve-2026-53198/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1645">
+      <c r="A1645" t="inlineStr">
+        <is>
+          <t>CVE-2026-53196</t>
+        </is>
+      </c>
+      <c r="B1645" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C1645" t="inlineStr">
+        <is>
+          <t>vulnerability VMware Photon OS: CVE-2026-53196 Published: 2026-06-25 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1645" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1645" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/vmware-photon_os-cve-2026-53196/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1646">
+      <c r="A1646" t="inlineStr">
+        <is>
+          <t>CVE-2026-53195</t>
+        </is>
+      </c>
+      <c r="B1646" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C1646" t="inlineStr">
+        <is>
+          <t>vulnerability VMware Photon OS: CVE-2026-53195 Published: 2026-06-25 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1646" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1646" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/vmware-photon_os-cve-2026-53195/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1647">
+      <c r="A1647" t="inlineStr">
+        <is>
+          <t>CVE-2026-53194</t>
+        </is>
+      </c>
+      <c r="B1647" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C1647" t="inlineStr">
+        <is>
+          <t>vulnerability VMware Photon OS: CVE-2026-53194 Published: 2026-06-25 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1647" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1647" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/vmware-photon_os-cve-2026-53194/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rapid7_cves.xlsx
+++ b/rapid7_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1647"/>
+  <dimension ref="A1:E1687"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44885,6 +44885,1086 @@
         </is>
       </c>
     </row>
+    <row r="1648">
+      <c r="A1648" t="inlineStr">
+        <is>
+          <t>CVE-2025-60021</t>
+        </is>
+      </c>
+      <c r="B1648" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="C1648" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1648" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1648" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1649">
+      <c r="A1649" t="inlineStr">
+        <is>
+          <t>CVE-2025-54472</t>
+        </is>
+      </c>
+      <c r="B1649" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="C1649" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1649" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1649" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1650">
+      <c r="A1650" t="inlineStr">
+        <is>
+          <t>CVE-2026-9669</t>
+        </is>
+      </c>
+      <c r="B1650" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="C1650" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1650" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1650" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1651">
+      <c r="A1651" t="inlineStr">
+        <is>
+          <t>CVE-2026-8851</t>
+        </is>
+      </c>
+      <c r="B1651" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="C1651" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1651" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1651" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1652">
+      <c r="A1652" t="inlineStr">
+        <is>
+          <t>CVE-2026-8496</t>
+        </is>
+      </c>
+      <c r="B1652" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="C1652" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1652" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1652" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1653">
+      <c r="A1653" t="inlineStr">
+        <is>
+          <t>CVE-2026-8328</t>
+        </is>
+      </c>
+      <c r="B1653" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="C1653" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1653" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1653" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1654">
+      <c r="A1654" t="inlineStr">
+        <is>
+          <t>CVE-2026-7774</t>
+        </is>
+      </c>
+      <c r="B1654" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="C1654" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1654" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1654" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1655">
+      <c r="A1655" t="inlineStr">
+        <is>
+          <t>CVE-2026-6841</t>
+        </is>
+      </c>
+      <c r="B1655" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="C1655" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1655" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1655" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1656">
+      <c r="A1656" t="inlineStr">
+        <is>
+          <t>CVE-2026-6100</t>
+        </is>
+      </c>
+      <c r="B1656" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="C1656" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1656" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1656" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1657">
+      <c r="A1657" t="inlineStr">
+        <is>
+          <t>CVE-2026-6019</t>
+        </is>
+      </c>
+      <c r="B1657" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="C1657" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1657" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1657" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1658">
+      <c r="A1658" t="inlineStr">
+        <is>
+          <t>CVE-2026-5713</t>
+        </is>
+      </c>
+      <c r="B1658" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="C1658" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1658" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1658" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1659">
+      <c r="A1659" t="inlineStr">
+        <is>
+          <t>CVE-2026-56123</t>
+        </is>
+      </c>
+      <c r="B1659" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="C1659" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1659" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1659" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1660">
+      <c r="A1660" t="inlineStr">
+        <is>
+          <t>CVE-2026-4786</t>
+        </is>
+      </c>
+      <c r="B1660" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="C1660" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1660" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1660" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1661">
+      <c r="A1661" t="inlineStr">
+        <is>
+          <t>CVE-2026-46446</t>
+        </is>
+      </c>
+      <c r="B1661" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="C1661" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1661" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1661" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1662">
+      <c r="A1662" t="inlineStr">
+        <is>
+          <t>CVE-2026-46445</t>
+        </is>
+      </c>
+      <c r="B1662" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="C1662" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1662" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1662" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1663">
+      <c r="A1663" t="inlineStr">
+        <is>
+          <t>CVE-2026-4519</t>
+        </is>
+      </c>
+      <c r="B1663" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="C1663" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1663" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1663" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1664">
+      <c r="A1664" t="inlineStr">
+        <is>
+          <t>CVE-2026-44231</t>
+        </is>
+      </c>
+      <c r="B1664" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="C1664" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1664" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1664" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1665">
+      <c r="A1665" t="inlineStr">
+        <is>
+          <t>CVE-2026-44230</t>
+        </is>
+      </c>
+      <c r="B1665" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="C1665" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1665" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1665" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1666">
+      <c r="A1666" t="inlineStr">
+        <is>
+          <t>CVE-2026-44229</t>
+        </is>
+      </c>
+      <c r="B1666" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="C1666" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1666" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1666" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1667">
+      <c r="A1667" t="inlineStr">
+        <is>
+          <t>CVE-2026-4224</t>
+        </is>
+      </c>
+      <c r="B1667" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="C1667" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1667" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1667" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1668">
+      <c r="A1668" t="inlineStr">
+        <is>
+          <t>CVE-2025-60021</t>
+        </is>
+      </c>
+      <c r="B1668" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="C1668" t="inlineStr">
+        <is>
+          <t>vulnerability Apache bRPC: CVE-2025-60021: Improper Neutralization of Special Elements used in a Command ('Command Injection') Published: 2025-10-08 |</t>
+        </is>
+      </c>
+      <c r="D1668" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1668" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/http-apache-brpc-cve-2025-60021/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1669">
+      <c r="A1669" t="inlineStr">
+        <is>
+          <t>CVE-2025-54472</t>
+        </is>
+      </c>
+      <c r="B1669" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="C1669" t="inlineStr">
+        <is>
+          <t>vulnerability Apache bRPC: CVE-2025-54472: Allocation of Resources Without Limits or Throttling Published: 2025-08-19 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1669" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1669" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/http-apache-brpc-cve-2025-54472/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1670">
+      <c r="A1670" t="inlineStr">
+        <is>
+          <t>CVE-2026-9669</t>
+        </is>
+      </c>
+      <c r="B1670" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1670" t="inlineStr">
+        <is>
+          <t>vulnerability Ubuntu: (CVE-2026-9669): python3.10 vulnerability Published: 2026-06-08 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1670" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1670" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ubuntu-cve-2026-9669/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1671">
+      <c r="A1671" t="inlineStr">
+        <is>
+          <t>CVE-2026-8851</t>
+        </is>
+      </c>
+      <c r="B1671" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="C1671" t="inlineStr">
+        <is>
+          <t>vulnerability Ubuntu: (CVE-2026-8851): sogo vulnerability Published: 2026-05-18 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1671" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1671" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ubuntu-cve-2026-8851/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1672">
+      <c r="A1672" t="inlineStr">
+        <is>
+          <t>CVE-2026-8496</t>
+        </is>
+      </c>
+      <c r="B1672" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C1672" t="inlineStr">
+        <is>
+          <t>vulnerability Ubuntu: (CVE-2026-8496): sogo vulnerability Published: 2026-05-13 | Severity: 6 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1672" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1672" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ubuntu-cve-2026-8496/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1673">
+      <c r="A1673" t="inlineStr">
+        <is>
+          <t>CVE-2026-8328</t>
+        </is>
+      </c>
+      <c r="B1673" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C1673" t="inlineStr">
+        <is>
+          <t>vulnerability Ubuntu: (CVE-2026-8328): python3.10 vulnerability Published: 2026-05-13 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1673" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1673" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ubuntu-cve-2026-8328/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1674">
+      <c r="A1674" t="inlineStr">
+        <is>
+          <t>CVE-2026-7774</t>
+        </is>
+      </c>
+      <c r="B1674" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C1674" t="inlineStr">
+        <is>
+          <t>vulnerability Ubuntu: (CVE-2026-7774): python3.12 vulnerability Published: 2026-06-04 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1674" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1674" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ubuntu-cve-2026-7774/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1675">
+      <c r="A1675" t="inlineStr">
+        <is>
+          <t>CVE-2026-6841</t>
+        </is>
+      </c>
+      <c r="B1675" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="C1675" t="inlineStr">
+        <is>
+          <t>vulnerability Ubuntu: (CVE-2026-6841): request-tracker5 vulnerability Published: 2026-05-21 | Severity: 6 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1675" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1675" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ubuntu-cve-2026-6841/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1676">
+      <c r="A1676" t="inlineStr">
+        <is>
+          <t>CVE-2026-6100</t>
+        </is>
+      </c>
+      <c r="B1676" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="C1676" t="inlineStr">
+        <is>
+          <t>vulnerability Ubuntu: (CVE-2026-6100): python3.10 vulnerability Published: 2026-04-13 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1676" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1676" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ubuntu-cve-2026-6100/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1677">
+      <c r="A1677" t="inlineStr">
+        <is>
+          <t>CVE-2026-6019</t>
+        </is>
+      </c>
+      <c r="B1677" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="C1677" t="inlineStr">
+        <is>
+          <t>vulnerability Ubuntu: (CVE-2026-6019): python3.10 vulnerability Published: 2026-04-22 | Severity: 6 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1677" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1677" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ubuntu-cve-2026-6019/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1678">
+      <c r="A1678" t="inlineStr">
+        <is>
+          <t>CVE-2026-5713</t>
+        </is>
+      </c>
+      <c r="B1678" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="C1678" t="inlineStr">
+        <is>
+          <t>vulnerability Ubuntu: (CVE-2026-5713): python3.14 vulnerability Published: 2026-04-14 | Severity: 6 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1678" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1678" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ubuntu-cve-2026-5713/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1679">
+      <c r="A1679" t="inlineStr">
+        <is>
+          <t>CVE-2026-56123</t>
+        </is>
+      </c>
+      <c r="B1679" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C1679" t="inlineStr">
+        <is>
+          <t>vulnerability Ubuntu: (CVE-2026-56123): socat vulnerability Published: 2026-06-25 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1679" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1679" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ubuntu-cve-2026-56123/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1680">
+      <c r="A1680" t="inlineStr">
+        <is>
+          <t>CVE-2026-4786</t>
+        </is>
+      </c>
+      <c r="B1680" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="C1680" t="inlineStr">
+        <is>
+          <t>vulnerability Ubuntu: (CVE-2026-4786): python3.10 vulnerability Published: 2026-04-13 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1680" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1680" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ubuntu-cve-2026-4786/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1681">
+      <c r="A1681" t="inlineStr">
+        <is>
+          <t>CVE-2026-46446</t>
+        </is>
+      </c>
+      <c r="B1681" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C1681" t="inlineStr">
+        <is>
+          <t>vulnerability Ubuntu: (CVE-2026-46446): sogo vulnerability Published: 2026-05-14 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1681" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1681" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ubuntu-cve-2026-46446/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1682">
+      <c r="A1682" t="inlineStr">
+        <is>
+          <t>CVE-2026-46445</t>
+        </is>
+      </c>
+      <c r="B1682" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C1682" t="inlineStr">
+        <is>
+          <t>vulnerability Ubuntu: (CVE-2026-46445): sogo vulnerability Published: 2026-05-14 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1682" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1682" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ubuntu-cve-2026-46445/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1683">
+      <c r="A1683" t="inlineStr">
+        <is>
+          <t>CVE-2026-4519</t>
+        </is>
+      </c>
+      <c r="B1683" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="C1683" t="inlineStr">
+        <is>
+          <t>vulnerability Ubuntu: (CVE-2026-4519): python3.10 vulnerability Published: 2026-03-20 | Severity: 2 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1683" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E1683" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ubuntu-cve-2026-4519/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1684">
+      <c r="A1684" t="inlineStr">
+        <is>
+          <t>CVE-2026-44231</t>
+        </is>
+      </c>
+      <c r="B1684" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="C1684" t="inlineStr">
+        <is>
+          <t>vulnerability Ubuntu: (CVE-2026-44231): request-tracker5 vulnerability Published: 2026-05-21 | Severity: 10 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1684" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1684" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ubuntu-cve-2026-44231/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1685">
+      <c r="A1685" t="inlineStr">
+        <is>
+          <t>CVE-2026-44230</t>
+        </is>
+      </c>
+      <c r="B1685" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="C1685" t="inlineStr">
+        <is>
+          <t>vulnerability Ubuntu: (CVE-2026-44230): request-tracker5 vulnerability Published: 2026-05-21 | Severity: 10 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1685" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1685" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ubuntu-cve-2026-44230/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1686">
+      <c r="A1686" t="inlineStr">
+        <is>
+          <t>CVE-2026-44229</t>
+        </is>
+      </c>
+      <c r="B1686" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="C1686" t="inlineStr">
+        <is>
+          <t>vulnerability Ubuntu: (CVE-2026-44229): request-tracker5 vulnerability Published: 2026-05-21 | Severity: 10 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1686" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1686" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ubuntu-cve-2026-44229/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1687">
+      <c r="A1687" t="inlineStr">
+        <is>
+          <t>CVE-2026-4224</t>
+        </is>
+      </c>
+      <c r="B1687" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="C1687" t="inlineStr">
+        <is>
+          <t>vulnerability Ubuntu: (CVE-2026-4224): python3.10 vulnerability Published: 2026-03-16 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1687" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1687" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ubuntu-cve-2026-4224/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rapid7_cves.xlsx
+++ b/rapid7_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1687"/>
+  <dimension ref="A1:E1727"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45965,6 +45965,1086 @@
         </is>
       </c>
     </row>
+    <row r="1688">
+      <c r="A1688" t="inlineStr">
+        <is>
+          <t>CVE-2025-12799</t>
+        </is>
+      </c>
+      <c r="B1688" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="C1688" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1688" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1688" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1689">
+      <c r="A1689" t="inlineStr">
+        <is>
+          <t>CVE-2026-9563</t>
+        </is>
+      </c>
+      <c r="B1689" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="C1689" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1689" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1689" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1690">
+      <c r="A1690" t="inlineStr">
+        <is>
+          <t>CVE-2026-8408</t>
+        </is>
+      </c>
+      <c r="B1690" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="C1690" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1690" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1690" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1691">
+      <c r="A1691" t="inlineStr">
+        <is>
+          <t>CVE-2026-34282</t>
+        </is>
+      </c>
+      <c r="B1691" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="C1691" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1691" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1691" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1692">
+      <c r="A1692" t="inlineStr">
+        <is>
+          <t>CVE-2026-34268</t>
+        </is>
+      </c>
+      <c r="B1692" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="C1692" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1692" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1692" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1693">
+      <c r="A1693" t="inlineStr">
+        <is>
+          <t>CVE-2026-23865</t>
+        </is>
+      </c>
+      <c r="B1693" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="C1693" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1693" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1693" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1694">
+      <c r="A1694" t="inlineStr">
+        <is>
+          <t>CVE-2026-22021</t>
+        </is>
+      </c>
+      <c r="B1694" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="C1694" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1694" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1694" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1695">
+      <c r="A1695" t="inlineStr">
+        <is>
+          <t>CVE-2026-22018</t>
+        </is>
+      </c>
+      <c r="B1695" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="C1695" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1695" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1695" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1696">
+      <c r="A1696" t="inlineStr">
+        <is>
+          <t>CVE-2026-22016</t>
+        </is>
+      </c>
+      <c r="B1696" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="C1696" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1696" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1696" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1697">
+      <c r="A1697" t="inlineStr">
+        <is>
+          <t>CVE-2026-22013</t>
+        </is>
+      </c>
+      <c r="B1697" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="C1697" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1697" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1697" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1698">
+      <c r="A1698" t="inlineStr">
+        <is>
+          <t>CVE-2026-22008</t>
+        </is>
+      </c>
+      <c r="B1698" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="C1698" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1698" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1698" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1699">
+      <c r="A1699" t="inlineStr">
+        <is>
+          <t>CVE-2026-22007</t>
+        </is>
+      </c>
+      <c r="B1699" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="C1699" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1699" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1699" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1700">
+      <c r="A1700" t="inlineStr">
+        <is>
+          <t>CVE-2026-20676</t>
+        </is>
+      </c>
+      <c r="B1700" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="C1700" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1700" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1700" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1701">
+      <c r="A1701" t="inlineStr">
+        <is>
+          <t>CVE-2026-20652</t>
+        </is>
+      </c>
+      <c r="B1701" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="C1701" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1701" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1701" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1702">
+      <c r="A1702" t="inlineStr">
+        <is>
+          <t>CVE-2026-20644</t>
+        </is>
+      </c>
+      <c r="B1702" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="C1702" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1702" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1702" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1703">
+      <c r="A1703" t="inlineStr">
+        <is>
+          <t>CVE-2026-20636</t>
+        </is>
+      </c>
+      <c r="B1703" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="C1703" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1703" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1703" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1704">
+      <c r="A1704" t="inlineStr">
+        <is>
+          <t>CVE-2026-20635</t>
+        </is>
+      </c>
+      <c r="B1704" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="C1704" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1704" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1704" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1705">
+      <c r="A1705" t="inlineStr">
+        <is>
+          <t>CVE-2026-20608</t>
+        </is>
+      </c>
+      <c r="B1705" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="C1705" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1705" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1705" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1706">
+      <c r="A1706" t="inlineStr">
+        <is>
+          <t>CVE-2025-43457</t>
+        </is>
+      </c>
+      <c r="B1706" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="C1706" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1706" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1706" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1707">
+      <c r="A1707" t="inlineStr">
+        <is>
+          <t>CVE-2020-2830</t>
+        </is>
+      </c>
+      <c r="B1707" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="C1707" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1707" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1707" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1708">
+      <c r="A1708" t="inlineStr">
+        <is>
+          <t>CVE-2025-12799</t>
+        </is>
+      </c>
+      <c r="B1708" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="C1708" t="inlineStr">
+        <is>
+          <t>vulnerability Red Hat JBoss EAP: CVE-2025-12799: Cross-site Scripting Published: 2026-07-07 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1708" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1708" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/red-hat-jboss-eap-cve-2025-12799/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1709">
+      <c r="A1709" t="inlineStr">
+        <is>
+          <t>CVE-2026-9563</t>
+        </is>
+      </c>
+      <c r="B1709" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C1709" t="inlineStr">
+        <is>
+          <t>vulnerability IBM WebSphere Application Server: CVE-2026-9563: IBM WebSphere Application Server Liberty is affected by a denial of service vulnerabili</t>
+        </is>
+      </c>
+      <c r="D1709" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1709" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ibm-was-cve-2026-9563/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1710">
+      <c r="A1710" t="inlineStr">
+        <is>
+          <t>CVE-2026-8408</t>
+        </is>
+      </c>
+      <c r="B1710" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="C1710" t="inlineStr">
+        <is>
+          <t>vulnerability IBM WebSphere Application Server: CVE-2026-8408: IBM WebSphere Application Server is affected by a cross-site request forgery vulnerabil</t>
+        </is>
+      </c>
+      <c r="D1710" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1710" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ibm-was-cve-2026-8408/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1711">
+      <c r="A1711" t="inlineStr">
+        <is>
+          <t>CVE-2026-34282</t>
+        </is>
+      </c>
+      <c r="B1711" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C1711" t="inlineStr">
+        <is>
+          <t>vulnerability Azul Zulu: CVE-2026-34282: Vulnerability with Networking component Published: 2026-04-21 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1711" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1711" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/azul-zulu-cve-2026-34282/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1712">
+      <c r="A1712" t="inlineStr">
+        <is>
+          <t>CVE-2026-34268</t>
+        </is>
+      </c>
+      <c r="B1712" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C1712" t="inlineStr">
+        <is>
+          <t>vulnerability Azul Zulu: CVE-2026-34268: Vulnerability with Security component Published: 2026-04-21 | Severity: 2 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1712" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E1712" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/azul-zulu-cve-2026-34268/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1713">
+      <c r="A1713" t="inlineStr">
+        <is>
+          <t>CVE-2026-23865</t>
+        </is>
+      </c>
+      <c r="B1713" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="C1713" t="inlineStr">
+        <is>
+          <t>vulnerability Azul Zulu: CVE-2026-23865: Vulnerability in Azul Zulu Published: 2026-03-02 | Severity: 4 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1713" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1713" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/azul-zulu-cve-2026-23865/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1714">
+      <c r="A1714" t="inlineStr">
+        <is>
+          <t>CVE-2026-22021</t>
+        </is>
+      </c>
+      <c r="B1714" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C1714" t="inlineStr">
+        <is>
+          <t>vulnerability Azul Zulu: CVE-2026-22021: Vulnerability with JSSE component Published: 2026-04-21 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1714" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1714" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/azul-zulu-cve-2026-22021/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1715">
+      <c r="A1715" t="inlineStr">
+        <is>
+          <t>CVE-2026-22018</t>
+        </is>
+      </c>
+      <c r="B1715" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C1715" t="inlineStr">
+        <is>
+          <t>vulnerability Azul Zulu: CVE-2026-22018: Vulnerability with Libraries component Published: 2026-04-21 | Severity: 4 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1715" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1715" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/azul-zulu-cve-2026-22018/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1716">
+      <c r="A1716" t="inlineStr">
+        <is>
+          <t>CVE-2026-22016</t>
+        </is>
+      </c>
+      <c r="B1716" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C1716" t="inlineStr">
+        <is>
+          <t>vulnerability Azul Zulu: CVE-2026-22016: Vulnerability with JAXP component Published: 2026-04-21 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1716" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1716" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/azul-zulu-cve-2026-22016/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1717">
+      <c r="A1717" t="inlineStr">
+        <is>
+          <t>CVE-2026-22013</t>
+        </is>
+      </c>
+      <c r="B1717" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C1717" t="inlineStr">
+        <is>
+          <t>vulnerability Azul Zulu: CVE-2026-22013: Vulnerability with JGSS component Published: 2026-04-21 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1717" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1717" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/azul-zulu-cve-2026-22013/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1718">
+      <c r="A1718" t="inlineStr">
+        <is>
+          <t>CVE-2026-22008</t>
+        </is>
+      </c>
+      <c r="B1718" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C1718" t="inlineStr">
+        <is>
+          <t>vulnerability Azul Zulu: CVE-2026-22008: Vulnerability with Libraries component Published: 2026-04-21 | Severity: 4 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1718" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1718" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/azul-zulu-cve-2026-22008/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1719">
+      <c r="A1719" t="inlineStr">
+        <is>
+          <t>CVE-2026-22007</t>
+        </is>
+      </c>
+      <c r="B1719" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C1719" t="inlineStr">
+        <is>
+          <t>vulnerability Azul Zulu: CVE-2026-22007: Vulnerability with Security component Published: 2026-04-21 | Severity: 2 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1719" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E1719" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/azul-zulu-cve-2026-22007/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1720">
+      <c r="A1720" t="inlineStr">
+        <is>
+          <t>CVE-2026-20676</t>
+        </is>
+      </c>
+      <c r="B1720" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="C1720" t="inlineStr">
+        <is>
+          <t>vulnerability Azul Zulu: CVE-2026-20676: Vulnerability in Azul Zulu Published: 2026-02-11 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1720" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1720" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/azul-zulu-cve-2026-20676/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1721">
+      <c r="A1721" t="inlineStr">
+        <is>
+          <t>CVE-2026-20652</t>
+        </is>
+      </c>
+      <c r="B1721" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="C1721" t="inlineStr">
+        <is>
+          <t>vulnerability Azul Zulu: CVE-2026-20652: Vulnerability in Azul Zulu Published: 2026-02-11 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1721" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1721" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/azul-zulu-cve-2026-20652/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1722">
+      <c r="A1722" t="inlineStr">
+        <is>
+          <t>CVE-2026-20644</t>
+        </is>
+      </c>
+      <c r="B1722" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="C1722" t="inlineStr">
+        <is>
+          <t>vulnerability Azul Zulu: CVE-2026-20644: Vulnerability in Azul Zulu Published: 2026-02-11 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1722" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1722" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/azul-zulu-cve-2026-20644/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1723">
+      <c r="A1723" t="inlineStr">
+        <is>
+          <t>CVE-2026-20636</t>
+        </is>
+      </c>
+      <c r="B1723" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="C1723" t="inlineStr">
+        <is>
+          <t>vulnerability Azul Zulu: CVE-2026-20636: Vulnerability in Azul Zulu Published: 2026-02-11 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1723" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1723" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/azul-zulu-cve-2026-20636/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1724">
+      <c r="A1724" t="inlineStr">
+        <is>
+          <t>CVE-2026-20635</t>
+        </is>
+      </c>
+      <c r="B1724" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="C1724" t="inlineStr">
+        <is>
+          <t>vulnerability Azul Zulu: CVE-2026-20635: Vulnerability in Azul Zulu Published: 2026-02-11 | Severity: 4 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1724" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1724" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/azul-zulu-cve-2026-20635/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1725">
+      <c r="A1725" t="inlineStr">
+        <is>
+          <t>CVE-2026-20608</t>
+        </is>
+      </c>
+      <c r="B1725" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="C1725" t="inlineStr">
+        <is>
+          <t>vulnerability Azul Zulu: CVE-2026-20608: Vulnerability in Azul Zulu Published: 2026-02-11 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1725" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1725" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/azul-zulu-cve-2026-20608/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1726">
+      <c r="A1726" t="inlineStr">
+        <is>
+          <t>CVE-2025-43457</t>
+        </is>
+      </c>
+      <c r="B1726" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="C1726" t="inlineStr">
+        <is>
+          <t>vulnerability Azul Zulu: CVE-2025-43457: Vulnerability in Azul Zulu Published: 2025-11-04 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1726" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1726" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/azul-zulu-cve-2025-43457/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1727">
+      <c r="A1727" t="inlineStr">
+        <is>
+          <t>CVE-2020-2830</t>
+        </is>
+      </c>
+      <c r="B1727" t="inlineStr">
+        <is>
+          <t>2020-04-15</t>
+        </is>
+      </c>
+      <c r="C1727" t="inlineStr">
+        <is>
+          <t>vulnerability Azul Zulu: CVE-2020-2830: Vulnerability with Concurrency component Published: 2020-04-15 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1727" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1727" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/azul-zulu-cve-2020-2830/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rapid7_cves.xlsx
+++ b/rapid7_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1727"/>
+  <dimension ref="A1:E1767"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47045,6 +47045,1086 @@
         </is>
       </c>
     </row>
+    <row r="1728">
+      <c r="A1728" t="inlineStr">
+        <is>
+          <t>CVE-2026-50656</t>
+        </is>
+      </c>
+      <c r="B1728" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C1728" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1728" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1728" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1729">
+      <c r="A1729" t="inlineStr">
+        <is>
+          <t>CVE-2026-8643</t>
+        </is>
+      </c>
+      <c r="B1729" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C1729" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1729" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1729" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1730">
+      <c r="A1730" t="inlineStr">
+        <is>
+          <t>CVE-2026-50031</t>
+        </is>
+      </c>
+      <c r="B1730" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C1730" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1730" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1730" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1731">
+      <c r="A1731" t="inlineStr">
+        <is>
+          <t>CVE-2026-46259</t>
+        </is>
+      </c>
+      <c r="B1731" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C1731" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1731" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1731" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1732">
+      <c r="A1732" t="inlineStr">
+        <is>
+          <t>CVE-2026-46227</t>
+        </is>
+      </c>
+      <c r="B1732" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C1732" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1732" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1732" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1733">
+      <c r="A1733" t="inlineStr">
+        <is>
+          <t>CVE-2026-46209</t>
+        </is>
+      </c>
+      <c r="B1733" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C1733" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1733" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1733" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1734">
+      <c r="A1734" t="inlineStr">
+        <is>
+          <t>CVE-2026-43450</t>
+        </is>
+      </c>
+      <c r="B1734" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C1734" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1734" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1734" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1735">
+      <c r="A1735" t="inlineStr">
+        <is>
+          <t>CVE-2026-43112</t>
+        </is>
+      </c>
+      <c r="B1735" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C1735" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1735" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1735" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1736">
+      <c r="A1736" t="inlineStr">
+        <is>
+          <t>CVE-2026-42055</t>
+        </is>
+      </c>
+      <c r="B1736" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C1736" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1736" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1736" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1737">
+      <c r="A1737" t="inlineStr">
+        <is>
+          <t>CVE-2026-35406</t>
+        </is>
+      </c>
+      <c r="B1737" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C1737" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1737" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1737" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1738">
+      <c r="A1738" t="inlineStr">
+        <is>
+          <t>CVE-2026-11774</t>
+        </is>
+      </c>
+      <c r="B1738" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C1738" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1738" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1738" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1739">
+      <c r="A1739" t="inlineStr">
+        <is>
+          <t>CVE-2026-11610</t>
+        </is>
+      </c>
+      <c r="B1739" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C1739" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1739" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1739" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1740">
+      <c r="A1740" t="inlineStr">
+        <is>
+          <t>CVE-2025-10263</t>
+        </is>
+      </c>
+      <c r="B1740" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C1740" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1740" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1740" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1741">
+      <c r="A1741" t="inlineStr">
+        <is>
+          <t>CVE-2026-56003</t>
+        </is>
+      </c>
+      <c r="B1741" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C1741" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1741" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1741" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1742">
+      <c r="A1742" t="inlineStr">
+        <is>
+          <t>CVE-2026-56002</t>
+        </is>
+      </c>
+      <c r="B1742" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C1742" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1742" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1742" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1743">
+      <c r="A1743" t="inlineStr">
+        <is>
+          <t>CVE-2026-56001</t>
+        </is>
+      </c>
+      <c r="B1743" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C1743" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1743" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1743" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1744">
+      <c r="A1744" t="inlineStr">
+        <is>
+          <t>CVE-2026-56000</t>
+        </is>
+      </c>
+      <c r="B1744" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C1744" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1744" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1744" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1745">
+      <c r="A1745" t="inlineStr">
+        <is>
+          <t>CVE-2026-55999</t>
+        </is>
+      </c>
+      <c r="B1745" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C1745" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1745" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1745" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1746">
+      <c r="A1746" t="inlineStr">
+        <is>
+          <t>CVE-2026-55645</t>
+        </is>
+      </c>
+      <c r="B1746" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C1746" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1746" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1746" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1747">
+      <c r="A1747" t="inlineStr">
+        <is>
+          <t>CVE-2026-55639</t>
+        </is>
+      </c>
+      <c r="B1747" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C1747" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1747" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1747" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1748">
+      <c r="A1748" t="inlineStr">
+        <is>
+          <t>CVE-2026-50656</t>
+        </is>
+      </c>
+      <c r="B1748" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C1748" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vulnerability Microsoft Windows Defender: CVE-2026-50656: Microsoft Defender Elevation of Privilege Vulnerability Published: 2026-06-16 | Severity: 7 </t>
+        </is>
+      </c>
+      <c r="D1748" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1748" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/windows-defender-cve-2026-50656/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1749">
+      <c r="A1749" t="inlineStr">
+        <is>
+          <t>CVE-2026-8643</t>
+        </is>
+      </c>
+      <c r="B1749" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="C1749" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-8643: Important: python3.14-pip security update (ALSA-2026-36315) Published: 2026-07-07 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1749" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1749" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-8643/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1750">
+      <c r="A1750" t="inlineStr">
+        <is>
+          <t>CVE-2026-50031</t>
+        </is>
+      </c>
+      <c r="B1750" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="C1750" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-50031: Moderate: freeipmi security update (Multiple Advisories) Published: 2026-07-07 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1750" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1750" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-50031/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1751">
+      <c r="A1751" t="inlineStr">
+        <is>
+          <t>CVE-2026-46259</t>
+        </is>
+      </c>
+      <c r="B1751" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="C1751" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-46259: Important: kernel-rt security, bug fix, and enhancement update (Multiple Advisories) Published: 2026-07-07 |</t>
+        </is>
+      </c>
+      <c r="D1751" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1751" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-46259/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1752">
+      <c r="A1752" t="inlineStr">
+        <is>
+          <t>CVE-2026-46227</t>
+        </is>
+      </c>
+      <c r="B1752" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="C1752" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-46227: Important: kernel-rt security, bug fix, and enhancement update (Multiple Advisories) Published: 2026-07-07 |</t>
+        </is>
+      </c>
+      <c r="D1752" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1752" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-46227/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1753">
+      <c r="A1753" t="inlineStr">
+        <is>
+          <t>CVE-2026-46209</t>
+        </is>
+      </c>
+      <c r="B1753" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="C1753" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-46209: Important: kernel-rt security, bug fix, and enhancement update (Multiple Advisories) Published: 2026-07-07 |</t>
+        </is>
+      </c>
+      <c r="D1753" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1753" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-46209/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1754">
+      <c r="A1754" t="inlineStr">
+        <is>
+          <t>CVE-2026-43450</t>
+        </is>
+      </c>
+      <c r="B1754" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="C1754" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-43450: Important: kernel-rt security, bug fix, and enhancement update (Multiple Advisories) Published: 2026-07-07 |</t>
+        </is>
+      </c>
+      <c r="D1754" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1754" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-43450/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1755">
+      <c r="A1755" t="inlineStr">
+        <is>
+          <t>CVE-2026-43112</t>
+        </is>
+      </c>
+      <c r="B1755" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="C1755" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-43112: Important: kernel-rt security update (Multiple Advisories) Published: 2026-07-07 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1755" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1755" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-43112/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1756">
+      <c r="A1756" t="inlineStr">
+        <is>
+          <t>CVE-2026-42055</t>
+        </is>
+      </c>
+      <c r="B1756" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="C1756" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-42055: Important: nginx security, bug fix, and enhancement update (ALSA-2026-36331) Published: 2026-07-07 | Severit</t>
+        </is>
+      </c>
+      <c r="D1756" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1756" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-42055/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1757">
+      <c r="A1757" t="inlineStr">
+        <is>
+          <t>CVE-2026-35406</t>
+        </is>
+      </c>
+      <c r="B1757" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="C1757" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-35406: Moderate: aardvark-dns security update (ALSA-2026-36318) Published: 2026-07-07 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1757" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1757" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-35406/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1758">
+      <c r="A1758" t="inlineStr">
+        <is>
+          <t>CVE-2026-11774</t>
+        </is>
+      </c>
+      <c r="B1758" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="C1758" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-11774: Important: 389-ds-base security update (ALSA-2026-36195) Published: 2026-07-07 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1758" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1758" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-11774/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1759">
+      <c r="A1759" t="inlineStr">
+        <is>
+          <t>CVE-2026-11610</t>
+        </is>
+      </c>
+      <c r="B1759" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="C1759" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2026-11610: Important: 389-ds-base security update (ALSA-2026-36195) Published: 2026-07-07 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1759" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1759" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2026-11610/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1760">
+      <c r="A1760" t="inlineStr">
+        <is>
+          <t>CVE-2025-10263</t>
+        </is>
+      </c>
+      <c r="B1760" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="C1760" t="inlineStr">
+        <is>
+          <t>vulnerability Alma Linux: CVE-2025-10263: Important: kernel-rt security, bug fix, and enhancement update (Multiple Advisories) Published: 2026-07-07 |</t>
+        </is>
+      </c>
+      <c r="D1760" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1760" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/alma_linux-cve-2025-10263/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1761">
+      <c r="A1761" t="inlineStr">
+        <is>
+          <t>CVE-2026-56003</t>
+        </is>
+      </c>
+      <c r="B1761" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="C1761" t="inlineStr">
+        <is>
+          <t>vulnerability FreeBSD: VID-9a1fdf39-7b10-11f1-a315-589cfc10a551 (CVE-2026-56003): libXfont2 -- Multiple vulnerabilities Published: 2026-07-08 | Severi</t>
+        </is>
+      </c>
+      <c r="D1761" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1761" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/freebsd-cve-2026-56003/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1762">
+      <c r="A1762" t="inlineStr">
+        <is>
+          <t>CVE-2026-56002</t>
+        </is>
+      </c>
+      <c r="B1762" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="C1762" t="inlineStr">
+        <is>
+          <t>vulnerability FreeBSD: VID-9a1fdf39-7b10-11f1-a315-589cfc10a551 (CVE-2026-56002): libXfont2 -- Multiple vulnerabilities Published: 2026-07-08 | Severi</t>
+        </is>
+      </c>
+      <c r="D1762" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1762" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/freebsd-cve-2026-56002/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1763">
+      <c r="A1763" t="inlineStr">
+        <is>
+          <t>CVE-2026-56001</t>
+        </is>
+      </c>
+      <c r="B1763" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="C1763" t="inlineStr">
+        <is>
+          <t>vulnerability FreeBSD: VID-9a1fdf39-7b10-11f1-a315-589cfc10a551 (CVE-2026-56001): libXfont2 -- Multiple vulnerabilities Published: 2026-07-08 | Severi</t>
+        </is>
+      </c>
+      <c r="D1763" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1763" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/freebsd-cve-2026-56001/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1764">
+      <c r="A1764" t="inlineStr">
+        <is>
+          <t>CVE-2026-56000</t>
+        </is>
+      </c>
+      <c r="B1764" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="C1764" t="inlineStr">
+        <is>
+          <t>vulnerability FreeBSD: (Multiple Advisories) (CVE-2026-56000) Published: 2026-07-08 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1764" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1764" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/freebsd-cve-2026-56000/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1765">
+      <c r="A1765" t="inlineStr">
+        <is>
+          <t>CVE-2026-55999</t>
+        </is>
+      </c>
+      <c r="B1765" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="C1765" t="inlineStr">
+        <is>
+          <t>vulnerability FreeBSD: (Multiple Advisories) (CVE-2026-55999) Published: 2026-07-08 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1765" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1765" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/freebsd-cve-2026-55999/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1766">
+      <c r="A1766" t="inlineStr">
+        <is>
+          <t>CVE-2026-55645</t>
+        </is>
+      </c>
+      <c r="B1766" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="C1766" t="inlineStr">
+        <is>
+          <t>vulnerability FreeBSD: VID-a3a34818-79a0-11f1-b295-98b78501ef2a (CVE-2026-55645): xrdp -- multiple vulnerabilities Published: 2026-07-06 | Severity: 1</t>
+        </is>
+      </c>
+      <c r="D1766" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1766" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/freebsd-cve-2026-55645/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1767">
+      <c r="A1767" t="inlineStr">
+        <is>
+          <t>CVE-2026-55639</t>
+        </is>
+      </c>
+      <c r="B1767" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="C1767" t="inlineStr">
+        <is>
+          <t>vulnerability FreeBSD: VID-a3a34818-79a0-11f1-b295-98b78501ef2a (CVE-2026-55639): xrdp -- multiple vulnerabilities Published: 2026-07-06 | Severity: 1</t>
+        </is>
+      </c>
+      <c r="D1767" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1767" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/freebsd-cve-2026-55639/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rapid7_cves.xlsx
+++ b/rapid7_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1767"/>
+  <dimension ref="A1:E1807"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48125,6 +48125,1086 @@
         </is>
       </c>
     </row>
+    <row r="1768">
+      <c r="A1768" t="inlineStr">
+        <is>
+          <t>CVE-2026-57053</t>
+        </is>
+      </c>
+      <c r="B1768" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C1768" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1768" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E1768" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1769">
+      <c r="A1769" t="inlineStr">
+        <is>
+          <t>CVE-2026-5342</t>
+        </is>
+      </c>
+      <c r="B1769" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C1769" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1769" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E1769" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1770">
+      <c r="A1770" t="inlineStr">
+        <is>
+          <t>CVE-2026-48913</t>
+        </is>
+      </c>
+      <c r="B1770" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C1770" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1770" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E1770" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1771">
+      <c r="A1771" t="inlineStr">
+        <is>
+          <t>CVE-2026-44631</t>
+        </is>
+      </c>
+      <c r="B1771" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C1771" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1771" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E1771" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1772">
+      <c r="A1772" t="inlineStr">
+        <is>
+          <t>CVE-2026-44186</t>
+        </is>
+      </c>
+      <c r="B1772" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C1772" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1772" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E1772" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1773">
+      <c r="A1773" t="inlineStr">
+        <is>
+          <t>CVE-2026-44185</t>
+        </is>
+      </c>
+      <c r="B1773" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C1773" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1773" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E1773" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1774">
+      <c r="A1774" t="inlineStr">
+        <is>
+          <t>CVE-2026-44119</t>
+        </is>
+      </c>
+      <c r="B1774" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C1774" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1774" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E1774" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1775">
+      <c r="A1775" t="inlineStr">
+        <is>
+          <t>CVE-2026-43951</t>
+        </is>
+      </c>
+      <c r="B1775" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C1775" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1775" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E1775" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1776">
+      <c r="A1776" t="inlineStr">
+        <is>
+          <t>CVE-2026-42536</t>
+        </is>
+      </c>
+      <c r="B1776" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C1776" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1776" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E1776" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1777">
+      <c r="A1777" t="inlineStr">
+        <is>
+          <t>CVE-2026-42535</t>
+        </is>
+      </c>
+      <c r="B1777" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C1777" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1777" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E1777" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1778">
+      <c r="A1778" t="inlineStr">
+        <is>
+          <t>CVE-2026-34356</t>
+        </is>
+      </c>
+      <c r="B1778" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C1778" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1778" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E1778" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1779">
+      <c r="A1779" t="inlineStr">
+        <is>
+          <t>CVE-2026-34355</t>
+        </is>
+      </c>
+      <c r="B1779" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C1779" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1779" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E1779" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1780">
+      <c r="A1780" t="inlineStr">
+        <is>
+          <t>CVE-2026-29170</t>
+        </is>
+      </c>
+      <c r="B1780" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C1780" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1780" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E1780" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1781">
+      <c r="A1781" t="inlineStr">
+        <is>
+          <t>CVE-2026-29167</t>
+        </is>
+      </c>
+      <c r="B1781" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C1781" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1781" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E1781" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1782">
+      <c r="A1782" t="inlineStr">
+        <is>
+          <t>CVE-2026-24660</t>
+        </is>
+      </c>
+      <c r="B1782" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C1782" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1782" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E1782" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1783">
+      <c r="A1783" t="inlineStr">
+        <is>
+          <t>CVE-2026-24450</t>
+        </is>
+      </c>
+      <c r="B1783" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C1783" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1783" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E1783" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1784">
+      <c r="A1784" t="inlineStr">
+        <is>
+          <t>CVE-2026-21413</t>
+        </is>
+      </c>
+      <c r="B1784" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C1784" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1784" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E1784" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1785">
+      <c r="A1785" t="inlineStr">
+        <is>
+          <t>CVE-2026-20889</t>
+        </is>
+      </c>
+      <c r="B1785" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C1785" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1785" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E1785" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1786">
+      <c r="A1786" t="inlineStr">
+        <is>
+          <t>CVE-2026-20884</t>
+        </is>
+      </c>
+      <c r="B1786" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C1786" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1786" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E1786" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1787">
+      <c r="A1787" t="inlineStr">
+        <is>
+          <t>CVE-2026-20244</t>
+        </is>
+      </c>
+      <c r="B1787" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C1787" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1787" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E1787" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1788">
+      <c r="A1788" t="inlineStr">
+        <is>
+          <t>CVE-2026-57053</t>
+        </is>
+      </c>
+      <c r="B1788" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C1788" t="inlineStr">
+        <is>
+          <t>vulnerability Ubuntu: (CVE-2026-57053): libidn vulnerability Published: 2026-06-23 | Severity: 3 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1788" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E1788" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ubuntu-cve-2026-57053/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1789">
+      <c r="A1789" t="inlineStr">
+        <is>
+          <t>CVE-2026-5342</t>
+        </is>
+      </c>
+      <c r="B1789" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="C1789" t="inlineStr">
+        <is>
+          <t>vulnerability Ubuntu: (CVE-2026-5342): libraw vulnerability Published: 2026-04-02 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1789" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1789" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ubuntu-cve-2026-5342/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1790">
+      <c r="A1790" t="inlineStr">
+        <is>
+          <t>CVE-2026-48913</t>
+        </is>
+      </c>
+      <c r="B1790" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="C1790" t="inlineStr">
+        <is>
+          <t>vulnerability Ubuntu: USN-8516-1 (CVE-2026-48913): Apache HTTP Server vulnerabilities Published: 2026-07-08 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1790" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1790" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ubuntu-cve-2026-48913/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1791">
+      <c r="A1791" t="inlineStr">
+        <is>
+          <t>CVE-2026-44631</t>
+        </is>
+      </c>
+      <c r="B1791" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="C1791" t="inlineStr">
+        <is>
+          <t>vulnerability Ubuntu: USN-8516-1 (CVE-2026-44631): Apache HTTP Server vulnerabilities Published: 2026-07-08 | Severity: 10 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1791" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1791" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ubuntu-cve-2026-44631/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1792">
+      <c r="A1792" t="inlineStr">
+        <is>
+          <t>CVE-2026-44186</t>
+        </is>
+      </c>
+      <c r="B1792" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="C1792" t="inlineStr">
+        <is>
+          <t>vulnerability Ubuntu: USN-8516-1 (CVE-2026-44186): Apache HTTP Server vulnerabilities Published: 2026-07-08 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1792" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1792" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ubuntu-cve-2026-44186/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1793">
+      <c r="A1793" t="inlineStr">
+        <is>
+          <t>CVE-2026-44185</t>
+        </is>
+      </c>
+      <c r="B1793" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="C1793" t="inlineStr">
+        <is>
+          <t>vulnerability Ubuntu: USN-8516-1 (CVE-2026-44185): Apache HTTP Server vulnerabilities Published: 2026-07-08 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1793" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1793" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ubuntu-cve-2026-44185/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1794">
+      <c r="A1794" t="inlineStr">
+        <is>
+          <t>CVE-2026-44119</t>
+        </is>
+      </c>
+      <c r="B1794" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="C1794" t="inlineStr">
+        <is>
+          <t>vulnerability Ubuntu: USN-8516-1 (CVE-2026-44119): Apache HTTP Server vulnerabilities Published: 2026-07-08 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1794" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1794" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ubuntu-cve-2026-44119/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1795">
+      <c r="A1795" t="inlineStr">
+        <is>
+          <t>CVE-2026-43951</t>
+        </is>
+      </c>
+      <c r="B1795" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="C1795" t="inlineStr">
+        <is>
+          <t>vulnerability Ubuntu: USN-8516-1 (CVE-2026-43951): Apache HTTP Server vulnerabilities Published: 2026-07-08 | Severity: 6 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1795" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1795" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ubuntu-cve-2026-43951/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1796">
+      <c r="A1796" t="inlineStr">
+        <is>
+          <t>CVE-2026-42536</t>
+        </is>
+      </c>
+      <c r="B1796" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="C1796" t="inlineStr">
+        <is>
+          <t>vulnerability Ubuntu: USN-8516-1 (CVE-2026-42536): Apache HTTP Server vulnerabilities Published: 2026-07-08 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1796" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1796" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ubuntu-cve-2026-42536/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1797">
+      <c r="A1797" t="inlineStr">
+        <is>
+          <t>CVE-2026-42535</t>
+        </is>
+      </c>
+      <c r="B1797" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="C1797" t="inlineStr">
+        <is>
+          <t>vulnerability Ubuntu: USN-8516-1 (CVE-2026-42535): Apache HTTP Server vulnerabilities Published: 2026-07-08 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1797" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1797" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ubuntu-cve-2026-42535/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1798">
+      <c r="A1798" t="inlineStr">
+        <is>
+          <t>CVE-2026-34356</t>
+        </is>
+      </c>
+      <c r="B1798" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="C1798" t="inlineStr">
+        <is>
+          <t>vulnerability Ubuntu: USN-8516-1 (CVE-2026-34356): Apache HTTP Server vulnerabilities Published: 2026-07-08 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1798" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1798" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ubuntu-cve-2026-34356/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1799">
+      <c r="A1799" t="inlineStr">
+        <is>
+          <t>CVE-2026-34355</t>
+        </is>
+      </c>
+      <c r="B1799" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="C1799" t="inlineStr">
+        <is>
+          <t>vulnerability Ubuntu: USN-8516-1 (CVE-2026-34355): Apache HTTP Server vulnerabilities Published: 2026-07-08 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1799" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1799" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ubuntu-cve-2026-34355/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1800">
+      <c r="A1800" t="inlineStr">
+        <is>
+          <t>CVE-2026-29170</t>
+        </is>
+      </c>
+      <c r="B1800" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="C1800" t="inlineStr">
+        <is>
+          <t>vulnerability Ubuntu: USN-8516-1 (CVE-2026-29170): Apache HTTP Server vulnerabilities Published: 2026-07-08 | Severity: 6 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1800" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1800" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ubuntu-cve-2026-29170/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1801">
+      <c r="A1801" t="inlineStr">
+        <is>
+          <t>CVE-2026-29167</t>
+        </is>
+      </c>
+      <c r="B1801" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="C1801" t="inlineStr">
+        <is>
+          <t>vulnerability Ubuntu: USN-8516-1 (CVE-2026-29167): Apache HTTP Server vulnerabilities Published: 2026-07-08 | Severity: 10 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1801" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1801" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ubuntu-cve-2026-29167/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1802">
+      <c r="A1802" t="inlineStr">
+        <is>
+          <t>CVE-2026-24660</t>
+        </is>
+      </c>
+      <c r="B1802" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="C1802" t="inlineStr">
+        <is>
+          <t>vulnerability Ubuntu: (CVE-2026-24660): libraw vulnerability Published: 2026-04-07 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1802" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1802" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ubuntu-cve-2026-24660/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1803">
+      <c r="A1803" t="inlineStr">
+        <is>
+          <t>CVE-2026-24450</t>
+        </is>
+      </c>
+      <c r="B1803" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="C1803" t="inlineStr">
+        <is>
+          <t>vulnerability Ubuntu: (CVE-2026-24450): libraw vulnerability Published: 2026-04-07 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1803" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1803" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ubuntu-cve-2026-24450/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1804">
+      <c r="A1804" t="inlineStr">
+        <is>
+          <t>CVE-2026-21413</t>
+        </is>
+      </c>
+      <c r="B1804" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="C1804" t="inlineStr">
+        <is>
+          <t>vulnerability Ubuntu: (CVE-2026-21413): libraw vulnerability Published: 2026-04-07 | Severity: 10 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1804" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1804" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ubuntu-cve-2026-21413/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1805">
+      <c r="A1805" t="inlineStr">
+        <is>
+          <t>CVE-2026-20889</t>
+        </is>
+      </c>
+      <c r="B1805" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="C1805" t="inlineStr">
+        <is>
+          <t>vulnerability Ubuntu: (CVE-2026-20889): libraw vulnerability Published: 2026-04-07 | Severity: 10 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1805" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1805" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ubuntu-cve-2026-20889/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1806">
+      <c r="A1806" t="inlineStr">
+        <is>
+          <t>CVE-2026-20884</t>
+        </is>
+      </c>
+      <c r="B1806" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="C1806" t="inlineStr">
+        <is>
+          <t>vulnerability Ubuntu: (CVE-2026-20884): libraw vulnerability Published: 2026-04-07 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1806" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1806" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ubuntu-cve-2026-20884/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1807">
+      <c r="A1807" t="inlineStr">
+        <is>
+          <t>CVE-2026-20244</t>
+        </is>
+      </c>
+      <c r="B1807" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="C1807" t="inlineStr">
+        <is>
+          <t>vulnerability Ubuntu: USN-8517-1 (CVE-2026-20244): ClamAV vulnerabilities Published: 2026-07-08 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1807" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1807" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/ubuntu-cve-2026-20244/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rapid7_cves.xlsx
+++ b/rapid7_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1807"/>
+  <dimension ref="A1:E1847"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49205,6 +49205,1086 @@
         </is>
       </c>
     </row>
+    <row r="1808">
+      <c r="A1808" t="inlineStr">
+        <is>
+          <t>CVE-2026-13020</t>
+        </is>
+      </c>
+      <c r="B1808" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="C1808" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1808" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1808" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1809">
+      <c r="A1809" t="inlineStr">
+        <is>
+          <t>CVE-2026-13019</t>
+        </is>
+      </c>
+      <c r="B1809" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="C1809" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1809" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1809" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1810">
+      <c r="A1810" t="inlineStr">
+        <is>
+          <t>CVE-2025-9142</t>
+        </is>
+      </c>
+      <c r="B1810" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="C1810" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1810" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1810" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1811">
+      <c r="A1811" t="inlineStr">
+        <is>
+          <t>CVE-2026-53341</t>
+        </is>
+      </c>
+      <c r="B1811" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="C1811" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1811" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1811" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1812">
+      <c r="A1812" t="inlineStr">
+        <is>
+          <t>CVE-2026-53327</t>
+        </is>
+      </c>
+      <c r="B1812" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="C1812" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1812" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1812" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1813">
+      <c r="A1813" t="inlineStr">
+        <is>
+          <t>CVE-2026-53325</t>
+        </is>
+      </c>
+      <c r="B1813" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="C1813" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1813" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1813" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1814">
+      <c r="A1814" t="inlineStr">
+        <is>
+          <t>CVE-2026-53273</t>
+        </is>
+      </c>
+      <c r="B1814" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="C1814" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1814" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1814" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1815">
+      <c r="A1815" t="inlineStr">
+        <is>
+          <t>CVE-2026-53271</t>
+        </is>
+      </c>
+      <c r="B1815" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="C1815" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1815" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1815" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1816">
+      <c r="A1816" t="inlineStr">
+        <is>
+          <t>CVE-2026-53263</t>
+        </is>
+      </c>
+      <c r="B1816" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="C1816" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1816" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1816" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1817">
+      <c r="A1817" t="inlineStr">
+        <is>
+          <t>CVE-2026-53261</t>
+        </is>
+      </c>
+      <c r="B1817" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="C1817" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1817" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1817" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1818">
+      <c r="A1818" t="inlineStr">
+        <is>
+          <t>CVE-2026-53251</t>
+        </is>
+      </c>
+      <c r="B1818" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="C1818" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1818" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1818" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1819">
+      <c r="A1819" t="inlineStr">
+        <is>
+          <t>CVE-2026-53247</t>
+        </is>
+      </c>
+      <c r="B1819" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="C1819" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1819" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1819" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1820">
+      <c r="A1820" t="inlineStr">
+        <is>
+          <t>CVE-2026-53241</t>
+        </is>
+      </c>
+      <c r="B1820" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="C1820" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1820" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1820" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1821">
+      <c r="A1821" t="inlineStr">
+        <is>
+          <t>CVE-2026-53235</t>
+        </is>
+      </c>
+      <c r="B1821" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="C1821" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1821" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1821" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1822">
+      <c r="A1822" t="inlineStr">
+        <is>
+          <t>CVE-2026-53234</t>
+        </is>
+      </c>
+      <c r="B1822" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="C1822" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1822" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1822" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1823">
+      <c r="A1823" t="inlineStr">
+        <is>
+          <t>CVE-2026-53233</t>
+        </is>
+      </c>
+      <c r="B1823" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="C1823" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1823" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1823" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1824">
+      <c r="A1824" t="inlineStr">
+        <is>
+          <t>CVE-2026-53214</t>
+        </is>
+      </c>
+      <c r="B1824" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="C1824" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1824" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1824" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1825">
+      <c r="A1825" t="inlineStr">
+        <is>
+          <t>CVE-2026-53210</t>
+        </is>
+      </c>
+      <c r="B1825" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="C1825" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1825" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1825" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1826">
+      <c r="A1826" t="inlineStr">
+        <is>
+          <t>CVE-2026-53205</t>
+        </is>
+      </c>
+      <c r="B1826" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="C1826" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1826" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1826" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1827">
+      <c r="A1827" t="inlineStr">
+        <is>
+          <t>CVE-2026-53203</t>
+        </is>
+      </c>
+      <c r="B1827" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="C1827" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1827" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1827" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1828">
+      <c r="A1828" t="inlineStr">
+        <is>
+          <t>CVE-2026-13020</t>
+        </is>
+      </c>
+      <c r="B1828" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="C1828" t="inlineStr">
+        <is>
+          <t>vulnerability Kubernetes: CVE-2026-13020: A Weak Password Recovery Mechanism for Forgotten Password exists in Esri Portal for ArcGIS versions 12.1 and</t>
+        </is>
+      </c>
+      <c r="D1828" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1828" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/kubernetes-cve-2026-13020/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1829">
+      <c r="A1829" t="inlineStr">
+        <is>
+          <t>CVE-2026-13019</t>
+        </is>
+      </c>
+      <c r="B1829" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="C1829" t="inlineStr">
+        <is>
+          <t>vulnerability Kubernetes: CVE-2026-13019: Esri Portal for ArcGIS versions 12.1 and earlier on Windows, Linux and Kubernetes have a missing authenticat</t>
+        </is>
+      </c>
+      <c r="D1829" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1829" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/kubernetes-cve-2026-13019/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1830">
+      <c r="A1830" t="inlineStr">
+        <is>
+          <t>CVE-2025-9142</t>
+        </is>
+      </c>
+      <c r="B1830" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="C1830" t="inlineStr">
+        <is>
+          <t>vulnerability Check Point Harmony SASE Windows Agent: CVE-2025-9142: Path Traversal Leading to Local Privilege Escalation Published: 2026-01-14 | Seve</t>
+        </is>
+      </c>
+      <c r="D1830" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1830" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/checkpoint-harmony-sase-cve-2025-9142/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1831">
+      <c r="A1831" t="inlineStr">
+        <is>
+          <t>CVE-2026-53341</t>
+        </is>
+      </c>
+      <c r="B1831" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C1831" t="inlineStr">
+        <is>
+          <t>vulnerability VMware Photon OS: CVE-2026-53341 Published: 2026-07-01 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1831" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1831" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/vmware-photon_os-cve-2026-53341/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1832">
+      <c r="A1832" t="inlineStr">
+        <is>
+          <t>CVE-2026-53327</t>
+        </is>
+      </c>
+      <c r="B1832" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C1832" t="inlineStr">
+        <is>
+          <t>vulnerability VMware Photon OS: CVE-2026-53327 Published: 2026-07-01 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1832" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1832" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/vmware-photon_os-cve-2026-53327/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1833">
+      <c r="A1833" t="inlineStr">
+        <is>
+          <t>CVE-2026-53325</t>
+        </is>
+      </c>
+      <c r="B1833" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C1833" t="inlineStr">
+        <is>
+          <t>vulnerability VMware Photon OS: CVE-2026-53325 Published: 2026-06-29 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1833" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1833" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/vmware-photon_os-cve-2026-53325/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1834">
+      <c r="A1834" t="inlineStr">
+        <is>
+          <t>CVE-2026-53273</t>
+        </is>
+      </c>
+      <c r="B1834" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C1834" t="inlineStr">
+        <is>
+          <t>vulnerability VMware Photon OS: CVE-2026-53273 Published: 2026-06-25 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1834" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1834" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/vmware-photon_os-cve-2026-53273/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1835">
+      <c r="A1835" t="inlineStr">
+        <is>
+          <t>CVE-2026-53271</t>
+        </is>
+      </c>
+      <c r="B1835" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C1835" t="inlineStr">
+        <is>
+          <t>vulnerability VMware Photon OS: CVE-2026-53271 Published: 2026-06-25 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1835" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1835" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/vmware-photon_os-cve-2026-53271/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1836">
+      <c r="A1836" t="inlineStr">
+        <is>
+          <t>CVE-2026-53263</t>
+        </is>
+      </c>
+      <c r="B1836" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C1836" t="inlineStr">
+        <is>
+          <t>vulnerability VMware Photon OS: CVE-2026-53263 Published: 2026-06-25 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1836" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1836" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/vmware-photon_os-cve-2026-53263/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1837">
+      <c r="A1837" t="inlineStr">
+        <is>
+          <t>CVE-2026-53261</t>
+        </is>
+      </c>
+      <c r="B1837" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C1837" t="inlineStr">
+        <is>
+          <t>vulnerability VMware Photon OS: CVE-2026-53261 Published: 2026-06-25 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1837" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1837" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/vmware-photon_os-cve-2026-53261/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1838">
+      <c r="A1838" t="inlineStr">
+        <is>
+          <t>CVE-2026-53251</t>
+        </is>
+      </c>
+      <c r="B1838" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C1838" t="inlineStr">
+        <is>
+          <t>vulnerability VMware Photon OS: CVE-2026-53251 Published: 2026-06-25 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1838" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1838" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/vmware-photon_os-cve-2026-53251/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1839">
+      <c r="A1839" t="inlineStr">
+        <is>
+          <t>CVE-2026-53247</t>
+        </is>
+      </c>
+      <c r="B1839" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C1839" t="inlineStr">
+        <is>
+          <t>vulnerability VMware Photon OS: CVE-2026-53247 Published: 2026-06-25 | Severity: 10 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1839" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1839" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/vmware-photon_os-cve-2026-53247/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1840">
+      <c r="A1840" t="inlineStr">
+        <is>
+          <t>CVE-2026-53241</t>
+        </is>
+      </c>
+      <c r="B1840" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C1840" t="inlineStr">
+        <is>
+          <t>vulnerability VMware Photon OS: CVE-2026-53241 Published: 2026-06-25 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1840" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1840" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/vmware-photon_os-cve-2026-53241/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1841">
+      <c r="A1841" t="inlineStr">
+        <is>
+          <t>CVE-2026-53235</t>
+        </is>
+      </c>
+      <c r="B1841" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C1841" t="inlineStr">
+        <is>
+          <t>vulnerability VMware Photon OS: CVE-2026-53235 Published: 2026-06-25 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1841" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1841" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/vmware-photon_os-cve-2026-53235/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1842">
+      <c r="A1842" t="inlineStr">
+        <is>
+          <t>CVE-2026-53234</t>
+        </is>
+      </c>
+      <c r="B1842" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C1842" t="inlineStr">
+        <is>
+          <t>vulnerability VMware Photon OS: CVE-2026-53234 Published: 2026-06-25 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1842" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1842" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/vmware-photon_os-cve-2026-53234/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1843">
+      <c r="A1843" t="inlineStr">
+        <is>
+          <t>CVE-2026-53233</t>
+        </is>
+      </c>
+      <c r="B1843" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C1843" t="inlineStr">
+        <is>
+          <t>vulnerability VMware Photon OS: CVE-2026-53233 Published: 2026-06-25 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1843" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1843" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/vmware-photon_os-cve-2026-53233/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1844">
+      <c r="A1844" t="inlineStr">
+        <is>
+          <t>CVE-2026-53214</t>
+        </is>
+      </c>
+      <c r="B1844" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C1844" t="inlineStr">
+        <is>
+          <t>vulnerability VMware Photon OS: CVE-2026-53214 Published: 2026-06-25 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1844" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1844" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/vmware-photon_os-cve-2026-53214/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1845">
+      <c r="A1845" t="inlineStr">
+        <is>
+          <t>CVE-2026-53210</t>
+        </is>
+      </c>
+      <c r="B1845" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C1845" t="inlineStr">
+        <is>
+          <t>vulnerability VMware Photon OS: CVE-2026-53210 Published: 2026-06-25 | Severity: 5 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1845" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1845" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/vmware-photon_os-cve-2026-53210/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1846">
+      <c r="A1846" t="inlineStr">
+        <is>
+          <t>CVE-2026-53205</t>
+        </is>
+      </c>
+      <c r="B1846" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C1846" t="inlineStr">
+        <is>
+          <t>vulnerability VMware Photon OS: CVE-2026-53205 Published: 2026-06-25 | Severity: 6 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1846" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1846" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/vmware-photon_os-cve-2026-53205/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1847">
+      <c r="A1847" t="inlineStr">
+        <is>
+          <t>CVE-2026-53203</t>
+        </is>
+      </c>
+      <c r="B1847" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C1847" t="inlineStr">
+        <is>
+          <t>vulnerability VMware Photon OS: CVE-2026-53203 Published: 2026-06-25 | Severity: 6 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1847" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1847" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/vmware-photon_os-cve-2026-53203/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rapid7_cves.xlsx
+++ b/rapid7_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1847"/>
+  <dimension ref="A1:E1887"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50285,6 +50285,1086 @@
         </is>
       </c>
     </row>
+    <row r="1848">
+      <c r="A1848" t="inlineStr">
+        <is>
+          <t>CVE-2026-12385</t>
+        </is>
+      </c>
+      <c r="B1848" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C1848" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1848" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1848" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1849">
+      <c r="A1849" t="inlineStr">
+        <is>
+          <t>CVE-2026-11390</t>
+        </is>
+      </c>
+      <c r="B1849" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C1849" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1849" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1849" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1850">
+      <c r="A1850" t="inlineStr">
+        <is>
+          <t>CVE-2026-12536</t>
+        </is>
+      </c>
+      <c r="B1850" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C1850" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1850" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1850" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1851">
+      <c r="A1851" t="inlineStr">
+        <is>
+          <t>CVE-2026-11802</t>
+        </is>
+      </c>
+      <c r="B1851" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C1851" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1851" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1851" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1852">
+      <c r="A1852" t="inlineStr">
+        <is>
+          <t>CVE-2026-7640</t>
+        </is>
+      </c>
+      <c r="B1852" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C1852" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1852" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1852" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1853">
+      <c r="A1853" t="inlineStr">
+        <is>
+          <t>CVE-2026-9341</t>
+        </is>
+      </c>
+      <c r="B1853" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C1853" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1853" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1853" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1854">
+      <c r="A1854" t="inlineStr">
+        <is>
+          <t>CVE-2026-48907</t>
+        </is>
+      </c>
+      <c r="B1854" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C1854" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1854" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1854" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1855">
+      <c r="A1855" t="inlineStr">
+        <is>
+          <t>CVE-2026-48558</t>
+        </is>
+      </c>
+      <c r="B1855" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C1855" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1855" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1855" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1856">
+      <c r="A1856" t="inlineStr">
+        <is>
+          <t>CVE-2026-40215</t>
+        </is>
+      </c>
+      <c r="B1856" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C1856" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1856" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1856" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1857">
+      <c r="A1857" t="inlineStr">
+        <is>
+          <t>CVE-2026-56003</t>
+        </is>
+      </c>
+      <c r="B1857" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C1857" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1857" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1857" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1858">
+      <c r="A1858" t="inlineStr">
+        <is>
+          <t>CVE-2026-56002</t>
+        </is>
+      </c>
+      <c r="B1858" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C1858" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1858" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1858" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1859">
+      <c r="A1859" t="inlineStr">
+        <is>
+          <t>CVE-2026-56001</t>
+        </is>
+      </c>
+      <c r="B1859" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C1859" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1859" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1859" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1860">
+      <c r="A1860" t="inlineStr">
+        <is>
+          <t>CVE-2026-15133</t>
+        </is>
+      </c>
+      <c r="B1860" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C1860" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1860" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1860" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1861">
+      <c r="A1861" t="inlineStr">
+        <is>
+          <t>CVE-2026-15132</t>
+        </is>
+      </c>
+      <c r="B1861" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C1861" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1861" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1861" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1862">
+      <c r="A1862" t="inlineStr">
+        <is>
+          <t>CVE-2026-15131</t>
+        </is>
+      </c>
+      <c r="B1862" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C1862" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1862" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1862" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1863">
+      <c r="A1863" t="inlineStr">
+        <is>
+          <t>CVE-2026-15130</t>
+        </is>
+      </c>
+      <c r="B1863" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C1863" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1863" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1863" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1864">
+      <c r="A1864" t="inlineStr">
+        <is>
+          <t>CVE-2026-15129</t>
+        </is>
+      </c>
+      <c r="B1864" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C1864" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1864" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1864" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1865">
+      <c r="A1865" t="inlineStr">
+        <is>
+          <t>CVE-2026-15128</t>
+        </is>
+      </c>
+      <c r="B1865" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C1865" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1865" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1865" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1866">
+      <c r="A1866" t="inlineStr">
+        <is>
+          <t>CVE-2026-15127</t>
+        </is>
+      </c>
+      <c r="B1866" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C1866" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1866" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1866" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1867">
+      <c r="A1867" t="inlineStr">
+        <is>
+          <t>CVE-2026-15126</t>
+        </is>
+      </c>
+      <c r="B1867" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C1867" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1867" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1867" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1868">
+      <c r="A1868" t="inlineStr">
+        <is>
+          <t>CVE-2026-12385</t>
+        </is>
+      </c>
+      <c r="B1868" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C1868" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: smart-slider-3: CVE-2026-12385: Exposure of Sensitive Information to an Unauthorized Actor Published: 2026-07-13 | Sev</t>
+        </is>
+      </c>
+      <c r="D1868" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1868" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/smart-slider-3-plugin-cve-2026-12385/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1869">
+      <c r="A1869" t="inlineStr">
+        <is>
+          <t>CVE-2026-11390</t>
+        </is>
+      </c>
+      <c r="B1869" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C1869" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: news-kit-elementor-addons: CVE-2026-11390: Improper Neutralization of Input During Web Page Generation ('Cross-site Sc</t>
+        </is>
+      </c>
+      <c r="D1869" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1869" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/news-kit-elementor-addons-plugin-cve-2026-11390/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1870">
+      <c r="A1870" t="inlineStr">
+        <is>
+          <t>CVE-2026-12536</t>
+        </is>
+      </c>
+      <c r="B1870" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C1870" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: fusion-builder: CVE-2026-12536: Improper Neutralization of Input During Web Page Generation ('Cross-site Scripting') P</t>
+        </is>
+      </c>
+      <c r="D1870" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1870" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/fusion-builder-plugin-cve-2026-12536/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1871">
+      <c r="A1871" t="inlineStr">
+        <is>
+          <t>CVE-2026-11802</t>
+        </is>
+      </c>
+      <c r="B1871" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C1871" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vulnerability WordPress Plugin: foodbook-light-online-food-ordering-system: CVE-2026-11802: Missing Authorization Published: 2026-07-13 | Severity: 5 </t>
+        </is>
+      </c>
+      <c r="D1871" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1871" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/foodbook-light-online-food-ordering-system-plugin-cve-2026-11802/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1872">
+      <c r="A1872" t="inlineStr">
+        <is>
+          <t>CVE-2026-7640</t>
+        </is>
+      </c>
+      <c r="B1872" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C1872" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: customer-area: CVE-2026-7640: Improper Neutralization of Input During Web Page Generation ('Cross-site Scripting') Pub</t>
+        </is>
+      </c>
+      <c r="D1872" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1872" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/customer-area-plugin-cve-2026-7640/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1873">
+      <c r="A1873" t="inlineStr">
+        <is>
+          <t>CVE-2026-9341</t>
+        </is>
+      </c>
+      <c r="B1873" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C1873" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Plugin: academy: CVE-2026-9341: Authorization Bypass Through User-Controlled Key Published: 2026-07-13 | Severity: 4 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1873" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1873" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/academy-plugin-cve-2026-9341/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1874">
+      <c r="A1874" t="inlineStr">
+        <is>
+          <t>CVE-2026-48907</t>
+        </is>
+      </c>
+      <c r="B1874" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C1874" t="inlineStr">
+        <is>
+          <t>vulnerability Widget Factory JCE (Joomla Content Editor): CVE-2026-48907: Unauthenticated Remote Code Execution via Improper Access Control Published:</t>
+        </is>
+      </c>
+      <c r="D1874" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1874" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/widgetfactory-jce-cve-2026-48907/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1875">
+      <c r="A1875" t="inlineStr">
+        <is>
+          <t>CVE-2026-48558</t>
+        </is>
+      </c>
+      <c r="B1875" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C1875" t="inlineStr">
+        <is>
+          <t>vulnerability SimpleHelp: CVE-2026-48558: Authentication Bypass in OIDC Authentication Flow Published: 2026-06-12 | Severity: 10 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1875" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1875" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/simplehelp-cve-2026-48558/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1876">
+      <c r="A1876" t="inlineStr">
+        <is>
+          <t>CVE-2026-40215</t>
+        </is>
+      </c>
+      <c r="B1876" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C1876" t="inlineStr">
+        <is>
+          <t>vulnerability Amazon Linux 2023: CVE-2026-40215: Medium priority package update for openvpn Published: 2026-06-08 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1876" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1876" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/amazon_linux_2023-cve-2026-40215/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1877">
+      <c r="A1877" t="inlineStr">
+        <is>
+          <t>CVE-2026-56003</t>
+        </is>
+      </c>
+      <c r="B1877" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C1877" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-56003: libxfont -- security update Published: 2026-07-13 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1877" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1877" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-56003/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1878">
+      <c r="A1878" t="inlineStr">
+        <is>
+          <t>CVE-2026-56002</t>
+        </is>
+      </c>
+      <c r="B1878" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C1878" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-56002: libxfont -- security update Published: 2026-07-13 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1878" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1878" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-56002/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1879">
+      <c r="A1879" t="inlineStr">
+        <is>
+          <t>CVE-2026-56001</t>
+        </is>
+      </c>
+      <c r="B1879" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C1879" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-56001: libxfont -- security update Published: 2026-07-13 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1879" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1879" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-56001/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1880">
+      <c r="A1880" t="inlineStr">
+        <is>
+          <t>CVE-2026-15133</t>
+        </is>
+      </c>
+      <c r="B1880" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C1880" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-15133: chromium -- security update Published: 2026-07-13 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1880" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1880" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-15133/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1881">
+      <c r="A1881" t="inlineStr">
+        <is>
+          <t>CVE-2026-15132</t>
+        </is>
+      </c>
+      <c r="B1881" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C1881" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-15132: chromium -- security update Published: 2026-07-13 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1881" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1881" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-15132/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1882">
+      <c r="A1882" t="inlineStr">
+        <is>
+          <t>CVE-2026-15131</t>
+        </is>
+      </c>
+      <c r="B1882" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C1882" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-15131: chromium -- security update Published: 2026-07-13 | Severity: 4 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1882" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1882" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-15131/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1883">
+      <c r="A1883" t="inlineStr">
+        <is>
+          <t>CVE-2026-15130</t>
+        </is>
+      </c>
+      <c r="B1883" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C1883" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-15130: chromium -- security update Published: 2026-07-13 | Severity: 4 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1883" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1883" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-15130/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1884">
+      <c r="A1884" t="inlineStr">
+        <is>
+          <t>CVE-2026-15129</t>
+        </is>
+      </c>
+      <c r="B1884" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C1884" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-15129: chromium -- security update Published: 2026-07-13 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1884" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1884" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-15129/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1885">
+      <c r="A1885" t="inlineStr">
+        <is>
+          <t>CVE-2026-15128</t>
+        </is>
+      </c>
+      <c r="B1885" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C1885" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-15128: chromium -- security update Published: 2026-07-13 | Severity: 6 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1885" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1885" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-15128/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1886">
+      <c r="A1886" t="inlineStr">
+        <is>
+          <t>CVE-2026-15127</t>
+        </is>
+      </c>
+      <c r="B1886" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C1886" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-15127: chromium -- security update Published: 2026-07-13 | Severity: 6 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1886" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1886" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-15127/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1887">
+      <c r="A1887" t="inlineStr">
+        <is>
+          <t>CVE-2026-15126</t>
+        </is>
+      </c>
+      <c r="B1887" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C1887" t="inlineStr">
+        <is>
+          <t>vulnerability Debian: CVE-2026-15126: chromium -- security update Published: 2026-07-13 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1887" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1887" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/debian-cve-2026-15126/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rapid7_cves.xlsx
+++ b/rapid7_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1887"/>
+  <dimension ref="A1:E1927"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51365,6 +51365,1086 @@
         </is>
       </c>
     </row>
+    <row r="1888">
+      <c r="A1888" t="inlineStr">
+        <is>
+          <t>CVE-2026-57405</t>
+        </is>
+      </c>
+      <c r="B1888" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="C1888" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1888" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1888" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1889">
+      <c r="A1889" t="inlineStr">
+        <is>
+          <t>CVE-2026-50650</t>
+        </is>
+      </c>
+      <c r="B1889" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="C1889" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1889" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1889" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1890">
+      <c r="A1890" t="inlineStr">
+        <is>
+          <t>CVE-2026-50648</t>
+        </is>
+      </c>
+      <c r="B1890" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="C1890" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1890" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1890" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1891">
+      <c r="A1891" t="inlineStr">
+        <is>
+          <t>CVE-2026-50646</t>
+        </is>
+      </c>
+      <c r="B1891" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="C1891" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1891" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1891" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1892">
+      <c r="A1892" t="inlineStr">
+        <is>
+          <t>CVE-2026-50527</t>
+        </is>
+      </c>
+      <c r="B1892" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="C1892" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1892" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1892" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1893">
+      <c r="A1893" t="inlineStr">
+        <is>
+          <t>CVE-2026-47302</t>
+        </is>
+      </c>
+      <c r="B1893" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="C1893" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1893" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1893" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1894">
+      <c r="A1894" t="inlineStr">
+        <is>
+          <t>CVE-2026-58379</t>
+        </is>
+      </c>
+      <c r="B1894" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="C1894" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1894" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1894" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1895">
+      <c r="A1895" t="inlineStr">
+        <is>
+          <t>CVE-2026-55380</t>
+        </is>
+      </c>
+      <c r="B1895" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="C1895" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1895" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1895" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1896">
+      <c r="A1896" t="inlineStr">
+        <is>
+          <t>CVE-2026-55379</t>
+        </is>
+      </c>
+      <c r="B1896" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="C1896" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1896" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1896" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1897">
+      <c r="A1897" t="inlineStr">
+        <is>
+          <t>CVE-2026-54060</t>
+        </is>
+      </c>
+      <c r="B1897" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="C1897" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1897" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1897" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1898">
+      <c r="A1898" t="inlineStr">
+        <is>
+          <t>CVE-2026-54059</t>
+        </is>
+      </c>
+      <c r="B1898" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="C1898" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1898" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1898" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1899">
+      <c r="A1899" t="inlineStr">
+        <is>
+          <t>CVE-2026-53016</t>
+        </is>
+      </c>
+      <c r="B1899" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="C1899" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1899" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1899" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1900">
+      <c r="A1900" t="inlineStr">
+        <is>
+          <t>CVE-2026-46086</t>
+        </is>
+      </c>
+      <c r="B1900" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="C1900" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1900" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1900" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1901">
+      <c r="A1901" t="inlineStr">
+        <is>
+          <t>CVE-2026-22979</t>
+        </is>
+      </c>
+      <c r="B1901" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="C1901" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1901" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1901" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1902">
+      <c r="A1902" t="inlineStr">
+        <is>
+          <t>CVE-2026-15308</t>
+        </is>
+      </c>
+      <c r="B1902" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="C1902" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1902" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1902" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1903">
+      <c r="A1903" t="inlineStr">
+        <is>
+          <t>CVE-2026-48337</t>
+        </is>
+      </c>
+      <c r="B1903" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="C1903" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1903" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1903" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1904">
+      <c r="A1904" t="inlineStr">
+        <is>
+          <t>CVE-2026-48336</t>
+        </is>
+      </c>
+      <c r="B1904" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="C1904" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1904" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1904" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1905">
+      <c r="A1905" t="inlineStr">
+        <is>
+          <t>CVE-2026-48335</t>
+        </is>
+      </c>
+      <c r="B1905" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="C1905" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1905" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1905" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1906">
+      <c r="A1906" t="inlineStr">
+        <is>
+          <t>CVE-2026-48334</t>
+        </is>
+      </c>
+      <c r="B1906" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="C1906" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1906" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1906" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1907">
+      <c r="A1907" t="inlineStr">
+        <is>
+          <t>CVE-2026-48275</t>
+        </is>
+      </c>
+      <c r="B1907" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="C1907" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1907" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1907" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1908">
+      <c r="A1908" t="inlineStr">
+        <is>
+          <t>CVE-2026-57405</t>
+        </is>
+      </c>
+      <c r="B1908" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="C1908" t="inlineStr">
+        <is>
+          <t>vulnerability WordPress Theme: open-shop: CVE-2026-57405: Missing Authorization Published: 2026-07-08 | Severity: 4 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1908" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E1908" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/open-shop-theme-cve-2026-57405/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1909">
+      <c r="A1909" t="inlineStr">
+        <is>
+          <t>CVE-2026-50650</t>
+        </is>
+      </c>
+      <c r="B1909" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="C1909" t="inlineStr">
+        <is>
+          <t>vulnerability Microsoft .NET Framework: CVE-2026-50650: .NET Framework Elevation of Privilege Vulnerability Published: 2026-07-14 | Severity: 7 EXPLOR</t>
+        </is>
+      </c>
+      <c r="D1909" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1909" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/microsoft-dot_net_framework-cve-2026-50650/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1910">
+      <c r="A1910" t="inlineStr">
+        <is>
+          <t>CVE-2026-50648</t>
+        </is>
+      </c>
+      <c r="B1910" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="C1910" t="inlineStr">
+        <is>
+          <t>vulnerability Microsoft .NET Framework: CVE-2026-50648: .NET Framework Denial of Service Vulnerability Published: 2026-07-14 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1910" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1910" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/microsoft-dot_net_framework-cve-2026-50648/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1911">
+      <c r="A1911" t="inlineStr">
+        <is>
+          <t>CVE-2026-50646</t>
+        </is>
+      </c>
+      <c r="B1911" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="C1911" t="inlineStr">
+        <is>
+          <t>vulnerability Microsoft .NET Framework: CVE-2026-50646: .NET Framework Remote Code Execution Vulnerability Published: 2026-07-14 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1911" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1911" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/microsoft-dot_net_framework-cve-2026-50646/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1912">
+      <c r="A1912" t="inlineStr">
+        <is>
+          <t>CVE-2026-50527</t>
+        </is>
+      </c>
+      <c r="B1912" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="C1912" t="inlineStr">
+        <is>
+          <t>vulnerability Microsoft .NET Framework: CVE-2026-50527: .NET Framework Denial of Service Vulnerability Published: 2026-07-14 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1912" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1912" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/microsoft-dot_net_framework-cve-2026-50527/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1913">
+      <c r="A1913" t="inlineStr">
+        <is>
+          <t>CVE-2026-47302</t>
+        </is>
+      </c>
+      <c r="B1913" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="C1913" t="inlineStr">
+        <is>
+          <t>vulnerability Microsoft .NET Framework: CVE-2026-47302: .NET Denial of Service Vulnerability Published: 2026-07-14 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1913" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1913" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/microsoft-dot_net_framework-cve-2026-47302/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1914">
+      <c r="A1914" t="inlineStr">
+        <is>
+          <t>CVE-2026-58379</t>
+        </is>
+      </c>
+      <c r="B1914" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="C1914" t="inlineStr">
+        <is>
+          <t>vulnerability Red Hat: CVE-2026-58379: gimp: gimp: Heap buffer overflow in read_channel_data() (Multiple Advisories) Published: 2026-04-11 | Severity:</t>
+        </is>
+      </c>
+      <c r="D1914" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1914" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/redhat_linux-cve-2026-58379/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1915">
+      <c r="A1915" t="inlineStr">
+        <is>
+          <t>CVE-2026-55380</t>
+        </is>
+      </c>
+      <c r="B1915" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="C1915" t="inlineStr">
+        <is>
+          <t>vulnerability Red Hat :CVE-2026-55380: python-pillow: Pillow: Denial of Service via crafted GD 2.x image file (Multiple Advisories) Published: 2026-07</t>
+        </is>
+      </c>
+      <c r="D1915" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1915" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/redhat_linux-cve-2026-55380/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1916">
+      <c r="A1916" t="inlineStr">
+        <is>
+          <t>CVE-2026-55379</t>
+        </is>
+      </c>
+      <c r="B1916" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="C1916" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vulnerability Red Hat :CVE-2026-55379: python-pillow: Pillow: Denial of Service via crafted BDF font file (Multiple Advisories) Published: 2026-07-06 </t>
+        </is>
+      </c>
+      <c r="D1916" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1916" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/redhat_linux-cve-2026-55379/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1917">
+      <c r="A1917" t="inlineStr">
+        <is>
+          <t>CVE-2026-54060</t>
+        </is>
+      </c>
+      <c r="B1917" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="C1917" t="inlineStr">
+        <is>
+          <t>vulnerability Red Hat :CVE-2026-54060: python-pillow: Pillow: Denial of Service via excessive memory allocation when processing font files (Multiple A</t>
+        </is>
+      </c>
+      <c r="D1917" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1917" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/redhat_linux-cve-2026-54060/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1918">
+      <c r="A1918" t="inlineStr">
+        <is>
+          <t>CVE-2026-54059</t>
+        </is>
+      </c>
+      <c r="B1918" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="C1918" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vulnerability Red Hat :CVE-2026-54059: python-pillow: Pillow: Denial of Service via crafted PCF font data (Multiple Advisories) Published: 2026-07-06 </t>
+        </is>
+      </c>
+      <c r="D1918" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1918" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/redhat_linux-cve-2026-54059/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1919">
+      <c r="A1919" t="inlineStr">
+        <is>
+          <t>CVE-2026-53016</t>
+        </is>
+      </c>
+      <c r="B1919" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C1919" t="inlineStr">
+        <is>
+          <t>vulnerability Red Hat: CVE-2026-53016: kernel: crypto: ccp - copy IV using skcipher ivsize (Multiple Advisories) Published: 2026-06-24 | Severity: 7 E</t>
+        </is>
+      </c>
+      <c r="D1919" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1919" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/redhat_linux-cve-2026-53016/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1920">
+      <c r="A1920" t="inlineStr">
+        <is>
+          <t>CVE-2026-46086</t>
+        </is>
+      </c>
+      <c r="B1920" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C1920" t="inlineStr">
+        <is>
+          <t>vulnerability Red Hat: CVE-2026-46086: kernel: net: bridge: use a stable FDB dst snapshot in RCU readers (Multiple Advisories) Published: 2026-05-27 |</t>
+        </is>
+      </c>
+      <c r="D1920" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1920" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/redhat_linux-cve-2026-46086/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1921">
+      <c r="A1921" t="inlineStr">
+        <is>
+          <t>CVE-2026-22979</t>
+        </is>
+      </c>
+      <c r="B1921" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="C1921" t="inlineStr">
+        <is>
+          <t>vulnerability Red Hat: CVE-2026-22979: kernel: Linux kernel: Memory leak in networking due to incorrect GRO packet handling (Multiple Advisories) Publ</t>
+        </is>
+      </c>
+      <c r="D1921" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1921" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/redhat_linux-cve-2026-22979/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1922">
+      <c r="A1922" t="inlineStr">
+        <is>
+          <t>CVE-2026-15308</t>
+        </is>
+      </c>
+      <c r="B1922" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="C1922" t="inlineStr">
+        <is>
+          <t>vulnerability Red Hat :CVE-2026-15308: python: Python: CPU Denial of Service in HTML parser via repeated unterminated markup declarations (Multiple Ad</t>
+        </is>
+      </c>
+      <c r="D1922" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1922" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/redhat_linux-cve-2026-15308/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1923">
+      <c r="A1923" t="inlineStr">
+        <is>
+          <t>CVE-2026-48337</t>
+        </is>
+      </c>
+      <c r="B1923" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="C1923" t="inlineStr">
+        <is>
+          <t>vulnerability Adobe Illustrator: CVE-2026-48337: Security updates available for Adobe Illustrator (APSB26-79) Published: 2026-07-14 | Severity: 7 EXPL</t>
+        </is>
+      </c>
+      <c r="D1923" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1923" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/adobe-illustrator-cve-2026-48337/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1924">
+      <c r="A1924" t="inlineStr">
+        <is>
+          <t>CVE-2026-48336</t>
+        </is>
+      </c>
+      <c r="B1924" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="C1924" t="inlineStr">
+        <is>
+          <t>vulnerability Adobe Illustrator: CVE-2026-48336: Security updates available for Adobe Illustrator (APSB26-79) Published: 2026-07-14 | Severity: 7 EXPL</t>
+        </is>
+      </c>
+      <c r="D1924" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1924" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/adobe-illustrator-cve-2026-48336/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1925">
+      <c r="A1925" t="inlineStr">
+        <is>
+          <t>CVE-2026-48335</t>
+        </is>
+      </c>
+      <c r="B1925" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="C1925" t="inlineStr">
+        <is>
+          <t>vulnerability Adobe Illustrator: CVE-2026-48335: Security updates available for Adobe Illustrator (APSB26-79) Published: 2026-07-14 | Severity: 7 EXPL</t>
+        </is>
+      </c>
+      <c r="D1925" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1925" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/adobe-illustrator-cve-2026-48335/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1926">
+      <c r="A1926" t="inlineStr">
+        <is>
+          <t>CVE-2026-48334</t>
+        </is>
+      </c>
+      <c r="B1926" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="C1926" t="inlineStr">
+        <is>
+          <t>vulnerability Adobe Illustrator: CVE-2026-48334: Security updates available for Adobe Illustrator (APSB26-79) Published: 2026-07-14 | Severity: 9 EXPL</t>
+        </is>
+      </c>
+      <c r="D1926" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1926" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/adobe-illustrator-cve-2026-48334/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1927">
+      <c r="A1927" t="inlineStr">
+        <is>
+          <t>CVE-2026-48275</t>
+        </is>
+      </c>
+      <c r="B1927" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="C1927" t="inlineStr">
+        <is>
+          <t>vulnerability Adobe Illustrator: CVE-2026-48275: Security updates available for Adobe Illustrator (APSB26-79) Published: 2026-07-14 | Severity: 7 EXPL</t>
+        </is>
+      </c>
+      <c r="D1927" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1927" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/adobe-illustrator-cve-2026-48275/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rapid7_cves.xlsx
+++ b/rapid7_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1927"/>
+  <dimension ref="A1:E1967"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52445,6 +52445,1086 @@
         </is>
       </c>
     </row>
+    <row r="1928">
+      <c r="A1928" t="inlineStr">
+        <is>
+          <t>CVE-2026-20146</t>
+        </is>
+      </c>
+      <c r="B1928" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="C1928" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1928" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1928" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1929">
+      <c r="A1929" t="inlineStr">
+        <is>
+          <t>CVE-2026-6482</t>
+        </is>
+      </c>
+      <c r="B1929" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="C1929" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1929" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1929" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1930">
+      <c r="A1930" t="inlineStr">
+        <is>
+          <t>CVE-2024-4741</t>
+        </is>
+      </c>
+      <c r="B1930" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="C1930" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1930" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1930" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1931">
+      <c r="A1931" t="inlineStr">
+        <is>
+          <t>CVE-2023-6237</t>
+        </is>
+      </c>
+      <c r="B1931" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="C1931" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1931" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1931" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1932">
+      <c r="A1932" t="inlineStr">
+        <is>
+          <t>CVE-2026-57825</t>
+        </is>
+      </c>
+      <c r="B1932" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="C1932" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1932" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1932" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1933">
+      <c r="A1933" t="inlineStr">
+        <is>
+          <t>CVE-2026-10118</t>
+        </is>
+      </c>
+      <c r="B1933" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="C1933" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1933" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1933" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1934">
+      <c r="A1934" t="inlineStr">
+        <is>
+          <t>CVE-2026-15778</t>
+        </is>
+      </c>
+      <c r="B1934" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="C1934" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1934" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1934" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1935">
+      <c r="A1935" t="inlineStr">
+        <is>
+          <t>CVE-2026-15777</t>
+        </is>
+      </c>
+      <c r="B1935" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="C1935" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1935" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1935" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1936">
+      <c r="A1936" t="inlineStr">
+        <is>
+          <t>CVE-2026-15776</t>
+        </is>
+      </c>
+      <c r="B1936" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="C1936" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1936" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1936" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1937">
+      <c r="A1937" t="inlineStr">
+        <is>
+          <t>CVE-2026-15775</t>
+        </is>
+      </c>
+      <c r="B1937" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="C1937" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1937" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1937" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1938">
+      <c r="A1938" t="inlineStr">
+        <is>
+          <t>CVE-2026-15774</t>
+        </is>
+      </c>
+      <c r="B1938" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="C1938" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1938" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1938" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1939">
+      <c r="A1939" t="inlineStr">
+        <is>
+          <t>CVE-2026-15773</t>
+        </is>
+      </c>
+      <c r="B1939" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="C1939" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1939" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1939" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1940">
+      <c r="A1940" t="inlineStr">
+        <is>
+          <t>CVE-2026-15772</t>
+        </is>
+      </c>
+      <c r="B1940" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="C1940" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1940" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1940" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1941">
+      <c r="A1941" t="inlineStr">
+        <is>
+          <t>CVE-2026-15771</t>
+        </is>
+      </c>
+      <c r="B1941" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="C1941" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1941" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1941" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1942">
+      <c r="A1942" t="inlineStr">
+        <is>
+          <t>CVE-2026-15770</t>
+        </is>
+      </c>
+      <c r="B1942" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="C1942" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1942" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1942" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1943">
+      <c r="A1943" t="inlineStr">
+        <is>
+          <t>CVE-2026-15769</t>
+        </is>
+      </c>
+      <c r="B1943" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="C1943" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1943" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1943" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1944">
+      <c r="A1944" t="inlineStr">
+        <is>
+          <t>CVE-2026-15768</t>
+        </is>
+      </c>
+      <c r="B1944" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="C1944" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1944" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1944" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1945">
+      <c r="A1945" t="inlineStr">
+        <is>
+          <t>CVE-2026-15767</t>
+        </is>
+      </c>
+      <c r="B1945" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="C1945" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1945" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1945" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1946">
+      <c r="A1946" t="inlineStr">
+        <is>
+          <t>CVE-2026-15766</t>
+        </is>
+      </c>
+      <c r="B1946" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="C1946" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1946" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1946" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1947">
+      <c r="A1947" t="inlineStr">
+        <is>
+          <t>CVE-2026-15765</t>
+        </is>
+      </c>
+      <c r="B1947" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="C1947" t="inlineStr">
+        <is>
+          <t>The Quarterly Threat Landscape Report is out. See what attackers are targeting now. Read report Platform Services Resources Partners Company Request D</t>
+        </is>
+      </c>
+      <c r="D1947" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1947" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1948">
+      <c r="A1948" t="inlineStr">
+        <is>
+          <t>CVE-2026-20146</t>
+        </is>
+      </c>
+      <c r="B1948" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="C1948" t="inlineStr">
+        <is>
+          <t>vulnerability Cisco ISE: CVE-2026-20146: Cisco Identity Services Engine Path Traversal Vulnerability Published: 2026-07-15 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1948" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1948" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/cisco-ise-cve-2026-20146/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1949">
+      <c r="A1949" t="inlineStr">
+        <is>
+          <t>CVE-2026-6482</t>
+        </is>
+      </c>
+      <c r="B1949" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="C1949" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vulnerability Rapid7 Insight Agent: CVE-2026-6482: Local Privilege Escalation via OpenSSL Configuration Hijacking Published: 2026-04-17 | Severity: 7 </t>
+        </is>
+      </c>
+      <c r="D1949" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1949" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/rapid7-insightagent-cve-2026-6482/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1950">
+      <c r="A1950" t="inlineStr">
+        <is>
+          <t>CVE-2024-4741</t>
+        </is>
+      </c>
+      <c r="B1950" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="C1950" t="inlineStr">
+        <is>
+          <t>vulnerability Dell PowerEdge: CVE-2024-4741: DSA-2026-316: Security Update for Dell PowerEdge Server for OpenSSL Vulnerabilities Published: 2026-07-14</t>
+        </is>
+      </c>
+      <c r="D1950" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1950" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/dell-poweredge-dsa2026316-cve-2024-4741/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1951">
+      <c r="A1951" t="inlineStr">
+        <is>
+          <t>CVE-2023-6237</t>
+        </is>
+      </c>
+      <c r="B1951" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="C1951" t="inlineStr">
+        <is>
+          <t>vulnerability Dell PowerEdge: CVE-2023-6237: DSA-2026-316: Security Update for Dell PowerEdge Server for OpenSSL Vulnerabilities Published: 2026-07-14</t>
+        </is>
+      </c>
+      <c r="D1951" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1951" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/dell-poweredge-dsa2026316-cve-2023-6237/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1952">
+      <c r="A1952" t="inlineStr">
+        <is>
+          <t>CVE-2026-57825</t>
+        </is>
+      </c>
+      <c r="B1952" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="C1952" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vulnerability FreeBSD: VID-b478ff13-7f6e-11f1-b594-3c7c3fba4204 (CVE-2026-57825): ocaml-opam -- opam install sandbox escape using symlinks Published: </t>
+        </is>
+      </c>
+      <c r="D1952" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1952" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/freebsd-cve-2026-57825/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1953">
+      <c r="A1953" t="inlineStr">
+        <is>
+          <t>CVE-2026-10118</t>
+        </is>
+      </c>
+      <c r="B1953" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="C1953" t="inlineStr">
+        <is>
+          <t>vulnerability FreeBSD: VID-74d0291e-7f81-11f1-83e9-901b0e13f1a0 (CVE-2026-10118): Poppler: integer overflow in tilingPatternFill Published: 2026-07-14</t>
+        </is>
+      </c>
+      <c r="D1953" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1953" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/freebsd-cve-2026-10118/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1954">
+      <c r="A1954" t="inlineStr">
+        <is>
+          <t>CVE-2026-15778</t>
+        </is>
+      </c>
+      <c r="B1954" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="C1954" t="inlineStr">
+        <is>
+          <t>vulnerability Google Chrome Vulnerability: CVE-2026-15778 Insufficient validation of untrusted input in Navigation Published: 2026-07-14 | Severity: 1</t>
+        </is>
+      </c>
+      <c r="D1954" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1954" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/google-chrome-cve-2026-15778/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1955">
+      <c r="A1955" t="inlineStr">
+        <is>
+          <t>CVE-2026-15777</t>
+        </is>
+      </c>
+      <c r="B1955" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="C1955" t="inlineStr">
+        <is>
+          <t>vulnerability Google Chrome Vulnerability: CVE-2026-15777 Use after free in UI Published: 2026-07-14 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1955" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1955" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/google-chrome-cve-2026-15777/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1956">
+      <c r="A1956" t="inlineStr">
+        <is>
+          <t>CVE-2026-15776</t>
+        </is>
+      </c>
+      <c r="B1956" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="C1956" t="inlineStr">
+        <is>
+          <t>vulnerability Google Chrome Vulnerability: CVE-2026-15776 Type Confusion in V8 Published: 2026-07-14 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1956" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1956" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/google-chrome-cve-2026-15776/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1957">
+      <c r="A1957" t="inlineStr">
+        <is>
+          <t>CVE-2026-15775</t>
+        </is>
+      </c>
+      <c r="B1957" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="C1957" t="inlineStr">
+        <is>
+          <t>vulnerability Google Chrome Vulnerability: CVE-2026-15775 Insufficient policy enforcement in V8 Published: 2026-07-14 | Severity: 10 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1957" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1957" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/google-chrome-cve-2026-15775/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1958">
+      <c r="A1958" t="inlineStr">
+        <is>
+          <t>CVE-2026-15774</t>
+        </is>
+      </c>
+      <c r="B1958" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="C1958" t="inlineStr">
+        <is>
+          <t>vulnerability Google Chrome Vulnerability: CVE-2026-15774 Use after free in Skia Published: 2026-07-14 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1958" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1958" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/google-chrome-cve-2026-15774/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1959">
+      <c r="A1959" t="inlineStr">
+        <is>
+          <t>CVE-2026-15773</t>
+        </is>
+      </c>
+      <c r="B1959" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="C1959" t="inlineStr">
+        <is>
+          <t>vulnerability Google Chrome Vulnerability: CVE-2026-15773 Use after free in Core Published: 2026-07-14 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1959" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1959" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/google-chrome-cve-2026-15773/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1960">
+      <c r="A1960" t="inlineStr">
+        <is>
+          <t>CVE-2026-15772</t>
+        </is>
+      </c>
+      <c r="B1960" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="C1960" t="inlineStr">
+        <is>
+          <t>vulnerability Google Chrome Vulnerability: CVE-2026-15772 Use after free in GPU Published: 2026-07-14 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1960" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1960" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/google-chrome-cve-2026-15772/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1961">
+      <c r="A1961" t="inlineStr">
+        <is>
+          <t>CVE-2026-15771</t>
+        </is>
+      </c>
+      <c r="B1961" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="C1961" t="inlineStr">
+        <is>
+          <t>vulnerability Google Chrome Vulnerability: CVE-2026-15771 Insufficient validation of untrusted input in Media Published: 2026-07-14 | Severity: 5 EXPL</t>
+        </is>
+      </c>
+      <c r="D1961" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E1961" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/google-chrome-cve-2026-15771/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1962">
+      <c r="A1962" t="inlineStr">
+        <is>
+          <t>CVE-2026-15770</t>
+        </is>
+      </c>
+      <c r="B1962" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="C1962" t="inlineStr">
+        <is>
+          <t>vulnerability Google Chrome Vulnerability: CVE-2026-15770 Uninitialized Use in V8 Published: 2026-07-14 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1962" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1962" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/google-chrome-cve-2026-15770/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1963">
+      <c r="A1963" t="inlineStr">
+        <is>
+          <t>CVE-2026-15769</t>
+        </is>
+      </c>
+      <c r="B1963" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="C1963" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vulnerability Google Chrome Vulnerability: CVE-2026-15769 Insufficient validation of untrusted input in Linux Toolkit Theming Published: 2026-07-14 | </t>
+        </is>
+      </c>
+      <c r="D1963" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1963" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/google-chrome-cve-2026-15769/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1964">
+      <c r="A1964" t="inlineStr">
+        <is>
+          <t>CVE-2026-15768</t>
+        </is>
+      </c>
+      <c r="B1964" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="C1964" t="inlineStr">
+        <is>
+          <t>vulnerability Google Chrome Vulnerability: CVE-2026-15768 Insufficient policy enforcement in HTML-in-Canvas Published: 2026-07-14 | Severity: 10 EXPLO</t>
+        </is>
+      </c>
+      <c r="D1964" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E1964" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/google-chrome-cve-2026-15768/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1965">
+      <c r="A1965" t="inlineStr">
+        <is>
+          <t>CVE-2026-15767</t>
+        </is>
+      </c>
+      <c r="B1965" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="C1965" t="inlineStr">
+        <is>
+          <t>vulnerability Google Chrome Vulnerability: CVE-2026-15767 Heap buffer overflow in libyuv Published: 2026-07-14 | Severity: 9 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1965" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1965" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/google-chrome-cve-2026-15767/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1966">
+      <c r="A1966" t="inlineStr">
+        <is>
+          <t>CVE-2026-15766</t>
+        </is>
+      </c>
+      <c r="B1966" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="C1966" t="inlineStr">
+        <is>
+          <t>vulnerability Google Chrome Vulnerability: CVE-2026-15766 Uninitialized Use in Skia Published: 2026-07-14 | Severity: 7 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1966" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1966" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/google-chrome-cve-2026-15766/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1967">
+      <c r="A1967" t="inlineStr">
+        <is>
+          <t>CVE-2026-15765</t>
+        </is>
+      </c>
+      <c r="B1967" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="C1967" t="inlineStr">
+        <is>
+          <t>vulnerability Google Chrome Vulnerability: CVE-2026-15765 Use after free in Ozone Published: 2026-07-14 | Severity: 8 EXPLORE</t>
+        </is>
+      </c>
+      <c r="D1967" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E1967" t="inlineStr">
+        <is>
+          <t>https://www.rapid7.com/db/vulnerabilities/google-chrome-cve-2026-15765/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
